--- a/input/reg_labourSupplyUtility.xlsx
+++ b/input/reg_labourSupplyUtility.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7947280B-9345-4D15-95B0-67E00BE4E580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA9CB5B4-5439-4317-B849-FE71566D5550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="17363" tabRatio="948" firstSheet="4" activeTab="7" xr2:uid="{CE10044B-DF17-4109-838C-2F682B85B23F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" tabRatio="948" activeTab="7" xr2:uid="{CE10044B-DF17-4109-838C-2F682B85B23F}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="7" r:id="rId1"/>
@@ -251,9 +251,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -294,13 +291,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -635,82 +628,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="5">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="3">
         <v>45617</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -724,7 +717,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85FEAAE6-65C5-44AD-94AB-B2F965791C43}">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="36.1328125" customWidth="1"/>
@@ -736,7 +729,7 @@
     <col min="7" max="7" width="25.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -771,7 +764,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -805,11 +798,8 @@
       <c r="K2">
         <v>4.9583298400290648E-4</v>
       </c>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -843,11 +833,8 @@
       <c r="K3">
         <v>-5.4921144273622889E-6</v>
       </c>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -881,11 +868,8 @@
       <c r="K4">
         <v>5.5211891517542024E-4</v>
       </c>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -919,11 +903,8 @@
       <c r="K5">
         <v>-9.5111089558609779E-7</v>
       </c>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -957,11 +938,8 @@
       <c r="K6">
         <v>-2.9396871156103787E-6</v>
       </c>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>55</v>
       </c>
@@ -995,11 +973,8 @@
       <c r="K7">
         <v>5.4641835898334738E-3</v>
       </c>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>52</v>
       </c>
@@ -1033,11 +1008,8 @@
       <c r="K8">
         <v>3.178020092841828E-4</v>
       </c>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -1071,11 +1043,8 @@
       <c r="K9">
         <v>3.1649560118443906E-4</v>
       </c>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -1109,54 +1078,6 @@
       <c r="K10">
         <v>4.3359555693368358E-4</v>
       </c>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="B11" s="2"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="B12" s="2"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="B13" s="2"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1165,7 +1086,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A5AD492-5570-405E-BE90-089FB56DBA70}">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="36.1328125" customWidth="1"/>
@@ -1184,7 +1105,7 @@
     <col min="14" max="14" width="12.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1219,7 +1140,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1253,11 +1174,8 @@
       <c r="K2">
         <v>2.2806933804126936E-4</v>
       </c>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1291,11 +1209,8 @@
       <c r="K3">
         <v>-2.8244898431382912E-6</v>
       </c>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1329,11 +1244,8 @@
       <c r="K4">
         <v>9.9178118968247129E-4</v>
       </c>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1367,11 +1279,8 @@
       <c r="K5">
         <v>-2.5607000063785053E-6</v>
       </c>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1405,11 +1314,8 @@
       <c r="K6">
         <v>-1.6957255154846407E-6</v>
       </c>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>56</v>
       </c>
@@ -1443,11 +1349,8 @@
       <c r="K7">
         <v>5.6626621649594842E-3</v>
       </c>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>49</v>
       </c>
@@ -1481,11 +1384,8 @@
       <c r="K8">
         <v>2.0667917895580149E-4</v>
       </c>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>50</v>
       </c>
@@ -1519,11 +1419,8 @@
       <c r="K9">
         <v>2.0505291902178977E-4</v>
       </c>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>51</v>
       </c>
@@ -1557,54 +1454,6 @@
       <c r="K10">
         <v>3.4262224658565587E-4</v>
       </c>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="B11" s="2"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="B12" s="2"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="B13" s="2"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9965,7 +9814,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6ABBF8F-3DA9-4957-ACE4-D5C4AAE8F601}">
-  <dimension ref="B1:T19"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="35.265625" customWidth="1"/>
@@ -9977,505 +9826,187 @@
     <col min="7" max="7" width="25.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
       <c r="E1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="H1" t="s">
+      <c r="B2">
+        <v>-0.16662524710631485</v>
+      </c>
+      <c r="C2">
+        <v>0.1728792676322764</v>
+      </c>
+      <c r="D2">
+        <v>-3.3102330039322071E-3</v>
+      </c>
+      <c r="E2">
+        <v>1.6801675764261361E-2</v>
+      </c>
+      <c r="F2">
+        <v>-3.7523438127478036E-5</v>
+      </c>
+      <c r="G2">
+        <v>-7.9669624815659321E-4</v>
+      </c>
+      <c r="H2">
+        <v>-5.0742490058465501E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="I1" t="s">
+      <c r="B3">
+        <v>1.7124019996642989E-3</v>
+      </c>
+      <c r="C3">
+        <v>-3.3102330039322071E-3</v>
+      </c>
+      <c r="D3">
+        <v>6.8480460571645284E-5</v>
+      </c>
+      <c r="E3">
+        <v>-3.0217514551310223E-4</v>
+      </c>
+      <c r="F3">
+        <v>6.7416249748660397E-7</v>
+      </c>
+      <c r="G3">
+        <v>1.511178186688263E-5</v>
+      </c>
+      <c r="H3">
+        <v>1.0215963890683134E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="J1" t="s">
+      <c r="B4">
+        <v>0.83862701009658536</v>
+      </c>
+      <c r="C4">
+        <v>1.6801675764261361E-2</v>
+      </c>
+      <c r="D4">
+        <v>-3.0217514551310223E-4</v>
+      </c>
+      <c r="E4">
+        <v>8.8954780221854324E-3</v>
+      </c>
+      <c r="F4">
+        <v>-2.9851119395480332E-5</v>
+      </c>
+      <c r="G4">
+        <v>-7.7039568687844569E-5</v>
+      </c>
+      <c r="H4">
+        <v>-9.6410402160268635E-5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="K1" t="s">
+      <c r="B5">
+        <v>-3.0347824294652491E-3</v>
+      </c>
+      <c r="C5">
+        <v>-3.7523438127478036E-5</v>
+      </c>
+      <c r="D5">
+        <v>6.7416249748660397E-7</v>
+      </c>
+      <c r="E5">
+        <v>-2.9851119395480332E-5</v>
+      </c>
+      <c r="F5">
+        <v>1.0329022852823616E-7</v>
+      </c>
+      <c r="G5">
+        <v>1.7690323754570854E-7</v>
+      </c>
+      <c r="H5">
+        <v>1.8397713081444418E-6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="L1" t="s">
+      <c r="B6">
+        <v>1.8591552061367022E-3</v>
+      </c>
+      <c r="C6">
+        <v>-7.9669624815659321E-4</v>
+      </c>
+      <c r="D6">
+        <v>1.511178186688263E-5</v>
+      </c>
+      <c r="E6">
+        <v>-7.7039568687844569E-5</v>
+      </c>
+      <c r="F6">
+        <v>1.7690323754570854E-7</v>
+      </c>
+      <c r="G6">
+        <v>3.9849105941291283E-6</v>
+      </c>
+      <c r="H6">
+        <v>1.6986551610282878E-5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="2" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>-0.16662524710631485</v>
-      </c>
-      <c r="G2">
-        <v>0.1728792676322764</v>
-      </c>
-      <c r="H2">
-        <v>-3.3102330039322071E-3</v>
-      </c>
-      <c r="I2">
-        <v>1.6801675764261361E-2</v>
-      </c>
-      <c r="J2">
-        <v>-3.7523438127478036E-5</v>
-      </c>
-      <c r="K2">
-        <v>-7.9669624815659321E-4</v>
-      </c>
-      <c r="L2">
+      <c r="B7">
+        <v>1.6000766647666365</v>
+      </c>
+      <c r="C7">
         <v>-5.0742490058465501E-3</v>
       </c>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-    </row>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>1.7124019996642989E-3</v>
-      </c>
-      <c r="G3">
-        <v>-3.3102330039322071E-3</v>
-      </c>
-      <c r="H3">
-        <v>6.8480460571645284E-5</v>
-      </c>
-      <c r="I3">
-        <v>-3.0217514551310223E-4</v>
-      </c>
-      <c r="J3">
-        <v>6.7416249748660397E-7</v>
-      </c>
-      <c r="K3">
-        <v>1.511178186688263E-5</v>
-      </c>
-      <c r="L3">
+      <c r="D7">
         <v>1.0215963890683134E-4</v>
       </c>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-    </row>
-    <row r="4" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4">
-        <v>0.83862701009658536</v>
-      </c>
-      <c r="G4">
-        <v>1.6801675764261361E-2</v>
-      </c>
-      <c r="H4">
-        <v>-3.0217514551310223E-4</v>
-      </c>
-      <c r="I4">
-        <v>8.8954780221854324E-3</v>
-      </c>
-      <c r="J4">
-        <v>-2.9851119395480332E-5</v>
-      </c>
-      <c r="K4">
-        <v>-7.7039568687844569E-5</v>
-      </c>
-      <c r="L4">
+      <c r="E7">
         <v>-9.6410402160268635E-5</v>
       </c>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-    </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>-3.0347824294652491E-3</v>
-      </c>
-      <c r="G5">
-        <v>-3.7523438127478036E-5</v>
-      </c>
-      <c r="H5">
-        <v>6.7416249748660397E-7</v>
-      </c>
-      <c r="I5">
-        <v>-2.9851119395480332E-5</v>
-      </c>
-      <c r="J5">
-        <v>1.0329022852823616E-7</v>
-      </c>
-      <c r="K5">
-        <v>1.7690323754570854E-7</v>
-      </c>
-      <c r="L5">
+      <c r="F7">
         <v>1.8397713081444418E-6</v>
       </c>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
-    </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>1.8591552061367022E-3</v>
-      </c>
-      <c r="G6">
-        <v>-7.9669624815659321E-4</v>
-      </c>
-      <c r="H6">
-        <v>1.511178186688263E-5</v>
-      </c>
-      <c r="I6">
-        <v>-7.7039568687844569E-5</v>
-      </c>
-      <c r="J6">
-        <v>1.7690323754570854E-7</v>
-      </c>
-      <c r="K6">
-        <v>3.9849105941291283E-6</v>
-      </c>
-      <c r="L6">
+      <c r="G7">
         <v>1.6986551610282878E-5</v>
       </c>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-    </row>
-    <row r="7" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7">
-        <v>1.6000766647666365</v>
-      </c>
-      <c r="G7">
-        <v>-5.0742490058465501E-3</v>
-      </c>
       <c r="H7">
-        <v>1.0215963890683134E-4</v>
-      </c>
-      <c r="I7">
-        <v>-9.6410402160268635E-5</v>
-      </c>
-      <c r="J7">
-        <v>1.8397713081444418E-6</v>
-      </c>
-      <c r="K7">
-        <v>1.6986551610282878E-5</v>
-      </c>
-      <c r="L7">
         <v>5.9381570022282136E-2</v>
       </c>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-    </row>
-    <row r="8" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-    </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-    </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-    </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
-    </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
-    </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="3"/>
-    </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="3"/>
-    </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
-    </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
-    </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10484,7 +10015,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86831B41-CE8C-4F34-B10B-C522104558DF}">
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="38.86328125" customWidth="1"/>
@@ -10496,7 +10027,7 @@
     <col min="7" max="7" width="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10522,7 +10053,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -10547,20 +10078,8 @@
       <c r="H2">
         <v>-5.0742490058465501E-3</v>
       </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -10585,20 +10104,8 @@
       <c r="H3">
         <v>1.0215963890683134E-4</v>
       </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -10623,20 +10130,8 @@
       <c r="H4">
         <v>-9.6410402160268635E-5</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -10661,20 +10156,8 @@
       <c r="H5">
         <v>1.8397713081444418E-6</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -10699,20 +10182,8 @@
       <c r="H6">
         <v>1.6986551610282878E-5</v>
       </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.45">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>56</v>
       </c>
@@ -10737,270 +10208,6 @@
       <c r="H7">
         <v>5.9381570022282136E-2</v>
       </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="3"/>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="3"/>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
-    </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
-    </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/input/reg_labourSupplyUtility.xlsx
+++ b/input/reg_labourSupplyUtility.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E318A25F-ADA1-4636-9349-18A516E283C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A31DD31A-C2F4-43D5-98D0-DF501A31C2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" tabRatio="948" activeTab="5" xr2:uid="{CE10044B-DF17-4109-838C-2F682B85B23F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" tabRatio="948" activeTab="7" xr2:uid="{CE10044B-DF17-4109-838C-2F682B85B23F}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="7" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="95">
   <si>
     <t>REGRESSOR</t>
   </si>
@@ -95,9 +95,6 @@
   </si>
   <si>
     <t>Liwwh_Female_3</t>
-  </si>
-  <si>
-    <t>Liwwh_10</t>
   </si>
   <si>
     <t>Hrs_40plus_Male</t>
@@ -833,31 +830,31 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" t="s">
         <v>36</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>37</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>38</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>39</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>40</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>41</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>42</v>
-      </c>
-      <c r="P1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.45">
@@ -1112,7 +1109,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>1.8067606605788387</v>
@@ -1162,7 +1159,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B8">
         <v>0.78280595823225274</v>
@@ -1212,7 +1209,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B9">
         <v>1.7070148068434357</v>
@@ -1262,7 +1259,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B10">
         <v>1.4615394957950483</v>
@@ -1312,7 +1309,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11">
         <v>2.4007920689266471</v>
@@ -1362,7 +1359,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12">
         <v>1.394220689814228</v>
@@ -1412,7 +1409,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B13">
         <v>2.3500109076624911</v>
@@ -1462,7 +1459,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B14">
         <v>0.52311547957153248</v>
@@ -1512,7 +1509,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B15">
         <v>1.7961678664693497</v>
@@ -1609,31 +1606,31 @@
         <v>10</v>
       </c>
       <c r="H1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" t="s">
         <v>28</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>29</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>30</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>31</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>32</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>33</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>34</v>
-      </c>
-      <c r="P1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.45">
@@ -1888,7 +1885,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B7">
         <v>1.273322259652246</v>
@@ -1938,7 +1935,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B8">
         <v>1.496942803641151</v>
@@ -1988,7 +1985,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9">
         <v>2.4156969201031724</v>
@@ -2038,7 +2035,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10">
         <v>2.1529572188566437</v>
@@ -2088,7 +2085,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B11">
         <v>2.8631502036476051</v>
@@ -2138,7 +2135,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12">
         <v>2.1650901489957248</v>
@@ -2188,7 +2185,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13">
         <v>3.1709601649539234</v>
@@ -2238,7 +2235,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B14">
         <v>1.9896119920284161</v>
@@ -2288,7 +2285,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B15">
         <v>2.7618448177590698</v>
@@ -2382,31 +2379,31 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" t="s">
         <v>36</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>37</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>38</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>39</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>40</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>41</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>42</v>
-      </c>
-      <c r="P1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.45">
@@ -2661,7 +2658,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>0.66244655613006742</v>
@@ -2711,7 +2708,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B8">
         <v>0.18995483773122268</v>
@@ -2761,7 +2758,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B9">
         <v>1.2961709555413379</v>
@@ -2811,7 +2808,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B10">
         <v>-7.3210872082070055E-2</v>
@@ -2861,7 +2858,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11">
         <v>0.70006244001338469</v>
@@ -2911,7 +2908,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12">
         <v>0.89353497807550597</v>
@@ -2961,7 +2958,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B13">
         <v>1.6670250933746278</v>
@@ -3011,7 +3008,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B14">
         <v>-0.62563412541408425</v>
@@ -3061,7 +3058,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B15">
         <v>0.27523486532997254</v>
@@ -3151,31 +3148,31 @@
         <v>10</v>
       </c>
       <c r="H1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" t="s">
         <v>28</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>29</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>30</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>31</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>32</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>33</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>34</v>
-      </c>
-      <c r="P1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.45">
@@ -3430,7 +3427,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B7">
         <v>2.7618410884019737</v>
@@ -3480,7 +3477,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B8">
         <v>1.1992519024312389</v>
@@ -3530,7 +3527,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9">
         <v>1.8939522030868186</v>
@@ -3580,7 +3577,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10">
         <v>2.4733218270055319</v>
@@ -3630,7 +3627,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B11">
         <v>3.1962990913528744</v>
@@ -3680,7 +3677,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12">
         <v>3.2086993294078234</v>
@@ -3730,7 +3727,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13">
         <v>4.4313529401866854</v>
@@ -3780,7 +3777,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B14">
         <v>2.4071820980797964</v>
@@ -3830,7 +3827,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B15">
         <v>3.3216371540992156</v>
@@ -3928,154 +3925,154 @@
         <v>10</v>
       </c>
       <c r="L1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" t="s">
         <v>20</v>
       </c>
-      <c r="M1" t="s">
-        <v>21</v>
-      </c>
       <c r="N1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O1" t="s">
         <v>44</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>45</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>46</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>47</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>48</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>49</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>50</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>51</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>52</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>53</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>54</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>55</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>56</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>57</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>58</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>59</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>60</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>61</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>62</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>63</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>64</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>65</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>66</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>67</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>68</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>69</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>70</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>71</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>72</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>73</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>74</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>75</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>76</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>77</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>78</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>79</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>80</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>81</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>82</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>83</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>84</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>85</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>86</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>87</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>88</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>89</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>90</v>
-      </c>
-      <c r="BI1" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:61" x14ac:dyDescent="0.45">
@@ -5745,7 +5742,7 @@
     </row>
     <row r="11" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11">
         <v>2.280079011348199</v>
@@ -5930,7 +5927,7 @@
     </row>
     <row r="12" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12">
         <v>0.95054983382640923</v>
@@ -6115,7 +6112,7 @@
     </row>
     <row r="13" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B13">
         <v>-0.3825249489289112</v>
@@ -6300,7 +6297,7 @@
     </row>
     <row r="14" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B14">
         <v>-1.4570344450246953</v>
@@ -6485,7 +6482,7 @@
     </row>
     <row r="15" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B15">
         <v>-0.30525285388556</v>
@@ -6670,7 +6667,7 @@
     </row>
     <row r="16" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16">
         <v>-1.6058917433520163</v>
@@ -6855,7 +6852,7 @@
     </row>
     <row r="17" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B17">
         <v>-0.96850522229139469</v>
@@ -7040,7 +7037,7 @@
     </row>
     <row r="18" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B18">
         <v>-1.9577346373503932</v>
@@ -7225,7 +7222,7 @@
     </row>
     <row r="19" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B19">
         <v>3.3294294691751755E-2</v>
@@ -7410,7 +7407,7 @@
     </row>
     <row r="20" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B20">
         <v>-2.1967973486469923</v>
@@ -7595,7 +7592,7 @@
     </row>
     <row r="21" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B21">
         <v>-1.7546179466956957</v>
@@ -7780,7 +7777,7 @@
     </row>
     <row r="22" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B22">
         <v>-2.1332750201992718</v>
@@ -7965,7 +7962,7 @@
     </row>
     <row r="23" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B23">
         <v>-1.0305197830759807</v>
@@ -8150,7 +8147,7 @@
     </row>
     <row r="24" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B24">
         <v>-2.8539854843168388</v>
@@ -8335,7 +8332,7 @@
     </row>
     <row r="25" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B25">
         <v>-1.0945089822189402</v>
@@ -8520,7 +8517,7 @@
     </row>
     <row r="26" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B26">
         <v>-2.7116365740556132</v>
@@ -8705,7 +8702,7 @@
     </row>
     <row r="27" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B27">
         <v>-1.0717946826551239</v>
@@ -8890,7 +8887,7 @@
     </row>
     <row r="28" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B28">
         <v>-3.3574928621401718</v>
@@ -9075,7 +9072,7 @@
     </row>
     <row r="29" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B29">
         <v>-1.6419687260897899</v>
@@ -9260,7 +9257,7 @@
     </row>
     <row r="30" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B30">
         <v>-4.2991488003165754</v>
@@ -9445,7 +9442,7 @@
     </row>
     <row r="31" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B31">
         <v>-0.72654442945992825</v>
@@ -9630,7 +9627,7 @@
     </row>
     <row r="32" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B32">
         <v>-1.9887577797520566</v>
@@ -9815,7 +9812,7 @@
     </row>
     <row r="33" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B33">
         <v>-0.22272284950478677</v>
@@ -10000,7 +9997,7 @@
     </row>
     <row r="34" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B34">
         <v>-2.0175932408756863</v>
@@ -10185,7 +10182,7 @@
     </row>
     <row r="35" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B35">
         <v>-0.76014742444184369</v>
@@ -10370,7 +10367,7 @@
     </row>
     <row r="36" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B36">
         <v>-2.7150896879160471</v>
@@ -10555,7 +10552,7 @@
     </row>
     <row r="37" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B37">
         <v>6.1015439045150485E-2</v>
@@ -10740,7 +10737,7 @@
     </row>
     <row r="38" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B38">
         <v>-1.839491685595563</v>
@@ -10925,7 +10922,7 @@
     </row>
     <row r="39" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B39">
         <v>-0.85618534334182217</v>
@@ -11110,7 +11107,7 @@
     </row>
     <row r="40" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B40">
         <v>-3.0259701179797358</v>
@@ -11295,7 +11292,7 @@
     </row>
     <row r="41" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B41">
         <v>-0.99202357109432981</v>
@@ -11480,7 +11477,7 @@
     </row>
     <row r="42" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B42">
         <v>-2.9563237105364686</v>
@@ -11665,7 +11662,7 @@
     </row>
     <row r="43" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B43">
         <v>-0.39979630927872528</v>
@@ -11850,7 +11847,7 @@
     </row>
     <row r="44" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B44">
         <v>-2.9704784738649566</v>
@@ -12035,7 +12032,7 @@
     </row>
     <row r="45" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B45">
         <v>-0.56118041763362481</v>
@@ -12220,7 +12217,7 @@
     </row>
     <row r="46" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B46">
         <v>-3.2275059616442499</v>
@@ -12405,7 +12402,7 @@
     </row>
     <row r="47" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B47">
         <v>-0.84942543375085922</v>
@@ -12590,7 +12587,7 @@
     </row>
     <row r="48" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B48">
         <v>-3.4412845645635213</v>
@@ -12775,7 +12772,7 @@
     </row>
     <row r="49" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B49">
         <v>-0.67438083224615064</v>
@@ -12960,7 +12957,7 @@
     </row>
     <row r="50" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B50">
         <v>-3.7242228528752919</v>
@@ -13145,7 +13142,7 @@
     </row>
     <row r="51" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B51">
         <v>-0.69261167133853629</v>
@@ -13330,7 +13327,7 @@
     </row>
     <row r="52" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B52">
         <v>-2.9982334066297023</v>
@@ -13515,7 +13512,7 @@
     </row>
     <row r="53" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B53">
         <v>-0.35801318131859206</v>
@@ -13700,7 +13697,7 @@
     </row>
     <row r="54" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B54">
         <v>-3.3415020992173341</v>
@@ -13885,7 +13882,7 @@
     </row>
     <row r="55" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B55">
         <v>-1.3293973495826605</v>
@@ -14070,7 +14067,7 @@
     </row>
     <row r="56" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B56">
         <v>-4.0314242472656892</v>
@@ -14255,7 +14252,7 @@
     </row>
     <row r="57" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B57">
         <v>-1.0728270285146131</v>
@@ -14440,7 +14437,7 @@
     </row>
     <row r="58" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B58">
         <v>-3.9926075163668124</v>
@@ -14625,7 +14622,7 @@
     </row>
     <row r="59" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B59">
         <v>-0.77480629193002126</v>
@@ -14810,7 +14807,7 @@
     </row>
     <row r="60" spans="1:61" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B60">
         <v>-3.6159982707690292</v>
@@ -15036,31 +15033,31 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I1" t="s">
         <v>13</v>
       </c>
       <c r="J1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K1" t="s">
         <v>14</v>
       </c>
       <c r="L1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M1" t="s">
         <v>15</v>
       </c>
       <c r="N1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O1" t="s">
+        <v>91</v>
+      </c>
+      <c r="P1" t="s">
         <v>92</v>
-      </c>
-      <c r="P1" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.45">
@@ -15315,7 +15312,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>2.1418420793565809</v>
@@ -15365,7 +15362,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B8">
         <v>1.305987682058532E-2</v>
@@ -15415,7 +15412,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>8.1153357288376042E-4</v>
@@ -15515,7 +15512,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11">
         <v>-5.2012428265580182E-4</v>
@@ -15615,7 +15612,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>-3.0516991026159217E-4</v>
@@ -15665,7 +15662,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B14">
         <v>6.2367460377600367E-2</v>
@@ -15715,7 +15712,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B15">
         <v>3.0636957694913112E-4</v>
@@ -15805,31 +15802,31 @@
         <v>10</v>
       </c>
       <c r="H1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I1" t="s">
         <v>16</v>
       </c>
       <c r="J1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K1" t="s">
         <v>17</v>
       </c>
       <c r="L1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M1" t="s">
         <v>18</v>
       </c>
       <c r="N1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O1" t="s">
+        <v>93</v>
+      </c>
+      <c r="P1" t="s">
         <v>94</v>
-      </c>
-      <c r="P1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.45">
@@ -16084,7 +16081,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B7">
         <v>2.1682208844995112</v>
@@ -16184,7 +16181,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B9">
         <v>-5.4953787207593361E-4</v>
@@ -16284,7 +16281,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11">
         <v>-2.1728856957897776E-3</v>
@@ -16384,7 +16381,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B13">
         <v>-1.8747522770179968E-3</v>
@@ -16434,7 +16431,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B14">
         <v>0.11698327499269433</v>
@@ -16484,7 +16481,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B15">
         <v>-9.6004663813509448E-5</v>

--- a/input/reg_labourSupplyUtility.xlsx
+++ b/input/reg_labourSupplyUtility.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A31DD31A-C2F4-43D5-98D0-DF501A31C2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0D2449C-E877-4340-942B-EAD1AB802124}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" tabRatio="948" activeTab="7" xr2:uid="{CE10044B-DF17-4109-838C-2F682B85B23F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="948" activeTab="7" xr2:uid="{CE10044B-DF17-4109-838C-2F682B85B23F}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="7" r:id="rId1"/>
-    <sheet name="IT_Single_Males" sheetId="1" r:id="rId2"/>
-    <sheet name="IT_Single_Females" sheetId="5" r:id="rId3"/>
-    <sheet name="IT_SingleAC_Males" sheetId="8" r:id="rId4"/>
-    <sheet name="IT_SingleAC_Females" sheetId="9" r:id="rId5"/>
-    <sheet name="IT_Couples" sheetId="6" r:id="rId6"/>
-    <sheet name="IT_Males_With_Dep" sheetId="20" r:id="rId7"/>
-    <sheet name="IT_Females_With_Dep" sheetId="21" r:id="rId8"/>
+    <sheet name="EL_Single_Males" sheetId="1" r:id="rId2"/>
+    <sheet name="EL_Single_Females" sheetId="5" r:id="rId3"/>
+    <sheet name="EL_SingleAC_Males" sheetId="8" r:id="rId4"/>
+    <sheet name="EL_SingleAC_Females" sheetId="9" r:id="rId5"/>
+    <sheet name="EL_Couples" sheetId="6" r:id="rId6"/>
+    <sheet name="EL_Males_With_Dep" sheetId="20" r:id="rId7"/>
+    <sheet name="EL_Females_With_Dep" sheetId="21" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -698,14 +698,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{851C952C-0730-457A-A376-78EF87C9F806}">
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.73046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.1328125" style="1"/>
+    <col min="2" max="2" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -717,7 +717,7 @@
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
     </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
@@ -727,7 +727,7 @@
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -735,7 +735,7 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -743,7 +743,7 @@
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -751,7 +751,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -759,7 +759,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -767,7 +767,7 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -775,7 +775,7 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -796,18 +796,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85FEAAE6-65C5-44AD-94AB-B2F965791C43}">
   <dimension ref="A1:P15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.1328125" customWidth="1"/>
-    <col min="2" max="2" width="12.73046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.86328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.73046875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.140625" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -857,7 +857,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -907,7 +907,7 @@
         <v>-4.1303026022930563E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -957,7 +957,7 @@
         <v>1.0138087187054717E-5</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1007,7 +1007,7 @@
         <v>5.6958279416736743E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>-1.8213299141134283E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>2.2135672641542299E-5</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1157,7 +1157,7 @@
         <v>6.7882463494384995E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>5.1509971206701498E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -1257,7 +1257,7 @@
         <v>0.12946484060918961</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -1307,7 +1307,7 @@
         <v>0.10225447483519083</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>0.18100559756010412</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -1407,7 +1407,7 @@
         <v>7.567524084092131E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -1457,7 +1457,7 @@
         <v>0.15490958625085985</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>0.20513993729931276</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1565,25 +1565,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A5AD492-5570-405E-BE90-089FB56DBA70}">
   <dimension ref="A1:P15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.1328125" customWidth="1"/>
-    <col min="2" max="2" width="12.73046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.86328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.140625" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="28" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.86328125" customWidth="1"/>
-    <col min="9" max="9" width="12.73046875" customWidth="1"/>
-    <col min="10" max="10" width="12.3984375" customWidth="1"/>
-    <col min="11" max="11" width="14.265625" customWidth="1"/>
-    <col min="12" max="12" width="15.1328125" customWidth="1"/>
-    <col min="13" max="13" width="11.86328125" customWidth="1"/>
-    <col min="14" max="14" width="12.59765625" customWidth="1"/>
+    <col min="8" max="8" width="20.85546875" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" customWidth="1"/>
+    <col min="13" max="13" width="11.85546875" customWidth="1"/>
+    <col min="14" max="14" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1633,7 +1633,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1683,7 +1683,7 @@
         <v>-1.2380790025430734E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1733,7 +1733,7 @@
         <v>1.2526943685672292E-6</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1783,7 +1783,7 @@
         <v>-4.6303896868221221E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1833,7 +1833,7 @@
         <v>1.6254813031192179E-5</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1883,7 +1883,7 @@
         <v>5.4338930542280062E-6</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>-3.5832874906259367E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -1983,7 +1983,7 @@
         <v>1.3395669676520398E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>4.8020065553522631E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>1.580232626415248E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -2133,7 +2133,7 @@
         <v>5.1043942771023407E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>1.5805255858361636E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -2233,7 +2233,7 @@
         <v>5.1373399770043612E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>5.1071509785487176E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -2341,22 +2341,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CF4F370-8F94-4471-B70B-705C22298390}">
   <dimension ref="A1:P15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.59765625" customWidth="1"/>
-    <col min="2" max="2" width="12.73046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.86328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.73046875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.86328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.1328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="31.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="18" width="12.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="42.5703125" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="18" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2406,7 +2406,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2456,7 +2456,7 @@
         <v>2.4303160070852357E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2506,7 +2506,7 @@
         <v>-1.734568012050522E-5</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -2556,7 +2556,7 @@
         <v>0.1338997214365325</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -2606,7 +2606,7 @@
         <v>-4.2452717287763876E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -2656,7 +2656,7 @@
         <v>-1.9900574285520433E-5</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -2706,7 +2706,7 @@
         <v>0.13282707701399771</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -2756,7 +2756,7 @@
         <v>0.12300677565243691</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -2806,7 +2806,7 @@
         <v>0.20620044215239472</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -2856,7 +2856,7 @@
         <v>0.23847474649923969</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -2906,7 +2906,7 @@
         <v>0.32305914441492861</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -2956,7 +2956,7 @@
         <v>0.19940349935077617</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -3006,7 +3006,7 @@
         <v>0.28479165906212417</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -3056,7 +3056,7 @@
         <v>0.49253746195074583</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -3114,18 +3114,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F0F2A53-AC1B-4E7D-AB71-4CE722E2A5F0}">
   <dimension ref="A1:P15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.3984375" customWidth="1"/>
-    <col min="2" max="2" width="12.73046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.86328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3175,7 +3175,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>3.9313822707888859E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>-9.5831977198290207E-6</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>-5.5922762047787428E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3375,7 +3375,7 @@
         <v>2.372862316230652E-5</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -3425,7 +3425,7 @@
         <v>-2.5596040904507815E-5</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>-0.25280579096977052</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -3525,7 +3525,7 @@
         <v>3.6960976726851447E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -3575,7 +3575,7 @@
         <v>8.1419455932170176E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -3625,7 +3625,7 @@
         <v>4.584389325268852E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -3675,7 +3675,7 @@
         <v>9.2357784249225264E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -3725,7 +3725,7 @@
         <v>4.8071403966398002E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -3775,7 +3775,7 @@
         <v>9.5437002378811892E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -3825,7 +3825,7 @@
         <v>0.30106454405810701</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -3884,13 +3884,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44E4BA5A-69F1-4BBC-84FF-1A1A1810CA5C}">
   <dimension ref="A1:BI60"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.1328125" customWidth="1"/>
-    <col min="2" max="2" width="13.1328125" customWidth="1"/>
+    <col min="1" max="1" width="40.140625" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4075,7 +4075,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -4260,7 +4260,7 @@
         <v>1.7389401769741617E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -4445,7 +4445,7 @@
         <v>-1.3613653649094759E-6</v>
       </c>
     </row>
-    <row r="4" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -4630,7 +4630,7 @@
         <v>-3.8557545180914754E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -4815,7 +4815,7 @@
         <v>-1.9934345816102907E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -5000,7 +5000,7 @@
         <v>8.3796654554168403E-5</v>
       </c>
     </row>
-    <row r="7" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -5185,7 +5185,7 @@
         <v>9.5705848238582384E-6</v>
       </c>
     </row>
-    <row r="8" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -5370,7 +5370,7 @@
         <v>1.3499608270928432E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -5555,7 +5555,7 @@
         <v>-1.0174559386537865E-5</v>
       </c>
     </row>
-    <row r="10" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -5740,7 +5740,7 @@
         <v>-2.7127573908897487E-6</v>
       </c>
     </row>
-    <row r="11" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -5925,7 +5925,7 @@
         <v>1.8218961510738832E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -6110,7 +6110,7 @@
         <v>-5.954788559602681E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>43</v>
       </c>
@@ -6295,7 +6295,7 @@
         <v>0.11796321762039662</v>
       </c>
     </row>
-    <row r="14" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -6480,7 +6480,7 @@
         <v>0.15397565325127316</v>
       </c>
     </row>
-    <row r="15" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>45</v>
       </c>
@@ -6665,7 +6665,7 @@
         <v>0.17393809539501776</v>
       </c>
     </row>
-    <row r="16" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>46</v>
       </c>
@@ -6850,7 +6850,7 @@
         <v>0.21098413112153436</v>
       </c>
     </row>
-    <row r="17" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>47</v>
       </c>
@@ -7035,7 +7035,7 @@
         <v>0.20653615397684663</v>
       </c>
     </row>
-    <row r="18" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>48</v>
       </c>
@@ -7220,7 +7220,7 @@
         <v>0.24413560224543851</v>
       </c>
     </row>
-    <row r="19" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -7405,7 +7405,7 @@
         <v>0.23382616105243839</v>
       </c>
     </row>
-    <row r="20" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>50</v>
       </c>
@@ -7590,7 +7590,7 @@
         <v>0.27178205760678759</v>
       </c>
     </row>
-    <row r="21" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>51</v>
       </c>
@@ -7775,7 +7775,7 @@
         <v>0.29076129448390819</v>
       </c>
     </row>
-    <row r="22" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>52</v>
       </c>
@@ -7960,7 +7960,7 @@
         <v>0.32832593007849215</v>
       </c>
     </row>
-    <row r="23" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -8145,7 +8145,7 @@
         <v>0.32505761399129751</v>
       </c>
     </row>
-    <row r="24" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -8330,7 +8330,7 @@
         <v>0.36406099206427128</v>
       </c>
     </row>
-    <row r="25" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -8515,7 +8515,7 @@
         <v>0.33909716430662462</v>
       </c>
     </row>
-    <row r="26" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>56</v>
       </c>
@@ -8700,7 +8700,7 @@
         <v>0.37871377790347488</v>
       </c>
     </row>
-    <row r="27" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>57</v>
       </c>
@@ -8885,7 +8885,7 @@
         <v>0.34651737724729215</v>
       </c>
     </row>
-    <row r="28" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -9070,7 +9070,7 @@
         <v>0.38646839138584832</v>
       </c>
     </row>
-    <row r="29" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>59</v>
       </c>
@@ -9255,7 +9255,7 @@
         <v>0.35700434836920064</v>
       </c>
     </row>
-    <row r="30" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>60</v>
       </c>
@@ -9440,7 +9440,7 @@
         <v>0.39715987380718965</v>
       </c>
     </row>
-    <row r="31" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>61</v>
       </c>
@@ -9625,7 +9625,7 @@
         <v>0.33022325121382984</v>
       </c>
     </row>
-    <row r="32" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>62</v>
       </c>
@@ -9810,7 +9810,7 @@
         <v>0.36814112172038554</v>
       </c>
     </row>
-    <row r="33" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>63</v>
       </c>
@@ -9995,7 +9995,7 @@
         <v>0.34777260969369372</v>
       </c>
     </row>
-    <row r="34" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>64</v>
       </c>
@@ -10180,7 +10180,7 @@
         <v>0.38708661809489342</v>
       </c>
     </row>
-    <row r="35" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>65</v>
       </c>
@@ -10365,7 +10365,7 @@
         <v>0.35342784789479914</v>
       </c>
     </row>
-    <row r="36" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>66</v>
       </c>
@@ -10550,7 +10550,7 @@
         <v>0.39331434811656585</v>
       </c>
     </row>
-    <row r="37" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>67</v>
       </c>
@@ -10735,7 +10735,7 @@
         <v>0.35581661402692638</v>
       </c>
     </row>
-    <row r="38" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>68</v>
       </c>
@@ -10920,7 +10920,7 @@
         <v>0.39600898176043575</v>
       </c>
     </row>
-    <row r="39" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>69</v>
       </c>
@@ -11105,7 +11105,7 @@
         <v>0.36294657547937992</v>
       </c>
     </row>
-    <row r="40" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>70</v>
       </c>
@@ -11290,7 +11290,7 @@
         <v>0.40332730110441728</v>
       </c>
     </row>
-    <row r="41" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>71</v>
       </c>
@@ -11475,7 +11475,7 @@
         <v>0.33483514176185414</v>
       </c>
     </row>
-    <row r="42" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>72</v>
       </c>
@@ -11660,7 +11660,7 @@
         <v>0.37297373876980183</v>
       </c>
     </row>
-    <row r="43" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>73</v>
       </c>
@@ -11845,7 +11845,7 @@
         <v>0.34121968706825978</v>
       </c>
     </row>
-    <row r="44" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>74</v>
       </c>
@@ -12030,7 +12030,7 @@
         <v>0.38073860384928093</v>
       </c>
     </row>
-    <row r="45" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>75</v>
       </c>
@@ -12215,7 +12215,7 @@
         <v>0.34128649677211759</v>
       </c>
     </row>
-    <row r="46" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>76</v>
       </c>
@@ -12400,7 +12400,7 @@
         <v>0.38135108593231715</v>
       </c>
     </row>
-    <row r="47" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>77</v>
       </c>
@@ -12585,7 +12585,7 @@
         <v>0.3403209028493851</v>
       </c>
     </row>
-    <row r="48" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>78</v>
       </c>
@@ -12770,7 +12770,7 @@
         <v>0.380668207613999</v>
       </c>
     </row>
-    <row r="49" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>79</v>
       </c>
@@ -12955,7 +12955,7 @@
         <v>0.34521401973700205</v>
       </c>
     </row>
-    <row r="50" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>80</v>
       </c>
@@ -13140,7 +13140,7 @@
         <v>0.38573697619558328</v>
       </c>
     </row>
-    <row r="51" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>81</v>
       </c>
@@ -13325,7 +13325,7 @@
         <v>0.37974170453899647</v>
       </c>
     </row>
-    <row r="52" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>82</v>
       </c>
@@ -13510,7 +13510,7 @@
         <v>0.41839688393272706</v>
       </c>
     </row>
-    <row r="53" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>83</v>
       </c>
@@ -13695,7 +13695,7 @@
         <v>0.35819711607115851</v>
       </c>
     </row>
-    <row r="54" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>84</v>
       </c>
@@ -13880,7 +13880,7 @@
         <v>0.39820763545167964</v>
       </c>
     </row>
-    <row r="55" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>85</v>
       </c>
@@ -14065,7 +14065,7 @@
         <v>0.34429239529886618</v>
       </c>
     </row>
-    <row r="56" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>86</v>
       </c>
@@ -14250,7 +14250,7 @@
         <v>0.38478077398552807</v>
       </c>
     </row>
-    <row r="57" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>87</v>
       </c>
@@ -14435,7 +14435,7 @@
         <v>0.33494510455771209</v>
       </c>
     </row>
-    <row r="58" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>88</v>
       </c>
@@ -14620,7 +14620,7 @@
         <v>0.37567648284290195</v>
       </c>
     </row>
-    <row r="59" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>89</v>
       </c>
@@ -14805,7 +14805,7 @@
         <v>0.33424729673380738</v>
       </c>
     </row>
-    <row r="60" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>90</v>
       </c>
@@ -14999,18 +14999,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6ABBF8F-3DA9-4957-ACE4-D5C4AAE8F601}">
   <dimension ref="A1:P15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.265625" customWidth="1"/>
-    <col min="2" max="2" width="12.73046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.86328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.73046875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.28515625" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -15060,7 +15060,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -15110,7 +15110,7 @@
         <v>2.4791215759218512E-5</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -15160,7 +15160,7 @@
         <v>-1.0353147730489873E-7</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -15210,7 +15210,7 @@
         <v>-5.7565467029892714E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -15260,7 +15260,7 @@
         <v>1.7526420380991433E-6</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -15310,7 +15310,7 @@
         <v>3.4867361296047746E-9</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -15360,7 +15360,7 @@
         <v>-8.6163196725572145E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -15410,7 +15410,7 @@
         <v>-1.943323859118462E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -15460,7 +15460,7 @@
         <v>4.4006537762031635E-6</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -15510,7 +15510,7 @@
         <v>-2.3826378078796521E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -15560,7 +15560,7 @@
         <v>5.0767302660559536E-6</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -15610,7 +15610,7 @@
         <v>-2.1259604047832274E-4</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -15660,7 +15660,7 @@
         <v>4.6623619911975674E-6</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>91</v>
       </c>
@@ -15710,7 +15710,7 @@
         <v>-3.3695634860242705E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>92</v>
       </c>
@@ -15768,18 +15768,18 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86831B41-CE8C-4F34-B10B-C522104558DF}">
   <dimension ref="A1:P15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="38.86328125" customWidth="1"/>
-    <col min="2" max="2" width="12.73046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.86328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.85546875" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -15829,7 +15829,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -15879,7 +15879,7 @@
         <v>5.7839138669941328E-6</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -15929,7 +15929,7 @@
         <v>-3.0438585803084671E-8</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -15979,7 +15979,7 @@
         <v>-1.876273738822693E-6</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -16029,7 +16029,7 @@
         <v>3.5670503579368312E-9</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -16079,7 +16079,7 @@
         <v>-8.3045518215310663E-9</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -16129,7 +16129,7 @@
         <v>4.5851270266908075E-5</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -16179,7 +16179,7 @@
         <v>-1.0280139676654469E-5</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -16229,7 +16229,7 @@
         <v>2.9539670379106738E-7</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -16279,7 +16279,7 @@
         <v>-1.1456371092644932E-5</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -16329,7 +16329,7 @@
         <v>3.0840224948516453E-7</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -16379,7 +16379,7 @@
         <v>-1.3000343587210044E-5</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -16429,7 +16429,7 @@
         <v>3.4250832591416637E-7</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>93</v>
       </c>
@@ -16479,7 +16479,7 @@
         <v>-2.1192590733527565E-5</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>94</v>
       </c>

--- a/input/reg_labourSupplyUtility.xlsx
+++ b/input/reg_labourSupplyUtility.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\andy_local\SimPaths project files\SimPaths\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0B80B9F-6C15-4355-B04D-1D328817DE64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E711D168-67C9-46C7-A4B9-2ABA38379D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{B28C262A-F414-4C9F-9F20-D497875F2897}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="7" xr2:uid="{B28C262A-F414-4C9F-9F20-D497875F2897}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="8" r:id="rId1"/>
-    <sheet name="UK_Single_Females" sheetId="9" r:id="rId2"/>
-    <sheet name="UK_Single_Males" sheetId="10" r:id="rId3"/>
-    <sheet name="UK_Couples" sheetId="11" r:id="rId4"/>
-    <sheet name="UK_Females_With_Dep" sheetId="12" r:id="rId5"/>
-    <sheet name="UK_Males_With_Dep" sheetId="13" r:id="rId6"/>
-    <sheet name="UK_SingleAC_Females" sheetId="14" r:id="rId7"/>
-    <sheet name="UK_SingleAC_Males" sheetId="15" r:id="rId8"/>
+    <sheet name="UK_Single_Females" sheetId="16" r:id="rId2"/>
+    <sheet name="UK_Single_Males" sheetId="17" r:id="rId3"/>
+    <sheet name="UK_Couples" sheetId="18" r:id="rId4"/>
+    <sheet name="UK_Females_With_Dep" sheetId="19" r:id="rId5"/>
+    <sheet name="UK_Males_With_Dep" sheetId="20" r:id="rId6"/>
+    <sheet name="UK_SingleAC_Females" sheetId="21" r:id="rId7"/>
+    <sheet name="UK_SingleAC_Males" sheetId="22" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="233">
   <si>
     <t>REGRESSOR</t>
   </si>
@@ -438,12 +438,6 @@
     <t>Hrs_36Plus_Male</t>
   </si>
   <si>
-    <t>Hrs_36plus_Male</t>
-  </si>
-  <si>
-    <t>Hrs_36plus_Female</t>
-  </si>
-  <si>
     <t>Liwwh_Male_1</t>
   </si>
   <si>
@@ -684,70 +678,70 @@
     <t>Liwwh_Female_440</t>
   </si>
   <si>
-    <t>Female_Leisure_North_West</t>
+    <t>FemaleLeisure_UKN</t>
   </si>
   <si>
-    <t>Female_Leisure_York_and_Humb</t>
+    <t>FemaleLeisure_UKM</t>
   </si>
   <si>
-    <t>Female_Leisure_East_Mid</t>
+    <t>FemaleLeisure_UKL</t>
   </si>
   <si>
-    <t>Female_Leisure_West_Mid</t>
+    <t>FemaleLeisure_UKK</t>
   </si>
   <si>
-    <t>Female_Leisure_East</t>
+    <t>FemaleLeisure_UKJ</t>
   </si>
   <si>
-    <t>Female_Leisure_London</t>
+    <t>FemaleLeisure_UKI</t>
   </si>
   <si>
-    <t>Female_Leisure_South_East</t>
+    <t>FemaleLeisure_UKH</t>
   </si>
   <si>
-    <t>Female_Leisure_South_West</t>
+    <t>FemaleLeisure_UKG</t>
   </si>
   <si>
-    <t>Female_Leisure_Wales</t>
+    <t>FemaleLeisure_UKF</t>
   </si>
   <si>
-    <t>Female_Leisure_Scotland</t>
+    <t>FemaleLeisure_UKE</t>
   </si>
   <si>
-    <t>Female_Leisure_N_Ireland</t>
+    <t>FemaleLeisure_UKD</t>
   </si>
   <si>
-    <t>Male_Leisure_North_West</t>
+    <t>MaleLeisure_UKN</t>
   </si>
   <si>
-    <t>Male_Leisure_York_and_Humb</t>
+    <t>MaleLeisure_UKM</t>
   </si>
   <si>
-    <t>Male_Leisure_East_Mid</t>
+    <t>MaleLeisure_UKL</t>
   </si>
   <si>
-    <t>Male_Leisure_West_Mid</t>
+    <t>MaleLeisure_UKK</t>
   </si>
   <si>
-    <t>Male_Leisure_East</t>
+    <t>MaleLeisure_UKJ</t>
   </si>
   <si>
-    <t>Male_Leisure_London</t>
+    <t>MaleLeisure_UKI</t>
   </si>
   <si>
-    <t>Male_Leisure_South_East</t>
+    <t>MaleLeisure_UKH</t>
   </si>
   <si>
-    <t>Male_Leisure_South_West</t>
+    <t>MaleLeisure_UKG</t>
   </si>
   <si>
-    <t>Male_Leisure_Wales</t>
+    <t>MaleLeisure_UKF</t>
   </si>
   <si>
-    <t>Male_Leisure_Scotland</t>
+    <t>MaleLeisure_UKE</t>
   </si>
   <si>
-    <t>Male_Leisure_N_Ireland</t>
+    <t>MaleLeisure_UKD</t>
   </si>
 </sst>
 </file>
@@ -1242,11 +1236,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A54708F7-E5DF-49D6-BFC9-764EDF2B3988}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2497E15-6FF7-4BEA-8049-BA4982ADFA83}">
   <dimension ref="A1:DD107"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="11.42578125" style="3"/>
+    <col min="1" max="1" width="28.28515625" style="3" customWidth="1"/>
+    <col min="2" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:108" x14ac:dyDescent="0.25">
@@ -36133,16 +36128,17 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4825F45A-4B0A-410B-A3E0-81D900AD6513}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DB56E65-A028-41C8-8E37-C957AEE6B4E5}">
   <dimension ref="A1:I8"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="11.42578125" style="3"/>
+    <col min="1" max="1" width="39.7109375" style="3" customWidth="1"/>
+    <col min="2" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -36379,16 +36375,17 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6658EE7-2D33-44C1-A6F2-93177E287D88}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{713A1631-5A78-441A-A83A-D84683700833}">
   <dimension ref="A1:CP93"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="11.42578125" style="3"/>
+    <col min="1" max="1" width="33" style="3" customWidth="1"/>
+    <col min="2" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:94" x14ac:dyDescent="0.25">
@@ -36429,250 +36426,250 @@
         <v>6</v>
       </c>
       <c r="M1" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AI1" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AK1" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AL1" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AM1" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AN1" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AO1" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AP1" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AR1" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AS1" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="AT1" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="AU1" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="AT1" s="3" t="s">
+      <c r="AV1" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="AU1" s="3" t="s">
+      <c r="AW1" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="AV1" s="3" t="s">
+      <c r="AX1" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="AW1" s="3" t="s">
+      <c r="AY1" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="AX1" s="3" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="AY1" s="3" t="s">
+      <c r="BA1" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="AZ1" s="3" t="s">
+      <c r="BB1" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="BA1" s="3" t="s">
+      <c r="BC1" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="BB1" s="3" t="s">
+      <c r="BD1" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="BC1" s="3" t="s">
+      <c r="BE1" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="BD1" s="3" t="s">
+      <c r="BF1" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="BE1" s="3" t="s">
+      <c r="BG1" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="BF1" s="3" t="s">
+      <c r="BH1" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="BG1" s="3" t="s">
+      <c r="BI1" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="BH1" s="3" t="s">
+      <c r="BJ1" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="BI1" s="3" t="s">
+      <c r="BK1" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="BJ1" s="3" t="s">
+      <c r="BL1" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="BK1" s="3" t="s">
+      <c r="BM1" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="BL1" s="3" t="s">
+      <c r="BN1" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="BM1" s="3" t="s">
+      <c r="BO1" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="BN1" s="3" t="s">
+      <c r="BP1" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="BO1" s="3" t="s">
+      <c r="BQ1" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="BP1" s="3" t="s">
+      <c r="BR1" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="BQ1" s="3" t="s">
+      <c r="BS1" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="BR1" s="3" t="s">
+      <c r="BT1" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="BS1" s="3" t="s">
+      <c r="BU1" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="BT1" s="3" t="s">
+      <c r="BV1" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="BU1" s="3" t="s">
+      <c r="BW1" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="BV1" s="3" t="s">
+      <c r="BX1" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="BW1" s="3" t="s">
+      <c r="BY1" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="BX1" s="3" t="s">
+      <c r="BZ1" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="BY1" s="3" t="s">
+      <c r="CA1" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="BZ1" s="3" t="s">
+      <c r="CB1" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="CA1" s="3" t="s">
+      <c r="CC1" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="CB1" s="3" t="s">
+      <c r="CD1" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="CC1" s="3" t="s">
+      <c r="CE1" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="CD1" s="3" t="s">
+      <c r="CF1" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="CE1" s="3" t="s">
+      <c r="CG1" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="CF1" s="3" t="s">
+      <c r="CH1" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="CG1" s="3" t="s">
+      <c r="CI1" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="CH1" s="3" t="s">
+      <c r="CJ1" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="CI1" s="3" t="s">
+      <c r="CK1" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="CJ1" s="3" t="s">
+      <c r="CL1" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="CK1" s="3" t="s">
+      <c r="CM1" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="CL1" s="3" t="s">
+      <c r="CN1" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="CM1" s="3" t="s">
+      <c r="CO1" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="CN1" s="3" t="s">
+      <c r="CP1" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="CO1" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="CP1" s="3" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:94" x14ac:dyDescent="0.25">
@@ -40085,7 +40082,7 @@
     </row>
     <row r="14" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B14" s="3">
         <v>-0.24851257653206699</v>
@@ -40369,7 +40366,7 @@
     </row>
     <row r="15" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B15" s="3">
         <v>-0.15501650152683599</v>
@@ -40653,7 +40650,7 @@
     </row>
     <row r="16" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B16" s="3">
         <v>-3.3557569295545202E-2</v>
@@ -40937,7 +40934,7 @@
     </row>
     <row r="17" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B17" s="3">
         <v>3.1086688130075299E-2</v>
@@ -41221,7 +41218,7 @@
     </row>
     <row r="18" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B18" s="3">
         <v>-3.54804655910477E-2</v>
@@ -41505,7 +41502,7 @@
     </row>
     <row r="19" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B19" s="3">
         <v>0.104490784522007</v>
@@ -41789,7 +41786,7 @@
     </row>
     <row r="20" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B20" s="3">
         <v>-1.6740910505204602E-2</v>
@@ -42073,7 +42070,7 @@
     </row>
     <row r="21" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B21" s="3">
         <v>2.68411381805354E-2</v>
@@ -42357,7 +42354,7 @@
     </row>
     <row r="22" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B22" s="3">
         <v>3.9140421628870901E-2</v>
@@ -42641,7 +42638,7 @@
     </row>
     <row r="23" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B23" s="3">
         <v>3.6009585048853501E-2</v>
@@ -42925,7 +42922,7 @@
     </row>
     <row r="24" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B24" s="3">
         <v>-4.1153464270304002E-2</v>
@@ -43209,7 +43206,7 @@
     </row>
     <row r="25" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B25" s="3">
         <v>5.2805973843852799E-2</v>
@@ -43493,7 +43490,7 @@
     </row>
     <row r="26" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B26" s="3">
         <v>-0.24664046507380399</v>
@@ -43777,7 +43774,7 @@
     </row>
     <row r="27" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B27" s="3">
         <v>-8.16818341777997E-2</v>
@@ -44061,7 +44058,7 @@
     </row>
     <row r="28" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B28" s="3">
         <v>-2.7376636525575999E-2</v>
@@ -44345,7 +44342,7 @@
     </row>
     <row r="29" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B29" s="3">
         <v>3.6859599206483303E-2</v>
@@ -44629,7 +44626,7 @@
     </row>
     <row r="30" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B30" s="3">
         <v>-0.266921014426866</v>
@@ -44913,7 +44910,7 @@
     </row>
     <row r="31" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B31" s="3">
         <v>-9.4004542275197001E-2</v>
@@ -45197,7 +45194,7 @@
     </row>
     <row r="32" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B32" s="3">
         <v>-1.28983256881103E-2</v>
@@ -45481,7 +45478,7 @@
     </row>
     <row r="33" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B33" s="3">
         <v>1.39806666058512E-2</v>
@@ -45765,7 +45762,7 @@
     </row>
     <row r="34" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B34" s="3">
         <v>-0.241530621994761</v>
@@ -46049,7 +46046,7 @@
     </row>
     <row r="35" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B35" s="3">
         <v>-0.147615297043832</v>
@@ -46333,7 +46330,7 @@
     </row>
     <row r="36" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B36" s="3">
         <v>-3.0341143642342298E-2</v>
@@ -46617,7 +46614,7 @@
     </row>
     <row r="37" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B37" s="3">
         <v>3.07085183522318E-2</v>
@@ -46901,7 +46898,7 @@
     </row>
     <row r="38" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B38" s="3">
         <v>-0.235620706291398</v>
@@ -47185,7 +47182,7 @@
     </row>
     <row r="39" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B39" s="3">
         <v>-0.14108344291893599</v>
@@ -47469,7 +47466,7 @@
     </row>
     <row r="40" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B40" s="3">
         <v>-3.1069493186529198E-2</v>
@@ -47753,7 +47750,7 @@
     </row>
     <row r="41" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B41" s="3">
         <v>4.4659950017029999E-2</v>
@@ -48037,7 +48034,7 @@
     </row>
     <row r="42" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B42" s="3">
         <v>-0.25460426377618001</v>
@@ -48321,7 +48318,7 @@
     </row>
     <row r="43" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B43" s="3">
         <v>-8.3970811896098896E-2</v>
@@ -48605,7 +48602,7 @@
     </row>
     <row r="44" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B44" s="3">
         <v>-2.3993425911259199E-2</v>
@@ -48889,7 +48886,7 @@
     </row>
     <row r="45" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B45" s="3">
         <v>4.06632647854046E-2</v>
@@ -49173,7 +49170,7 @@
     </row>
     <row r="46" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B46" s="3">
         <v>-0.245869225848625</v>
@@ -49457,7 +49454,7 @@
     </row>
     <row r="47" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B47" s="3">
         <v>-8.1010365828426203E-2</v>
@@ -49741,7 +49738,7 @@
     </row>
     <row r="48" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B48" s="3">
         <v>-2.7620053894158701E-2</v>
@@ -50025,7 +50022,7 @@
     </row>
     <row r="49" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B49" s="3">
         <v>3.3648476392357199E-2</v>
@@ -50309,7 +50306,7 @@
     </row>
     <row r="50" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B50" s="3">
         <v>-0.27974082537358902</v>
@@ -50593,7 +50590,7 @@
     </row>
     <row r="51" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B51" s="3">
         <v>-7.9125985712695704E-2</v>
@@ -50877,7 +50874,7 @@
     </row>
     <row r="52" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B52" s="3">
         <v>1.16923849670512E-2</v>
@@ -51161,7 +51158,7 @@
     </row>
     <row r="53" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B53" s="3">
         <v>-2.37213448911E-3</v>
@@ -51445,7 +51442,7 @@
     </row>
     <row r="54" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B54" s="3">
         <v>-0.23817014524878</v>
@@ -51729,7 +51726,7 @@
     </row>
     <row r="55" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B55" s="3">
         <v>-0.143863760962225</v>
@@ -52013,7 +52010,7 @@
     </row>
     <row r="56" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B56" s="3">
         <v>-1.9193132946093001E-2</v>
@@ -52297,7 +52294,7 @@
     </row>
     <row r="57" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B57" s="3">
         <v>2.9104616195848799E-2</v>
@@ -52581,7 +52578,7 @@
     </row>
     <row r="58" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B58" s="3">
         <v>-0.26222573600960403</v>
@@ -52865,7 +52862,7 @@
     </row>
     <row r="59" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B59" s="3">
         <v>-8.7324478884078599E-2</v>
@@ -53149,7 +53146,7 @@
     </row>
     <row r="60" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B60" s="3">
         <v>-8.0538958530602008E-3</v>
@@ -53433,7 +53430,7 @@
     </row>
     <row r="61" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B61" s="3">
         <v>3.4468551042118899E-2</v>
@@ -53717,7 +53714,7 @@
     </row>
     <row r="62" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B62" s="3">
         <v>-5.8149600710401704E-3</v>
@@ -54001,7 +53998,7 @@
     </row>
     <row r="63" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B63" s="3">
         <v>3.2403465051017197E-2</v>
@@ -54285,7 +54282,7 @@
     </row>
     <row r="64" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B64" s="3">
         <v>-1.95968544991071E-2</v>
@@ -54569,7 +54566,7 @@
     </row>
     <row r="65" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B65" s="3">
         <v>4.3088570435007703E-2</v>
@@ -54853,7 +54850,7 @@
     </row>
     <row r="66" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B66" s="3">
         <v>1.3782593123408699E-2</v>
@@ -55137,7 +55134,7 @@
     </row>
     <row r="67" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B67" s="3">
         <v>4.2217819515446E-3</v>
@@ -55421,7 +55418,7 @@
     </row>
     <row r="68" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B68" s="3">
         <v>-0.24101550673286201</v>
@@ -55705,7 +55702,7 @@
     </row>
     <row r="69" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B69" s="3">
         <v>-0.14407589532802201</v>
@@ -55989,7 +55986,7 @@
     </row>
     <row r="70" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B70" s="3">
         <v>-1.37294896327869E-2</v>
@@ -56273,7 +56270,7 @@
     </row>
     <row r="71" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B71" s="3">
         <v>3.73680753415431E-2</v>
@@ -56557,7 +56554,7 @@
     </row>
     <row r="72" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B72" s="3">
         <v>-0.26682852387940398</v>
@@ -56841,7 +56838,7 @@
     </row>
     <row r="73" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B73" s="3">
         <v>-8.8436226125812104E-2</v>
@@ -57125,7 +57122,7 @@
     </row>
     <row r="74" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B74" s="3">
         <v>6.8005805226868698E-4</v>
@@ -57409,7 +57406,7 @@
     </row>
     <row r="75" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B75" s="3">
         <v>3.3848348666552203E-2</v>
@@ -57693,7 +57690,7 @@
     </row>
     <row r="76" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B76" s="3">
         <v>-8.8371173287494901E-4</v>
@@ -57977,7 +57974,7 @@
     </row>
     <row r="77" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B77" s="3">
         <v>4.04919256273501E-2</v>
@@ -58261,7 +58258,7 @@
     </row>
     <row r="78" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B78" s="3">
         <v>-1.24503691831E-2</v>
@@ -58545,7 +58542,7 @@
     </row>
     <row r="79" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B79" s="3">
         <v>4.4795385372791097E-2</v>
@@ -58829,7 +58826,7 @@
     </row>
     <row r="80" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B80" s="3">
         <v>2.0286667152899299E-3</v>
@@ -59113,7 +59110,7 @@
     </row>
     <row r="81" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B81" s="3">
         <v>3.6560329427985602E-3</v>
@@ -59397,7 +59394,7 @@
     </row>
     <row r="82" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B82" s="3">
         <v>7.0307314940585106E-2</v>
@@ -59681,7 +59678,7 @@
     </row>
     <row r="83" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B83" s="3">
         <v>-1.33212316156076</v>
@@ -59965,7 +59962,7 @@
     </row>
     <row r="84" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B84" s="3">
         <v>-8.9552728282690404E-3</v>
@@ -60249,7 +60246,7 @@
     </row>
     <row r="85" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B85" s="3">
         <v>1.9935071355956201E-2</v>
@@ -60533,7 +60530,7 @@
     </row>
     <row r="86" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B86" s="3">
         <v>-0.28281924164622801</v>
@@ -60817,7 +60814,7 @@
     </row>
     <row r="87" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B87" s="3">
         <v>-9.6856980827706898E-2</v>
@@ -61101,7 +61098,7 @@
     </row>
     <row r="88" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B88" s="3">
         <v>-1.0029218489704599E-2</v>
@@ -61385,7 +61382,7 @@
     </row>
     <row r="89" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B89" s="3">
         <v>3.4912659661339801E-2</v>
@@ -61669,7 +61666,7 @@
     </row>
     <row r="90" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B90" s="3">
         <v>-6.8797262004654299E-3</v>
@@ -61953,7 +61950,7 @@
     </row>
     <row r="91" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B91" s="3">
         <v>3.8238204748118503E-2</v>
@@ -62237,7 +62234,7 @@
     </row>
     <row r="92" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B92" s="3">
         <v>-1.19181161641839E-2</v>
@@ -62521,7 +62518,7 @@
     </row>
     <row r="93" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B93" s="3">
         <v>3.7717663714500901E-2</v>
@@ -62805,16 +62802,17 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9416BC3F-8B82-4765-A088-74681707CDEE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A52A53A-8337-4C79-8847-E5AFC5268D50}">
   <dimension ref="A1:I8"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="11.42578125" style="3"/>
+    <col min="1" max="1" width="33.42578125" style="3" customWidth="1"/>
+    <col min="2" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -63051,16 +63049,17 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09372B0C-F30D-4D98-96DC-582249BCF77D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9164393-5E7D-4422-9A61-B7FFE1623344}">
   <dimension ref="A1:I8"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="11.42578125" style="3"/>
+    <col min="1" max="1" width="30" style="3" customWidth="1"/>
+    <col min="2" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -63297,16 +63296,17 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0FB52BB-C20E-4BC6-976E-47599FA26233}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46DFF46C-488E-4562-9683-A336EF32C45A}">
   <dimension ref="A1:T19"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="11.42578125" style="3"/>
+    <col min="1" max="1" width="46.140625" style="3" customWidth="1"/>
+    <col min="2" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -63338,37 +63338,37 @@
         <v>29</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>217</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
@@ -63807,7 +63807,7 @@
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B9" s="3">
         <v>-8.1972965338796E-3</v>
@@ -63869,7 +63869,7 @@
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B10" s="3">
         <v>-6.8212570985156198E-4</v>
@@ -63931,7 +63931,7 @@
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B11" s="3">
         <v>-4.4596424160110298E-4</v>
@@ -63993,7 +63993,7 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B12" s="3">
         <v>-5.4173523046E-3</v>
@@ -64117,7 +64117,7 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B14" s="3">
         <v>7.0813954923913802E-3</v>
@@ -64179,7 +64179,7 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B15" s="3">
         <v>-8.6466993167642007E-3</v>
@@ -64241,7 +64241,7 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B16" s="3">
         <v>-1.52704841429614E-2</v>
@@ -64303,7 +64303,7 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="B17" s="3">
         <v>6.8823809369989702E-3</v>
@@ -64365,7 +64365,7 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="B18" s="3">
         <v>-1.56186443086244E-2</v>
@@ -64427,7 +64427,7 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="B19" s="3">
         <v>-1.07160697847995E-2</v>
@@ -64489,16 +64489,17 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F9CCDAC-EBCE-4616-82D5-20E839EE650F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DFE8567-67A3-41A3-9804-ADC448CEC0EA}">
   <dimension ref="A1:T19"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="11.42578125" style="3"/>
+    <col min="1" max="1" width="32.140625" style="3" customWidth="1"/>
+    <col min="2" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -64530,37 +64531,37 @@
         <v>130</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>228</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
@@ -64999,7 +65000,7 @@
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="B9" s="3">
         <v>-8.1972965338796E-3</v>
@@ -65061,7 +65062,7 @@
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B10" s="3">
         <v>-6.8212570985156198E-4</v>
@@ -65123,7 +65124,7 @@
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B11" s="3">
         <v>-4.4596424160110298E-4</v>
@@ -65185,7 +65186,7 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B12" s="3">
         <v>-5.4173523046E-3</v>
@@ -65309,7 +65310,7 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B14" s="3">
         <v>7.0813954923913802E-3</v>
@@ -65371,7 +65372,7 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B15" s="3">
         <v>-8.6466993167642007E-3</v>
@@ -65433,7 +65434,7 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B16" s="3">
         <v>-1.52704841429614E-2</v>
@@ -65495,7 +65496,7 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B17" s="3">
         <v>6.8823809369989702E-3</v>
@@ -65557,7 +65558,7 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="B18" s="3">
         <v>-1.56186443086244E-2</v>
@@ -65619,7 +65620,7 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="B19" s="3">
         <v>-1.07160697847995E-2</v>
@@ -65681,6 +65682,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/input/reg_labourSupplyUtility.xlsx
+++ b/input/reg_labourSupplyUtility.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\andy_local\SimPaths project files\SimPaths\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E711D168-67C9-46C7-A4B9-2ABA38379D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D899717B-DFCA-4FB0-91B0-5DDF60A2240C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="7" xr2:uid="{B28C262A-F414-4C9F-9F20-D497875F2897}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B28C262A-F414-4C9F-9F20-D497875F2897}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="8" r:id="rId1"/>
-    <sheet name="UK_Single_Females" sheetId="16" r:id="rId2"/>
-    <sheet name="UK_Single_Males" sheetId="17" r:id="rId3"/>
-    <sheet name="UK_Couples" sheetId="18" r:id="rId4"/>
-    <sheet name="UK_Females_With_Dep" sheetId="19" r:id="rId5"/>
-    <sheet name="UK_Males_With_Dep" sheetId="20" r:id="rId6"/>
-    <sheet name="UK_SingleAC_Females" sheetId="21" r:id="rId7"/>
-    <sheet name="UK_SingleAC_Males" sheetId="22" r:id="rId8"/>
+    <sheet name="UK_Single_Females" sheetId="23" r:id="rId2"/>
+    <sheet name="UK_Single_Males" sheetId="24" r:id="rId3"/>
+    <sheet name="UK_Couples" sheetId="25" r:id="rId4"/>
+    <sheet name="UK_Females_With_Dep" sheetId="26" r:id="rId5"/>
+    <sheet name="UK_Males_With_Dep" sheetId="27" r:id="rId6"/>
+    <sheet name="UK_SingleAC_Females" sheetId="28" r:id="rId7"/>
+    <sheet name="UK_SingleAC_Males" sheetId="29" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="232">
   <si>
     <t>REGRESSOR</t>
   </si>
@@ -247,9 +247,6 @@
   </si>
   <si>
     <t>UKH_20</t>
-  </si>
-  <si>
-    <t>UKI_2-0</t>
   </si>
   <si>
     <t>UKJ_20</t>
@@ -678,70 +675,70 @@
     <t>Liwwh_Female_440</t>
   </si>
   <si>
-    <t>FemaleLeisure_UKN</t>
+    <t>FemaleIncomeDiv100</t>
   </si>
   <si>
-    <t>FemaleLeisure_UKM</t>
+    <t>FemaleIncomeSqDiv10000</t>
   </si>
   <si>
-    <t>FemaleLeisure_UKL</t>
+    <t>MaleIncomeDiv100</t>
   </si>
   <si>
-    <t>FemaleLeisure_UKK</t>
+    <t>MaleIncomeSqDiv10000</t>
   </si>
   <si>
-    <t>FemaleLeisure_UKJ</t>
+    <t>FixedCost_Female</t>
   </si>
   <si>
-    <t>FemaleLeisure_UKI</t>
+    <t>Liwwh_1</t>
   </si>
   <si>
-    <t>FemaleLeisure_UKH</t>
+    <t>Liwwh_10</t>
   </si>
   <si>
-    <t>FemaleLeisure_UKG</t>
+    <t>Liwwh_11</t>
   </si>
   <si>
-    <t>FemaleLeisure_UKF</t>
+    <t>Liwwh_20</t>
   </si>
   <si>
-    <t>FemaleLeisure_UKE</t>
+    <t>Liwwh_21</t>
   </si>
   <si>
-    <t>FemaleLeisure_UKD</t>
+    <t>Liwwh_30</t>
   </si>
   <si>
-    <t>MaleLeisure_UKN</t>
+    <t>Liwwh_31</t>
   </si>
   <si>
-    <t>MaleLeisure_UKM</t>
+    <t>Liwwh_40</t>
   </si>
   <si>
-    <t>MaleLeisure_UKL</t>
+    <t>Liwwh_41</t>
   </si>
   <si>
-    <t>MaleLeisure_UKK</t>
+    <t>Liwwh_100</t>
   </si>
   <si>
-    <t>MaleLeisure_UKJ</t>
+    <t>Liwwh_101</t>
   </si>
   <si>
-    <t>MaleLeisure_UKI</t>
+    <t>Liwwh_200</t>
   </si>
   <si>
-    <t>MaleLeisure_UKH</t>
+    <t>Liwwh_201</t>
   </si>
   <si>
-    <t>MaleLeisure_UKG</t>
+    <t>Liwwh_300</t>
   </si>
   <si>
-    <t>MaleLeisure_UKF</t>
+    <t>Liwwh_301</t>
   </si>
   <si>
-    <t>MaleLeisure_UKE</t>
+    <t>Liwwh_400</t>
   </si>
   <si>
-    <t>MaleLeisure_UKD</t>
+    <t>Liwwh_401</t>
   </si>
 </sst>
 </file>
@@ -1236,12 +1233,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2497E15-6FF7-4BEA-8049-BA4982ADFA83}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{144D37F1-E874-493E-874F-A5B6CB3C3127}">
   <dimension ref="A1:DD107"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.28515625" style="3" customWidth="1"/>
-    <col min="2" max="16384" width="11.42578125" style="3"/>
+    <col min="1" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:108" x14ac:dyDescent="0.25">
@@ -1387,187 +1383,187 @@
         <v>67</v>
       </c>
       <c r="AV1" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AW1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="AW1" s="3" t="s">
+      <c r="AX1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="AX1" s="3" t="s">
+      <c r="AY1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="AY1" s="3" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="AZ1" s="3" t="s">
+      <c r="BA1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="BA1" s="3" t="s">
+      <c r="BB1" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="BB1" s="3" t="s">
+      <c r="BC1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="BC1" s="3" t="s">
+      <c r="BD1" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="BD1" s="3" t="s">
+      <c r="BE1" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="BE1" s="3" t="s">
+      <c r="BF1" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="BF1" s="3" t="s">
+      <c r="BG1" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="BG1" s="3" t="s">
+      <c r="BH1" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="BH1" s="3" t="s">
+      <c r="BI1" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="BI1" s="3" t="s">
+      <c r="BJ1" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="BJ1" s="3" t="s">
+      <c r="BK1" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="BK1" s="3" t="s">
+      <c r="BL1" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="BL1" s="3" t="s">
+      <c r="BM1" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="BM1" s="3" t="s">
+      <c r="BN1" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="BN1" s="3" t="s">
+      <c r="BO1" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="BO1" s="3" t="s">
+      <c r="BP1" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="BP1" s="3" t="s">
+      <c r="BQ1" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="BQ1" s="3" t="s">
+      <c r="BR1" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="BR1" s="3" t="s">
+      <c r="BS1" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="BS1" s="3" t="s">
+      <c r="BT1" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="BT1" s="3" t="s">
+      <c r="BU1" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="BU1" s="3" t="s">
+      <c r="BV1" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="BV1" s="3" t="s">
+      <c r="BW1" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="BW1" s="3" t="s">
+      <c r="BX1" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="BX1" s="3" t="s">
+      <c r="BY1" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="BY1" s="3" t="s">
+      <c r="BZ1" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="BZ1" s="3" t="s">
+      <c r="CA1" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="CA1" s="3" t="s">
+      <c r="CB1" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="CB1" s="3" t="s">
+      <c r="CC1" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="CC1" s="3" t="s">
+      <c r="CD1" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="CD1" s="3" t="s">
+      <c r="CE1" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="CE1" s="3" t="s">
+      <c r="CF1" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="CF1" s="3" t="s">
+      <c r="CG1" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="CG1" s="3" t="s">
+      <c r="CH1" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="CH1" s="3" t="s">
+      <c r="CI1" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="CI1" s="3" t="s">
+      <c r="CJ1" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="CJ1" s="3" t="s">
+      <c r="CK1" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="CK1" s="3" t="s">
+      <c r="CL1" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="CL1" s="3" t="s">
+      <c r="CM1" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="CM1" s="3" t="s">
+      <c r="CN1" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="CN1" s="3" t="s">
+      <c r="CO1" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="CO1" s="3" t="s">
+      <c r="CP1" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="CP1" s="3" t="s">
+      <c r="CQ1" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="CQ1" s="3" t="s">
+      <c r="CR1" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="CR1" s="3" t="s">
+      <c r="CS1" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="CS1" s="3" t="s">
+      <c r="CT1" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="CT1" s="3" t="s">
+      <c r="CU1" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="CU1" s="3" t="s">
+      <c r="CV1" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="CV1" s="3" t="s">
+      <c r="CW1" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="CW1" s="3" t="s">
+      <c r="CX1" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="CX1" s="3" t="s">
+      <c r="CY1" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="CY1" s="3" t="s">
+      <c r="CZ1" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="CZ1" s="3" t="s">
+      <c r="DA1" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="DA1" s="3" t="s">
+      <c r="DB1" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="DB1" s="3" t="s">
+      <c r="DC1" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="DC1" s="3" t="s">
+      <c r="DD1" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="DD1" s="3" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:108" x14ac:dyDescent="0.25">
@@ -16242,7 +16238,7 @@
     </row>
     <row r="47" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B47" s="3">
         <v>0.32911331288270901</v>
@@ -16568,7 +16564,7 @@
     </row>
     <row r="48" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B48" s="3">
         <v>0.45997248895694198</v>
@@ -16894,7 +16890,7 @@
     </row>
     <row r="49" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B49" s="3">
         <v>0.614402059337812</v>
@@ -17220,7 +17216,7 @@
     </row>
     <row r="50" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B50" s="3">
         <v>0.40166801846043998</v>
@@ -17546,7 +17542,7 @@
     </row>
     <row r="51" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B51" s="3">
         <v>0.74839241815767299</v>
@@ -17872,7 +17868,7 @@
     </row>
     <row r="52" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B52" s="3">
         <v>0.15716690481010401</v>
@@ -18198,7 +18194,7 @@
     </row>
     <row r="53" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B53" s="3">
         <v>3.0431555359667799</v>
@@ -18524,7 +18520,7 @@
     </row>
     <row r="54" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B54" s="3">
         <v>2.1883363678169001</v>
@@ -18850,7 +18846,7 @@
     </row>
     <row r="55" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B55" s="3">
         <v>0.96359623739205003</v>
@@ -19176,7 +19172,7 @@
     </row>
     <row r="56" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B56" s="3">
         <v>1.66965909179537</v>
@@ -19502,7 +19498,7 @@
     </row>
     <row r="57" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B57" s="3">
         <v>-15.7318676354512</v>
@@ -19828,7 +19824,7 @@
     </row>
     <row r="58" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B58" s="3">
         <v>0.24070453007246401</v>
@@ -20154,7 +20150,7 @@
     </row>
     <row r="59" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B59" s="3">
         <v>1.9554590678089501</v>
@@ -20480,7 +20476,7 @@
     </row>
     <row r="60" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B60" s="3">
         <v>1.6577650756654301</v>
@@ -20806,7 +20802,7 @@
     </row>
     <row r="61" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B61" s="3">
         <v>1.12894494926212</v>
@@ -21132,7 +21128,7 @@
     </row>
     <row r="62" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B62" s="3">
         <v>1.99296722813993</v>
@@ -21458,7 +21454,7 @@
     </row>
     <row r="63" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B63" s="3">
         <v>-0.23446454411062401</v>
@@ -21784,7 +21780,7 @@
     </row>
     <row r="64" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B64" s="3">
         <v>1.2087767744831099</v>
@@ -22110,7 +22106,7 @@
     </row>
     <row r="65" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B65" s="3">
         <v>0.81982745729659701</v>
@@ -22436,7 +22432,7 @@
     </row>
     <row r="66" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B66" s="3">
         <v>0.85579426617710297</v>
@@ -22762,7 +22758,7 @@
     </row>
     <row r="67" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B67" s="3">
         <v>0.85055520989919497</v>
@@ -23088,7 +23084,7 @@
     </row>
     <row r="68" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B68" s="3">
         <v>1.08489702603608</v>
@@ -23414,7 +23410,7 @@
     </row>
     <row r="69" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B69" s="3">
         <v>0.52963387601230505</v>
@@ -23740,7 +23736,7 @@
     </row>
     <row r="70" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B70" s="3">
         <v>0.60433852964892198</v>
@@ -24066,7 +24062,7 @@
     </row>
     <row r="71" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B71" s="3">
         <v>0.67531150898639403</v>
@@ -24392,7 +24388,7 @@
     </row>
     <row r="72" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B72" s="3">
         <v>0.761953243874393</v>
@@ -24718,7 +24714,7 @@
     </row>
     <row r="73" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B73" s="3">
         <v>0.84761871661198696</v>
@@ -25044,7 +25040,7 @@
     </row>
     <row r="74" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B74" s="3">
         <v>3.2313787165111199E-2</v>
@@ -25370,7 +25366,7 @@
     </row>
     <row r="75" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B75" s="3">
         <v>1.3743912216502701</v>
@@ -25696,7 +25692,7 @@
     </row>
     <row r="76" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B76" s="3">
         <v>1.1413033658515599</v>
@@ -26022,7 +26018,7 @@
     </row>
     <row r="77" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B77" s="3">
         <v>-15.573977076464001</v>
@@ -26348,7 +26344,7 @@
     </row>
     <row r="78" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B78" s="3">
         <v>0.98908927873806296</v>
@@ -26674,7 +26670,7 @@
     </row>
     <row r="79" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B79" s="3">
         <v>-15.4540437289527</v>
@@ -27000,7 +26996,7 @@
     </row>
     <row r="80" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B80" s="3">
         <v>2.0279809393841801</v>
@@ -27326,7 +27322,7 @@
     </row>
     <row r="81" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B81" s="3">
         <v>-15.3887942610164</v>
@@ -27652,7 +27648,7 @@
     </row>
     <row r="82" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B82" s="3">
         <v>-15.423251370342999</v>
@@ -27978,7 +27974,7 @@
     </row>
     <row r="83" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B83" s="3">
         <v>2.34711565303735</v>
@@ -28304,7 +28300,7 @@
     </row>
     <row r="84" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B84" s="3">
         <v>1.21360351738299</v>
@@ -28630,7 +28626,7 @@
     </row>
     <row r="85" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B85" s="3">
         <v>-15.973537729956901</v>
@@ -28956,7 +28952,7 @@
     </row>
     <row r="86" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B86" s="3">
         <v>1.30007945773239</v>
@@ -29282,7 +29278,7 @@
     </row>
     <row r="87" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B87" s="3">
         <v>0.73840566099272398</v>
@@ -29608,7 +29604,7 @@
     </row>
     <row r="88" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B88" s="3">
         <v>0.21778564323168101</v>
@@ -29934,7 +29930,7 @@
     </row>
     <row r="89" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B89" s="3">
         <v>0.80106059086288695</v>
@@ -30260,7 +30256,7 @@
     </row>
     <row r="90" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B90" s="3">
         <v>0.935798561797897</v>
@@ -30586,7 +30582,7 @@
     </row>
     <row r="91" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B91" s="3">
         <v>0.71958372166728302</v>
@@ -30912,7 +30908,7 @@
     </row>
     <row r="92" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B92" s="3">
         <v>0.83314270312517502</v>
@@ -31238,7 +31234,7 @@
     </row>
     <row r="93" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B93" s="3">
         <v>0.59198516916880295</v>
@@ -31564,7 +31560,7 @@
     </row>
     <row r="94" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B94" s="3">
         <v>1.3087267214679701</v>
@@ -31890,7 +31886,7 @@
     </row>
     <row r="95" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B95" s="3">
         <v>1.2306438372528901</v>
@@ -32216,7 +32212,7 @@
     </row>
     <row r="96" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B96" s="3">
         <v>-0.37863775445417303</v>
@@ -32542,7 +32538,7 @@
     </row>
     <row r="97" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B97" s="3">
         <v>1.0771617064993999</v>
@@ -32868,7 +32864,7 @@
     </row>
     <row r="98" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B98" s="3">
         <v>0.83808859567167704</v>
@@ -33194,7 +33190,7 @@
     </row>
     <row r="99" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B99" s="3">
         <v>0.289305021165008</v>
@@ -33520,7 +33516,7 @@
     </row>
     <row r="100" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B100" s="3">
         <v>0.72322716375276397</v>
@@ -33846,7 +33842,7 @@
     </row>
     <row r="101" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B101" s="3">
         <v>0.53196355282499797</v>
@@ -34172,7 +34168,7 @@
     </row>
     <row r="102" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B102" s="3">
         <v>0.62844340538296295</v>
@@ -34498,7 +34494,7 @@
     </row>
     <row r="103" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B103" s="3">
         <v>-15.6126122275612</v>
@@ -34824,7 +34820,7 @@
     </row>
     <row r="104" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B104" s="3">
         <v>-15.643508532469101</v>
@@ -35150,7 +35146,7 @@
     </row>
     <row r="105" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B105" s="3">
         <v>-15.412131421771701</v>
@@ -35476,7 +35472,7 @@
     </row>
     <row r="106" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B106" s="3">
         <v>-15.4735629004484</v>
@@ -35802,7 +35798,7 @@
     </row>
     <row r="107" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B107" s="3">
         <v>-16.204091179354201</v>
@@ -36133,12 +36129,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DB56E65-A028-41C8-8E37-C957AEE6B4E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{055024F4-33A1-4F47-A2A4-B66D5D612658}">
   <dimension ref="A1:I8"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.7109375" style="3" customWidth="1"/>
-    <col min="2" max="16384" width="11.42578125" style="3"/>
+    <col min="1" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -36167,7 +36162,7 @@
         <v>9</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -36346,7 +36341,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B8" s="3">
         <v>0.54258700000000004</v>
@@ -36380,12 +36375,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{713A1631-5A78-441A-A83A-D84683700833}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{380EAEAD-4CDB-4A7C-AFE3-0A8A39C9D904}">
   <dimension ref="A1:CP93"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33" style="3" customWidth="1"/>
-    <col min="2" max="16384" width="11.42578125" style="3"/>
+    <col min="1" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:94" x14ac:dyDescent="0.25">
@@ -36426,250 +36420,250 @@
         <v>6</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>29</v>
       </c>
       <c r="O1" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="P1" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AI1" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AK1" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AL1" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AM1" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AN1" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AO1" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AP1" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AR1" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="AS1" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="AT1" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="AT1" s="3" t="s">
+      <c r="AU1" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="AU1" s="3" t="s">
+      <c r="AV1" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="AV1" s="3" t="s">
+      <c r="AW1" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="AW1" s="3" t="s">
+      <c r="AX1" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="AX1" s="3" t="s">
+      <c r="AY1" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="AY1" s="3" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="AZ1" s="3" t="s">
+      <c r="BA1" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="BA1" s="3" t="s">
+      <c r="BB1" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="BB1" s="3" t="s">
+      <c r="BC1" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="BC1" s="3" t="s">
+      <c r="BD1" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="BD1" s="3" t="s">
+      <c r="BE1" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="BE1" s="3" t="s">
+      <c r="BF1" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="BF1" s="3" t="s">
+      <c r="BG1" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="BG1" s="3" t="s">
+      <c r="BH1" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="BH1" s="3" t="s">
+      <c r="BI1" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="BI1" s="3" t="s">
+      <c r="BJ1" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="BJ1" s="3" t="s">
+      <c r="BK1" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="BK1" s="3" t="s">
+      <c r="BL1" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="BL1" s="3" t="s">
+      <c r="BM1" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="BM1" s="3" t="s">
+      <c r="BN1" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="BN1" s="3" t="s">
+      <c r="BO1" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="BO1" s="3" t="s">
+      <c r="BP1" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="BP1" s="3" t="s">
+      <c r="BQ1" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="BQ1" s="3" t="s">
+      <c r="BR1" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="BR1" s="3" t="s">
+      <c r="BS1" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="BS1" s="3" t="s">
+      <c r="BT1" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="BT1" s="3" t="s">
+      <c r="BU1" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="BU1" s="3" t="s">
+      <c r="BV1" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="BV1" s="3" t="s">
+      <c r="BW1" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="BW1" s="3" t="s">
+      <c r="BX1" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="BX1" s="3" t="s">
+      <c r="BY1" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="BY1" s="3" t="s">
+      <c r="BZ1" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="BZ1" s="3" t="s">
+      <c r="CA1" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="CA1" s="3" t="s">
+      <c r="CB1" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="CB1" s="3" t="s">
+      <c r="CC1" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="CC1" s="3" t="s">
+      <c r="CD1" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="CD1" s="3" t="s">
+      <c r="CE1" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="CE1" s="3" t="s">
+      <c r="CF1" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="CF1" s="3" t="s">
+      <c r="CG1" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="CG1" s="3" t="s">
+      <c r="CH1" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="CH1" s="3" t="s">
+      <c r="CI1" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="CI1" s="3" t="s">
+      <c r="CJ1" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="CJ1" s="3" t="s">
+      <c r="CK1" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="CK1" s="3" t="s">
+      <c r="CL1" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="CL1" s="3" t="s">
+      <c r="CM1" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="CM1" s="3" t="s">
+      <c r="CN1" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="CN1" s="3" t="s">
+      <c r="CO1" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="CO1" s="3" t="s">
+      <c r="CP1" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="CP1" s="3" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:94" x14ac:dyDescent="0.25">
@@ -39514,7 +39508,7 @@
     </row>
     <row r="12" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B12" s="3">
         <v>3.56416819514497</v>
@@ -40082,7 +40076,7 @@
     </row>
     <row r="14" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B14" s="3">
         <v>-0.24851257653206699</v>
@@ -40366,7 +40360,7 @@
     </row>
     <row r="15" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B15" s="3">
         <v>-0.15501650152683599</v>
@@ -40650,7 +40644,7 @@
     </row>
     <row r="16" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B16" s="3">
         <v>-3.3557569295545202E-2</v>
@@ -40934,7 +40928,7 @@
     </row>
     <row r="17" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B17" s="3">
         <v>3.1086688130075299E-2</v>
@@ -41218,7 +41212,7 @@
     </row>
     <row r="18" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B18" s="3">
         <v>-3.54804655910477E-2</v>
@@ -41502,7 +41496,7 @@
     </row>
     <row r="19" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B19" s="3">
         <v>0.104490784522007</v>
@@ -41786,7 +41780,7 @@
     </row>
     <row r="20" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B20" s="3">
         <v>-1.6740910505204602E-2</v>
@@ -42070,7 +42064,7 @@
     </row>
     <row r="21" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B21" s="3">
         <v>2.68411381805354E-2</v>
@@ -42354,7 +42348,7 @@
     </row>
     <row r="22" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B22" s="3">
         <v>3.9140421628870901E-2</v>
@@ -42638,7 +42632,7 @@
     </row>
     <row r="23" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B23" s="3">
         <v>3.6009585048853501E-2</v>
@@ -42922,7 +42916,7 @@
     </row>
     <row r="24" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B24" s="3">
         <v>-4.1153464270304002E-2</v>
@@ -43206,7 +43200,7 @@
     </row>
     <row r="25" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B25" s="3">
         <v>5.2805973843852799E-2</v>
@@ -43490,7 +43484,7 @@
     </row>
     <row r="26" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B26" s="3">
         <v>-0.24664046507380399</v>
@@ -43774,7 +43768,7 @@
     </row>
     <row r="27" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B27" s="3">
         <v>-8.16818341777997E-2</v>
@@ -44058,7 +44052,7 @@
     </row>
     <row r="28" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B28" s="3">
         <v>-2.7376636525575999E-2</v>
@@ -44342,7 +44336,7 @@
     </row>
     <row r="29" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B29" s="3">
         <v>3.6859599206483303E-2</v>
@@ -44626,7 +44620,7 @@
     </row>
     <row r="30" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B30" s="3">
         <v>-0.266921014426866</v>
@@ -44910,7 +44904,7 @@
     </row>
     <row r="31" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B31" s="3">
         <v>-9.4004542275197001E-2</v>
@@ -45194,7 +45188,7 @@
     </row>
     <row r="32" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B32" s="3">
         <v>-1.28983256881103E-2</v>
@@ -45478,7 +45472,7 @@
     </row>
     <row r="33" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B33" s="3">
         <v>1.39806666058512E-2</v>
@@ -45762,7 +45756,7 @@
     </row>
     <row r="34" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B34" s="3">
         <v>-0.241530621994761</v>
@@ -46046,7 +46040,7 @@
     </row>
     <row r="35" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B35" s="3">
         <v>-0.147615297043832</v>
@@ -46330,7 +46324,7 @@
     </row>
     <row r="36" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B36" s="3">
         <v>-3.0341143642342298E-2</v>
@@ -46614,7 +46608,7 @@
     </row>
     <row r="37" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B37" s="3">
         <v>3.07085183522318E-2</v>
@@ -46898,7 +46892,7 @@
     </row>
     <row r="38" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B38" s="3">
         <v>-0.235620706291398</v>
@@ -47182,7 +47176,7 @@
     </row>
     <row r="39" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B39" s="3">
         <v>-0.14108344291893599</v>
@@ -47466,7 +47460,7 @@
     </row>
     <row r="40" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B40" s="3">
         <v>-3.1069493186529198E-2</v>
@@ -47750,7 +47744,7 @@
     </row>
     <row r="41" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B41" s="3">
         <v>4.4659950017029999E-2</v>
@@ -48034,7 +48028,7 @@
     </row>
     <row r="42" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B42" s="3">
         <v>-0.25460426377618001</v>
@@ -48318,7 +48312,7 @@
     </row>
     <row r="43" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B43" s="3">
         <v>-8.3970811896098896E-2</v>
@@ -48602,7 +48596,7 @@
     </row>
     <row r="44" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B44" s="3">
         <v>-2.3993425911259199E-2</v>
@@ -48886,7 +48880,7 @@
     </row>
     <row r="45" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B45" s="3">
         <v>4.06632647854046E-2</v>
@@ -49170,7 +49164,7 @@
     </row>
     <row r="46" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B46" s="3">
         <v>-0.245869225848625</v>
@@ -49454,7 +49448,7 @@
     </row>
     <row r="47" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B47" s="3">
         <v>-8.1010365828426203E-2</v>
@@ -49738,7 +49732,7 @@
     </row>
     <row r="48" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B48" s="3">
         <v>-2.7620053894158701E-2</v>
@@ -50022,7 +50016,7 @@
     </row>
     <row r="49" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B49" s="3">
         <v>3.3648476392357199E-2</v>
@@ -50306,7 +50300,7 @@
     </row>
     <row r="50" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B50" s="3">
         <v>-0.27974082537358902</v>
@@ -50590,7 +50584,7 @@
     </row>
     <row r="51" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B51" s="3">
         <v>-7.9125985712695704E-2</v>
@@ -50874,7 +50868,7 @@
     </row>
     <row r="52" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B52" s="3">
         <v>1.16923849670512E-2</v>
@@ -51158,7 +51152,7 @@
     </row>
     <row r="53" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B53" s="3">
         <v>-2.37213448911E-3</v>
@@ -51442,7 +51436,7 @@
     </row>
     <row r="54" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B54" s="3">
         <v>-0.23817014524878</v>
@@ -51726,7 +51720,7 @@
     </row>
     <row r="55" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B55" s="3">
         <v>-0.143863760962225</v>
@@ -52010,7 +52004,7 @@
     </row>
     <row r="56" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B56" s="3">
         <v>-1.9193132946093001E-2</v>
@@ -52294,7 +52288,7 @@
     </row>
     <row r="57" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B57" s="3">
         <v>2.9104616195848799E-2</v>
@@ -52578,7 +52572,7 @@
     </row>
     <row r="58" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B58" s="3">
         <v>-0.26222573600960403</v>
@@ -52862,7 +52856,7 @@
     </row>
     <row r="59" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B59" s="3">
         <v>-8.7324478884078599E-2</v>
@@ -53146,7 +53140,7 @@
     </row>
     <row r="60" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B60" s="3">
         <v>-8.0538958530602008E-3</v>
@@ -53430,7 +53424,7 @@
     </row>
     <row r="61" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B61" s="3">
         <v>3.4468551042118899E-2</v>
@@ -53714,7 +53708,7 @@
     </row>
     <row r="62" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B62" s="3">
         <v>-5.8149600710401704E-3</v>
@@ -53998,7 +53992,7 @@
     </row>
     <row r="63" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B63" s="3">
         <v>3.2403465051017197E-2</v>
@@ -54282,7 +54276,7 @@
     </row>
     <row r="64" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B64" s="3">
         <v>-1.95968544991071E-2</v>
@@ -54566,7 +54560,7 @@
     </row>
     <row r="65" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B65" s="3">
         <v>4.3088570435007703E-2</v>
@@ -54850,7 +54844,7 @@
     </row>
     <row r="66" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B66" s="3">
         <v>1.3782593123408699E-2</v>
@@ -55134,7 +55128,7 @@
     </row>
     <row r="67" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B67" s="3">
         <v>4.2217819515446E-3</v>
@@ -55418,7 +55412,7 @@
     </row>
     <row r="68" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B68" s="3">
         <v>-0.24101550673286201</v>
@@ -55702,7 +55696,7 @@
     </row>
     <row r="69" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B69" s="3">
         <v>-0.14407589532802201</v>
@@ -55986,7 +55980,7 @@
     </row>
     <row r="70" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B70" s="3">
         <v>-1.37294896327869E-2</v>
@@ -56270,7 +56264,7 @@
     </row>
     <row r="71" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B71" s="3">
         <v>3.73680753415431E-2</v>
@@ -56554,7 +56548,7 @@
     </row>
     <row r="72" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B72" s="3">
         <v>-0.26682852387940398</v>
@@ -56838,7 +56832,7 @@
     </row>
     <row r="73" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B73" s="3">
         <v>-8.8436226125812104E-2</v>
@@ -57122,7 +57116,7 @@
     </row>
     <row r="74" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B74" s="3">
         <v>6.8005805226868698E-4</v>
@@ -57406,7 +57400,7 @@
     </row>
     <row r="75" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B75" s="3">
         <v>3.3848348666552203E-2</v>
@@ -57690,7 +57684,7 @@
     </row>
     <row r="76" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B76" s="3">
         <v>-8.8371173287494901E-4</v>
@@ -57974,7 +57968,7 @@
     </row>
     <row r="77" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B77" s="3">
         <v>4.04919256273501E-2</v>
@@ -58258,7 +58252,7 @@
     </row>
     <row r="78" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B78" s="3">
         <v>-1.24503691831E-2</v>
@@ -58542,7 +58536,7 @@
     </row>
     <row r="79" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B79" s="3">
         <v>4.4795385372791097E-2</v>
@@ -58826,7 +58820,7 @@
     </row>
     <row r="80" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B80" s="3">
         <v>2.0286667152899299E-3</v>
@@ -59110,7 +59104,7 @@
     </row>
     <row r="81" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B81" s="3">
         <v>3.6560329427985602E-3</v>
@@ -59394,7 +59388,7 @@
     </row>
     <row r="82" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B82" s="3">
         <v>7.0307314940585106E-2</v>
@@ -59678,7 +59672,7 @@
     </row>
     <row r="83" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B83" s="3">
         <v>-1.33212316156076</v>
@@ -59962,7 +59956,7 @@
     </row>
     <row r="84" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B84" s="3">
         <v>-8.9552728282690404E-3</v>
@@ -60246,7 +60240,7 @@
     </row>
     <row r="85" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B85" s="3">
         <v>1.9935071355956201E-2</v>
@@ -60530,7 +60524,7 @@
     </row>
     <row r="86" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B86" s="3">
         <v>-0.28281924164622801</v>
@@ -60814,7 +60808,7 @@
     </row>
     <row r="87" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B87" s="3">
         <v>-9.6856980827706898E-2</v>
@@ -61098,7 +61092,7 @@
     </row>
     <row r="88" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B88" s="3">
         <v>-1.0029218489704599E-2</v>
@@ -61382,7 +61376,7 @@
     </row>
     <row r="89" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B89" s="3">
         <v>3.4912659661339801E-2</v>
@@ -61666,7 +61660,7 @@
     </row>
     <row r="90" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B90" s="3">
         <v>-6.8797262004654299E-3</v>
@@ -61950,7 +61944,7 @@
     </row>
     <row r="91" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B91" s="3">
         <v>3.8238204748118503E-2</v>
@@ -62234,7 +62228,7 @@
     </row>
     <row r="92" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B92" s="3">
         <v>-1.19181161641839E-2</v>
@@ -62518,7 +62512,7 @@
     </row>
     <row r="93" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B93" s="3">
         <v>3.7717663714500901E-2</v>
@@ -62807,12 +62801,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A52A53A-8337-4C79-8847-E5AFC5268D50}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DD78F2F-CA77-4446-BA41-A05647792E31}">
   <dimension ref="A1:I8"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.42578125" style="3" customWidth="1"/>
-    <col min="2" max="16384" width="11.42578125" style="3"/>
+    <col min="1" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -63054,12 +63047,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9164393-5E7D-4422-9A61-B7FFE1623344}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D14D180-CF6C-4231-A992-F9B2E75CDC6D}">
   <dimension ref="A1:I8"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30" style="3" customWidth="1"/>
-    <col min="2" max="16384" width="11.42578125" style="3"/>
+    <col min="1" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -63088,7 +63080,7 @@
         <v>9</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -63267,7 +63259,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B8" s="3">
         <v>0.99929437674511601</v>
@@ -63301,15 +63293,14 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46DFF46C-488E-4562-9683-A336EF32C45A}">
-  <dimension ref="A1:T19"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4EAA4B1-7298-4DD6-AF4D-494334F187ED}">
+  <dimension ref="A1:AE30"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46.140625" style="3" customWidth="1"/>
-    <col min="2" max="16384" width="11.42578125" style="3"/>
+    <col min="1" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -63320,10 +63311,10 @@
         <v>28</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>2</v>
+        <v>210</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>3</v>
+        <v>211</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>4</v>
@@ -63335,1156 +63326,2828 @@
         <v>6</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>29</v>
+        <v>212</v>
       </c>
       <c r="J1" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="U1" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>211</v>
+      <c r="V1" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="Z1" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="AA1" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="AB1" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="AC1" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="AD1" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="AE1" s="3" t="s">
+        <v>231</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B2" s="3">
-        <v>-4.0410153827671103</v>
+        <v>-1.0073555552515301</v>
       </c>
       <c r="C2" s="3">
-        <v>0.21581828600289299</v>
+        <v>2.9856881717883501E-2</v>
       </c>
       <c r="D2" s="3">
-        <v>-3.6000664365707898E-3</v>
+        <v>-5.8994148035503802E-5</v>
       </c>
       <c r="E2" s="3">
-        <v>1.7992908634939001E-5</v>
+        <v>5.7386565427299501E-8</v>
       </c>
       <c r="F2" s="3">
-        <v>-9.4737634710239304E-4</v>
+        <v>-2.0510879438839099E-4</v>
       </c>
       <c r="G2" s="3">
-        <v>4.6046051895759601E-7</v>
+        <v>2.32207103902407E-7</v>
       </c>
       <c r="H2" s="3">
-        <v>1.03941423048226E-5</v>
+        <v>4.2627333639507602E-7</v>
       </c>
       <c r="I2" s="3">
-        <v>-6.9841930969792099E-4</v>
+        <v>-1.9450413424968002E-5</v>
       </c>
       <c r="J2" s="3">
-        <v>-1.9951459761529201E-5</v>
+        <v>-5.7012562247928403E-9</v>
       </c>
       <c r="K2" s="3">
-        <v>-1.56280416303169E-5</v>
+        <v>5.4792089090609801E-5</v>
       </c>
       <c r="L2" s="3">
-        <v>-1.6085496742759701E-5</v>
+        <v>-2.2681141620312401E-7</v>
       </c>
       <c r="M2" s="3">
-        <v>-1.6810972813864102E-5</v>
+        <v>1.3345356051517001E-7</v>
       </c>
       <c r="N2" s="3">
-        <v>2.8045648463842E-5</v>
+        <v>-1.45976076676486E-3</v>
       </c>
       <c r="O2" s="3">
-        <v>-1.69121915246763E-4</v>
+        <v>-4.4239560392802401E-4</v>
       </c>
       <c r="P2" s="3">
-        <v>-3.7489818026374599E-6</v>
+        <v>-1.38273208057125E-5</v>
       </c>
       <c r="Q2" s="3">
-        <v>5.7103493780468003E-5</v>
+        <v>-5.7002713262109203E-4</v>
       </c>
       <c r="R2" s="3">
-        <v>2.9753483553440498E-6</v>
+        <v>-3.2806140748527603E-5</v>
       </c>
       <c r="S2" s="3">
-        <v>-4.3012352796894299E-5</v>
+        <v>-3.2657794885813701E-4</v>
       </c>
       <c r="T2" s="3">
-        <v>3.7008445852146098E-5</v>
+        <v>-4.4083097124947101E-5</v>
+      </c>
+      <c r="U2" s="3">
+        <v>-3.2367230722205498E-4</v>
+      </c>
+      <c r="V2" s="3">
+        <v>-4.3004050441810102E-5</v>
+      </c>
+      <c r="W2" s="3">
+        <v>-1.3131505351304499E-2</v>
+      </c>
+      <c r="X2" s="3">
+        <v>-4.98718667466059E-6</v>
+      </c>
+      <c r="Y2" s="3">
+        <v>-7.4770951320942802E-4</v>
+      </c>
+      <c r="Z2" s="3">
+        <v>-3.37532068332918E-5</v>
+      </c>
+      <c r="AA2" s="3">
+        <v>-2.6582967533709399E-2</v>
+      </c>
+      <c r="AB2" s="3">
+        <v>-4.7165081493678701E-5</v>
+      </c>
+      <c r="AC2" s="3">
+        <v>-2.7998752126199601E-2</v>
+      </c>
+      <c r="AD2" s="3">
+        <v>-4.5599648325824797E-5</v>
+      </c>
+      <c r="AE2" s="3">
+        <v>-2.2330706184271899E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>2</v>
+        <v>210</v>
       </c>
       <c r="B3" s="3">
-        <v>-0.14537907813996001</v>
+        <v>1.23361213363856E-2</v>
       </c>
       <c r="C3" s="3">
-        <v>-3.6000664365707898E-3</v>
+        <v>-5.8994148035503802E-5</v>
       </c>
       <c r="D3" s="3">
-        <v>4.37059910039388E-3</v>
+        <v>2.0618273889906101E-3</v>
       </c>
       <c r="E3" s="3">
-        <v>-1.96417855377994E-5</v>
+        <v>-5.6033360392489203E-6</v>
       </c>
       <c r="F3" s="3">
-        <v>1.44751455474659E-3</v>
+        <v>1.6703013930095499E-3</v>
       </c>
       <c r="G3" s="3">
-        <v>-3.0367310729731402E-6</v>
+        <v>-5.0389905385463597E-6</v>
       </c>
       <c r="H3" s="3">
-        <v>-2.20678822207496E-5</v>
+        <v>-1.2730687267039199E-5</v>
       </c>
       <c r="I3" s="3">
-        <v>-2.12410488986844E-4</v>
+        <v>-2.06160105552984E-3</v>
       </c>
       <c r="J3" s="3">
-        <v>6.1214312387262998E-6</v>
+        <v>5.6033032571383701E-6</v>
       </c>
       <c r="K3" s="3">
-        <v>8.6132197989848994E-6</v>
+        <v>-1.66963385651895E-3</v>
       </c>
       <c r="L3" s="3">
-        <v>2.2536356875863299E-5</v>
+        <v>5.0383735027121401E-6</v>
       </c>
       <c r="M3" s="3">
-        <v>1.81868866518548E-5</v>
+        <v>1.2728986499007001E-5</v>
       </c>
       <c r="N3" s="3">
-        <v>-9.3509941745020897E-7</v>
+        <v>7.7905118409062795E-6</v>
       </c>
       <c r="O3" s="3">
-        <v>4.96156039309976E-6</v>
+        <v>-1.3099796384693701E-8</v>
       </c>
       <c r="P3" s="3">
-        <v>3.0444920369570299E-5</v>
+        <v>8.8767747496532897E-8</v>
       </c>
       <c r="Q3" s="3">
-        <v>1.42405086502582E-5</v>
+        <v>-5.5865571930154203E-6</v>
       </c>
       <c r="R3" s="3">
-        <v>-6.9696922151638896E-6</v>
+        <v>1.2827442790502899E-7</v>
       </c>
       <c r="S3" s="3">
-        <v>1.3029580279298299E-5</v>
+        <v>-5.7799354375200503E-6</v>
       </c>
       <c r="T3" s="3">
-        <v>1.42629557258721E-5</v>
+        <v>-1.1773492092786599E-6</v>
+      </c>
+      <c r="U3" s="3">
+        <v>-3.9686892538799602E-6</v>
+      </c>
+      <c r="V3" s="3">
+        <v>-3.37284148752009E-6</v>
+      </c>
+      <c r="W3" s="3">
+        <v>2.2205913617525199E-4</v>
+      </c>
+      <c r="X3" s="3">
+        <v>-3.7473548779964399E-8</v>
+      </c>
+      <c r="Y3" s="3">
+        <v>1.41243484717148E-6</v>
+      </c>
+      <c r="Z3" s="3">
+        <v>4.6697030234485799E-8</v>
+      </c>
+      <c r="AA3" s="3">
+        <v>5.4139270552216797E-5</v>
+      </c>
+      <c r="AB3" s="3">
+        <v>8.9180820089915702E-8</v>
+      </c>
+      <c r="AC3" s="3">
+        <v>5.8856609363805299E-5</v>
+      </c>
+      <c r="AD3" s="3">
+        <v>6.0364329442624597E-8</v>
+      </c>
+      <c r="AE3" s="3">
+        <v>4.3812634503501296E-6</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>3</v>
+        <v>211</v>
       </c>
       <c r="B4" s="3">
-        <v>4.2860594032363897E-4</v>
+        <v>-9.85002475685855E-5</v>
       </c>
       <c r="C4" s="3">
-        <v>1.7992908634939001E-5</v>
+        <v>5.7386565427299501E-8</v>
       </c>
       <c r="D4" s="3">
-        <v>-1.96417855377994E-5</v>
+        <v>-5.6033360392489203E-6</v>
       </c>
       <c r="E4" s="3">
-        <v>1.0460874449851E-7</v>
+        <v>2.4048571711024799E-8</v>
       </c>
       <c r="F4" s="3">
-        <v>-6.2739541160480204E-6</v>
+        <v>-3.93022265644805E-6</v>
       </c>
       <c r="G4" s="3">
-        <v>1.26134153255488E-8</v>
+        <v>1.0919523456037499E-8</v>
       </c>
       <c r="H4" s="3">
-        <v>9.3244115645968599E-8</v>
+        <v>2.89037012688621E-8</v>
       </c>
       <c r="I4" s="3">
-        <v>-1.67647453075414E-6</v>
+        <v>5.6158890554165002E-6</v>
       </c>
       <c r="J4" s="3">
-        <v>8.4998118401502599E-8</v>
+        <v>-2.4037970488982201E-8</v>
       </c>
       <c r="K4" s="3">
-        <v>3.23626215977667E-8</v>
+        <v>3.8888376684996798E-6</v>
       </c>
       <c r="L4" s="3">
-        <v>3.4279766294984102E-9</v>
+        <v>-1.08547654697684E-8</v>
       </c>
       <c r="M4" s="3">
-        <v>5.00464040914354E-8</v>
+        <v>-2.9015396737953202E-8</v>
       </c>
       <c r="N4" s="3">
-        <v>1.26981749798527E-7</v>
+        <v>-8.42224261010507E-7</v>
       </c>
       <c r="O4" s="3">
-        <v>6.7466998015694194E-8</v>
+        <v>-1.5768931082986501E-9</v>
       </c>
       <c r="P4" s="3">
-        <v>2.9257034913650999E-8</v>
+        <v>1.2794883453042E-8</v>
       </c>
       <c r="Q4" s="3">
-        <v>7.8520358290831098E-8</v>
+        <v>1.7855419920635701E-8</v>
       </c>
       <c r="R4" s="3">
-        <v>7.8818250748758297E-8</v>
+        <v>1.99766442914547E-8</v>
       </c>
       <c r="S4" s="3">
-        <v>1.5682050871755901E-8</v>
+        <v>2.32256623767341E-8</v>
       </c>
       <c r="T4" s="3">
-        <v>-2.5143497513425999E-8</v>
+        <v>1.47597078118045E-8</v>
+      </c>
+      <c r="U4" s="3">
+        <v>1.07615780554663E-8</v>
+      </c>
+      <c r="V4" s="3">
+        <v>6.8335268027798396E-9</v>
+      </c>
+      <c r="W4" s="3">
+        <v>-1.4392591456924201E-6</v>
+      </c>
+      <c r="X4" s="3">
+        <v>-2.3475894752501299E-9</v>
+      </c>
+      <c r="Y4" s="3">
+        <v>-4.6272621780540504E-9</v>
+      </c>
+      <c r="Z4" s="3">
+        <v>-4.0507049891447397E-9</v>
+      </c>
+      <c r="AA4" s="3">
+        <v>-3.2418727783093902E-7</v>
+      </c>
+      <c r="AB4" s="3">
+        <v>-5.7142343693600102E-9</v>
+      </c>
+      <c r="AC4" s="3">
+        <v>-5.5960630678884497E-7</v>
+      </c>
+      <c r="AD4" s="3">
+        <v>-8.0603069833631301E-10</v>
+      </c>
+      <c r="AE4" s="3">
+        <v>1.55477749858987E-10</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>-4.04007740193267E-2</v>
+        <v>8.5664508032301606E-2</v>
       </c>
       <c r="C5" s="3">
-        <v>-9.4737634710239304E-4</v>
+        <v>-2.0510879438839099E-4</v>
       </c>
       <c r="D5" s="3">
-        <v>1.44751455474659E-3</v>
+        <v>1.6703013930095499E-3</v>
       </c>
       <c r="E5" s="3">
-        <v>-6.2739541160480204E-6</v>
+        <v>-3.93022265644805E-6</v>
       </c>
       <c r="F5" s="3">
-        <v>1.1618200264724499E-3</v>
+        <v>2.1916298571871E-3</v>
       </c>
       <c r="G5" s="3">
-        <v>-2.8739050191418401E-6</v>
+        <v>-6.85746585669935E-6</v>
       </c>
       <c r="H5" s="3">
-        <v>-7.5835894890573899E-6</v>
+        <v>-1.07550805011178E-5</v>
       </c>
       <c r="I5" s="3">
-        <v>1.08148072343284E-3</v>
+        <v>-1.6899105423629601E-3</v>
       </c>
       <c r="J5" s="3">
-        <v>-1.31449874069332E-4</v>
+        <v>3.9132371300900496E-6</v>
       </c>
       <c r="K5" s="3">
-        <v>-1.4110878557804701E-4</v>
+        <v>-2.1239481131728301E-3</v>
       </c>
       <c r="L5" s="3">
-        <v>-1.16254410988808E-4</v>
+        <v>6.7523665847881301E-6</v>
       </c>
       <c r="M5" s="3">
-        <v>-1.1205120093657801E-4</v>
+        <v>1.0930183137874E-5</v>
       </c>
       <c r="N5" s="3">
-        <v>-1.2246688883600201E-4</v>
+        <v>1.3648730633539401E-3</v>
       </c>
       <c r="O5" s="3">
-        <v>-1.16349003759329E-4</v>
+        <v>2.0305308604558202E-6</v>
       </c>
       <c r="P5" s="3">
-        <v>-1.12737357219583E-4</v>
+        <v>-2.3901403872406398E-6</v>
       </c>
       <c r="Q5" s="3">
-        <v>-1.13525292221057E-4</v>
+        <v>-7.7677387885546099E-6</v>
       </c>
       <c r="R5" s="3">
-        <v>-1.28598471605231E-4</v>
+        <v>1.51652690158799E-6</v>
       </c>
       <c r="S5" s="3">
-        <v>-1.15812272087677E-4</v>
+        <v>-2.7993631971185E-6</v>
       </c>
       <c r="T5" s="3">
-        <v>-1.3430966264520999E-4</v>
+        <v>5.7273347152628699E-6</v>
+      </c>
+      <c r="U5" s="3">
+        <v>4.33079258177218E-6</v>
+      </c>
+      <c r="V5" s="3">
+        <v>1.2500867592743E-6</v>
+      </c>
+      <c r="W5" s="3">
+        <v>2.0962679688493001E-4</v>
+      </c>
+      <c r="X5" s="3">
+        <v>3.65862187673918E-6</v>
+      </c>
+      <c r="Y5" s="3">
+        <v>1.0080933112939599E-5</v>
+      </c>
+      <c r="Z5" s="3">
+        <v>6.5591850107535598E-6</v>
+      </c>
+      <c r="AA5" s="3">
+        <v>6.2344193356711302E-4</v>
+      </c>
+      <c r="AB5" s="3">
+        <v>9.3103839991541404E-6</v>
+      </c>
+      <c r="AC5" s="3">
+        <v>1.0101186114218801E-3</v>
+      </c>
+      <c r="AD5" s="3">
+        <v>1.38971764114735E-6</v>
+      </c>
+      <c r="AE5" s="3">
+        <v>8.1497248508666505E-6</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>1.4390902176363699E-4</v>
+        <v>-7.7383786237344803E-5</v>
       </c>
       <c r="C6" s="3">
-        <v>4.6046051895759601E-7</v>
+        <v>2.32207103902407E-7</v>
       </c>
       <c r="D6" s="3">
-        <v>-3.0367310729731402E-6</v>
+        <v>-5.0389905385463597E-6</v>
       </c>
       <c r="E6" s="3">
-        <v>1.26134153255488E-8</v>
+        <v>1.0919523456037499E-8</v>
       </c>
       <c r="F6" s="3">
-        <v>-2.8739050191418401E-6</v>
+        <v>-6.85746585669935E-6</v>
       </c>
       <c r="G6" s="3">
-        <v>8.6486014744328504E-9</v>
+        <v>2.1950280876478901E-8</v>
       </c>
       <c r="H6" s="3">
-        <v>1.7276047392776699E-8</v>
+        <v>3.35153263200716E-8</v>
       </c>
       <c r="I6" s="3">
-        <v>-2.3635878554329899E-6</v>
+        <v>5.0754976343013002E-6</v>
       </c>
       <c r="J6" s="3">
-        <v>1.8569949547692401E-8</v>
+        <v>-1.08884644638723E-8</v>
       </c>
       <c r="K6" s="3">
-        <v>4.9362830960052602E-8</v>
+        <v>6.73467369315291E-6</v>
       </c>
       <c r="L6" s="3">
-        <v>-2.97719140735268E-8</v>
+        <v>-2.1758561176163999E-8</v>
       </c>
       <c r="M6" s="3">
-        <v>-4.4378821342023198E-8</v>
+        <v>-3.3840560782707297E-8</v>
       </c>
       <c r="N6" s="3">
-        <v>-1.84627955760693E-8</v>
+        <v>-2.4887305256268201E-6</v>
       </c>
       <c r="O6" s="3">
-        <v>-1.95762401573888E-8</v>
+        <v>-3.2854750580198301E-9</v>
       </c>
       <c r="P6" s="3">
-        <v>-3.6634297609672803E-8</v>
+        <v>1.6150131807205499E-8</v>
       </c>
       <c r="Q6" s="3">
-        <v>-4.5318350624731501E-8</v>
+        <v>3.7241227150176697E-8</v>
       </c>
       <c r="R6" s="3">
-        <v>-6.6291409138536298E-10</v>
+        <v>1.02422739239568E-8</v>
       </c>
       <c r="S6" s="3">
-        <v>-2.649256276039E-8</v>
+        <v>2.7873815411059302E-8</v>
       </c>
       <c r="T6" s="3">
-        <v>2.5363953227354399E-8</v>
+        <v>2.7910252330068198E-9</v>
+      </c>
+      <c r="U6" s="3">
+        <v>1.37649092255024E-8</v>
+      </c>
+      <c r="V6" s="3">
+        <v>8.9633571572751406E-9</v>
+      </c>
+      <c r="W6" s="3">
+        <v>6.2164446363434603E-8</v>
+      </c>
+      <c r="X6" s="3">
+        <v>-6.7816117227708904E-9</v>
+      </c>
+      <c r="Y6" s="3">
+        <v>-1.5014541176193999E-8</v>
+      </c>
+      <c r="Z6" s="3">
+        <v>-1.19142248251213E-8</v>
+      </c>
+      <c r="AA6" s="3">
+        <v>-1.01277183497874E-6</v>
+      </c>
+      <c r="AB6" s="3">
+        <v>-1.6868568583899298E-8</v>
+      </c>
+      <c r="AC6" s="3">
+        <v>-1.7119884677995299E-6</v>
+      </c>
+      <c r="AD6" s="3">
+        <v>-2.38728256149929E-9</v>
+      </c>
+      <c r="AE6" s="3">
+        <v>-4.2281946664544297E-9</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>1.24602766933448E-3</v>
+        <v>5.5861475364458103E-5</v>
       </c>
       <c r="C7" s="3">
-        <v>1.03941423048226E-5</v>
+        <v>4.2627333639507602E-7</v>
       </c>
       <c r="D7" s="3">
-        <v>-2.20678822207496E-5</v>
+        <v>-1.2730687267039199E-5</v>
       </c>
       <c r="E7" s="3">
-        <v>9.3244115645968599E-8</v>
+        <v>2.89037012688621E-8</v>
       </c>
       <c r="F7" s="3">
-        <v>-7.5835894890573899E-6</v>
+        <v>-1.07550805011178E-5</v>
       </c>
       <c r="G7" s="3">
-        <v>1.7276047392776699E-8</v>
+        <v>3.35153263200716E-8</v>
       </c>
       <c r="H7" s="3">
-        <v>1.2018761467241101E-7</v>
+        <v>8.4342195222668002E-8</v>
       </c>
       <c r="I7" s="3">
-        <v>2.4896603746977202E-6</v>
+        <v>1.2720708958473899E-5</v>
       </c>
       <c r="J7" s="3">
-        <v>-4.6649077666843097E-8</v>
+        <v>-2.8910371809689999E-8</v>
       </c>
       <c r="K7" s="3">
-        <v>-5.4253202543022897E-8</v>
+        <v>1.0776633131646701E-5</v>
       </c>
       <c r="L7" s="3">
-        <v>-1.40962918782938E-7</v>
+        <v>-3.3552400714094101E-8</v>
       </c>
       <c r="M7" s="3">
-        <v>-1.25313845761621E-7</v>
+        <v>-8.4255885474116597E-8</v>
       </c>
       <c r="N7" s="3">
-        <v>-3.87969118862372E-8</v>
+        <v>4.85171799704477E-7</v>
       </c>
       <c r="O7" s="3">
-        <v>7.1569427468724803E-8</v>
+        <v>1.4718208970971601E-9</v>
       </c>
       <c r="P7" s="3">
-        <v>-1.98445037526611E-7</v>
+        <v>-1.08912156633368E-8</v>
       </c>
       <c r="Q7" s="3">
-        <v>-1.50424457315999E-7</v>
+        <v>2.11765600072742E-8</v>
       </c>
       <c r="R7" s="3">
-        <v>3.1528826670931298E-8</v>
+        <v>-2.1509396451579401E-8</v>
       </c>
       <c r="S7" s="3">
-        <v>-5.4401984672664301E-8</v>
+        <v>1.7858979455248701E-8</v>
       </c>
       <c r="T7" s="3">
-        <v>-1.12458184845013E-7</v>
+        <v>-1.07598233820826E-8</v>
+      </c>
+      <c r="U7" s="3">
+        <v>1.5763048125408299E-8</v>
+      </c>
+      <c r="V7" s="3">
+        <v>1.0591673151090299E-8</v>
+      </c>
+      <c r="W7" s="3">
+        <v>-2.7545664026340501E-8</v>
+      </c>
+      <c r="X7" s="3">
+        <v>1.8410488850628699E-9</v>
+      </c>
+      <c r="Y7" s="3">
+        <v>-8.0628341323405592E-9</v>
+      </c>
+      <c r="Z7" s="3">
+        <v>2.2777434251636898E-9</v>
+      </c>
+      <c r="AA7" s="3">
+        <v>-2.1505393777460999E-7</v>
+      </c>
+      <c r="AB7" s="3">
+        <v>3.0206602250118798E-9</v>
+      </c>
+      <c r="AC7" s="3">
+        <v>-9.9609670178794306E-8</v>
+      </c>
+      <c r="AD7" s="3">
+        <v>6.1800208495018004E-11</v>
+      </c>
+      <c r="AE7" s="3">
+        <v>-3.4521369531308798E-8</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B8" s="3">
+        <v>1.5674779902935899E-2</v>
+      </c>
+      <c r="C8" s="3">
+        <v>-1.9450413424968002E-5</v>
+      </c>
+      <c r="D8" s="3">
+        <v>-2.06160105552984E-3</v>
+      </c>
+      <c r="E8" s="3">
+        <v>5.6158890554165002E-6</v>
+      </c>
+      <c r="F8" s="3">
+        <v>-1.6899105423629601E-3</v>
+      </c>
+      <c r="G8" s="3">
+        <v>5.0754976343013002E-6</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1.2720708958473899E-5</v>
+      </c>
+      <c r="I8" s="3">
+        <v>4.0682581136420601E-3</v>
+      </c>
+      <c r="J8" s="3">
+        <v>-9.2610457276485895E-6</v>
+      </c>
+      <c r="K8" s="3">
+        <v>3.3314503288669802E-3</v>
+      </c>
+      <c r="L8" s="3">
+        <v>-1.0102331975707099E-5</v>
+      </c>
+      <c r="M8" s="3">
+        <v>-2.5822408089234501E-5</v>
+      </c>
+      <c r="N8" s="3">
+        <v>-3.60314256785438E-4</v>
+      </c>
+      <c r="O8" s="3">
+        <v>-1.0918987652906199E-7</v>
+      </c>
+      <c r="P8" s="3">
+        <v>-1.0221124129057E-6</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>5.9238585619971002E-6</v>
+      </c>
+      <c r="R8" s="3">
+        <v>-1.70294284882643E-6</v>
+      </c>
+      <c r="S8" s="3">
+        <v>4.8283917176307801E-6</v>
+      </c>
+      <c r="T8" s="3">
+        <v>-1.0869179829134801E-6</v>
+      </c>
+      <c r="U8" s="3">
+        <v>2.1773710138984202E-6</v>
+      </c>
+      <c r="V8" s="3">
+        <v>3.1564170494286799E-6</v>
+      </c>
+      <c r="W8" s="3">
+        <v>-1.6330136371509201E-4</v>
+      </c>
+      <c r="X8" s="3">
+        <v>4.8464491858741802E-6</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>-7.8366137303311205E-6</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>5.3127332084190401E-6</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>-4.5652088834934702E-4</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>3.0300240647553599E-7</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>-4.1624261082025998E-4</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>-6.1937828808712196E-6</v>
+      </c>
+      <c r="AE8" s="3">
+        <v>3.96136649828362E-5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1.9799246364819599E-6</v>
+      </c>
+      <c r="C9" s="3">
+        <v>-5.7012562247928403E-9</v>
+      </c>
+      <c r="D9" s="3">
+        <v>5.6033032571383701E-6</v>
+      </c>
+      <c r="E9" s="3">
+        <v>-2.4037970488982201E-8</v>
+      </c>
+      <c r="F9" s="3">
+        <v>3.9132371300900496E-6</v>
+      </c>
+      <c r="G9" s="3">
+        <v>-1.08884644638723E-8</v>
+      </c>
+      <c r="H9" s="3">
+        <v>-2.8910371809689999E-8</v>
+      </c>
+      <c r="I9" s="3">
+        <v>-9.2610457276485895E-6</v>
+      </c>
+      <c r="J9" s="3">
+        <v>3.7039295322054999E-8</v>
+      </c>
+      <c r="K9" s="3">
+        <v>-6.3868700491256098E-6</v>
+      </c>
+      <c r="L9" s="3">
+        <v>1.7578178552832399E-8</v>
+      </c>
+      <c r="M9" s="3">
+        <v>4.78439499748889E-8</v>
+      </c>
+      <c r="N9" s="3">
+        <v>5.4551901115884604E-7</v>
+      </c>
+      <c r="O9" s="3">
+        <v>-3.5846327869169501E-10</v>
+      </c>
+      <c r="P9" s="3">
+        <v>-1.36258977667542E-8</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>-1.9808713530690699E-8</v>
+      </c>
+      <c r="R9" s="3">
+        <v>-2.1409803017793801E-8</v>
+      </c>
+      <c r="S9" s="3">
+        <v>-2.5290579834443499E-8</v>
+      </c>
+      <c r="T9" s="3">
+        <v>-1.680557053617E-8</v>
+      </c>
+      <c r="U9" s="3">
+        <v>-1.3507741620132001E-8</v>
+      </c>
+      <c r="V9" s="3">
+        <v>-7.1843560648331799E-9</v>
+      </c>
+      <c r="W9" s="3">
+        <v>1.4366113284974601E-6</v>
+      </c>
+      <c r="X9" s="3">
+        <v>8.8624719149530201E-9</v>
+      </c>
+      <c r="Y9" s="3">
+        <v>2.39359101820782E-8</v>
+      </c>
+      <c r="Z9" s="3">
+        <v>1.6284997251971601E-8</v>
+      </c>
+      <c r="AA9" s="3">
+        <v>8.4304809464155598E-7</v>
+      </c>
+      <c r="AB9" s="3">
+        <v>1.6328844638368399E-8</v>
+      </c>
+      <c r="AC9" s="3">
+        <v>-2.38213687960778E-7</v>
+      </c>
+      <c r="AD9" s="3">
+        <v>8.9490495832072994E-9</v>
+      </c>
+      <c r="AE9" s="3">
+        <v>-2.49820286317083E-7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3">
+        <v>2.6758213703980401E-2</v>
+      </c>
+      <c r="C10" s="3">
+        <v>5.4792089090609801E-5</v>
+      </c>
+      <c r="D10" s="3">
+        <v>-1.66963385651895E-3</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3.8888376684996798E-6</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-2.1239481131728301E-3</v>
+      </c>
+      <c r="G10" s="3">
+        <v>6.73467369315291E-6</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1.0776633131646701E-5</v>
+      </c>
+      <c r="I10" s="3">
+        <v>3.3314503288669802E-3</v>
+      </c>
+      <c r="J10" s="3">
+        <v>-6.3868700491256098E-6</v>
+      </c>
+      <c r="K10" s="3">
+        <v>4.6108070650138101E-3</v>
+      </c>
+      <c r="L10" s="3">
+        <v>-1.47718493978646E-5</v>
+      </c>
+      <c r="M10" s="3">
+        <v>-2.20546317335719E-5</v>
+      </c>
+      <c r="N10" s="3">
+        <v>-1.80713894866647E-4</v>
+      </c>
+      <c r="O10" s="3">
+        <v>-1.88335156310336E-6</v>
+      </c>
+      <c r="P10" s="3">
+        <v>5.2792204415593798E-6</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>1.3969282250554E-5</v>
+      </c>
+      <c r="R10" s="3">
+        <v>3.8255747140326004E-6</v>
+      </c>
+      <c r="S10" s="3">
+        <v>1.00859771508938E-5</v>
+      </c>
+      <c r="T10" s="3">
+        <v>2.0783965526135399E-6</v>
+      </c>
+      <c r="U10" s="3">
+        <v>5.7277235040851903E-6</v>
+      </c>
+      <c r="V10" s="3">
+        <v>-2.0387022210041599E-7</v>
+      </c>
+      <c r="W10" s="3">
+        <v>-2.20139485419299E-4</v>
+      </c>
+      <c r="X10" s="3">
+        <v>-8.4216674854528906E-6</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>-2.9167573376397699E-5</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>-5.6181224798459203E-6</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>-1.4426314321205301E-3</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>-4.8313977370567103E-6</v>
+      </c>
+      <c r="AC10" s="3">
+        <v>-1.13668757442359E-3</v>
+      </c>
+      <c r="AD10" s="3">
+        <v>-2.7588637946059201E-6</v>
+      </c>
+      <c r="AE10" s="3">
+        <v>3.2304296443269002E-5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3">
+        <v>-1.2273139232720301E-4</v>
+      </c>
+      <c r="C11" s="3">
+        <v>-2.2681141620312401E-7</v>
+      </c>
+      <c r="D11" s="3">
+        <v>5.0383735027121401E-6</v>
+      </c>
+      <c r="E11" s="3">
+        <v>-1.08547654697684E-8</v>
+      </c>
+      <c r="F11" s="3">
+        <v>6.7523665847881301E-6</v>
+      </c>
+      <c r="G11" s="3">
+        <v>-2.1758561176163999E-8</v>
+      </c>
+      <c r="H11" s="3">
+        <v>-3.3552400714094101E-8</v>
+      </c>
+      <c r="I11" s="3">
+        <v>-1.0102331975707099E-5</v>
+      </c>
+      <c r="J11" s="3">
+        <v>1.7578178552832399E-8</v>
+      </c>
+      <c r="K11" s="3">
+        <v>-1.47718493978646E-5</v>
+      </c>
+      <c r="L11" s="3">
+        <v>4.8079992001042799E-8</v>
+      </c>
+      <c r="M11" s="3">
+        <v>6.9020313175408906E-8</v>
+      </c>
+      <c r="N11" s="3">
+        <v>6.3347858642379704E-7</v>
+      </c>
+      <c r="O11" s="3">
+        <v>6.7171700757923099E-9</v>
+      </c>
+      <c r="P11" s="3">
+        <v>-2.0582819260719701E-8</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>-4.2577530733342301E-8</v>
+      </c>
+      <c r="R11" s="3">
+        <v>-1.8397198617289299E-8</v>
+      </c>
+      <c r="S11" s="3">
+        <v>-3.6814641556084201E-8</v>
+      </c>
+      <c r="T11" s="3">
+        <v>-1.47430468131336E-8</v>
+      </c>
+      <c r="U11" s="3">
+        <v>-2.7098997092493899E-8</v>
+      </c>
+      <c r="V11" s="3">
+        <v>-1.02694825328009E-8</v>
+      </c>
+      <c r="W11" s="3">
+        <v>5.6115990202953503E-8</v>
+      </c>
+      <c r="X11" s="3">
+        <v>2.9392240946629E-8</v>
+      </c>
+      <c r="Y11" s="3">
+        <v>8.9129318340567906E-8</v>
+      </c>
+      <c r="Z11" s="3">
+        <v>2.5466241507931901E-8</v>
+      </c>
+      <c r="AA11" s="3">
+        <v>4.9028998842065999E-6</v>
+      </c>
+      <c r="AB11" s="3">
+        <v>2.5602908621452001E-8</v>
+      </c>
+      <c r="AC11" s="3">
+        <v>4.5476868020242098E-6</v>
+      </c>
+      <c r="AD11" s="3">
+        <v>2.08158788748257E-8</v>
+      </c>
+      <c r="AE11" s="3">
+        <v>1.0551011155236501E-8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3">
+        <v>-1.3829572049644501E-4</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1.3345356051517001E-7</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1.2728986499007001E-5</v>
+      </c>
+      <c r="E12" s="3">
+        <v>-2.9015396737953202E-8</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1.0930183137874E-5</v>
+      </c>
+      <c r="G12" s="3">
+        <v>-3.3840560782707297E-8</v>
+      </c>
+      <c r="H12" s="3">
+        <v>-8.4255885474116597E-8</v>
+      </c>
+      <c r="I12" s="3">
+        <v>-2.5822408089234501E-5</v>
+      </c>
+      <c r="J12" s="3">
+        <v>4.78439499748889E-8</v>
+      </c>
+      <c r="K12" s="3">
+        <v>-2.20546317335719E-5</v>
+      </c>
+      <c r="L12" s="3">
+        <v>6.9020313175408906E-8</v>
+      </c>
+      <c r="M12" s="3">
+        <v>1.75215649450174E-7</v>
+      </c>
+      <c r="N12" s="3">
+        <v>2.65238874080156E-6</v>
+      </c>
+      <c r="O12" s="3">
+        <v>1.23953466027715E-9</v>
+      </c>
+      <c r="P12" s="3">
+        <v>1.9219483819745199E-8</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>-2.1589330938787101E-8</v>
+      </c>
+      <c r="R12" s="3">
+        <v>3.5625296281652297E-8</v>
+      </c>
+      <c r="S12" s="3">
+        <v>-7.9312539776170302E-9</v>
+      </c>
+      <c r="T12" s="3">
+        <v>3.1054006457303099E-8</v>
+      </c>
+      <c r="U12" s="3">
+        <v>1.61208966174969E-9</v>
+      </c>
+      <c r="V12" s="3">
+        <v>-8.4887729327274501E-9</v>
+      </c>
+      <c r="W12" s="3">
+        <v>-4.33838734377108E-7</v>
+      </c>
+      <c r="X12" s="3">
+        <v>-4.7401609513606601E-8</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>2.7956348290028201E-8</v>
+      </c>
+      <c r="Z12" s="3">
+        <v>-6.15497249934948E-8</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>3.0354419539865501E-6</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>-2.3891852682965301E-8</v>
+      </c>
+      <c r="AC12" s="3">
+        <v>4.2850359803336201E-6</v>
+      </c>
+      <c r="AD12" s="3">
+        <v>3.1453763039611501E-8</v>
+      </c>
+      <c r="AE12" s="3">
+        <v>-1.5113910206191199E-8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="3">
-        <v>0.99572501928013102</v>
-      </c>
-      <c r="C8" s="3">
-        <v>-6.9841930969792099E-4</v>
-      </c>
-      <c r="D8" s="3">
-        <v>-2.12410488986844E-4</v>
-      </c>
-      <c r="E8" s="3">
-        <v>-1.67647453075414E-6</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1.08148072343284E-3</v>
-      </c>
-      <c r="G8" s="3">
-        <v>-2.3635878554329899E-6</v>
-      </c>
-      <c r="H8" s="3">
-        <v>2.4896603746977202E-6</v>
-      </c>
-      <c r="I8" s="3">
-        <v>1.60895116724665E-2</v>
-      </c>
-      <c r="J8" s="3">
-        <v>-4.6727534814555196E-6</v>
-      </c>
-      <c r="K8" s="3">
-        <v>-3.7158793142576402E-5</v>
-      </c>
-      <c r="L8" s="3">
-        <v>-1.3780982442612601E-5</v>
-      </c>
-      <c r="M8" s="3">
-        <v>5.1049345243527497E-6</v>
-      </c>
-      <c r="N8" s="3">
-        <v>6.2379790741545796E-6</v>
-      </c>
-      <c r="O8" s="3">
-        <v>1.7583205855964999E-5</v>
-      </c>
-      <c r="P8" s="3">
-        <v>-2.1144908080539602E-6</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>1.6718531950615899E-5</v>
-      </c>
-      <c r="R8" s="3">
-        <v>-2.0035426825111801E-5</v>
-      </c>
-      <c r="S8" s="3">
-        <v>4.9436262853670103E-5</v>
-      </c>
-      <c r="T8" s="3">
-        <v>-8.6720788823514795E-6</v>
+      <c r="B13" s="3">
+        <v>2.2705466677337101</v>
+      </c>
+      <c r="C13" s="3">
+        <v>-1.45976076676486E-3</v>
+      </c>
+      <c r="D13" s="3">
+        <v>7.7905118409062795E-6</v>
+      </c>
+      <c r="E13" s="3">
+        <v>-8.42224261010507E-7</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1.3648730633539401E-3</v>
+      </c>
+      <c r="G13" s="3">
+        <v>-2.4887305256268201E-6</v>
+      </c>
+      <c r="H13" s="3">
+        <v>4.85171799704477E-7</v>
+      </c>
+      <c r="I13" s="3">
+        <v>-3.60314256785438E-4</v>
+      </c>
+      <c r="J13" s="3">
+        <v>5.4551901115884604E-7</v>
+      </c>
+      <c r="K13" s="3">
+        <v>-1.80713894866647E-4</v>
+      </c>
+      <c r="L13" s="3">
+        <v>6.3347858642379704E-7</v>
+      </c>
+      <c r="M13" s="3">
+        <v>2.65238874080156E-6</v>
+      </c>
+      <c r="N13" s="3">
+        <v>2.4002318081982301E-2</v>
+      </c>
+      <c r="O13" s="3">
+        <v>6.7497504647905401E-6</v>
+      </c>
+      <c r="P13" s="3">
+        <v>5.9670896535975101E-5</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>9.7790571324122096E-5</v>
+      </c>
+      <c r="R13" s="3">
+        <v>1.08213961413623E-4</v>
+      </c>
+      <c r="S13" s="3">
+        <v>1.3215419949606899E-4</v>
+      </c>
+      <c r="T13" s="3">
+        <v>1.5757211478519399E-4</v>
+      </c>
+      <c r="U13" s="3">
+        <v>1.88510316173865E-4</v>
+      </c>
+      <c r="V13" s="3">
+        <v>2.0094480297840898E-5</v>
+      </c>
+      <c r="W13" s="3">
+        <v>-9.31251023493098E-4</v>
+      </c>
+      <c r="X13" s="3">
+        <v>6.4462625566343999E-5</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>1.2416583230065201E-4</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>1.13553584448123E-4</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>9.0860139493382005E-3</v>
+      </c>
+      <c r="AB13" s="3">
+        <v>1.61155868338051E-4</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>1.5811559315374198E-2</v>
+      </c>
+      <c r="AD13" s="3">
+        <v>2.1354969270057898E-5</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>-1.7818291051150901E-5</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B14" s="3">
+        <v>-1.35734328536476E-2</v>
+      </c>
+      <c r="C14" s="3">
+        <v>-4.4239560392802401E-4</v>
+      </c>
+      <c r="D14" s="3">
+        <v>-1.3099796384693701E-8</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-1.5768931082986501E-9</v>
+      </c>
+      <c r="F14" s="3">
+        <v>2.0305308604558202E-6</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-3.2854750580198301E-9</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1.4718208970971601E-9</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-1.0918987652906199E-7</v>
+      </c>
+      <c r="J14" s="3">
+        <v>-3.5846327869169501E-10</v>
+      </c>
+      <c r="K14" s="3">
+        <v>-1.88335156310336E-6</v>
+      </c>
+      <c r="L14" s="3">
+        <v>6.7171700757923099E-9</v>
+      </c>
+      <c r="M14" s="3">
+        <v>1.23953466027715E-9</v>
+      </c>
+      <c r="N14" s="3">
+        <v>6.7497504647905401E-6</v>
+      </c>
+      <c r="O14" s="3">
+        <v>1.5787346552941502E-5</v>
+      </c>
+      <c r="P14" s="3">
+        <v>7.2649059269395601E-7</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>9.1323982152296103E-6</v>
+      </c>
+      <c r="R14" s="3">
+        <v>8.6875804931833099E-7</v>
+      </c>
+      <c r="S14" s="3">
+        <v>5.2530493865776296E-6</v>
+      </c>
+      <c r="T14" s="3">
+        <v>9.5920177027588999E-7</v>
+      </c>
+      <c r="U14" s="3">
+        <v>5.1186424449172196E-6</v>
+      </c>
+      <c r="V14" s="3">
+        <v>1.0025458430046899E-6</v>
+      </c>
+      <c r="W14" s="3">
+        <v>1.90475354578235E-4</v>
+      </c>
+      <c r="X14" s="3">
+        <v>6.6498492243387699E-7</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>1.18894871016752E-5</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>8.7843892578780003E-7</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>3.8885890278582701E-4</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>9.816471018495259E-7</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>3.9990612529965E-4</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>1.0148492182875601E-6</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>3.3219196627751998E-5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B15" s="3">
+        <v>-2.0050798941757802E-3</v>
+      </c>
+      <c r="C15" s="3">
+        <v>-1.38273208057125E-5</v>
+      </c>
+      <c r="D15" s="3">
+        <v>8.8767747496532897E-8</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1.2794883453042E-8</v>
+      </c>
+      <c r="F15" s="3">
+        <v>-2.3901403872406398E-6</v>
+      </c>
+      <c r="G15" s="3">
+        <v>1.6150131807205499E-8</v>
+      </c>
+      <c r="H15" s="3">
+        <v>-1.08912156633368E-8</v>
+      </c>
+      <c r="I15" s="3">
+        <v>-1.0221124129057E-6</v>
+      </c>
+      <c r="J15" s="3">
+        <v>-1.36258977667542E-8</v>
+      </c>
+      <c r="K15" s="3">
+        <v>5.2792204415593798E-6</v>
+      </c>
+      <c r="L15" s="3">
+        <v>-2.0582819260719701E-8</v>
+      </c>
+      <c r="M15" s="3">
+        <v>1.9219483819745199E-8</v>
+      </c>
+      <c r="N15" s="3">
+        <v>5.9670896535975101E-5</v>
+      </c>
+      <c r="O15" s="3">
+        <v>7.2649059269395601E-7</v>
+      </c>
+      <c r="P15" s="3">
+        <v>3.9905239920756798E-6</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>1.74371422187407E-6</v>
+      </c>
+      <c r="R15" s="3">
+        <v>1.8611587352190899E-6</v>
+      </c>
+      <c r="S15" s="3">
+        <v>1.9963008630753399E-6</v>
+      </c>
+      <c r="T15" s="3">
+        <v>2.0477484583210298E-6</v>
+      </c>
+      <c r="U15" s="3">
+        <v>2.20403362953372E-6</v>
+      </c>
+      <c r="V15" s="3">
+        <v>1.70850762373849E-6</v>
+      </c>
+      <c r="W15" s="3">
+        <v>1.3914505646704801E-5</v>
+      </c>
+      <c r="X15" s="3">
+        <v>1.9881954989842001E-7</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>6.1461366950348299E-7</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>3.1860895281410102E-7</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>3.1494834524757201E-5</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>4.3653847812177798E-7</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>4.8209162137823403E-5</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>8.9518303641746302E-8</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>7.2427379996700101E-7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B16" s="3">
+        <v>-2.2808771051673199E-2</v>
+      </c>
+      <c r="C16" s="3">
+        <v>-5.7002713262109203E-4</v>
+      </c>
+      <c r="D16" s="3">
+        <v>-5.5865571930154203E-6</v>
+      </c>
+      <c r="E16" s="3">
+        <v>1.7855419920635701E-8</v>
+      </c>
+      <c r="F16" s="3">
+        <v>-7.7677387885546099E-6</v>
+      </c>
+      <c r="G16" s="3">
+        <v>3.7241227150176697E-8</v>
+      </c>
+      <c r="H16" s="3">
+        <v>2.11765600072742E-8</v>
+      </c>
+      <c r="I16" s="3">
+        <v>5.9238585619971002E-6</v>
+      </c>
+      <c r="J16" s="3">
+        <v>-1.9808713530690699E-8</v>
+      </c>
+      <c r="K16" s="3">
+        <v>1.3969282250554E-5</v>
+      </c>
+      <c r="L16" s="3">
+        <v>-4.2577530733342301E-8</v>
+      </c>
+      <c r="M16" s="3">
+        <v>-2.1589330938787101E-8</v>
+      </c>
+      <c r="N16" s="3">
+        <v>9.7790571324122096E-5</v>
+      </c>
+      <c r="O16" s="3">
+        <v>9.1323982152296103E-6</v>
+      </c>
+      <c r="P16" s="3">
+        <v>1.74371422187407E-6</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>1.00898477309969E-4</v>
+      </c>
+      <c r="R16" s="3">
+        <v>2.2187747043785398E-6</v>
+      </c>
+      <c r="S16" s="3">
+        <v>8.0524148358984206E-6</v>
+      </c>
+      <c r="T16" s="3">
+        <v>2.5553660184364099E-6</v>
+      </c>
+      <c r="U16" s="3">
+        <v>8.0723356333049807E-6</v>
+      </c>
+      <c r="V16" s="3">
+        <v>2.0687690594699399E-6</v>
+      </c>
+      <c r="W16" s="3">
+        <v>2.4645639759330402E-4</v>
+      </c>
+      <c r="X16" s="3">
+        <v>3.3277008861697502E-7</v>
+      </c>
+      <c r="Y16" s="3">
+        <v>1.4599664530026599E-5</v>
+      </c>
+      <c r="Z16" s="3">
+        <v>1.0068060718133701E-6</v>
+      </c>
+      <c r="AA16" s="3">
+        <v>5.3025685080780203E-4</v>
+      </c>
+      <c r="AB16" s="3">
+        <v>1.3947852225007701E-6</v>
+      </c>
+      <c r="AC16" s="3">
+        <v>5.7627705007456704E-4</v>
+      </c>
+      <c r="AD16" s="3">
+        <v>9.54243449060503E-7</v>
+      </c>
+      <c r="AE16" s="3">
+        <v>4.2266834945770703E-5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B17" s="3">
+        <v>1.5803642417603601E-2</v>
+      </c>
+      <c r="C17" s="3">
+        <v>-3.2806140748527603E-5</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1.2827442790502899E-7</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1.99766442914547E-8</v>
+      </c>
+      <c r="F17" s="3">
+        <v>1.51652690158799E-6</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1.02422739239568E-8</v>
+      </c>
+      <c r="H17" s="3">
+        <v>-2.1509396451579401E-8</v>
+      </c>
+      <c r="I17" s="3">
+        <v>-1.70294284882643E-6</v>
+      </c>
+      <c r="J17" s="3">
+        <v>-2.1409803017793801E-8</v>
+      </c>
+      <c r="K17" s="3">
+        <v>3.8255747140326004E-6</v>
+      </c>
+      <c r="L17" s="3">
+        <v>-1.8397198617289299E-8</v>
+      </c>
+      <c r="M17" s="3">
+        <v>3.5625296281652297E-8</v>
+      </c>
+      <c r="N17" s="3">
+        <v>1.08213961413623E-4</v>
+      </c>
+      <c r="O17" s="3">
+        <v>8.6875804931833099E-7</v>
+      </c>
+      <c r="P17" s="3">
+        <v>1.8611587352190899E-6</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>2.2187747043785398E-6</v>
+      </c>
+      <c r="R17" s="3">
+        <v>3.0165964169052899E-6</v>
+      </c>
+      <c r="S17" s="3">
+        <v>2.83261234577191E-6</v>
+      </c>
+      <c r="T17" s="3">
+        <v>2.9383419141466999E-6</v>
+      </c>
+      <c r="U17" s="3">
+        <v>3.27033734169333E-6</v>
+      </c>
+      <c r="V17" s="3">
+        <v>2.4122779296801099E-6</v>
+      </c>
+      <c r="W17" s="3">
+        <v>3.1872630737884599E-5</v>
+      </c>
+      <c r="X17" s="3">
+        <v>3.22284399571829E-7</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>1.2539624543418201E-6</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>5.5740761552043E-7</v>
+      </c>
+      <c r="AA17" s="3">
+        <v>6.3887113516178601E-5</v>
+      </c>
+      <c r="AB17" s="3">
+        <v>7.78057907697776E-7</v>
+      </c>
+      <c r="AC17" s="3">
+        <v>9.4814081961460301E-5</v>
+      </c>
+      <c r="AD17" s="3">
+        <v>1.52395911667508E-7</v>
+      </c>
+      <c r="AE17" s="3">
+        <v>1.8904408457533699E-6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B18" s="3">
+        <v>9.9177244178018896E-3</v>
+      </c>
+      <c r="C18" s="3">
+        <v>-3.2657794885813701E-4</v>
+      </c>
+      <c r="D18" s="3">
+        <v>-5.7799354375200503E-6</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2.32256623767341E-8</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-2.7993631971185E-6</v>
+      </c>
+      <c r="G18" s="3">
+        <v>2.7873815411059302E-8</v>
+      </c>
+      <c r="H18" s="3">
+        <v>1.7858979455248701E-8</v>
+      </c>
+      <c r="I18" s="3">
+        <v>4.8283917176307801E-6</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-2.5290579834443499E-8</v>
+      </c>
+      <c r="K18" s="3">
+        <v>1.00859771508938E-5</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-3.6814641556084201E-8</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-7.9312539776170302E-9</v>
+      </c>
+      <c r="N18" s="3">
+        <v>1.3215419949606899E-4</v>
+      </c>
+      <c r="O18" s="3">
+        <v>5.2530493865776296E-6</v>
+      </c>
+      <c r="P18" s="3">
+        <v>1.9963008630753399E-6</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>8.0524148358984206E-6</v>
+      </c>
+      <c r="R18" s="3">
+        <v>2.83261234577191E-6</v>
+      </c>
+      <c r="S18" s="3">
+        <v>2.5105415915978999E-5</v>
+      </c>
+      <c r="T18" s="3">
+        <v>3.3850573630791099E-6</v>
+      </c>
+      <c r="U18" s="3">
+        <v>6.9411978985472099E-6</v>
+      </c>
+      <c r="V18" s="3">
+        <v>2.82136290694417E-6</v>
+      </c>
+      <c r="W18" s="3">
+        <v>1.58726801581819E-4</v>
+      </c>
+      <c r="X18" s="3">
+        <v>3.9961202020835003E-7</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>8.6494912281384898E-6</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>9.3611507080432402E-7</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>3.2856112513123599E-4</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>1.30724854001861E-6</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>3.7605886421803603E-4</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>6.1014253744220205E-7</v>
+      </c>
+      <c r="AE18" s="3">
+        <v>2.3811754538130601E-5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B19" s="3">
+        <v>2.2488293912465498E-2</v>
+      </c>
+      <c r="C19" s="3">
+        <v>-4.4083097124947101E-5</v>
+      </c>
+      <c r="D19" s="3">
+        <v>-1.1773492092786599E-6</v>
+      </c>
+      <c r="E19" s="3">
+        <v>1.47597078118045E-8</v>
+      </c>
+      <c r="F19" s="3">
+        <v>5.7273347152628699E-6</v>
+      </c>
+      <c r="G19" s="3">
+        <v>2.7910252330068198E-9</v>
+      </c>
+      <c r="H19" s="3">
+        <v>-1.07598233820826E-8</v>
+      </c>
+      <c r="I19" s="3">
+        <v>-1.0869179829134801E-6</v>
+      </c>
+      <c r="J19" s="3">
+        <v>-1.680557053617E-8</v>
+      </c>
+      <c r="K19" s="3">
+        <v>2.0783965526135399E-6</v>
+      </c>
+      <c r="L19" s="3">
+        <v>-1.47430468131336E-8</v>
+      </c>
+      <c r="M19" s="3">
+        <v>3.1054006457303099E-8</v>
+      </c>
+      <c r="N19" s="3">
+        <v>1.5757211478519399E-4</v>
+      </c>
+      <c r="O19" s="3">
+        <v>9.5920177027588999E-7</v>
+      </c>
+      <c r="P19" s="3">
+        <v>2.0477484583210298E-6</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>2.5553660184364099E-6</v>
+      </c>
+      <c r="R19" s="3">
+        <v>2.9383419141466999E-6</v>
+      </c>
+      <c r="S19" s="3">
+        <v>3.3850573630791099E-6</v>
+      </c>
+      <c r="T19" s="3">
+        <v>3.9077793697805003E-6</v>
+      </c>
+      <c r="U19" s="3">
+        <v>4.0249455424304601E-6</v>
+      </c>
+      <c r="V19" s="3">
+        <v>2.8510125047791102E-6</v>
+      </c>
+      <c r="W19" s="3">
+        <v>4.3420305045676701E-5</v>
+      </c>
+      <c r="X19" s="3">
+        <v>4.5197342012618002E-7</v>
+      </c>
+      <c r="Y19" s="3">
+        <v>1.7107070791313099E-6</v>
+      </c>
+      <c r="Z19" s="3">
+        <v>7.9613280323215095E-7</v>
+      </c>
+      <c r="AA19" s="3">
+        <v>8.9808522990028405E-5</v>
+      </c>
+      <c r="AB19" s="3">
+        <v>1.1179285224098299E-6</v>
+      </c>
+      <c r="AC19" s="3">
+        <v>1.34874783864406E-4</v>
+      </c>
+      <c r="AD19" s="3">
+        <v>2.06862585445913E-7</v>
+      </c>
+      <c r="AE19" s="3">
+        <v>2.47460032621245E-6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="B9" s="3">
-        <v>-8.1972965338796E-3</v>
-      </c>
-      <c r="C9" s="3">
-        <v>-1.9951459761529201E-5</v>
-      </c>
-      <c r="D9" s="3">
-        <v>6.1214312387262998E-6</v>
-      </c>
-      <c r="E9" s="3">
-        <v>8.4998118401502599E-8</v>
-      </c>
-      <c r="F9" s="3">
-        <v>-1.31449874069332E-4</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1.8569949547692401E-8</v>
-      </c>
-      <c r="H9" s="3">
-        <v>-4.6649077666843097E-8</v>
-      </c>
-      <c r="I9" s="3">
-        <v>-4.6727534814555196E-6</v>
-      </c>
-      <c r="J9" s="3">
-        <v>1.8271885283959599E-4</v>
-      </c>
-      <c r="K9" s="3">
-        <v>1.2861587344386601E-4</v>
-      </c>
-      <c r="L9" s="3">
-        <v>1.28589387989384E-4</v>
-      </c>
-      <c r="M9" s="3">
-        <v>1.2874140956800799E-4</v>
-      </c>
-      <c r="N9" s="3">
-        <v>1.2867264665216999E-4</v>
-      </c>
-      <c r="O9" s="3">
-        <v>1.28798172267812E-4</v>
-      </c>
-      <c r="P9" s="3">
-        <v>1.2908218446648799E-4</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>1.2871086317220299E-4</v>
-      </c>
-      <c r="R9" s="3">
-        <v>1.28157377023514E-4</v>
-      </c>
-      <c r="S9" s="3">
-        <v>1.2850517839577201E-4</v>
-      </c>
-      <c r="T9" s="3">
-        <v>1.2823071191081999E-4</v>
+      <c r="B20" s="3">
+        <v>1.28100266221424E-2</v>
+      </c>
+      <c r="C20" s="3">
+        <v>-3.2367230722205498E-4</v>
+      </c>
+      <c r="D20" s="3">
+        <v>-3.9686892538799602E-6</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1.07615780554663E-8</v>
+      </c>
+      <c r="F20" s="3">
+        <v>4.33079258177218E-6</v>
+      </c>
+      <c r="G20" s="3">
+        <v>1.37649092255024E-8</v>
+      </c>
+      <c r="H20" s="3">
+        <v>1.5763048125408299E-8</v>
+      </c>
+      <c r="I20" s="3">
+        <v>2.1773710138984202E-6</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-1.3507741620132001E-8</v>
+      </c>
+      <c r="K20" s="3">
+        <v>5.7277235040851903E-6</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-2.7098997092493899E-8</v>
+      </c>
+      <c r="M20" s="3">
+        <v>1.61208966174969E-9</v>
+      </c>
+      <c r="N20" s="3">
+        <v>1.88510316173865E-4</v>
+      </c>
+      <c r="O20" s="3">
+        <v>5.1186424449172196E-6</v>
+      </c>
+      <c r="P20" s="3">
+        <v>2.20403362953372E-6</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>8.0723356333049807E-6</v>
+      </c>
+      <c r="R20" s="3">
+        <v>3.27033734169333E-6</v>
+      </c>
+      <c r="S20" s="3">
+        <v>6.9411978985472099E-6</v>
+      </c>
+      <c r="T20" s="3">
+        <v>4.0249455424304601E-6</v>
+      </c>
+      <c r="U20" s="3">
+        <v>5.7135421380955798E-5</v>
+      </c>
+      <c r="V20" s="3">
+        <v>3.2426650992799402E-6</v>
+      </c>
+      <c r="W20" s="3">
+        <v>1.68120147784875E-4</v>
+      </c>
+      <c r="X20" s="3">
+        <v>5.4689304561624302E-7</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>8.7782861841766895E-6</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>1.1942906010439699E-6</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>3.4435782274324598E-4</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>1.67535851537749E-6</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>4.0746789479650198E-4</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>6.4871772972224199E-7</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>2.3294289001235301E-5</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B10" s="3">
-        <v>-6.8212570985156198E-4</v>
-      </c>
-      <c r="C10" s="3">
-        <v>-1.56280416303169E-5</v>
-      </c>
-      <c r="D10" s="3">
-        <v>8.6132197989848994E-6</v>
-      </c>
-      <c r="E10" s="3">
-        <v>3.23626215977667E-8</v>
-      </c>
-      <c r="F10" s="3">
-        <v>-1.4110878557804701E-4</v>
-      </c>
-      <c r="G10" s="3">
-        <v>4.9362830960052602E-8</v>
-      </c>
-      <c r="H10" s="3">
-        <v>-5.4253202543022897E-8</v>
-      </c>
-      <c r="I10" s="3">
-        <v>-3.7158793142576402E-5</v>
-      </c>
-      <c r="J10" s="3">
-        <v>1.2861587344386601E-4</v>
-      </c>
-      <c r="K10" s="3">
-        <v>1.9429699234282E-4</v>
-      </c>
-      <c r="L10" s="3">
-        <v>1.28268875179628E-4</v>
-      </c>
-      <c r="M10" s="3">
-        <v>1.2823086318456201E-4</v>
-      </c>
-      <c r="N10" s="3">
-        <v>1.28263976140674E-4</v>
-      </c>
-      <c r="O10" s="3">
-        <v>1.2815158340243201E-4</v>
-      </c>
-      <c r="P10" s="3">
-        <v>1.2857424237435299E-4</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>1.2823793376952401E-4</v>
-      </c>
-      <c r="R10" s="3">
-        <v>1.2800878876395E-4</v>
-      </c>
-      <c r="S10" s="3">
-        <v>1.2806925814576499E-4</v>
-      </c>
-      <c r="T10" s="3">
-        <v>1.2837966944789301E-4</v>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B21" s="3">
+        <v>1.7396586469329098E-2</v>
+      </c>
+      <c r="C21" s="3">
+        <v>-4.3004050441810102E-5</v>
+      </c>
+      <c r="D21" s="3">
+        <v>-3.37284148752009E-6</v>
+      </c>
+      <c r="E21" s="3">
+        <v>6.8335268027798396E-9</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1.2500867592743E-6</v>
+      </c>
+      <c r="G21" s="3">
+        <v>8.9633571572751406E-9</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1.0591673151090299E-8</v>
+      </c>
+      <c r="I21" s="3">
+        <v>3.1564170494286799E-6</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-7.1843560648331799E-9</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-2.0387022210041599E-7</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-1.02694825328009E-8</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-8.4887729327274501E-9</v>
+      </c>
+      <c r="N21" s="3">
+        <v>2.0094480297840898E-5</v>
+      </c>
+      <c r="O21" s="3">
+        <v>1.0025458430046899E-6</v>
+      </c>
+      <c r="P21" s="3">
+        <v>1.70850762373849E-6</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>2.0687690594699399E-6</v>
+      </c>
+      <c r="R21" s="3">
+        <v>2.4122779296801099E-6</v>
+      </c>
+      <c r="S21" s="3">
+        <v>2.82136290694417E-6</v>
+      </c>
+      <c r="T21" s="3">
+        <v>2.8510125047791102E-6</v>
+      </c>
+      <c r="U21" s="3">
+        <v>3.2426650992799402E-6</v>
+      </c>
+      <c r="V21" s="3">
+        <v>3.2318151967271399E-6</v>
+      </c>
+      <c r="W21" s="3">
+        <v>6.3758249088219094E-5</v>
+      </c>
+      <c r="X21" s="3">
+        <v>8.1226195860351397E-8</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>1.1781359996067501E-6</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>1.5103326048991601E-7</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>4.4134912942978601E-5</v>
+      </c>
+      <c r="AB21" s="3">
+        <v>2.0293873847977999E-7</v>
+      </c>
+      <c r="AC21" s="3">
+        <v>5.0942068467121303E-5</v>
+      </c>
+      <c r="AD21" s="3">
+        <v>9.4391075617084197E-8</v>
+      </c>
+      <c r="AE21" s="3">
+        <v>3.1230377465330602E-6</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B11" s="3">
-        <v>-4.4596424160110298E-4</v>
-      </c>
-      <c r="C11" s="3">
-        <v>-1.6085496742759701E-5</v>
-      </c>
-      <c r="D11" s="3">
-        <v>2.2536356875863299E-5</v>
-      </c>
-      <c r="E11" s="3">
-        <v>3.4279766294984102E-9</v>
-      </c>
-      <c r="F11" s="3">
-        <v>-1.16254410988808E-4</v>
-      </c>
-      <c r="G11" s="3">
-        <v>-2.97719140735268E-8</v>
-      </c>
-      <c r="H11" s="3">
-        <v>-1.40962918782938E-7</v>
-      </c>
-      <c r="I11" s="3">
-        <v>-1.3780982442612601E-5</v>
-      </c>
-      <c r="J11" s="3">
-        <v>1.28589387989384E-4</v>
-      </c>
-      <c r="K11" s="3">
-        <v>1.28268875179628E-4</v>
-      </c>
-      <c r="L11" s="3">
-        <v>2.19627493319524E-4</v>
-      </c>
-      <c r="M11" s="3">
-        <v>1.2884193331577599E-4</v>
-      </c>
-      <c r="N11" s="3">
-        <v>1.2863839335840199E-4</v>
-      </c>
-      <c r="O11" s="3">
-        <v>1.28716701703317E-4</v>
-      </c>
-      <c r="P11" s="3">
-        <v>1.2909668980630199E-4</v>
-      </c>
-      <c r="Q11" s="3">
-        <v>1.2881053694984901E-4</v>
-      </c>
-      <c r="R11" s="3">
-        <v>1.2813856128638499E-4</v>
-      </c>
-      <c r="S11" s="3">
-        <v>1.2847479183651601E-4</v>
-      </c>
-      <c r="T11" s="3">
-        <v>1.2804314241824901E-4</v>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B22" s="3">
+        <v>-5.54366381774049</v>
+      </c>
+      <c r="C22" s="3">
+        <v>-1.3131505351304499E-2</v>
+      </c>
+      <c r="D22" s="3">
+        <v>2.2205913617525199E-4</v>
+      </c>
+      <c r="E22" s="3">
+        <v>-1.4392591456924201E-6</v>
+      </c>
+      <c r="F22" s="3">
+        <v>2.0962679688493001E-4</v>
+      </c>
+      <c r="G22" s="3">
+        <v>6.2164446363434603E-8</v>
+      </c>
+      <c r="H22" s="3">
+        <v>-2.7545664026340501E-8</v>
+      </c>
+      <c r="I22" s="3">
+        <v>-1.6330136371509201E-4</v>
+      </c>
+      <c r="J22" s="3">
+        <v>1.4366113284974601E-6</v>
+      </c>
+      <c r="K22" s="3">
+        <v>-2.20139485419299E-4</v>
+      </c>
+      <c r="L22" s="3">
+        <v>5.6115990202953503E-8</v>
+      </c>
+      <c r="M22" s="3">
+        <v>-4.33838734377108E-7</v>
+      </c>
+      <c r="N22" s="3">
+        <v>-9.31251023493098E-4</v>
+      </c>
+      <c r="O22" s="3">
+        <v>1.90475354578235E-4</v>
+      </c>
+      <c r="P22" s="3">
+        <v>1.3914505646704801E-5</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>2.4645639759330402E-4</v>
+      </c>
+      <c r="R22" s="3">
+        <v>3.1872630737884599E-5</v>
+      </c>
+      <c r="S22" s="3">
+        <v>1.58726801581819E-4</v>
+      </c>
+      <c r="T22" s="3">
+        <v>4.3420305045676701E-5</v>
+      </c>
+      <c r="U22" s="3">
+        <v>1.68120147784875E-4</v>
+      </c>
+      <c r="V22" s="3">
+        <v>6.3758249088219094E-5</v>
+      </c>
+      <c r="W22" s="3">
+        <v>180965.413391195</v>
+      </c>
+      <c r="X22" s="3">
+        <v>-2.3756800638668999E-6</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>3.2261829690493E-4</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>7.24192615771289E-6</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>1.11797997728235E-2</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>1.0090793471891E-5</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>1.13680680694851E-2</v>
+      </c>
+      <c r="AD22" s="3">
+        <v>1.8604867054813401E-5</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>9.9045831466263909E-4</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B12" s="3">
-        <v>-5.4173523046E-3</v>
-      </c>
-      <c r="C12" s="3">
-        <v>-1.6810972813864102E-5</v>
-      </c>
-      <c r="D12" s="3">
-        <v>1.81868866518548E-5</v>
-      </c>
-      <c r="E12" s="3">
-        <v>5.00464040914354E-8</v>
-      </c>
-      <c r="F12" s="3">
-        <v>-1.1205120093657801E-4</v>
-      </c>
-      <c r="G12" s="3">
-        <v>-4.4378821342023198E-8</v>
-      </c>
-      <c r="H12" s="3">
-        <v>-1.25313845761621E-7</v>
-      </c>
-      <c r="I12" s="3">
-        <v>5.1049345243527497E-6</v>
-      </c>
-      <c r="J12" s="3">
-        <v>1.2874140956800799E-4</v>
-      </c>
-      <c r="K12" s="3">
-        <v>1.2823086318456201E-4</v>
-      </c>
-      <c r="L12" s="3">
-        <v>1.2884193331577599E-4</v>
-      </c>
-      <c r="M12" s="3">
-        <v>2.0167687277329699E-4</v>
-      </c>
-      <c r="N12" s="3">
-        <v>1.2889660150704901E-4</v>
-      </c>
-      <c r="O12" s="3">
-        <v>1.29047466392553E-4</v>
-      </c>
-      <c r="P12" s="3">
-        <v>1.29395492257354E-4</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>1.2910775674281099E-4</v>
-      </c>
-      <c r="R12" s="3">
-        <v>1.2822982475839699E-4</v>
-      </c>
-      <c r="S12" s="3">
-        <v>1.2871723215705601E-4</v>
-      </c>
-      <c r="T12" s="3">
-        <v>1.2797977117152899E-4</v>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B23" s="3">
+        <v>-1.53561020646784E-2</v>
+      </c>
+      <c r="C23" s="3">
+        <v>-4.98718667466059E-6</v>
+      </c>
+      <c r="D23" s="3">
+        <v>-3.7473548779964399E-8</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-2.3475894752501299E-9</v>
+      </c>
+      <c r="F23" s="3">
+        <v>3.65862187673918E-6</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-6.7816117227708904E-9</v>
+      </c>
+      <c r="H23" s="3">
+        <v>1.8410488850628699E-9</v>
+      </c>
+      <c r="I23" s="3">
+        <v>4.8464491858741802E-6</v>
+      </c>
+      <c r="J23" s="3">
+        <v>8.8624719149530201E-9</v>
+      </c>
+      <c r="K23" s="3">
+        <v>-8.4216674854528906E-6</v>
+      </c>
+      <c r="L23" s="3">
+        <v>2.9392240946629E-8</v>
+      </c>
+      <c r="M23" s="3">
+        <v>-4.7401609513606601E-8</v>
+      </c>
+      <c r="N23" s="3">
+        <v>6.4462625566343999E-5</v>
+      </c>
+      <c r="O23" s="3">
+        <v>6.6498492243387699E-7</v>
+      </c>
+      <c r="P23" s="3">
+        <v>1.9881954989842001E-7</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>3.3277008861697502E-7</v>
+      </c>
+      <c r="R23" s="3">
+        <v>3.22284399571829E-7</v>
+      </c>
+      <c r="S23" s="3">
+        <v>3.9961202020835003E-7</v>
+      </c>
+      <c r="T23" s="3">
+        <v>4.5197342012618002E-7</v>
+      </c>
+      <c r="U23" s="3">
+        <v>5.4689304561624302E-7</v>
+      </c>
+      <c r="V23" s="3">
+        <v>8.1226195860351397E-8</v>
+      </c>
+      <c r="W23" s="3">
+        <v>-2.3756800638668999E-6</v>
+      </c>
+      <c r="X23" s="3">
+        <v>1.11277617700828E-5</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>2.1923723492404899E-6</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>1.9927526473481899E-6</v>
+      </c>
+      <c r="AA23" s="3">
+        <v>4.1546726855648198E-5</v>
+      </c>
+      <c r="AB23" s="3">
+        <v>2.0383028853820201E-6</v>
+      </c>
+      <c r="AC23" s="3">
+        <v>5.6576407337050302E-5</v>
+      </c>
+      <c r="AD23" s="3">
+        <v>1.4846901326516201E-6</v>
+      </c>
+      <c r="AE23" s="3">
+        <v>1.94750503173308E-6</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B13" s="3">
-        <v>-8.3842014307038606E-3</v>
-      </c>
-      <c r="C13" s="3">
-        <v>2.8045648463842E-5</v>
-      </c>
-      <c r="D13" s="3">
-        <v>-9.3509941745020897E-7</v>
-      </c>
-      <c r="E13" s="3">
-        <v>1.26981749798527E-7</v>
-      </c>
-      <c r="F13" s="3">
-        <v>-1.2246688883600201E-4</v>
-      </c>
-      <c r="G13" s="3">
-        <v>-1.84627955760693E-8</v>
-      </c>
-      <c r="H13" s="3">
-        <v>-3.87969118862372E-8</v>
-      </c>
-      <c r="I13" s="3">
-        <v>6.2379790741545796E-6</v>
-      </c>
-      <c r="J13" s="3">
-        <v>1.2867264665216999E-4</v>
-      </c>
-      <c r="K13" s="3">
-        <v>1.28263976140674E-4</v>
-      </c>
-      <c r="L13" s="3">
-        <v>1.2863839335840199E-4</v>
-      </c>
-      <c r="M13" s="3">
-        <v>1.2889660150704901E-4</v>
-      </c>
-      <c r="N13" s="3">
-        <v>1.8497035979113499E-4</v>
-      </c>
-      <c r="O13" s="3">
-        <v>1.2861294772255899E-4</v>
-      </c>
-      <c r="P13" s="3">
-        <v>1.2912919417246599E-4</v>
-      </c>
-      <c r="Q13" s="3">
-        <v>1.2898803287014299E-4</v>
-      </c>
-      <c r="R13" s="3">
-        <v>1.28185529936824E-4</v>
-      </c>
-      <c r="S13" s="3">
-        <v>1.2851062493150799E-4</v>
-      </c>
-      <c r="T13" s="3">
-        <v>1.2806928906562701E-4</v>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B24" s="3">
+        <v>-3.7360726666322598E-2</v>
+      </c>
+      <c r="C24" s="3">
+        <v>-7.4770951320942802E-4</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1.41243484717148E-6</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-4.6272621780540504E-9</v>
+      </c>
+      <c r="F24" s="3">
+        <v>1.0080933112939599E-5</v>
+      </c>
+      <c r="G24" s="3">
+        <v>-1.5014541176193999E-8</v>
+      </c>
+      <c r="H24" s="3">
+        <v>-8.0628341323405592E-9</v>
+      </c>
+      <c r="I24" s="3">
+        <v>-7.8366137303311205E-6</v>
+      </c>
+      <c r="J24" s="3">
+        <v>2.39359101820782E-8</v>
+      </c>
+      <c r="K24" s="3">
+        <v>-2.9167573376397699E-5</v>
+      </c>
+      <c r="L24" s="3">
+        <v>8.9129318340567906E-8</v>
+      </c>
+      <c r="M24" s="3">
+        <v>2.7956348290028201E-8</v>
+      </c>
+      <c r="N24" s="3">
+        <v>1.2416583230065201E-4</v>
+      </c>
+      <c r="O24" s="3">
+        <v>1.18894871016752E-5</v>
+      </c>
+      <c r="P24" s="3">
+        <v>6.1461366950348299E-7</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>1.4599664530026599E-5</v>
+      </c>
+      <c r="R24" s="3">
+        <v>1.2539624543418201E-6</v>
+      </c>
+      <c r="S24" s="3">
+        <v>8.6494912281384898E-6</v>
+      </c>
+      <c r="T24" s="3">
+        <v>1.7107070791313099E-6</v>
+      </c>
+      <c r="U24" s="3">
+        <v>8.7782861841766895E-6</v>
+      </c>
+      <c r="V24" s="3">
+        <v>1.1781359996067501E-6</v>
+      </c>
+      <c r="W24" s="3">
+        <v>3.2261829690493E-4</v>
+      </c>
+      <c r="X24" s="3">
+        <v>2.1923723492404899E-6</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>2.71122548519406E-4</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>2.5860546501435299E-6</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>7.2915130476653204E-4</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>2.8355353644538502E-6</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>7.624437791238E-4</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>1.9956415163245901E-6</v>
+      </c>
+      <c r="AE24" s="3">
+        <v>5.9539551208076402E-5</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="B14" s="3">
-        <v>7.0813954923913802E-3</v>
-      </c>
-      <c r="C14" s="3">
-        <v>-1.69121915246763E-4</v>
-      </c>
-      <c r="D14" s="3">
-        <v>4.96156039309976E-6</v>
-      </c>
-      <c r="E14" s="3">
-        <v>6.7466998015694194E-8</v>
-      </c>
-      <c r="F14" s="3">
-        <v>-1.16349003759329E-4</v>
-      </c>
-      <c r="G14" s="3">
-        <v>-1.95762401573888E-8</v>
-      </c>
-      <c r="H14" s="3">
-        <v>7.1569427468724803E-8</v>
-      </c>
-      <c r="I14" s="3">
-        <v>1.7583205855964999E-5</v>
-      </c>
-      <c r="J14" s="3">
-        <v>1.28798172267812E-4</v>
-      </c>
-      <c r="K14" s="3">
-        <v>1.2815158340243201E-4</v>
-      </c>
-      <c r="L14" s="3">
-        <v>1.28716701703317E-4</v>
-      </c>
-      <c r="M14" s="3">
-        <v>1.29047466392553E-4</v>
-      </c>
-      <c r="N14" s="3">
-        <v>1.2861294772255899E-4</v>
-      </c>
-      <c r="O14" s="3">
-        <v>2.0162779045955801E-4</v>
-      </c>
-      <c r="P14" s="3">
-        <v>1.29149652459675E-4</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>1.2825370519533501E-4</v>
-      </c>
-      <c r="R14" s="3">
-        <v>1.28387798462399E-4</v>
-      </c>
-      <c r="S14" s="3">
-        <v>1.29171340856517E-4</v>
-      </c>
-      <c r="T14" s="3">
-        <v>1.2725999699466701E-4</v>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B25" s="3">
+        <v>3.57891790059023E-3</v>
+      </c>
+      <c r="C25" s="3">
+        <v>-3.37532068332918E-5</v>
+      </c>
+      <c r="D25" s="3">
+        <v>4.6697030234485799E-8</v>
+      </c>
+      <c r="E25" s="3">
+        <v>-4.0507049891447397E-9</v>
+      </c>
+      <c r="F25" s="3">
+        <v>6.5591850107535598E-6</v>
+      </c>
+      <c r="G25" s="3">
+        <v>-1.19142248251213E-8</v>
+      </c>
+      <c r="H25" s="3">
+        <v>2.2777434251636898E-9</v>
+      </c>
+      <c r="I25" s="3">
+        <v>5.3127332084190401E-6</v>
+      </c>
+      <c r="J25" s="3">
+        <v>1.6284997251971601E-8</v>
+      </c>
+      <c r="K25" s="3">
+        <v>-5.6181224798459203E-6</v>
+      </c>
+      <c r="L25" s="3">
+        <v>2.5466241507931901E-8</v>
+      </c>
+      <c r="M25" s="3">
+        <v>-6.15497249934948E-8</v>
+      </c>
+      <c r="N25" s="3">
+        <v>1.13553584448123E-4</v>
+      </c>
+      <c r="O25" s="3">
+        <v>8.7843892578780003E-7</v>
+      </c>
+      <c r="P25" s="3">
+        <v>3.1860895281410102E-7</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>1.0068060718133701E-6</v>
+      </c>
+      <c r="R25" s="3">
+        <v>5.5740761552043E-7</v>
+      </c>
+      <c r="S25" s="3">
+        <v>9.3611507080432402E-7</v>
+      </c>
+      <c r="T25" s="3">
+        <v>7.9613280323215095E-7</v>
+      </c>
+      <c r="U25" s="3">
+        <v>1.1942906010439699E-6</v>
+      </c>
+      <c r="V25" s="3">
+        <v>1.5103326048991601E-7</v>
+      </c>
+      <c r="W25" s="3">
+        <v>7.24192615771289E-6</v>
+      </c>
+      <c r="X25" s="3">
+        <v>1.9927526473481899E-6</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>2.5860546501435299E-6</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>4.82446404640032E-6</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>8.4675770933115806E-5</v>
+      </c>
+      <c r="AB25" s="3">
+        <v>3.2483271297367001E-6</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>1.3265384960738799E-4</v>
+      </c>
+      <c r="AD25" s="3">
+        <v>2.5695133733992802E-6</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>6.0782956779033998E-6</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B15" s="3">
-        <v>-8.6466993167642007E-3</v>
-      </c>
-      <c r="C15" s="3">
-        <v>-3.7489818026374599E-6</v>
-      </c>
-      <c r="D15" s="3">
-        <v>3.0444920369570299E-5</v>
-      </c>
-      <c r="E15" s="3">
-        <v>2.9257034913650999E-8</v>
-      </c>
-      <c r="F15" s="3">
-        <v>-1.12737357219583E-4</v>
-      </c>
-      <c r="G15" s="3">
-        <v>-3.6634297609672803E-8</v>
-      </c>
-      <c r="H15" s="3">
-        <v>-1.98445037526611E-7</v>
-      </c>
-      <c r="I15" s="3">
-        <v>-2.1144908080539602E-6</v>
-      </c>
-      <c r="J15" s="3">
-        <v>1.2908218446648799E-4</v>
-      </c>
-      <c r="K15" s="3">
-        <v>1.2857424237435299E-4</v>
-      </c>
-      <c r="L15" s="3">
-        <v>1.2909668980630199E-4</v>
-      </c>
-      <c r="M15" s="3">
-        <v>1.29395492257354E-4</v>
-      </c>
-      <c r="N15" s="3">
-        <v>1.2912919417246599E-4</v>
-      </c>
-      <c r="O15" s="3">
-        <v>1.29149652459675E-4</v>
-      </c>
-      <c r="P15" s="3">
-        <v>1.6985912726237101E-4</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>1.2940122871540999E-4</v>
-      </c>
-      <c r="R15" s="3">
-        <v>1.28288053350757E-4</v>
-      </c>
-      <c r="S15" s="3">
-        <v>1.28876243626055E-4</v>
-      </c>
-      <c r="T15" s="3">
-        <v>1.28239416372725E-4</v>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B26" s="3">
+        <v>-10.3024581492006</v>
+      </c>
+      <c r="C26" s="3">
+        <v>-2.6582967533709399E-2</v>
+      </c>
+      <c r="D26" s="3">
+        <v>5.4139270552216797E-5</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-3.2418727783093902E-7</v>
+      </c>
+      <c r="F26" s="3">
+        <v>6.2344193356711302E-4</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-1.01277183497874E-6</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-2.1505393777460999E-7</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-4.5652088834934702E-4</v>
+      </c>
+      <c r="J26" s="3">
+        <v>8.4304809464155598E-7</v>
+      </c>
+      <c r="K26" s="3">
+        <v>-1.4426314321205301E-3</v>
+      </c>
+      <c r="L26" s="3">
+        <v>4.9028998842065999E-6</v>
+      </c>
+      <c r="M26" s="3">
+        <v>3.0354419539865501E-6</v>
+      </c>
+      <c r="N26" s="3">
+        <v>9.0860139493382005E-3</v>
+      </c>
+      <c r="O26" s="3">
+        <v>3.8885890278582701E-4</v>
+      </c>
+      <c r="P26" s="3">
+        <v>3.1494834524757201E-5</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>5.3025685080780203E-4</v>
+      </c>
+      <c r="R26" s="3">
+        <v>6.3887113516178601E-5</v>
+      </c>
+      <c r="S26" s="3">
+        <v>3.2856112513123599E-4</v>
+      </c>
+      <c r="T26" s="3">
+        <v>8.9808522990028405E-5</v>
+      </c>
+      <c r="U26" s="3">
+        <v>3.4435782274324598E-4</v>
+      </c>
+      <c r="V26" s="3">
+        <v>4.4134912942978601E-5</v>
+      </c>
+      <c r="W26" s="3">
+        <v>1.11797997728235E-2</v>
+      </c>
+      <c r="X26" s="3">
+        <v>4.1546726855648198E-5</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>7.2915130476653204E-4</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>8.4675770933115806E-5</v>
+      </c>
+      <c r="AA26" s="3">
+        <v>856957.56080078403</v>
+      </c>
+      <c r="AB26" s="3">
+        <v>1.09604996617301E-4</v>
+      </c>
+      <c r="AC26" s="3">
+        <v>1.0304112192745301</v>
+      </c>
+      <c r="AD26" s="3">
+        <v>5.6523492884616402E-5</v>
+      </c>
+      <c r="AE26" s="3">
+        <v>1.9575599343321999E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B16" s="3">
-        <v>-1.52704841429614E-2</v>
-      </c>
-      <c r="C16" s="3">
-        <v>5.7103493780468003E-5</v>
-      </c>
-      <c r="D16" s="3">
-        <v>1.42405086502582E-5</v>
-      </c>
-      <c r="E16" s="3">
-        <v>7.8520358290831098E-8</v>
-      </c>
-      <c r="F16" s="3">
-        <v>-1.13525292221057E-4</v>
-      </c>
-      <c r="G16" s="3">
-        <v>-4.5318350624731501E-8</v>
-      </c>
-      <c r="H16" s="3">
-        <v>-1.50424457315999E-7</v>
-      </c>
-      <c r="I16" s="3">
-        <v>1.6718531950615899E-5</v>
-      </c>
-      <c r="J16" s="3">
-        <v>1.2871086317220299E-4</v>
-      </c>
-      <c r="K16" s="3">
-        <v>1.2823793376952401E-4</v>
-      </c>
-      <c r="L16" s="3">
-        <v>1.2881053694984901E-4</v>
-      </c>
-      <c r="M16" s="3">
-        <v>1.2910775674281099E-4</v>
-      </c>
-      <c r="N16" s="3">
-        <v>1.2898803287014299E-4</v>
-      </c>
-      <c r="O16" s="3">
-        <v>1.2825370519533501E-4</v>
-      </c>
-      <c r="P16" s="3">
-        <v>1.2940122871540999E-4</v>
-      </c>
-      <c r="Q16" s="3">
-        <v>1.9031549287813301E-4</v>
-      </c>
-      <c r="R16" s="3">
-        <v>1.2815557511586801E-4</v>
-      </c>
-      <c r="S16" s="3">
-        <v>1.28557353679376E-4</v>
-      </c>
-      <c r="T16" s="3">
-        <v>1.2823405924706699E-4</v>
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B27" s="3">
+        <v>1.3622042802456401E-2</v>
+      </c>
+      <c r="C27" s="3">
+        <v>-4.7165081493678701E-5</v>
+      </c>
+      <c r="D27" s="3">
+        <v>8.9180820089915702E-8</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-5.7142343693600102E-9</v>
+      </c>
+      <c r="F27" s="3">
+        <v>9.3103839991541404E-6</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-1.6868568583899298E-8</v>
+      </c>
+      <c r="H27" s="3">
+        <v>3.0206602250118798E-9</v>
+      </c>
+      <c r="I27" s="3">
+        <v>3.0300240647553599E-7</v>
+      </c>
+      <c r="J27" s="3">
+        <v>1.6328844638368399E-8</v>
+      </c>
+      <c r="K27" s="3">
+        <v>-4.8313977370567103E-6</v>
+      </c>
+      <c r="L27" s="3">
+        <v>2.5602908621452001E-8</v>
+      </c>
+      <c r="M27" s="3">
+        <v>-2.3891852682965301E-8</v>
+      </c>
+      <c r="N27" s="3">
+        <v>1.61155868338051E-4</v>
+      </c>
+      <c r="O27" s="3">
+        <v>9.816471018495259E-7</v>
+      </c>
+      <c r="P27" s="3">
+        <v>4.3653847812177798E-7</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>1.3947852225007701E-6</v>
+      </c>
+      <c r="R27" s="3">
+        <v>7.78057907697776E-7</v>
+      </c>
+      <c r="S27" s="3">
+        <v>1.30724854001861E-6</v>
+      </c>
+      <c r="T27" s="3">
+        <v>1.1179285224098299E-6</v>
+      </c>
+      <c r="U27" s="3">
+        <v>1.67535851537749E-6</v>
+      </c>
+      <c r="V27" s="3">
+        <v>2.0293873847977999E-7</v>
+      </c>
+      <c r="W27" s="3">
+        <v>1.0090793471891E-5</v>
+      </c>
+      <c r="X27" s="3">
+        <v>2.0383028853820201E-6</v>
+      </c>
+      <c r="Y27" s="3">
+        <v>2.8355353644538502E-6</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>3.2483271297367001E-6</v>
+      </c>
+      <c r="AA27" s="3">
+        <v>1.09604996617301E-4</v>
+      </c>
+      <c r="AB27" s="3">
+        <v>4.8167789408419004E-6</v>
+      </c>
+      <c r="AC27" s="3">
+        <v>1.83336115491247E-4</v>
+      </c>
+      <c r="AD27" s="3">
+        <v>3.1387210313176601E-6</v>
+      </c>
+      <c r="AE27" s="3">
+        <v>8.5759200785433493E-6</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="B17" s="3">
-        <v>6.8823809369989702E-3</v>
-      </c>
-      <c r="C17" s="3">
-        <v>2.9753483553440498E-6</v>
-      </c>
-      <c r="D17" s="3">
-        <v>-6.9696922151638896E-6</v>
-      </c>
-      <c r="E17" s="3">
-        <v>7.8818250748758297E-8</v>
-      </c>
-      <c r="F17" s="3">
-        <v>-1.28598471605231E-4</v>
-      </c>
-      <c r="G17" s="3">
-        <v>-6.6291409138536298E-10</v>
-      </c>
-      <c r="H17" s="3">
-        <v>3.1528826670931298E-8</v>
-      </c>
-      <c r="I17" s="3">
-        <v>-2.0035426825111801E-5</v>
-      </c>
-      <c r="J17" s="3">
-        <v>1.28157377023514E-4</v>
-      </c>
-      <c r="K17" s="3">
-        <v>1.2800878876395E-4</v>
-      </c>
-      <c r="L17" s="3">
-        <v>1.2813856128638499E-4</v>
-      </c>
-      <c r="M17" s="3">
-        <v>1.2822982475839699E-4</v>
-      </c>
-      <c r="N17" s="3">
-        <v>1.28185529936824E-4</v>
-      </c>
-      <c r="O17" s="3">
-        <v>1.28387798462399E-4</v>
-      </c>
-      <c r="P17" s="3">
-        <v>1.28288053350757E-4</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>1.2815557511586801E-4</v>
-      </c>
-      <c r="R17" s="3">
-        <v>2.32080654378979E-4</v>
-      </c>
-      <c r="S17" s="3">
-        <v>1.2807525024838501E-4</v>
-      </c>
-      <c r="T17" s="3">
-        <v>1.27809838639794E-4</v>
+    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B28" s="3">
+        <v>-10.6084327042271</v>
+      </c>
+      <c r="C28" s="3">
+        <v>-2.7998752126199601E-2</v>
+      </c>
+      <c r="D28" s="3">
+        <v>5.8856609363805299E-5</v>
+      </c>
+      <c r="E28" s="3">
+        <v>-5.5960630678884497E-7</v>
+      </c>
+      <c r="F28" s="3">
+        <v>1.0101186114218801E-3</v>
+      </c>
+      <c r="G28" s="3">
+        <v>-1.7119884677995299E-6</v>
+      </c>
+      <c r="H28" s="3">
+        <v>-9.9609670178794306E-8</v>
+      </c>
+      <c r="I28" s="3">
+        <v>-4.1624261082025998E-4</v>
+      </c>
+      <c r="J28" s="3">
+        <v>-2.38213687960778E-7</v>
+      </c>
+      <c r="K28" s="3">
+        <v>-1.13668757442359E-3</v>
+      </c>
+      <c r="L28" s="3">
+        <v>4.5476868020242098E-6</v>
+      </c>
+      <c r="M28" s="3">
+        <v>4.2850359803336201E-6</v>
+      </c>
+      <c r="N28" s="3">
+        <v>1.5811559315374198E-2</v>
+      </c>
+      <c r="O28" s="3">
+        <v>3.9990612529965E-4</v>
+      </c>
+      <c r="P28" s="3">
+        <v>4.8209162137823403E-5</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>5.7627705007456704E-4</v>
+      </c>
+      <c r="R28" s="3">
+        <v>9.4814081961460301E-5</v>
+      </c>
+      <c r="S28" s="3">
+        <v>3.7605886421803603E-4</v>
+      </c>
+      <c r="T28" s="3">
+        <v>1.34874783864406E-4</v>
+      </c>
+      <c r="U28" s="3">
+        <v>4.0746789479650198E-4</v>
+      </c>
+      <c r="V28" s="3">
+        <v>5.0942068467121303E-5</v>
+      </c>
+      <c r="W28" s="3">
+        <v>1.13680680694851E-2</v>
+      </c>
+      <c r="X28" s="3">
+        <v>5.6576407337050302E-5</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>7.624437791238E-4</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>1.3265384960738799E-4</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>1.0304112192745301</v>
+      </c>
+      <c r="AB28" s="3">
+        <v>1.83336115491247E-4</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>1916068.6111050099</v>
+      </c>
+      <c r="AD28" s="3">
+        <v>1.04417393733796E-4</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>2.2818452156688901E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B18" s="3">
-        <v>-1.56186443086244E-2</v>
-      </c>
-      <c r="C18" s="3">
-        <v>-4.3012352796894299E-5</v>
-      </c>
-      <c r="D18" s="3">
-        <v>1.3029580279298299E-5</v>
-      </c>
-      <c r="E18" s="3">
-        <v>1.5682050871755901E-8</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-1.15812272087677E-4</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-2.649256276039E-8</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-5.4401984672664301E-8</v>
-      </c>
-      <c r="I18" s="3">
-        <v>4.9436262853670103E-5</v>
-      </c>
-      <c r="J18" s="3">
-        <v>1.2850517839577201E-4</v>
-      </c>
-      <c r="K18" s="3">
-        <v>1.2806925814576499E-4</v>
-      </c>
-      <c r="L18" s="3">
-        <v>1.2847479183651601E-4</v>
-      </c>
-      <c r="M18" s="3">
-        <v>1.2871723215705601E-4</v>
-      </c>
-      <c r="N18" s="3">
-        <v>1.2851062493150799E-4</v>
-      </c>
-      <c r="O18" s="3">
-        <v>1.29171340856517E-4</v>
-      </c>
-      <c r="P18" s="3">
-        <v>1.28876243626055E-4</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>1.28557353679376E-4</v>
-      </c>
-      <c r="R18" s="3">
-        <v>1.2807525024838501E-4</v>
-      </c>
-      <c r="S18" s="3">
-        <v>1.9081121324572101E-4</v>
-      </c>
-      <c r="T18" s="3">
-        <v>1.2781627363187101E-4</v>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B29" s="3">
+        <v>1.7355003996953899E-2</v>
+      </c>
+      <c r="C29" s="3">
+        <v>-4.5599648325824797E-5</v>
+      </c>
+      <c r="D29" s="3">
+        <v>6.0364329442624597E-8</v>
+      </c>
+      <c r="E29" s="3">
+        <v>-8.0603069833631301E-10</v>
+      </c>
+      <c r="F29" s="3">
+        <v>1.38971764114735E-6</v>
+      </c>
+      <c r="G29" s="3">
+        <v>-2.38728256149929E-9</v>
+      </c>
+      <c r="H29" s="3">
+        <v>6.1800208495018004E-11</v>
+      </c>
+      <c r="I29" s="3">
+        <v>-6.1937828808712196E-6</v>
+      </c>
+      <c r="J29" s="3">
+        <v>8.9490495832072994E-9</v>
+      </c>
+      <c r="K29" s="3">
+        <v>-2.7588637946059201E-6</v>
+      </c>
+      <c r="L29" s="3">
+        <v>2.08158788748257E-8</v>
+      </c>
+      <c r="M29" s="3">
+        <v>3.1453763039611501E-8</v>
+      </c>
+      <c r="N29" s="3">
+        <v>2.1354969270057898E-5</v>
+      </c>
+      <c r="O29" s="3">
+        <v>1.0148492182875601E-6</v>
+      </c>
+      <c r="P29" s="3">
+        <v>8.9518303641746302E-8</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>9.54243449060503E-7</v>
+      </c>
+      <c r="R29" s="3">
+        <v>1.52395911667508E-7</v>
+      </c>
+      <c r="S29" s="3">
+        <v>6.1014253744220205E-7</v>
+      </c>
+      <c r="T29" s="3">
+        <v>2.06862585445913E-7</v>
+      </c>
+      <c r="U29" s="3">
+        <v>6.4871772972224199E-7</v>
+      </c>
+      <c r="V29" s="3">
+        <v>9.4391075617084197E-8</v>
+      </c>
+      <c r="W29" s="3">
+        <v>1.8604867054813401E-5</v>
+      </c>
+      <c r="X29" s="3">
+        <v>1.4846901326516201E-6</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>1.9956415163245901E-6</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>2.5695133733992802E-6</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>5.6523492884616402E-5</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>3.1387210313176601E-6</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>1.04417393733796E-4</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>3.52589795475612E-6</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>1.1074340482789701E-5</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="B19" s="3">
-        <v>-1.07160697847995E-2</v>
-      </c>
-      <c r="C19" s="3">
-        <v>3.7008445852146098E-5</v>
-      </c>
-      <c r="D19" s="3">
-        <v>1.42629557258721E-5</v>
-      </c>
-      <c r="E19" s="3">
-        <v>-2.5143497513425999E-8</v>
-      </c>
-      <c r="F19" s="3">
-        <v>-1.3430966264520999E-4</v>
-      </c>
-      <c r="G19" s="3">
-        <v>2.5363953227354399E-8</v>
-      </c>
-      <c r="H19" s="3">
-        <v>-1.12458184845013E-7</v>
-      </c>
-      <c r="I19" s="3">
-        <v>-8.6720788823514795E-6</v>
-      </c>
-      <c r="J19" s="3">
-        <v>1.2823071191081999E-4</v>
-      </c>
-      <c r="K19" s="3">
-        <v>1.2837966944789301E-4</v>
-      </c>
-      <c r="L19" s="3">
-        <v>1.2804314241824901E-4</v>
-      </c>
-      <c r="M19" s="3">
-        <v>1.2797977117152899E-4</v>
-      </c>
-      <c r="N19" s="3">
-        <v>1.2806928906562701E-4</v>
-      </c>
-      <c r="O19" s="3">
-        <v>1.2725999699466701E-4</v>
-      </c>
-      <c r="P19" s="3">
-        <v>1.28239416372725E-4</v>
-      </c>
-      <c r="Q19" s="3">
-        <v>1.2823405924706699E-4</v>
-      </c>
-      <c r="R19" s="3">
-        <v>1.27809838639794E-4</v>
-      </c>
-      <c r="S19" s="3">
-        <v>1.2781627363187101E-4</v>
-      </c>
-      <c r="T19" s="3">
-        <v>2.34453101567099E-4</v>
+    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B30" s="3">
+        <v>-0.145958808742086</v>
+      </c>
+      <c r="C30" s="3">
+        <v>-2.2330706184271899E-3</v>
+      </c>
+      <c r="D30" s="3">
+        <v>4.3812634503501296E-6</v>
+      </c>
+      <c r="E30" s="3">
+        <v>1.55477749858987E-10</v>
+      </c>
+      <c r="F30" s="3">
+        <v>8.1497248508666505E-6</v>
+      </c>
+      <c r="G30" s="3">
+        <v>-4.2281946664544297E-9</v>
+      </c>
+      <c r="H30" s="3">
+        <v>-3.4521369531308798E-8</v>
+      </c>
+      <c r="I30" s="3">
+        <v>3.96136649828362E-5</v>
+      </c>
+      <c r="J30" s="3">
+        <v>-2.49820286317083E-7</v>
+      </c>
+      <c r="K30" s="3">
+        <v>3.2304296443269002E-5</v>
+      </c>
+      <c r="L30" s="3">
+        <v>1.0551011155236501E-8</v>
+      </c>
+      <c r="M30" s="3">
+        <v>-1.5113910206191199E-8</v>
+      </c>
+      <c r="N30" s="3">
+        <v>-1.7818291051150901E-5</v>
+      </c>
+      <c r="O30" s="3">
+        <v>3.3219196627751998E-5</v>
+      </c>
+      <c r="P30" s="3">
+        <v>7.2427379996700101E-7</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>4.2266834945770703E-5</v>
+      </c>
+      <c r="R30" s="3">
+        <v>1.8904408457533699E-6</v>
+      </c>
+      <c r="S30" s="3">
+        <v>2.3811754538130601E-5</v>
+      </c>
+      <c r="T30" s="3">
+        <v>2.47460032621245E-6</v>
+      </c>
+      <c r="U30" s="3">
+        <v>2.3294289001235301E-5</v>
+      </c>
+      <c r="V30" s="3">
+        <v>3.1230377465330602E-6</v>
+      </c>
+      <c r="W30" s="3">
+        <v>9.9045831466263909E-4</v>
+      </c>
+      <c r="X30" s="3">
+        <v>1.94750503173308E-6</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>5.9539551208076402E-5</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>6.0782956779033998E-6</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>1.9575599343321999E-3</v>
+      </c>
+      <c r="AB30" s="3">
+        <v>8.5759200785433493E-6</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>2.2818452156688901E-3</v>
+      </c>
+      <c r="AD30" s="3">
+        <v>1.1074340482789701E-5</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>3.91235661825894E-2</v>
       </c>
     </row>
   </sheetData>
@@ -64494,15 +66157,14 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DFE8567-67A3-41A3-9804-ADC448CEC0EA}">
-  <dimension ref="A1:T19"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC885E71-EA21-464C-BF5E-AB7813186B3F}">
+  <dimension ref="A1:AE30"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.140625" style="3" customWidth="1"/>
-    <col min="2" max="16384" width="11.42578125" style="3"/>
+    <col min="1" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -64513,1171 +66175,2843 @@
         <v>28</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>2</v>
+        <v>210</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>3</v>
+        <v>211</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="K1" s="3" t="s">
+      <c r="N1" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="Z1" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="AA1" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="AB1" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="AC1" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="AD1" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="AE1" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="L1" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>222</v>
-      </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B2" s="3">
-        <v>-4.0410153827671103</v>
+        <v>-1.0073555552515301</v>
       </c>
       <c r="C2" s="3">
-        <v>0.21581828600289299</v>
+        <v>2.9856881717883501E-2</v>
       </c>
       <c r="D2" s="3">
-        <v>-3.6000664365707898E-3</v>
+        <v>-5.8994148035503802E-5</v>
       </c>
       <c r="E2" s="3">
-        <v>1.7992908634939001E-5</v>
+        <v>5.7386565427299501E-8</v>
       </c>
       <c r="F2" s="3">
-        <v>-9.4737634710239304E-4</v>
+        <v>-2.0510879438839099E-4</v>
       </c>
       <c r="G2" s="3">
-        <v>4.6046051895759601E-7</v>
+        <v>2.32207103902407E-7</v>
       </c>
       <c r="H2" s="3">
-        <v>1.03941423048226E-5</v>
+        <v>4.2627333639507602E-7</v>
       </c>
       <c r="I2" s="3">
-        <v>-6.9841930969792099E-4</v>
+        <v>-1.9450413424968002E-5</v>
       </c>
       <c r="J2" s="3">
-        <v>-1.9951459761529201E-5</v>
+        <v>-5.7012562247928403E-9</v>
       </c>
       <c r="K2" s="3">
-        <v>-1.56280416303169E-5</v>
+        <v>5.4792089090609801E-5</v>
       </c>
       <c r="L2" s="3">
-        <v>-1.6085496742759701E-5</v>
+        <v>-2.2681141620312401E-7</v>
       </c>
       <c r="M2" s="3">
-        <v>-1.6810972813864102E-5</v>
+        <v>1.3345356051517001E-7</v>
       </c>
       <c r="N2" s="3">
-        <v>2.8045648463842E-5</v>
+        <v>-1.45976076676486E-3</v>
       </c>
       <c r="O2" s="3">
-        <v>-1.69121915246763E-4</v>
+        <v>-4.4239560392802401E-4</v>
       </c>
       <c r="P2" s="3">
-        <v>-3.7489818026374599E-6</v>
+        <v>-1.38273208057125E-5</v>
       </c>
       <c r="Q2" s="3">
-        <v>5.7103493780468003E-5</v>
+        <v>-5.7002713262109203E-4</v>
       </c>
       <c r="R2" s="3">
-        <v>2.9753483553440498E-6</v>
+        <v>-3.2806140748527603E-5</v>
       </c>
       <c r="S2" s="3">
-        <v>-4.3012352796894299E-5</v>
+        <v>-3.2657794885813701E-4</v>
       </c>
       <c r="T2" s="3">
-        <v>3.7008445852146098E-5</v>
+        <v>-4.4083097124947101E-5</v>
+      </c>
+      <c r="U2" s="3">
+        <v>-3.2367230722205498E-4</v>
+      </c>
+      <c r="V2" s="3">
+        <v>-4.3004050441810102E-5</v>
+      </c>
+      <c r="W2" s="3">
+        <v>-1.3131505351304499E-2</v>
+      </c>
+      <c r="X2" s="3">
+        <v>-4.98718667466059E-6</v>
+      </c>
+      <c r="Y2" s="3">
+        <v>-7.4770951320942802E-4</v>
+      </c>
+      <c r="Z2" s="3">
+        <v>-3.37532068332918E-5</v>
+      </c>
+      <c r="AA2" s="3">
+        <v>-2.6582967533709399E-2</v>
+      </c>
+      <c r="AB2" s="3">
+        <v>-4.7165081493678701E-5</v>
+      </c>
+      <c r="AC2" s="3">
+        <v>-2.7998752126199601E-2</v>
+      </c>
+      <c r="AD2" s="3">
+        <v>-4.5599648325824797E-5</v>
+      </c>
+      <c r="AE2" s="3">
+        <v>-2.2330706184271899E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>2</v>
+        <v>210</v>
       </c>
       <c r="B3" s="3">
-        <v>-0.14537907813996001</v>
+        <v>1.23361213363856E-2</v>
       </c>
       <c r="C3" s="3">
-        <v>-3.6000664365707898E-3</v>
+        <v>-5.8994148035503802E-5</v>
       </c>
       <c r="D3" s="3">
-        <v>4.37059910039388E-3</v>
+        <v>2.0618273889906101E-3</v>
       </c>
       <c r="E3" s="3">
-        <v>-1.96417855377994E-5</v>
+        <v>-5.6033360392489203E-6</v>
       </c>
       <c r="F3" s="3">
-        <v>1.44751455474659E-3</v>
+        <v>1.6703013930095499E-3</v>
       </c>
       <c r="G3" s="3">
-        <v>-3.0367310729731402E-6</v>
+        <v>-5.0389905385463597E-6</v>
       </c>
       <c r="H3" s="3">
-        <v>-2.20678822207496E-5</v>
+        <v>-1.2730687267039199E-5</v>
       </c>
       <c r="I3" s="3">
-        <v>-2.12410488986844E-4</v>
+        <v>-2.06160105552984E-3</v>
       </c>
       <c r="J3" s="3">
-        <v>6.1214312387262998E-6</v>
+        <v>5.6033032571383701E-6</v>
       </c>
       <c r="K3" s="3">
-        <v>8.6132197989848994E-6</v>
+        <v>-1.66963385651895E-3</v>
       </c>
       <c r="L3" s="3">
-        <v>2.2536356875863299E-5</v>
+        <v>5.0383735027121401E-6</v>
       </c>
       <c r="M3" s="3">
-        <v>1.81868866518548E-5</v>
+        <v>1.2728986499007001E-5</v>
       </c>
       <c r="N3" s="3">
-        <v>-9.3509941745020897E-7</v>
+        <v>7.7905118409062795E-6</v>
       </c>
       <c r="O3" s="3">
-        <v>4.96156039309976E-6</v>
+        <v>-1.3099796384693701E-8</v>
       </c>
       <c r="P3" s="3">
-        <v>3.0444920369570299E-5</v>
+        <v>8.8767747496532897E-8</v>
       </c>
       <c r="Q3" s="3">
-        <v>1.42405086502582E-5</v>
+        <v>-5.5865571930154203E-6</v>
       </c>
       <c r="R3" s="3">
-        <v>-6.9696922151638896E-6</v>
+        <v>1.2827442790502899E-7</v>
       </c>
       <c r="S3" s="3">
-        <v>1.3029580279298299E-5</v>
+        <v>-5.7799354375200503E-6</v>
       </c>
       <c r="T3" s="3">
-        <v>1.42629557258721E-5</v>
+        <v>-1.1773492092786599E-6</v>
+      </c>
+      <c r="U3" s="3">
+        <v>-3.9686892538799602E-6</v>
+      </c>
+      <c r="V3" s="3">
+        <v>-3.37284148752009E-6</v>
+      </c>
+      <c r="W3" s="3">
+        <v>2.2205913617525199E-4</v>
+      </c>
+      <c r="X3" s="3">
+        <v>-3.7473548779964399E-8</v>
+      </c>
+      <c r="Y3" s="3">
+        <v>1.41243484717148E-6</v>
+      </c>
+      <c r="Z3" s="3">
+        <v>4.6697030234485799E-8</v>
+      </c>
+      <c r="AA3" s="3">
+        <v>5.4139270552216797E-5</v>
+      </c>
+      <c r="AB3" s="3">
+        <v>8.9180820089915702E-8</v>
+      </c>
+      <c r="AC3" s="3">
+        <v>5.8856609363805299E-5</v>
+      </c>
+      <c r="AD3" s="3">
+        <v>6.0364329442624597E-8</v>
+      </c>
+      <c r="AE3" s="3">
+        <v>4.3812634503501296E-6</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>3</v>
+        <v>211</v>
       </c>
       <c r="B4" s="3">
-        <v>4.2860594032363897E-4</v>
+        <v>-9.85002475685855E-5</v>
       </c>
       <c r="C4" s="3">
-        <v>1.7992908634939001E-5</v>
+        <v>5.7386565427299501E-8</v>
       </c>
       <c r="D4" s="3">
-        <v>-1.96417855377994E-5</v>
+        <v>-5.6033360392489203E-6</v>
       </c>
       <c r="E4" s="3">
-        <v>1.0460874449851E-7</v>
+        <v>2.4048571711024799E-8</v>
       </c>
       <c r="F4" s="3">
-        <v>-6.2739541160480204E-6</v>
+        <v>-3.93022265644805E-6</v>
       </c>
       <c r="G4" s="3">
-        <v>1.26134153255488E-8</v>
+        <v>1.0919523456037499E-8</v>
       </c>
       <c r="H4" s="3">
-        <v>9.3244115645968599E-8</v>
+        <v>2.89037012688621E-8</v>
       </c>
       <c r="I4" s="3">
-        <v>-1.67647453075414E-6</v>
+        <v>5.6158890554165002E-6</v>
       </c>
       <c r="J4" s="3">
-        <v>8.4998118401502599E-8</v>
+        <v>-2.4037970488982201E-8</v>
       </c>
       <c r="K4" s="3">
-        <v>3.23626215977667E-8</v>
+        <v>3.8888376684996798E-6</v>
       </c>
       <c r="L4" s="3">
-        <v>3.4279766294984102E-9</v>
+        <v>-1.08547654697684E-8</v>
       </c>
       <c r="M4" s="3">
-        <v>5.00464040914354E-8</v>
+        <v>-2.9015396737953202E-8</v>
       </c>
       <c r="N4" s="3">
-        <v>1.26981749798527E-7</v>
+        <v>-8.42224261010507E-7</v>
       </c>
       <c r="O4" s="3">
-        <v>6.7466998015694194E-8</v>
+        <v>-1.5768931082986501E-9</v>
       </c>
       <c r="P4" s="3">
-        <v>2.9257034913650999E-8</v>
+        <v>1.2794883453042E-8</v>
       </c>
       <c r="Q4" s="3">
-        <v>7.8520358290831098E-8</v>
+        <v>1.7855419920635701E-8</v>
       </c>
       <c r="R4" s="3">
-        <v>7.8818250748758297E-8</v>
+        <v>1.99766442914547E-8</v>
       </c>
       <c r="S4" s="3">
-        <v>1.5682050871755901E-8</v>
+        <v>2.32256623767341E-8</v>
       </c>
       <c r="T4" s="3">
-        <v>-2.5143497513425999E-8</v>
+        <v>1.47597078118045E-8</v>
+      </c>
+      <c r="U4" s="3">
+        <v>1.07615780554663E-8</v>
+      </c>
+      <c r="V4" s="3">
+        <v>6.8335268027798396E-9</v>
+      </c>
+      <c r="W4" s="3">
+        <v>-1.4392591456924201E-6</v>
+      </c>
+      <c r="X4" s="3">
+        <v>-2.3475894752501299E-9</v>
+      </c>
+      <c r="Y4" s="3">
+        <v>-4.6272621780540504E-9</v>
+      </c>
+      <c r="Z4" s="3">
+        <v>-4.0507049891447397E-9</v>
+      </c>
+      <c r="AA4" s="3">
+        <v>-3.2418727783093902E-7</v>
+      </c>
+      <c r="AB4" s="3">
+        <v>-5.7142343693600102E-9</v>
+      </c>
+      <c r="AC4" s="3">
+        <v>-5.5960630678884497E-7</v>
+      </c>
+      <c r="AD4" s="3">
+        <v>-8.0603069833631301E-10</v>
+      </c>
+      <c r="AE4" s="3">
+        <v>1.55477749858987E-10</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3">
+        <v>8.5664508032301606E-2</v>
+      </c>
+      <c r="C5" s="3">
+        <v>-2.0510879438839099E-4</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1.6703013930095499E-3</v>
+      </c>
+      <c r="E5" s="3">
+        <v>-3.93022265644805E-6</v>
+      </c>
+      <c r="F5" s="3">
+        <v>2.1916298571871E-3</v>
+      </c>
+      <c r="G5" s="3">
+        <v>-6.85746585669935E-6</v>
+      </c>
+      <c r="H5" s="3">
+        <v>-1.07550805011178E-5</v>
+      </c>
+      <c r="I5" s="3">
+        <v>-1.6899105423629601E-3</v>
+      </c>
+      <c r="J5" s="3">
+        <v>3.9132371300900496E-6</v>
+      </c>
+      <c r="K5" s="3">
+        <v>-2.1239481131728301E-3</v>
+      </c>
+      <c r="L5" s="3">
+        <v>6.7523665847881301E-6</v>
+      </c>
+      <c r="M5" s="3">
+        <v>1.0930183137874E-5</v>
+      </c>
+      <c r="N5" s="3">
+        <v>1.3648730633539401E-3</v>
+      </c>
+      <c r="O5" s="3">
+        <v>2.0305308604558202E-6</v>
+      </c>
+      <c r="P5" s="3">
+        <v>-2.3901403872406398E-6</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>-7.7677387885546099E-6</v>
+      </c>
+      <c r="R5" s="3">
+        <v>1.51652690158799E-6</v>
+      </c>
+      <c r="S5" s="3">
+        <v>-2.7993631971185E-6</v>
+      </c>
+      <c r="T5" s="3">
+        <v>5.7273347152628699E-6</v>
+      </c>
+      <c r="U5" s="3">
+        <v>4.33079258177218E-6</v>
+      </c>
+      <c r="V5" s="3">
+        <v>1.2500867592743E-6</v>
+      </c>
+      <c r="W5" s="3">
+        <v>2.0962679688493001E-4</v>
+      </c>
+      <c r="X5" s="3">
+        <v>3.65862187673918E-6</v>
+      </c>
+      <c r="Y5" s="3">
+        <v>1.0080933112939599E-5</v>
+      </c>
+      <c r="Z5" s="3">
+        <v>6.5591850107535598E-6</v>
+      </c>
+      <c r="AA5" s="3">
+        <v>6.2344193356711302E-4</v>
+      </c>
+      <c r="AB5" s="3">
+        <v>9.3103839991541404E-6</v>
+      </c>
+      <c r="AC5" s="3">
+        <v>1.0101186114218801E-3</v>
+      </c>
+      <c r="AD5" s="3">
+        <v>1.38971764114735E-6</v>
+      </c>
+      <c r="AE5" s="3">
+        <v>8.1497248508666505E-6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3">
+        <v>-7.7383786237344803E-5</v>
+      </c>
+      <c r="C6" s="3">
+        <v>2.32207103902407E-7</v>
+      </c>
+      <c r="D6" s="3">
+        <v>-5.0389905385463597E-6</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1.0919523456037499E-8</v>
+      </c>
+      <c r="F6" s="3">
+        <v>-6.85746585669935E-6</v>
+      </c>
+      <c r="G6" s="3">
+        <v>2.1950280876478901E-8</v>
+      </c>
+      <c r="H6" s="3">
+        <v>3.35153263200716E-8</v>
+      </c>
+      <c r="I6" s="3">
+        <v>5.0754976343013002E-6</v>
+      </c>
+      <c r="J6" s="3">
+        <v>-1.08884644638723E-8</v>
+      </c>
+      <c r="K6" s="3">
+        <v>6.73467369315291E-6</v>
+      </c>
+      <c r="L6" s="3">
+        <v>-2.1758561176163999E-8</v>
+      </c>
+      <c r="M6" s="3">
+        <v>-3.3840560782707297E-8</v>
+      </c>
+      <c r="N6" s="3">
+        <v>-2.4887305256268201E-6</v>
+      </c>
+      <c r="O6" s="3">
+        <v>-3.2854750580198301E-9</v>
+      </c>
+      <c r="P6" s="3">
+        <v>1.6150131807205499E-8</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>3.7241227150176697E-8</v>
+      </c>
+      <c r="R6" s="3">
+        <v>1.02422739239568E-8</v>
+      </c>
+      <c r="S6" s="3">
+        <v>2.7873815411059302E-8</v>
+      </c>
+      <c r="T6" s="3">
+        <v>2.7910252330068198E-9</v>
+      </c>
+      <c r="U6" s="3">
+        <v>1.37649092255024E-8</v>
+      </c>
+      <c r="V6" s="3">
+        <v>8.9633571572751406E-9</v>
+      </c>
+      <c r="W6" s="3">
+        <v>6.2164446363434603E-8</v>
+      </c>
+      <c r="X6" s="3">
+        <v>-6.7816117227708904E-9</v>
+      </c>
+      <c r="Y6" s="3">
+        <v>-1.5014541176193999E-8</v>
+      </c>
+      <c r="Z6" s="3">
+        <v>-1.19142248251213E-8</v>
+      </c>
+      <c r="AA6" s="3">
+        <v>-1.01277183497874E-6</v>
+      </c>
+      <c r="AB6" s="3">
+        <v>-1.6868568583899298E-8</v>
+      </c>
+      <c r="AC6" s="3">
+        <v>-1.7119884677995299E-6</v>
+      </c>
+      <c r="AD6" s="3">
+        <v>-2.38728256149929E-9</v>
+      </c>
+      <c r="AE6" s="3">
+        <v>-4.2281946664544297E-9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3">
+        <v>5.5861475364458103E-5</v>
+      </c>
+      <c r="C7" s="3">
+        <v>4.2627333639507602E-7</v>
+      </c>
+      <c r="D7" s="3">
+        <v>-1.2730687267039199E-5</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2.89037012688621E-8</v>
+      </c>
+      <c r="F7" s="3">
+        <v>-1.07550805011178E-5</v>
+      </c>
+      <c r="G7" s="3">
+        <v>3.35153263200716E-8</v>
+      </c>
+      <c r="H7" s="3">
+        <v>8.4342195222668002E-8</v>
+      </c>
+      <c r="I7" s="3">
+        <v>1.2720708958473899E-5</v>
+      </c>
+      <c r="J7" s="3">
+        <v>-2.8910371809689999E-8</v>
+      </c>
+      <c r="K7" s="3">
+        <v>1.0776633131646701E-5</v>
+      </c>
+      <c r="L7" s="3">
+        <v>-3.3552400714094101E-8</v>
+      </c>
+      <c r="M7" s="3">
+        <v>-8.4255885474116597E-8</v>
+      </c>
+      <c r="N7" s="3">
+        <v>4.85171799704477E-7</v>
+      </c>
+      <c r="O7" s="3">
+        <v>1.4718208970971601E-9</v>
+      </c>
+      <c r="P7" s="3">
+        <v>-1.08912156633368E-8</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>2.11765600072742E-8</v>
+      </c>
+      <c r="R7" s="3">
+        <v>-2.1509396451579401E-8</v>
+      </c>
+      <c r="S7" s="3">
+        <v>1.7858979455248701E-8</v>
+      </c>
+      <c r="T7" s="3">
+        <v>-1.07598233820826E-8</v>
+      </c>
+      <c r="U7" s="3">
+        <v>1.5763048125408299E-8</v>
+      </c>
+      <c r="V7" s="3">
+        <v>1.0591673151090299E-8</v>
+      </c>
+      <c r="W7" s="3">
+        <v>-2.7545664026340501E-8</v>
+      </c>
+      <c r="X7" s="3">
+        <v>1.8410488850628699E-9</v>
+      </c>
+      <c r="Y7" s="3">
+        <v>-8.0628341323405592E-9</v>
+      </c>
+      <c r="Z7" s="3">
+        <v>2.2777434251636898E-9</v>
+      </c>
+      <c r="AA7" s="3">
+        <v>-2.1505393777460999E-7</v>
+      </c>
+      <c r="AB7" s="3">
+        <v>3.0206602250118798E-9</v>
+      </c>
+      <c r="AC7" s="3">
+        <v>-9.9609670178794306E-8</v>
+      </c>
+      <c r="AD7" s="3">
+        <v>6.1800208495018004E-11</v>
+      </c>
+      <c r="AE7" s="3">
+        <v>-3.4521369531308798E-8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B8" s="3">
+        <v>1.5674779902935899E-2</v>
+      </c>
+      <c r="C8" s="3">
+        <v>-1.9450413424968002E-5</v>
+      </c>
+      <c r="D8" s="3">
+        <v>-2.06160105552984E-3</v>
+      </c>
+      <c r="E8" s="3">
+        <v>5.6158890554165002E-6</v>
+      </c>
+      <c r="F8" s="3">
+        <v>-1.6899105423629601E-3</v>
+      </c>
+      <c r="G8" s="3">
+        <v>5.0754976343013002E-6</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1.2720708958473899E-5</v>
+      </c>
+      <c r="I8" s="3">
+        <v>4.0682581136420601E-3</v>
+      </c>
+      <c r="J8" s="3">
+        <v>-9.2610457276485895E-6</v>
+      </c>
+      <c r="K8" s="3">
+        <v>3.3314503288669802E-3</v>
+      </c>
+      <c r="L8" s="3">
+        <v>-1.0102331975707099E-5</v>
+      </c>
+      <c r="M8" s="3">
+        <v>-2.5822408089234501E-5</v>
+      </c>
+      <c r="N8" s="3">
+        <v>-3.60314256785438E-4</v>
+      </c>
+      <c r="O8" s="3">
+        <v>-1.0918987652906199E-7</v>
+      </c>
+      <c r="P8" s="3">
+        <v>-1.0221124129057E-6</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>5.9238585619971002E-6</v>
+      </c>
+      <c r="R8" s="3">
+        <v>-1.70294284882643E-6</v>
+      </c>
+      <c r="S8" s="3">
+        <v>4.8283917176307801E-6</v>
+      </c>
+      <c r="T8" s="3">
+        <v>-1.0869179829134801E-6</v>
+      </c>
+      <c r="U8" s="3">
+        <v>2.1773710138984202E-6</v>
+      </c>
+      <c r="V8" s="3">
+        <v>3.1564170494286799E-6</v>
+      </c>
+      <c r="W8" s="3">
+        <v>-1.6330136371509201E-4</v>
+      </c>
+      <c r="X8" s="3">
+        <v>4.8464491858741802E-6</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>-7.8366137303311205E-6</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>5.3127332084190401E-6</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>-4.5652088834934702E-4</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>3.0300240647553599E-7</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>-4.1624261082025998E-4</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>-6.1937828808712196E-6</v>
+      </c>
+      <c r="AE8" s="3">
+        <v>3.96136649828362E-5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1.9799246364819599E-6</v>
+      </c>
+      <c r="C9" s="3">
+        <v>-5.7012562247928403E-9</v>
+      </c>
+      <c r="D9" s="3">
+        <v>5.6033032571383701E-6</v>
+      </c>
+      <c r="E9" s="3">
+        <v>-2.4037970488982201E-8</v>
+      </c>
+      <c r="F9" s="3">
+        <v>3.9132371300900496E-6</v>
+      </c>
+      <c r="G9" s="3">
+        <v>-1.08884644638723E-8</v>
+      </c>
+      <c r="H9" s="3">
+        <v>-2.8910371809689999E-8</v>
+      </c>
+      <c r="I9" s="3">
+        <v>-9.2610457276485895E-6</v>
+      </c>
+      <c r="J9" s="3">
+        <v>3.7039295322054999E-8</v>
+      </c>
+      <c r="K9" s="3">
+        <v>-6.3868700491256098E-6</v>
+      </c>
+      <c r="L9" s="3">
+        <v>1.7578178552832399E-8</v>
+      </c>
+      <c r="M9" s="3">
+        <v>4.78439499748889E-8</v>
+      </c>
+      <c r="N9" s="3">
+        <v>5.4551901115884604E-7</v>
+      </c>
+      <c r="O9" s="3">
+        <v>-3.5846327869169501E-10</v>
+      </c>
+      <c r="P9" s="3">
+        <v>-1.36258977667542E-8</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>-1.9808713530690699E-8</v>
+      </c>
+      <c r="R9" s="3">
+        <v>-2.1409803017793801E-8</v>
+      </c>
+      <c r="S9" s="3">
+        <v>-2.5290579834443499E-8</v>
+      </c>
+      <c r="T9" s="3">
+        <v>-1.680557053617E-8</v>
+      </c>
+      <c r="U9" s="3">
+        <v>-1.3507741620132001E-8</v>
+      </c>
+      <c r="V9" s="3">
+        <v>-7.1843560648331799E-9</v>
+      </c>
+      <c r="W9" s="3">
+        <v>1.4366113284974601E-6</v>
+      </c>
+      <c r="X9" s="3">
+        <v>8.8624719149530201E-9</v>
+      </c>
+      <c r="Y9" s="3">
+        <v>2.39359101820782E-8</v>
+      </c>
+      <c r="Z9" s="3">
+        <v>1.6284997251971601E-8</v>
+      </c>
+      <c r="AA9" s="3">
+        <v>8.4304809464155598E-7</v>
+      </c>
+      <c r="AB9" s="3">
+        <v>1.6328844638368399E-8</v>
+      </c>
+      <c r="AC9" s="3">
+        <v>-2.38213687960778E-7</v>
+      </c>
+      <c r="AD9" s="3">
+        <v>8.9490495832072994E-9</v>
+      </c>
+      <c r="AE9" s="3">
+        <v>-2.49820286317083E-7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3">
-        <v>-4.04007740193267E-2</v>
-      </c>
-      <c r="C5" s="3">
-        <v>-9.4737634710239304E-4</v>
-      </c>
-      <c r="D5" s="3">
-        <v>1.44751455474659E-3</v>
-      </c>
-      <c r="E5" s="3">
-        <v>-6.2739541160480204E-6</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1.1618200264724499E-3</v>
-      </c>
-      <c r="G5" s="3">
-        <v>-2.8739050191418401E-6</v>
-      </c>
-      <c r="H5" s="3">
-        <v>-7.5835894890573899E-6</v>
-      </c>
-      <c r="I5" s="3">
-        <v>1.08148072343284E-3</v>
-      </c>
-      <c r="J5" s="3">
-        <v>-1.31449874069332E-4</v>
-      </c>
-      <c r="K5" s="3">
-        <v>-1.4110878557804701E-4</v>
-      </c>
-      <c r="L5" s="3">
-        <v>-1.16254410988808E-4</v>
-      </c>
-      <c r="M5" s="3">
-        <v>-1.1205120093657801E-4</v>
-      </c>
-      <c r="N5" s="3">
-        <v>-1.2246688883600201E-4</v>
-      </c>
-      <c r="O5" s="3">
-        <v>-1.16349003759329E-4</v>
-      </c>
-      <c r="P5" s="3">
-        <v>-1.12737357219583E-4</v>
-      </c>
-      <c r="Q5" s="3">
-        <v>-1.13525292221057E-4</v>
-      </c>
-      <c r="R5" s="3">
-        <v>-1.28598471605231E-4</v>
-      </c>
-      <c r="S5" s="3">
-        <v>-1.15812272087677E-4</v>
-      </c>
-      <c r="T5" s="3">
-        <v>-1.3430966264520999E-4</v>
+      <c r="B10" s="3">
+        <v>2.6758213703980401E-2</v>
+      </c>
+      <c r="C10" s="3">
+        <v>5.4792089090609801E-5</v>
+      </c>
+      <c r="D10" s="3">
+        <v>-1.66963385651895E-3</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3.8888376684996798E-6</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-2.1239481131728301E-3</v>
+      </c>
+      <c r="G10" s="3">
+        <v>6.73467369315291E-6</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1.0776633131646701E-5</v>
+      </c>
+      <c r="I10" s="3">
+        <v>3.3314503288669802E-3</v>
+      </c>
+      <c r="J10" s="3">
+        <v>-6.3868700491256098E-6</v>
+      </c>
+      <c r="K10" s="3">
+        <v>4.6108070650138101E-3</v>
+      </c>
+      <c r="L10" s="3">
+        <v>-1.47718493978646E-5</v>
+      </c>
+      <c r="M10" s="3">
+        <v>-2.20546317335719E-5</v>
+      </c>
+      <c r="N10" s="3">
+        <v>-1.80713894866647E-4</v>
+      </c>
+      <c r="O10" s="3">
+        <v>-1.88335156310336E-6</v>
+      </c>
+      <c r="P10" s="3">
+        <v>5.2792204415593798E-6</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>1.3969282250554E-5</v>
+      </c>
+      <c r="R10" s="3">
+        <v>3.8255747140326004E-6</v>
+      </c>
+      <c r="S10" s="3">
+        <v>1.00859771508938E-5</v>
+      </c>
+      <c r="T10" s="3">
+        <v>2.0783965526135399E-6</v>
+      </c>
+      <c r="U10" s="3">
+        <v>5.7277235040851903E-6</v>
+      </c>
+      <c r="V10" s="3">
+        <v>-2.0387022210041599E-7</v>
+      </c>
+      <c r="W10" s="3">
+        <v>-2.20139485419299E-4</v>
+      </c>
+      <c r="X10" s="3">
+        <v>-8.4216674854528906E-6</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>-2.9167573376397699E-5</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>-5.6181224798459203E-6</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>-1.4426314321205301E-3</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>-4.8313977370567103E-6</v>
+      </c>
+      <c r="AC10" s="3">
+        <v>-1.13668757442359E-3</v>
+      </c>
+      <c r="AD10" s="3">
+        <v>-2.7588637946059201E-6</v>
+      </c>
+      <c r="AE10" s="3">
+        <v>3.2304296443269002E-5</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3">
-        <v>1.4390902176363699E-4</v>
-      </c>
-      <c r="C6" s="3">
-        <v>4.6046051895759601E-7</v>
-      </c>
-      <c r="D6" s="3">
-        <v>-3.0367310729731402E-6</v>
-      </c>
-      <c r="E6" s="3">
-        <v>1.26134153255488E-8</v>
-      </c>
-      <c r="F6" s="3">
-        <v>-2.8739050191418401E-6</v>
-      </c>
-      <c r="G6" s="3">
-        <v>8.6486014744328504E-9</v>
-      </c>
-      <c r="H6" s="3">
-        <v>1.7276047392776699E-8</v>
-      </c>
-      <c r="I6" s="3">
-        <v>-2.3635878554329899E-6</v>
-      </c>
-      <c r="J6" s="3">
-        <v>1.8569949547692401E-8</v>
-      </c>
-      <c r="K6" s="3">
-        <v>4.9362830960052602E-8</v>
-      </c>
-      <c r="L6" s="3">
-        <v>-2.97719140735268E-8</v>
-      </c>
-      <c r="M6" s="3">
-        <v>-4.4378821342023198E-8</v>
-      </c>
-      <c r="N6" s="3">
-        <v>-1.84627955760693E-8</v>
-      </c>
-      <c r="O6" s="3">
-        <v>-1.95762401573888E-8</v>
-      </c>
-      <c r="P6" s="3">
-        <v>-3.6634297609672803E-8</v>
-      </c>
-      <c r="Q6" s="3">
-        <v>-4.5318350624731501E-8</v>
-      </c>
-      <c r="R6" s="3">
-        <v>-6.6291409138536298E-10</v>
-      </c>
-      <c r="S6" s="3">
-        <v>-2.649256276039E-8</v>
-      </c>
-      <c r="T6" s="3">
-        <v>2.5363953227354399E-8</v>
+      <c r="B11" s="3">
+        <v>-1.2273139232720301E-4</v>
+      </c>
+      <c r="C11" s="3">
+        <v>-2.2681141620312401E-7</v>
+      </c>
+      <c r="D11" s="3">
+        <v>5.0383735027121401E-6</v>
+      </c>
+      <c r="E11" s="3">
+        <v>-1.08547654697684E-8</v>
+      </c>
+      <c r="F11" s="3">
+        <v>6.7523665847881301E-6</v>
+      </c>
+      <c r="G11" s="3">
+        <v>-2.1758561176163999E-8</v>
+      </c>
+      <c r="H11" s="3">
+        <v>-3.3552400714094101E-8</v>
+      </c>
+      <c r="I11" s="3">
+        <v>-1.0102331975707099E-5</v>
+      </c>
+      <c r="J11" s="3">
+        <v>1.7578178552832399E-8</v>
+      </c>
+      <c r="K11" s="3">
+        <v>-1.47718493978646E-5</v>
+      </c>
+      <c r="L11" s="3">
+        <v>4.8079992001042799E-8</v>
+      </c>
+      <c r="M11" s="3">
+        <v>6.9020313175408906E-8</v>
+      </c>
+      <c r="N11" s="3">
+        <v>6.3347858642379704E-7</v>
+      </c>
+      <c r="O11" s="3">
+        <v>6.7171700757923099E-9</v>
+      </c>
+      <c r="P11" s="3">
+        <v>-2.0582819260719701E-8</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>-4.2577530733342301E-8</v>
+      </c>
+      <c r="R11" s="3">
+        <v>-1.8397198617289299E-8</v>
+      </c>
+      <c r="S11" s="3">
+        <v>-3.6814641556084201E-8</v>
+      </c>
+      <c r="T11" s="3">
+        <v>-1.47430468131336E-8</v>
+      </c>
+      <c r="U11" s="3">
+        <v>-2.7098997092493899E-8</v>
+      </c>
+      <c r="V11" s="3">
+        <v>-1.02694825328009E-8</v>
+      </c>
+      <c r="W11" s="3">
+        <v>5.6115990202953503E-8</v>
+      </c>
+      <c r="X11" s="3">
+        <v>2.9392240946629E-8</v>
+      </c>
+      <c r="Y11" s="3">
+        <v>8.9129318340567906E-8</v>
+      </c>
+      <c r="Z11" s="3">
+        <v>2.5466241507931901E-8</v>
+      </c>
+      <c r="AA11" s="3">
+        <v>4.9028998842065999E-6</v>
+      </c>
+      <c r="AB11" s="3">
+        <v>2.5602908621452001E-8</v>
+      </c>
+      <c r="AC11" s="3">
+        <v>4.5476868020242098E-6</v>
+      </c>
+      <c r="AD11" s="3">
+        <v>2.08158788748257E-8</v>
+      </c>
+      <c r="AE11" s="3">
+        <v>1.0551011155236501E-8</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="3">
-        <v>1.24602766933448E-3</v>
-      </c>
-      <c r="C7" s="3">
-        <v>1.03941423048226E-5</v>
-      </c>
-      <c r="D7" s="3">
-        <v>-2.20678822207496E-5</v>
-      </c>
-      <c r="E7" s="3">
-        <v>9.3244115645968599E-8</v>
-      </c>
-      <c r="F7" s="3">
-        <v>-7.5835894890573899E-6</v>
-      </c>
-      <c r="G7" s="3">
-        <v>1.7276047392776699E-8</v>
-      </c>
-      <c r="H7" s="3">
-        <v>1.2018761467241101E-7</v>
-      </c>
-      <c r="I7" s="3">
-        <v>2.4896603746977202E-6</v>
-      </c>
-      <c r="J7" s="3">
-        <v>-4.6649077666843097E-8</v>
-      </c>
-      <c r="K7" s="3">
-        <v>-5.4253202543022897E-8</v>
-      </c>
-      <c r="L7" s="3">
-        <v>-1.40962918782938E-7</v>
-      </c>
-      <c r="M7" s="3">
-        <v>-1.25313845761621E-7</v>
-      </c>
-      <c r="N7" s="3">
-        <v>-3.87969118862372E-8</v>
-      </c>
-      <c r="O7" s="3">
-        <v>7.1569427468724803E-8</v>
-      </c>
-      <c r="P7" s="3">
-        <v>-1.98445037526611E-7</v>
-      </c>
-      <c r="Q7" s="3">
-        <v>-1.50424457315999E-7</v>
-      </c>
-      <c r="R7" s="3">
-        <v>3.1528826670931298E-8</v>
-      </c>
-      <c r="S7" s="3">
-        <v>-5.4401984672664301E-8</v>
-      </c>
-      <c r="T7" s="3">
-        <v>-1.12458184845013E-7</v>
+      <c r="B12" s="3">
+        <v>-1.3829572049644501E-4</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1.3345356051517001E-7</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1.2728986499007001E-5</v>
+      </c>
+      <c r="E12" s="3">
+        <v>-2.9015396737953202E-8</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1.0930183137874E-5</v>
+      </c>
+      <c r="G12" s="3">
+        <v>-3.3840560782707297E-8</v>
+      </c>
+      <c r="H12" s="3">
+        <v>-8.4255885474116597E-8</v>
+      </c>
+      <c r="I12" s="3">
+        <v>-2.5822408089234501E-5</v>
+      </c>
+      <c r="J12" s="3">
+        <v>4.78439499748889E-8</v>
+      </c>
+      <c r="K12" s="3">
+        <v>-2.20546317335719E-5</v>
+      </c>
+      <c r="L12" s="3">
+        <v>6.9020313175408906E-8</v>
+      </c>
+      <c r="M12" s="3">
+        <v>1.75215649450174E-7</v>
+      </c>
+      <c r="N12" s="3">
+        <v>2.65238874080156E-6</v>
+      </c>
+      <c r="O12" s="3">
+        <v>1.23953466027715E-9</v>
+      </c>
+      <c r="P12" s="3">
+        <v>1.9219483819745199E-8</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>-2.1589330938787101E-8</v>
+      </c>
+      <c r="R12" s="3">
+        <v>3.5625296281652297E-8</v>
+      </c>
+      <c r="S12" s="3">
+        <v>-7.9312539776170302E-9</v>
+      </c>
+      <c r="T12" s="3">
+        <v>3.1054006457303099E-8</v>
+      </c>
+      <c r="U12" s="3">
+        <v>1.61208966174969E-9</v>
+      </c>
+      <c r="V12" s="3">
+        <v>-8.4887729327274501E-9</v>
+      </c>
+      <c r="W12" s="3">
+        <v>-4.33838734377108E-7</v>
+      </c>
+      <c r="X12" s="3">
+        <v>-4.7401609513606601E-8</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>2.7956348290028201E-8</v>
+      </c>
+      <c r="Z12" s="3">
+        <v>-6.15497249934948E-8</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>3.0354419539865501E-6</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>-2.3891852682965301E-8</v>
+      </c>
+      <c r="AC12" s="3">
+        <v>4.2850359803336201E-6</v>
+      </c>
+      <c r="AD12" s="3">
+        <v>3.1453763039611501E-8</v>
+      </c>
+      <c r="AE12" s="3">
+        <v>-1.5113910206191199E-8</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0.99572501928013102</v>
-      </c>
-      <c r="C8" s="3">
-        <v>-6.9841930969792099E-4</v>
-      </c>
-      <c r="D8" s="3">
-        <v>-2.12410488986844E-4</v>
-      </c>
-      <c r="E8" s="3">
-        <v>-1.67647453075414E-6</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1.08148072343284E-3</v>
-      </c>
-      <c r="G8" s="3">
-        <v>-2.3635878554329899E-6</v>
-      </c>
-      <c r="H8" s="3">
-        <v>2.4896603746977202E-6</v>
-      </c>
-      <c r="I8" s="3">
-        <v>1.60895116724665E-2</v>
-      </c>
-      <c r="J8" s="3">
-        <v>-4.6727534814555196E-6</v>
-      </c>
-      <c r="K8" s="3">
-        <v>-3.7158793142576402E-5</v>
-      </c>
-      <c r="L8" s="3">
-        <v>-1.3780982442612601E-5</v>
-      </c>
-      <c r="M8" s="3">
-        <v>5.1049345243527497E-6</v>
-      </c>
-      <c r="N8" s="3">
-        <v>6.2379790741545796E-6</v>
-      </c>
-      <c r="O8" s="3">
-        <v>1.7583205855964999E-5</v>
-      </c>
-      <c r="P8" s="3">
-        <v>-2.1144908080539602E-6</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>1.6718531950615899E-5</v>
-      </c>
-      <c r="R8" s="3">
-        <v>-2.0035426825111801E-5</v>
-      </c>
-      <c r="S8" s="3">
-        <v>4.9436262853670103E-5</v>
-      </c>
-      <c r="T8" s="3">
-        <v>-8.6720788823514795E-6</v>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B13" s="3">
+        <v>2.2705466677337101</v>
+      </c>
+      <c r="C13" s="3">
+        <v>-1.45976076676486E-3</v>
+      </c>
+      <c r="D13" s="3">
+        <v>7.7905118409062795E-6</v>
+      </c>
+      <c r="E13" s="3">
+        <v>-8.42224261010507E-7</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1.3648730633539401E-3</v>
+      </c>
+      <c r="G13" s="3">
+        <v>-2.4887305256268201E-6</v>
+      </c>
+      <c r="H13" s="3">
+        <v>4.85171799704477E-7</v>
+      </c>
+      <c r="I13" s="3">
+        <v>-3.60314256785438E-4</v>
+      </c>
+      <c r="J13" s="3">
+        <v>5.4551901115884604E-7</v>
+      </c>
+      <c r="K13" s="3">
+        <v>-1.80713894866647E-4</v>
+      </c>
+      <c r="L13" s="3">
+        <v>6.3347858642379704E-7</v>
+      </c>
+      <c r="M13" s="3">
+        <v>2.65238874080156E-6</v>
+      </c>
+      <c r="N13" s="3">
+        <v>2.4002318081982301E-2</v>
+      </c>
+      <c r="O13" s="3">
+        <v>6.7497504647905401E-6</v>
+      </c>
+      <c r="P13" s="3">
+        <v>5.9670896535975101E-5</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>9.7790571324122096E-5</v>
+      </c>
+      <c r="R13" s="3">
+        <v>1.08213961413623E-4</v>
+      </c>
+      <c r="S13" s="3">
+        <v>1.3215419949606899E-4</v>
+      </c>
+      <c r="T13" s="3">
+        <v>1.5757211478519399E-4</v>
+      </c>
+      <c r="U13" s="3">
+        <v>1.88510316173865E-4</v>
+      </c>
+      <c r="V13" s="3">
+        <v>2.0094480297840898E-5</v>
+      </c>
+      <c r="W13" s="3">
+        <v>-9.31251023493098E-4</v>
+      </c>
+      <c r="X13" s="3">
+        <v>6.4462625566343999E-5</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>1.2416583230065201E-4</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>1.13553584448123E-4</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>9.0860139493382005E-3</v>
+      </c>
+      <c r="AB13" s="3">
+        <v>1.61155868338051E-4</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>1.5811559315374198E-2</v>
+      </c>
+      <c r="AD13" s="3">
+        <v>2.1354969270057898E-5</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>-1.7818291051150901E-5</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="B9" s="3">
-        <v>-8.1972965338796E-3</v>
-      </c>
-      <c r="C9" s="3">
-        <v>-1.9951459761529201E-5</v>
-      </c>
-      <c r="D9" s="3">
-        <v>6.1214312387262998E-6</v>
-      </c>
-      <c r="E9" s="3">
-        <v>8.4998118401502599E-8</v>
-      </c>
-      <c r="F9" s="3">
-        <v>-1.31449874069332E-4</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1.8569949547692401E-8</v>
-      </c>
-      <c r="H9" s="3">
-        <v>-4.6649077666843097E-8</v>
-      </c>
-      <c r="I9" s="3">
-        <v>-4.6727534814555196E-6</v>
-      </c>
-      <c r="J9" s="3">
-        <v>1.8271885283959599E-4</v>
-      </c>
-      <c r="K9" s="3">
-        <v>1.2861587344386601E-4</v>
-      </c>
-      <c r="L9" s="3">
-        <v>1.28589387989384E-4</v>
-      </c>
-      <c r="M9" s="3">
-        <v>1.2874140956800799E-4</v>
-      </c>
-      <c r="N9" s="3">
-        <v>1.2867264665216999E-4</v>
-      </c>
-      <c r="O9" s="3">
-        <v>1.28798172267812E-4</v>
-      </c>
-      <c r="P9" s="3">
-        <v>1.2908218446648799E-4</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>1.2871086317220299E-4</v>
-      </c>
-      <c r="R9" s="3">
-        <v>1.28157377023514E-4</v>
-      </c>
-      <c r="S9" s="3">
-        <v>1.2850517839577201E-4</v>
-      </c>
-      <c r="T9" s="3">
-        <v>1.2823071191081999E-4</v>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B14" s="3">
+        <v>-1.35734328536476E-2</v>
+      </c>
+      <c r="C14" s="3">
+        <v>-4.4239560392802401E-4</v>
+      </c>
+      <c r="D14" s="3">
+        <v>-1.3099796384693701E-8</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-1.5768931082986501E-9</v>
+      </c>
+      <c r="F14" s="3">
+        <v>2.0305308604558202E-6</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-3.2854750580198301E-9</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1.4718208970971601E-9</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-1.0918987652906199E-7</v>
+      </c>
+      <c r="J14" s="3">
+        <v>-3.5846327869169501E-10</v>
+      </c>
+      <c r="K14" s="3">
+        <v>-1.88335156310336E-6</v>
+      </c>
+      <c r="L14" s="3">
+        <v>6.7171700757923099E-9</v>
+      </c>
+      <c r="M14" s="3">
+        <v>1.23953466027715E-9</v>
+      </c>
+      <c r="N14" s="3">
+        <v>6.7497504647905401E-6</v>
+      </c>
+      <c r="O14" s="3">
+        <v>1.5787346552941502E-5</v>
+      </c>
+      <c r="P14" s="3">
+        <v>7.2649059269395601E-7</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>9.1323982152296103E-6</v>
+      </c>
+      <c r="R14" s="3">
+        <v>8.6875804931833099E-7</v>
+      </c>
+      <c r="S14" s="3">
+        <v>5.2530493865776296E-6</v>
+      </c>
+      <c r="T14" s="3">
+        <v>9.5920177027588999E-7</v>
+      </c>
+      <c r="U14" s="3">
+        <v>5.1186424449172196E-6</v>
+      </c>
+      <c r="V14" s="3">
+        <v>1.0025458430046899E-6</v>
+      </c>
+      <c r="W14" s="3">
+        <v>1.90475354578235E-4</v>
+      </c>
+      <c r="X14" s="3">
+        <v>6.6498492243387699E-7</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>1.18894871016752E-5</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>8.7843892578780003E-7</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>3.8885890278582701E-4</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>9.816471018495259E-7</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>3.9990612529965E-4</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>1.0148492182875601E-6</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>3.3219196627751998E-5</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B15" s="3">
+        <v>-2.0050798941757802E-3</v>
+      </c>
+      <c r="C15" s="3">
+        <v>-1.38273208057125E-5</v>
+      </c>
+      <c r="D15" s="3">
+        <v>8.8767747496532897E-8</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1.2794883453042E-8</v>
+      </c>
+      <c r="F15" s="3">
+        <v>-2.3901403872406398E-6</v>
+      </c>
+      <c r="G15" s="3">
+        <v>1.6150131807205499E-8</v>
+      </c>
+      <c r="H15" s="3">
+        <v>-1.08912156633368E-8</v>
+      </c>
+      <c r="I15" s="3">
+        <v>-1.0221124129057E-6</v>
+      </c>
+      <c r="J15" s="3">
+        <v>-1.36258977667542E-8</v>
+      </c>
+      <c r="K15" s="3">
+        <v>5.2792204415593798E-6</v>
+      </c>
+      <c r="L15" s="3">
+        <v>-2.0582819260719701E-8</v>
+      </c>
+      <c r="M15" s="3">
+        <v>1.9219483819745199E-8</v>
+      </c>
+      <c r="N15" s="3">
+        <v>5.9670896535975101E-5</v>
+      </c>
+      <c r="O15" s="3">
+        <v>7.2649059269395601E-7</v>
+      </c>
+      <c r="P15" s="3">
+        <v>3.9905239920756798E-6</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>1.74371422187407E-6</v>
+      </c>
+      <c r="R15" s="3">
+        <v>1.8611587352190899E-6</v>
+      </c>
+      <c r="S15" s="3">
+        <v>1.9963008630753399E-6</v>
+      </c>
+      <c r="T15" s="3">
+        <v>2.0477484583210298E-6</v>
+      </c>
+      <c r="U15" s="3">
+        <v>2.20403362953372E-6</v>
+      </c>
+      <c r="V15" s="3">
+        <v>1.70850762373849E-6</v>
+      </c>
+      <c r="W15" s="3">
+        <v>1.3914505646704801E-5</v>
+      </c>
+      <c r="X15" s="3">
+        <v>1.9881954989842001E-7</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>6.1461366950348299E-7</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>3.1860895281410102E-7</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>3.1494834524757201E-5</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>4.3653847812177798E-7</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>4.8209162137823403E-5</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>8.9518303641746302E-8</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>7.2427379996700101E-7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B16" s="3">
+        <v>-2.2808771051673199E-2</v>
+      </c>
+      <c r="C16" s="3">
+        <v>-5.7002713262109203E-4</v>
+      </c>
+      <c r="D16" s="3">
+        <v>-5.5865571930154203E-6</v>
+      </c>
+      <c r="E16" s="3">
+        <v>1.7855419920635701E-8</v>
+      </c>
+      <c r="F16" s="3">
+        <v>-7.7677387885546099E-6</v>
+      </c>
+      <c r="G16" s="3">
+        <v>3.7241227150176697E-8</v>
+      </c>
+      <c r="H16" s="3">
+        <v>2.11765600072742E-8</v>
+      </c>
+      <c r="I16" s="3">
+        <v>5.9238585619971002E-6</v>
+      </c>
+      <c r="J16" s="3">
+        <v>-1.9808713530690699E-8</v>
+      </c>
+      <c r="K16" s="3">
+        <v>1.3969282250554E-5</v>
+      </c>
+      <c r="L16" s="3">
+        <v>-4.2577530733342301E-8</v>
+      </c>
+      <c r="M16" s="3">
+        <v>-2.1589330938787101E-8</v>
+      </c>
+      <c r="N16" s="3">
+        <v>9.7790571324122096E-5</v>
+      </c>
+      <c r="O16" s="3">
+        <v>9.1323982152296103E-6</v>
+      </c>
+      <c r="P16" s="3">
+        <v>1.74371422187407E-6</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>1.00898477309969E-4</v>
+      </c>
+      <c r="R16" s="3">
+        <v>2.2187747043785398E-6</v>
+      </c>
+      <c r="S16" s="3">
+        <v>8.0524148358984206E-6</v>
+      </c>
+      <c r="T16" s="3">
+        <v>2.5553660184364099E-6</v>
+      </c>
+      <c r="U16" s="3">
+        <v>8.0723356333049807E-6</v>
+      </c>
+      <c r="V16" s="3">
+        <v>2.0687690594699399E-6</v>
+      </c>
+      <c r="W16" s="3">
+        <v>2.4645639759330402E-4</v>
+      </c>
+      <c r="X16" s="3">
+        <v>3.3277008861697502E-7</v>
+      </c>
+      <c r="Y16" s="3">
+        <v>1.4599664530026599E-5</v>
+      </c>
+      <c r="Z16" s="3">
+        <v>1.0068060718133701E-6</v>
+      </c>
+      <c r="AA16" s="3">
+        <v>5.3025685080780203E-4</v>
+      </c>
+      <c r="AB16" s="3">
+        <v>1.3947852225007701E-6</v>
+      </c>
+      <c r="AC16" s="3">
+        <v>5.7627705007456704E-4</v>
+      </c>
+      <c r="AD16" s="3">
+        <v>9.54243449060503E-7</v>
+      </c>
+      <c r="AE16" s="3">
+        <v>4.2266834945770703E-5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B17" s="3">
+        <v>1.5803642417603601E-2</v>
+      </c>
+      <c r="C17" s="3">
+        <v>-3.2806140748527603E-5</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1.2827442790502899E-7</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1.99766442914547E-8</v>
+      </c>
+      <c r="F17" s="3">
+        <v>1.51652690158799E-6</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1.02422739239568E-8</v>
+      </c>
+      <c r="H17" s="3">
+        <v>-2.1509396451579401E-8</v>
+      </c>
+      <c r="I17" s="3">
+        <v>-1.70294284882643E-6</v>
+      </c>
+      <c r="J17" s="3">
+        <v>-2.1409803017793801E-8</v>
+      </c>
+      <c r="K17" s="3">
+        <v>3.8255747140326004E-6</v>
+      </c>
+      <c r="L17" s="3">
+        <v>-1.8397198617289299E-8</v>
+      </c>
+      <c r="M17" s="3">
+        <v>3.5625296281652297E-8</v>
+      </c>
+      <c r="N17" s="3">
+        <v>1.08213961413623E-4</v>
+      </c>
+      <c r="O17" s="3">
+        <v>8.6875804931833099E-7</v>
+      </c>
+      <c r="P17" s="3">
+        <v>1.8611587352190899E-6</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>2.2187747043785398E-6</v>
+      </c>
+      <c r="R17" s="3">
+        <v>3.0165964169052899E-6</v>
+      </c>
+      <c r="S17" s="3">
+        <v>2.83261234577191E-6</v>
+      </c>
+      <c r="T17" s="3">
+        <v>2.9383419141466999E-6</v>
+      </c>
+      <c r="U17" s="3">
+        <v>3.27033734169333E-6</v>
+      </c>
+      <c r="V17" s="3">
+        <v>2.4122779296801099E-6</v>
+      </c>
+      <c r="W17" s="3">
+        <v>3.1872630737884599E-5</v>
+      </c>
+      <c r="X17" s="3">
+        <v>3.22284399571829E-7</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>1.2539624543418201E-6</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>5.5740761552043E-7</v>
+      </c>
+      <c r="AA17" s="3">
+        <v>6.3887113516178601E-5</v>
+      </c>
+      <c r="AB17" s="3">
+        <v>7.78057907697776E-7</v>
+      </c>
+      <c r="AC17" s="3">
+        <v>9.4814081961460301E-5</v>
+      </c>
+      <c r="AD17" s="3">
+        <v>1.52395911667508E-7</v>
+      </c>
+      <c r="AE17" s="3">
+        <v>1.8904408457533699E-6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B18" s="3">
+        <v>9.9177244178018896E-3</v>
+      </c>
+      <c r="C18" s="3">
+        <v>-3.2657794885813701E-4</v>
+      </c>
+      <c r="D18" s="3">
+        <v>-5.7799354375200503E-6</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2.32256623767341E-8</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-2.7993631971185E-6</v>
+      </c>
+      <c r="G18" s="3">
+        <v>2.7873815411059302E-8</v>
+      </c>
+      <c r="H18" s="3">
+        <v>1.7858979455248701E-8</v>
+      </c>
+      <c r="I18" s="3">
+        <v>4.8283917176307801E-6</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-2.5290579834443499E-8</v>
+      </c>
+      <c r="K18" s="3">
+        <v>1.00859771508938E-5</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-3.6814641556084201E-8</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-7.9312539776170302E-9</v>
+      </c>
+      <c r="N18" s="3">
+        <v>1.3215419949606899E-4</v>
+      </c>
+      <c r="O18" s="3">
+        <v>5.2530493865776296E-6</v>
+      </c>
+      <c r="P18" s="3">
+        <v>1.9963008630753399E-6</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>8.0524148358984206E-6</v>
+      </c>
+      <c r="R18" s="3">
+        <v>2.83261234577191E-6</v>
+      </c>
+      <c r="S18" s="3">
+        <v>2.5105415915978999E-5</v>
+      </c>
+      <c r="T18" s="3">
+        <v>3.3850573630791099E-6</v>
+      </c>
+      <c r="U18" s="3">
+        <v>6.9411978985472099E-6</v>
+      </c>
+      <c r="V18" s="3">
+        <v>2.82136290694417E-6</v>
+      </c>
+      <c r="W18" s="3">
+        <v>1.58726801581819E-4</v>
+      </c>
+      <c r="X18" s="3">
+        <v>3.9961202020835003E-7</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>8.6494912281384898E-6</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>9.3611507080432402E-7</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>3.2856112513123599E-4</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>1.30724854001861E-6</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>3.7605886421803603E-4</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>6.1014253744220205E-7</v>
+      </c>
+      <c r="AE18" s="3">
+        <v>2.3811754538130601E-5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B19" s="3">
+        <v>2.2488293912465498E-2</v>
+      </c>
+      <c r="C19" s="3">
+        <v>-4.4083097124947101E-5</v>
+      </c>
+      <c r="D19" s="3">
+        <v>-1.1773492092786599E-6</v>
+      </c>
+      <c r="E19" s="3">
+        <v>1.47597078118045E-8</v>
+      </c>
+      <c r="F19" s="3">
+        <v>5.7273347152628699E-6</v>
+      </c>
+      <c r="G19" s="3">
+        <v>2.7910252330068198E-9</v>
+      </c>
+      <c r="H19" s="3">
+        <v>-1.07598233820826E-8</v>
+      </c>
+      <c r="I19" s="3">
+        <v>-1.0869179829134801E-6</v>
+      </c>
+      <c r="J19" s="3">
+        <v>-1.680557053617E-8</v>
+      </c>
+      <c r="K19" s="3">
+        <v>2.0783965526135399E-6</v>
+      </c>
+      <c r="L19" s="3">
+        <v>-1.47430468131336E-8</v>
+      </c>
+      <c r="M19" s="3">
+        <v>3.1054006457303099E-8</v>
+      </c>
+      <c r="N19" s="3">
+        <v>1.5757211478519399E-4</v>
+      </c>
+      <c r="O19" s="3">
+        <v>9.5920177027588999E-7</v>
+      </c>
+      <c r="P19" s="3">
+        <v>2.0477484583210298E-6</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>2.5553660184364099E-6</v>
+      </c>
+      <c r="R19" s="3">
+        <v>2.9383419141466999E-6</v>
+      </c>
+      <c r="S19" s="3">
+        <v>3.3850573630791099E-6</v>
+      </c>
+      <c r="T19" s="3">
+        <v>3.9077793697805003E-6</v>
+      </c>
+      <c r="U19" s="3">
+        <v>4.0249455424304601E-6</v>
+      </c>
+      <c r="V19" s="3">
+        <v>2.8510125047791102E-6</v>
+      </c>
+      <c r="W19" s="3">
+        <v>4.3420305045676701E-5</v>
+      </c>
+      <c r="X19" s="3">
+        <v>4.5197342012618002E-7</v>
+      </c>
+      <c r="Y19" s="3">
+        <v>1.7107070791313099E-6</v>
+      </c>
+      <c r="Z19" s="3">
+        <v>7.9613280323215095E-7</v>
+      </c>
+      <c r="AA19" s="3">
+        <v>8.9808522990028405E-5</v>
+      </c>
+      <c r="AB19" s="3">
+        <v>1.1179285224098299E-6</v>
+      </c>
+      <c r="AC19" s="3">
+        <v>1.34874783864406E-4</v>
+      </c>
+      <c r="AD19" s="3">
+        <v>2.06862585445913E-7</v>
+      </c>
+      <c r="AE19" s="3">
+        <v>2.47460032621245E-6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B20" s="3">
+        <v>1.28100266221424E-2</v>
+      </c>
+      <c r="C20" s="3">
+        <v>-3.2367230722205498E-4</v>
+      </c>
+      <c r="D20" s="3">
+        <v>-3.9686892538799602E-6</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1.07615780554663E-8</v>
+      </c>
+      <c r="F20" s="3">
+        <v>4.33079258177218E-6</v>
+      </c>
+      <c r="G20" s="3">
+        <v>1.37649092255024E-8</v>
+      </c>
+      <c r="H20" s="3">
+        <v>1.5763048125408299E-8</v>
+      </c>
+      <c r="I20" s="3">
+        <v>2.1773710138984202E-6</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-1.3507741620132001E-8</v>
+      </c>
+      <c r="K20" s="3">
+        <v>5.7277235040851903E-6</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-2.7098997092493899E-8</v>
+      </c>
+      <c r="M20" s="3">
+        <v>1.61208966174969E-9</v>
+      </c>
+      <c r="N20" s="3">
+        <v>1.88510316173865E-4</v>
+      </c>
+      <c r="O20" s="3">
+        <v>5.1186424449172196E-6</v>
+      </c>
+      <c r="P20" s="3">
+        <v>2.20403362953372E-6</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>8.0723356333049807E-6</v>
+      </c>
+      <c r="R20" s="3">
+        <v>3.27033734169333E-6</v>
+      </c>
+      <c r="S20" s="3">
+        <v>6.9411978985472099E-6</v>
+      </c>
+      <c r="T20" s="3">
+        <v>4.0249455424304601E-6</v>
+      </c>
+      <c r="U20" s="3">
+        <v>5.7135421380955798E-5</v>
+      </c>
+      <c r="V20" s="3">
+        <v>3.2426650992799402E-6</v>
+      </c>
+      <c r="W20" s="3">
+        <v>1.68120147784875E-4</v>
+      </c>
+      <c r="X20" s="3">
+        <v>5.4689304561624302E-7</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>8.7782861841766895E-6</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>1.1942906010439699E-6</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>3.4435782274324598E-4</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>1.67535851537749E-6</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>4.0746789479650198E-4</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>6.4871772972224199E-7</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>2.3294289001235301E-5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B21" s="3">
+        <v>1.7396586469329098E-2</v>
+      </c>
+      <c r="C21" s="3">
+        <v>-4.3004050441810102E-5</v>
+      </c>
+      <c r="D21" s="3">
+        <v>-3.37284148752009E-6</v>
+      </c>
+      <c r="E21" s="3">
+        <v>6.8335268027798396E-9</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1.2500867592743E-6</v>
+      </c>
+      <c r="G21" s="3">
+        <v>8.9633571572751406E-9</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1.0591673151090299E-8</v>
+      </c>
+      <c r="I21" s="3">
+        <v>3.1564170494286799E-6</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-7.1843560648331799E-9</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-2.0387022210041599E-7</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-1.02694825328009E-8</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-8.4887729327274501E-9</v>
+      </c>
+      <c r="N21" s="3">
+        <v>2.0094480297840898E-5</v>
+      </c>
+      <c r="O21" s="3">
+        <v>1.0025458430046899E-6</v>
+      </c>
+      <c r="P21" s="3">
+        <v>1.70850762373849E-6</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>2.0687690594699399E-6</v>
+      </c>
+      <c r="R21" s="3">
+        <v>2.4122779296801099E-6</v>
+      </c>
+      <c r="S21" s="3">
+        <v>2.82136290694417E-6</v>
+      </c>
+      <c r="T21" s="3">
+        <v>2.8510125047791102E-6</v>
+      </c>
+      <c r="U21" s="3">
+        <v>3.2426650992799402E-6</v>
+      </c>
+      <c r="V21" s="3">
+        <v>3.2318151967271399E-6</v>
+      </c>
+      <c r="W21" s="3">
+        <v>6.3758249088219094E-5</v>
+      </c>
+      <c r="X21" s="3">
+        <v>8.1226195860351397E-8</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>1.1781359996067501E-6</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>1.5103326048991601E-7</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>4.4134912942978601E-5</v>
+      </c>
+      <c r="AB21" s="3">
+        <v>2.0293873847977999E-7</v>
+      </c>
+      <c r="AC21" s="3">
+        <v>5.0942068467121303E-5</v>
+      </c>
+      <c r="AD21" s="3">
+        <v>9.4391075617084197E-8</v>
+      </c>
+      <c r="AE21" s="3">
+        <v>3.1230377465330602E-6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B22" s="3">
+        <v>-5.54366381774049</v>
+      </c>
+      <c r="C22" s="3">
+        <v>-1.3131505351304499E-2</v>
+      </c>
+      <c r="D22" s="3">
+        <v>2.2205913617525199E-4</v>
+      </c>
+      <c r="E22" s="3">
+        <v>-1.4392591456924201E-6</v>
+      </c>
+      <c r="F22" s="3">
+        <v>2.0962679688493001E-4</v>
+      </c>
+      <c r="G22" s="3">
+        <v>6.2164446363434603E-8</v>
+      </c>
+      <c r="H22" s="3">
+        <v>-2.7545664026340501E-8</v>
+      </c>
+      <c r="I22" s="3">
+        <v>-1.6330136371509201E-4</v>
+      </c>
+      <c r="J22" s="3">
+        <v>1.4366113284974601E-6</v>
+      </c>
+      <c r="K22" s="3">
+        <v>-2.20139485419299E-4</v>
+      </c>
+      <c r="L22" s="3">
+        <v>5.6115990202953503E-8</v>
+      </c>
+      <c r="M22" s="3">
+        <v>-4.33838734377108E-7</v>
+      </c>
+      <c r="N22" s="3">
+        <v>-9.31251023493098E-4</v>
+      </c>
+      <c r="O22" s="3">
+        <v>1.90475354578235E-4</v>
+      </c>
+      <c r="P22" s="3">
+        <v>1.3914505646704801E-5</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>2.4645639759330402E-4</v>
+      </c>
+      <c r="R22" s="3">
+        <v>3.1872630737884599E-5</v>
+      </c>
+      <c r="S22" s="3">
+        <v>1.58726801581819E-4</v>
+      </c>
+      <c r="T22" s="3">
+        <v>4.3420305045676701E-5</v>
+      </c>
+      <c r="U22" s="3">
+        <v>1.68120147784875E-4</v>
+      </c>
+      <c r="V22" s="3">
+        <v>6.3758249088219094E-5</v>
+      </c>
+      <c r="W22" s="3">
+        <v>180965.413391195</v>
+      </c>
+      <c r="X22" s="3">
+        <v>-2.3756800638668999E-6</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>3.2261829690493E-4</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>7.24192615771289E-6</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>1.11797997728235E-2</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>1.0090793471891E-5</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>1.13680680694851E-2</v>
+      </c>
+      <c r="AD22" s="3">
+        <v>1.8604867054813401E-5</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>9.9045831466263909E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B23" s="3">
+        <v>-1.53561020646784E-2</v>
+      </c>
+      <c r="C23" s="3">
+        <v>-4.98718667466059E-6</v>
+      </c>
+      <c r="D23" s="3">
+        <v>-3.7473548779964399E-8</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-2.3475894752501299E-9</v>
+      </c>
+      <c r="F23" s="3">
+        <v>3.65862187673918E-6</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-6.7816117227708904E-9</v>
+      </c>
+      <c r="H23" s="3">
+        <v>1.8410488850628699E-9</v>
+      </c>
+      <c r="I23" s="3">
+        <v>4.8464491858741802E-6</v>
+      </c>
+      <c r="J23" s="3">
+        <v>8.8624719149530201E-9</v>
+      </c>
+      <c r="K23" s="3">
+        <v>-8.4216674854528906E-6</v>
+      </c>
+      <c r="L23" s="3">
+        <v>2.9392240946629E-8</v>
+      </c>
+      <c r="M23" s="3">
+        <v>-4.7401609513606601E-8</v>
+      </c>
+      <c r="N23" s="3">
+        <v>6.4462625566343999E-5</v>
+      </c>
+      <c r="O23" s="3">
+        <v>6.6498492243387699E-7</v>
+      </c>
+      <c r="P23" s="3">
+        <v>1.9881954989842001E-7</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>3.3277008861697502E-7</v>
+      </c>
+      <c r="R23" s="3">
+        <v>3.22284399571829E-7</v>
+      </c>
+      <c r="S23" s="3">
+        <v>3.9961202020835003E-7</v>
+      </c>
+      <c r="T23" s="3">
+        <v>4.5197342012618002E-7</v>
+      </c>
+      <c r="U23" s="3">
+        <v>5.4689304561624302E-7</v>
+      </c>
+      <c r="V23" s="3">
+        <v>8.1226195860351397E-8</v>
+      </c>
+      <c r="W23" s="3">
+        <v>-2.3756800638668999E-6</v>
+      </c>
+      <c r="X23" s="3">
+        <v>1.11277617700828E-5</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>2.1923723492404899E-6</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>1.9927526473481899E-6</v>
+      </c>
+      <c r="AA23" s="3">
+        <v>4.1546726855648198E-5</v>
+      </c>
+      <c r="AB23" s="3">
+        <v>2.0383028853820201E-6</v>
+      </c>
+      <c r="AC23" s="3">
+        <v>5.6576407337050302E-5</v>
+      </c>
+      <c r="AD23" s="3">
+        <v>1.4846901326516201E-6</v>
+      </c>
+      <c r="AE23" s="3">
+        <v>1.94750503173308E-6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B24" s="3">
+        <v>-3.7360726666322598E-2</v>
+      </c>
+      <c r="C24" s="3">
+        <v>-7.4770951320942802E-4</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1.41243484717148E-6</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-4.6272621780540504E-9</v>
+      </c>
+      <c r="F24" s="3">
+        <v>1.0080933112939599E-5</v>
+      </c>
+      <c r="G24" s="3">
+        <v>-1.5014541176193999E-8</v>
+      </c>
+      <c r="H24" s="3">
+        <v>-8.0628341323405592E-9</v>
+      </c>
+      <c r="I24" s="3">
+        <v>-7.8366137303311205E-6</v>
+      </c>
+      <c r="J24" s="3">
+        <v>2.39359101820782E-8</v>
+      </c>
+      <c r="K24" s="3">
+        <v>-2.9167573376397699E-5</v>
+      </c>
+      <c r="L24" s="3">
+        <v>8.9129318340567906E-8</v>
+      </c>
+      <c r="M24" s="3">
+        <v>2.7956348290028201E-8</v>
+      </c>
+      <c r="N24" s="3">
+        <v>1.2416583230065201E-4</v>
+      </c>
+      <c r="O24" s="3">
+        <v>1.18894871016752E-5</v>
+      </c>
+      <c r="P24" s="3">
+        <v>6.1461366950348299E-7</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>1.4599664530026599E-5</v>
+      </c>
+      <c r="R24" s="3">
+        <v>1.2539624543418201E-6</v>
+      </c>
+      <c r="S24" s="3">
+        <v>8.6494912281384898E-6</v>
+      </c>
+      <c r="T24" s="3">
+        <v>1.7107070791313099E-6</v>
+      </c>
+      <c r="U24" s="3">
+        <v>8.7782861841766895E-6</v>
+      </c>
+      <c r="V24" s="3">
+        <v>1.1781359996067501E-6</v>
+      </c>
+      <c r="W24" s="3">
+        <v>3.2261829690493E-4</v>
+      </c>
+      <c r="X24" s="3">
+        <v>2.1923723492404899E-6</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>2.71122548519406E-4</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>2.5860546501435299E-6</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>7.2915130476653204E-4</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>2.8355353644538502E-6</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>7.624437791238E-4</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>1.9956415163245901E-6</v>
+      </c>
+      <c r="AE24" s="3">
+        <v>5.9539551208076402E-5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B25" s="3">
+        <v>3.57891790059023E-3</v>
+      </c>
+      <c r="C25" s="3">
+        <v>-3.37532068332918E-5</v>
+      </c>
+      <c r="D25" s="3">
+        <v>4.6697030234485799E-8</v>
+      </c>
+      <c r="E25" s="3">
+        <v>-4.0507049891447397E-9</v>
+      </c>
+      <c r="F25" s="3">
+        <v>6.5591850107535598E-6</v>
+      </c>
+      <c r="G25" s="3">
+        <v>-1.19142248251213E-8</v>
+      </c>
+      <c r="H25" s="3">
+        <v>2.2777434251636898E-9</v>
+      </c>
+      <c r="I25" s="3">
+        <v>5.3127332084190401E-6</v>
+      </c>
+      <c r="J25" s="3">
+        <v>1.6284997251971601E-8</v>
+      </c>
+      <c r="K25" s="3">
+        <v>-5.6181224798459203E-6</v>
+      </c>
+      <c r="L25" s="3">
+        <v>2.5466241507931901E-8</v>
+      </c>
+      <c r="M25" s="3">
+        <v>-6.15497249934948E-8</v>
+      </c>
+      <c r="N25" s="3">
+        <v>1.13553584448123E-4</v>
+      </c>
+      <c r="O25" s="3">
+        <v>8.7843892578780003E-7</v>
+      </c>
+      <c r="P25" s="3">
+        <v>3.1860895281410102E-7</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>1.0068060718133701E-6</v>
+      </c>
+      <c r="R25" s="3">
+        <v>5.5740761552043E-7</v>
+      </c>
+      <c r="S25" s="3">
+        <v>9.3611507080432402E-7</v>
+      </c>
+      <c r="T25" s="3">
+        <v>7.9613280323215095E-7</v>
+      </c>
+      <c r="U25" s="3">
+        <v>1.1942906010439699E-6</v>
+      </c>
+      <c r="V25" s="3">
+        <v>1.5103326048991601E-7</v>
+      </c>
+      <c r="W25" s="3">
+        <v>7.24192615771289E-6</v>
+      </c>
+      <c r="X25" s="3">
+        <v>1.9927526473481899E-6</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>2.5860546501435299E-6</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>4.82446404640032E-6</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>8.4675770933115806E-5</v>
+      </c>
+      <c r="AB25" s="3">
+        <v>3.2483271297367001E-6</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>1.3265384960738799E-4</v>
+      </c>
+      <c r="AD25" s="3">
+        <v>2.5695133733992802E-6</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>6.0782956779033998E-6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B26" s="3">
+        <v>-10.3024581492006</v>
+      </c>
+      <c r="C26" s="3">
+        <v>-2.6582967533709399E-2</v>
+      </c>
+      <c r="D26" s="3">
+        <v>5.4139270552216797E-5</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-3.2418727783093902E-7</v>
+      </c>
+      <c r="F26" s="3">
+        <v>6.2344193356711302E-4</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-1.01277183497874E-6</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-2.1505393777460999E-7</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-4.5652088834934702E-4</v>
+      </c>
+      <c r="J26" s="3">
+        <v>8.4304809464155598E-7</v>
+      </c>
+      <c r="K26" s="3">
+        <v>-1.4426314321205301E-3</v>
+      </c>
+      <c r="L26" s="3">
+        <v>4.9028998842065999E-6</v>
+      </c>
+      <c r="M26" s="3">
+        <v>3.0354419539865501E-6</v>
+      </c>
+      <c r="N26" s="3">
+        <v>9.0860139493382005E-3</v>
+      </c>
+      <c r="O26" s="3">
+        <v>3.8885890278582701E-4</v>
+      </c>
+      <c r="P26" s="3">
+        <v>3.1494834524757201E-5</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>5.3025685080780203E-4</v>
+      </c>
+      <c r="R26" s="3">
+        <v>6.3887113516178601E-5</v>
+      </c>
+      <c r="S26" s="3">
+        <v>3.2856112513123599E-4</v>
+      </c>
+      <c r="T26" s="3">
+        <v>8.9808522990028405E-5</v>
+      </c>
+      <c r="U26" s="3">
+        <v>3.4435782274324598E-4</v>
+      </c>
+      <c r="V26" s="3">
+        <v>4.4134912942978601E-5</v>
+      </c>
+      <c r="W26" s="3">
+        <v>1.11797997728235E-2</v>
+      </c>
+      <c r="X26" s="3">
+        <v>4.1546726855648198E-5</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>7.2915130476653204E-4</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>8.4675770933115806E-5</v>
+      </c>
+      <c r="AA26" s="3">
+        <v>856957.56080078403</v>
+      </c>
+      <c r="AB26" s="3">
+        <v>1.09604996617301E-4</v>
+      </c>
+      <c r="AC26" s="3">
+        <v>1.0304112192745301</v>
+      </c>
+      <c r="AD26" s="3">
+        <v>5.6523492884616402E-5</v>
+      </c>
+      <c r="AE26" s="3">
+        <v>1.9575599343321999E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B27" s="3">
+        <v>1.3622042802456401E-2</v>
+      </c>
+      <c r="C27" s="3">
+        <v>-4.7165081493678701E-5</v>
+      </c>
+      <c r="D27" s="3">
+        <v>8.9180820089915702E-8</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-5.7142343693600102E-9</v>
+      </c>
+      <c r="F27" s="3">
+        <v>9.3103839991541404E-6</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-1.6868568583899298E-8</v>
+      </c>
+      <c r="H27" s="3">
+        <v>3.0206602250118798E-9</v>
+      </c>
+      <c r="I27" s="3">
+        <v>3.0300240647553599E-7</v>
+      </c>
+      <c r="J27" s="3">
+        <v>1.6328844638368399E-8</v>
+      </c>
+      <c r="K27" s="3">
+        <v>-4.8313977370567103E-6</v>
+      </c>
+      <c r="L27" s="3">
+        <v>2.5602908621452001E-8</v>
+      </c>
+      <c r="M27" s="3">
+        <v>-2.3891852682965301E-8</v>
+      </c>
+      <c r="N27" s="3">
+        <v>1.61155868338051E-4</v>
+      </c>
+      <c r="O27" s="3">
+        <v>9.816471018495259E-7</v>
+      </c>
+      <c r="P27" s="3">
+        <v>4.3653847812177798E-7</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>1.3947852225007701E-6</v>
+      </c>
+      <c r="R27" s="3">
+        <v>7.78057907697776E-7</v>
+      </c>
+      <c r="S27" s="3">
+        <v>1.30724854001861E-6</v>
+      </c>
+      <c r="T27" s="3">
+        <v>1.1179285224098299E-6</v>
+      </c>
+      <c r="U27" s="3">
+        <v>1.67535851537749E-6</v>
+      </c>
+      <c r="V27" s="3">
+        <v>2.0293873847977999E-7</v>
+      </c>
+      <c r="W27" s="3">
+        <v>1.0090793471891E-5</v>
+      </c>
+      <c r="X27" s="3">
+        <v>2.0383028853820201E-6</v>
+      </c>
+      <c r="Y27" s="3">
+        <v>2.8355353644538502E-6</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>3.2483271297367001E-6</v>
+      </c>
+      <c r="AA27" s="3">
+        <v>1.09604996617301E-4</v>
+      </c>
+      <c r="AB27" s="3">
+        <v>4.8167789408419004E-6</v>
+      </c>
+      <c r="AC27" s="3">
+        <v>1.83336115491247E-4</v>
+      </c>
+      <c r="AD27" s="3">
+        <v>3.1387210313176601E-6</v>
+      </c>
+      <c r="AE27" s="3">
+        <v>8.5759200785433493E-6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B28" s="3">
+        <v>-10.6084327042271</v>
+      </c>
+      <c r="C28" s="3">
+        <v>-2.7998752126199601E-2</v>
+      </c>
+      <c r="D28" s="3">
+        <v>5.8856609363805299E-5</v>
+      </c>
+      <c r="E28" s="3">
+        <v>-5.5960630678884497E-7</v>
+      </c>
+      <c r="F28" s="3">
+        <v>1.0101186114218801E-3</v>
+      </c>
+      <c r="G28" s="3">
+        <v>-1.7119884677995299E-6</v>
+      </c>
+      <c r="H28" s="3">
+        <v>-9.9609670178794306E-8</v>
+      </c>
+      <c r="I28" s="3">
+        <v>-4.1624261082025998E-4</v>
+      </c>
+      <c r="J28" s="3">
+        <v>-2.38213687960778E-7</v>
+      </c>
+      <c r="K28" s="3">
+        <v>-1.13668757442359E-3</v>
+      </c>
+      <c r="L28" s="3">
+        <v>4.5476868020242098E-6</v>
+      </c>
+      <c r="M28" s="3">
+        <v>4.2850359803336201E-6</v>
+      </c>
+      <c r="N28" s="3">
+        <v>1.5811559315374198E-2</v>
+      </c>
+      <c r="O28" s="3">
+        <v>3.9990612529965E-4</v>
+      </c>
+      <c r="P28" s="3">
+        <v>4.8209162137823403E-5</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>5.7627705007456704E-4</v>
+      </c>
+      <c r="R28" s="3">
+        <v>9.4814081961460301E-5</v>
+      </c>
+      <c r="S28" s="3">
+        <v>3.7605886421803603E-4</v>
+      </c>
+      <c r="T28" s="3">
+        <v>1.34874783864406E-4</v>
+      </c>
+      <c r="U28" s="3">
+        <v>4.0746789479650198E-4</v>
+      </c>
+      <c r="V28" s="3">
+        <v>5.0942068467121303E-5</v>
+      </c>
+      <c r="W28" s="3">
+        <v>1.13680680694851E-2</v>
+      </c>
+      <c r="X28" s="3">
+        <v>5.6576407337050302E-5</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>7.624437791238E-4</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>1.3265384960738799E-4</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>1.0304112192745301</v>
+      </c>
+      <c r="AB28" s="3">
+        <v>1.83336115491247E-4</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>1916068.6111050099</v>
+      </c>
+      <c r="AD28" s="3">
+        <v>1.04417393733796E-4</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>2.2818452156688901E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B29" s="3">
+        <v>1.7355003996953899E-2</v>
+      </c>
+      <c r="C29" s="3">
+        <v>-4.5599648325824797E-5</v>
+      </c>
+      <c r="D29" s="3">
+        <v>6.0364329442624597E-8</v>
+      </c>
+      <c r="E29" s="3">
+        <v>-8.0603069833631301E-10</v>
+      </c>
+      <c r="F29" s="3">
+        <v>1.38971764114735E-6</v>
+      </c>
+      <c r="G29" s="3">
+        <v>-2.38728256149929E-9</v>
+      </c>
+      <c r="H29" s="3">
+        <v>6.1800208495018004E-11</v>
+      </c>
+      <c r="I29" s="3">
+        <v>-6.1937828808712196E-6</v>
+      </c>
+      <c r="J29" s="3">
+        <v>8.9490495832072994E-9</v>
+      </c>
+      <c r="K29" s="3">
+        <v>-2.7588637946059201E-6</v>
+      </c>
+      <c r="L29" s="3">
+        <v>2.08158788748257E-8</v>
+      </c>
+      <c r="M29" s="3">
+        <v>3.1453763039611501E-8</v>
+      </c>
+      <c r="N29" s="3">
+        <v>2.1354969270057898E-5</v>
+      </c>
+      <c r="O29" s="3">
+        <v>1.0148492182875601E-6</v>
+      </c>
+      <c r="P29" s="3">
+        <v>8.9518303641746302E-8</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>9.54243449060503E-7</v>
+      </c>
+      <c r="R29" s="3">
+        <v>1.52395911667508E-7</v>
+      </c>
+      <c r="S29" s="3">
+        <v>6.1014253744220205E-7</v>
+      </c>
+      <c r="T29" s="3">
+        <v>2.06862585445913E-7</v>
+      </c>
+      <c r="U29" s="3">
+        <v>6.4871772972224199E-7</v>
+      </c>
+      <c r="V29" s="3">
+        <v>9.4391075617084197E-8</v>
+      </c>
+      <c r="W29" s="3">
+        <v>1.8604867054813401E-5</v>
+      </c>
+      <c r="X29" s="3">
+        <v>1.4846901326516201E-6</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>1.9956415163245901E-6</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>2.5695133733992802E-6</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>5.6523492884616402E-5</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>3.1387210313176601E-6</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>1.04417393733796E-4</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>3.52589795475612E-6</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>1.1074340482789701E-5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="B10" s="3">
-        <v>-6.8212570985156198E-4</v>
-      </c>
-      <c r="C10" s="3">
-        <v>-1.56280416303169E-5</v>
-      </c>
-      <c r="D10" s="3">
-        <v>8.6132197989848994E-6</v>
-      </c>
-      <c r="E10" s="3">
-        <v>3.23626215977667E-8</v>
-      </c>
-      <c r="F10" s="3">
-        <v>-1.4110878557804701E-4</v>
-      </c>
-      <c r="G10" s="3">
-        <v>4.9362830960052602E-8</v>
-      </c>
-      <c r="H10" s="3">
-        <v>-5.4253202543022897E-8</v>
-      </c>
-      <c r="I10" s="3">
-        <v>-3.7158793142576402E-5</v>
-      </c>
-      <c r="J10" s="3">
-        <v>1.2861587344386601E-4</v>
-      </c>
-      <c r="K10" s="3">
-        <v>1.9429699234282E-4</v>
-      </c>
-      <c r="L10" s="3">
-        <v>1.28268875179628E-4</v>
-      </c>
-      <c r="M10" s="3">
-        <v>1.2823086318456201E-4</v>
-      </c>
-      <c r="N10" s="3">
-        <v>1.28263976140674E-4</v>
-      </c>
-      <c r="O10" s="3">
-        <v>1.2815158340243201E-4</v>
-      </c>
-      <c r="P10" s="3">
-        <v>1.2857424237435299E-4</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>1.2823793376952401E-4</v>
-      </c>
-      <c r="R10" s="3">
-        <v>1.2800878876395E-4</v>
-      </c>
-      <c r="S10" s="3">
-        <v>1.2806925814576499E-4</v>
-      </c>
-      <c r="T10" s="3">
-        <v>1.2837966944789301E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="B11" s="3">
-        <v>-4.4596424160110298E-4</v>
-      </c>
-      <c r="C11" s="3">
-        <v>-1.6085496742759701E-5</v>
-      </c>
-      <c r="D11" s="3">
-        <v>2.2536356875863299E-5</v>
-      </c>
-      <c r="E11" s="3">
-        <v>3.4279766294984102E-9</v>
-      </c>
-      <c r="F11" s="3">
-        <v>-1.16254410988808E-4</v>
-      </c>
-      <c r="G11" s="3">
-        <v>-2.97719140735268E-8</v>
-      </c>
-      <c r="H11" s="3">
-        <v>-1.40962918782938E-7</v>
-      </c>
-      <c r="I11" s="3">
-        <v>-1.3780982442612601E-5</v>
-      </c>
-      <c r="J11" s="3">
-        <v>1.28589387989384E-4</v>
-      </c>
-      <c r="K11" s="3">
-        <v>1.28268875179628E-4</v>
-      </c>
-      <c r="L11" s="3">
-        <v>2.19627493319524E-4</v>
-      </c>
-      <c r="M11" s="3">
-        <v>1.2884193331577599E-4</v>
-      </c>
-      <c r="N11" s="3">
-        <v>1.2863839335840199E-4</v>
-      </c>
-      <c r="O11" s="3">
-        <v>1.28716701703317E-4</v>
-      </c>
-      <c r="P11" s="3">
-        <v>1.2909668980630199E-4</v>
-      </c>
-      <c r="Q11" s="3">
-        <v>1.2881053694984901E-4</v>
-      </c>
-      <c r="R11" s="3">
-        <v>1.2813856128638499E-4</v>
-      </c>
-      <c r="S11" s="3">
-        <v>1.2847479183651601E-4</v>
-      </c>
-      <c r="T11" s="3">
-        <v>1.2804314241824901E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="B12" s="3">
-        <v>-5.4173523046E-3</v>
-      </c>
-      <c r="C12" s="3">
-        <v>-1.6810972813864102E-5</v>
-      </c>
-      <c r="D12" s="3">
-        <v>1.81868866518548E-5</v>
-      </c>
-      <c r="E12" s="3">
-        <v>5.00464040914354E-8</v>
-      </c>
-      <c r="F12" s="3">
-        <v>-1.1205120093657801E-4</v>
-      </c>
-      <c r="G12" s="3">
-        <v>-4.4378821342023198E-8</v>
-      </c>
-      <c r="H12" s="3">
-        <v>-1.25313845761621E-7</v>
-      </c>
-      <c r="I12" s="3">
-        <v>5.1049345243527497E-6</v>
-      </c>
-      <c r="J12" s="3">
-        <v>1.2874140956800799E-4</v>
-      </c>
-      <c r="K12" s="3">
-        <v>1.2823086318456201E-4</v>
-      </c>
-      <c r="L12" s="3">
-        <v>1.2884193331577599E-4</v>
-      </c>
-      <c r="M12" s="3">
-        <v>2.0167687277329699E-4</v>
-      </c>
-      <c r="N12" s="3">
-        <v>1.2889660150704901E-4</v>
-      </c>
-      <c r="O12" s="3">
-        <v>1.29047466392553E-4</v>
-      </c>
-      <c r="P12" s="3">
-        <v>1.29395492257354E-4</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>1.2910775674281099E-4</v>
-      </c>
-      <c r="R12" s="3">
-        <v>1.2822982475839699E-4</v>
-      </c>
-      <c r="S12" s="3">
-        <v>1.2871723215705601E-4</v>
-      </c>
-      <c r="T12" s="3">
-        <v>1.2797977117152899E-4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="B13" s="3">
-        <v>-8.3842014307038606E-3</v>
-      </c>
-      <c r="C13" s="3">
-        <v>2.8045648463842E-5</v>
-      </c>
-      <c r="D13" s="3">
-        <v>-9.3509941745020897E-7</v>
-      </c>
-      <c r="E13" s="3">
-        <v>1.26981749798527E-7</v>
-      </c>
-      <c r="F13" s="3">
-        <v>-1.2246688883600201E-4</v>
-      </c>
-      <c r="G13" s="3">
-        <v>-1.84627955760693E-8</v>
-      </c>
-      <c r="H13" s="3">
-        <v>-3.87969118862372E-8</v>
-      </c>
-      <c r="I13" s="3">
-        <v>6.2379790741545796E-6</v>
-      </c>
-      <c r="J13" s="3">
-        <v>1.2867264665216999E-4</v>
-      </c>
-      <c r="K13" s="3">
-        <v>1.28263976140674E-4</v>
-      </c>
-      <c r="L13" s="3">
-        <v>1.2863839335840199E-4</v>
-      </c>
-      <c r="M13" s="3">
-        <v>1.2889660150704901E-4</v>
-      </c>
-      <c r="N13" s="3">
-        <v>1.8497035979113499E-4</v>
-      </c>
-      <c r="O13" s="3">
-        <v>1.2861294772255899E-4</v>
-      </c>
-      <c r="P13" s="3">
-        <v>1.2912919417246599E-4</v>
-      </c>
-      <c r="Q13" s="3">
-        <v>1.2898803287014299E-4</v>
-      </c>
-      <c r="R13" s="3">
-        <v>1.28185529936824E-4</v>
-      </c>
-      <c r="S13" s="3">
-        <v>1.2851062493150799E-4</v>
-      </c>
-      <c r="T13" s="3">
-        <v>1.2806928906562701E-4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="B14" s="3">
-        <v>7.0813954923913802E-3</v>
-      </c>
-      <c r="C14" s="3">
-        <v>-1.69121915246763E-4</v>
-      </c>
-      <c r="D14" s="3">
-        <v>4.96156039309976E-6</v>
-      </c>
-      <c r="E14" s="3">
-        <v>6.7466998015694194E-8</v>
-      </c>
-      <c r="F14" s="3">
-        <v>-1.16349003759329E-4</v>
-      </c>
-      <c r="G14" s="3">
-        <v>-1.95762401573888E-8</v>
-      </c>
-      <c r="H14" s="3">
-        <v>7.1569427468724803E-8</v>
-      </c>
-      <c r="I14" s="3">
-        <v>1.7583205855964999E-5</v>
-      </c>
-      <c r="J14" s="3">
-        <v>1.28798172267812E-4</v>
-      </c>
-      <c r="K14" s="3">
-        <v>1.2815158340243201E-4</v>
-      </c>
-      <c r="L14" s="3">
-        <v>1.28716701703317E-4</v>
-      </c>
-      <c r="M14" s="3">
-        <v>1.29047466392553E-4</v>
-      </c>
-      <c r="N14" s="3">
-        <v>1.2861294772255899E-4</v>
-      </c>
-      <c r="O14" s="3">
-        <v>2.0162779045955801E-4</v>
-      </c>
-      <c r="P14" s="3">
-        <v>1.29149652459675E-4</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>1.2825370519533501E-4</v>
-      </c>
-      <c r="R14" s="3">
-        <v>1.28387798462399E-4</v>
-      </c>
-      <c r="S14" s="3">
-        <v>1.29171340856517E-4</v>
-      </c>
-      <c r="T14" s="3">
-        <v>1.2725999699466701E-4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="B15" s="3">
-        <v>-8.6466993167642007E-3</v>
-      </c>
-      <c r="C15" s="3">
-        <v>-3.7489818026374599E-6</v>
-      </c>
-      <c r="D15" s="3">
-        <v>3.0444920369570299E-5</v>
-      </c>
-      <c r="E15" s="3">
-        <v>2.9257034913650999E-8</v>
-      </c>
-      <c r="F15" s="3">
-        <v>-1.12737357219583E-4</v>
-      </c>
-      <c r="G15" s="3">
-        <v>-3.6634297609672803E-8</v>
-      </c>
-      <c r="H15" s="3">
-        <v>-1.98445037526611E-7</v>
-      </c>
-      <c r="I15" s="3">
-        <v>-2.1144908080539602E-6</v>
-      </c>
-      <c r="J15" s="3">
-        <v>1.2908218446648799E-4</v>
-      </c>
-      <c r="K15" s="3">
-        <v>1.2857424237435299E-4</v>
-      </c>
-      <c r="L15" s="3">
-        <v>1.2909668980630199E-4</v>
-      </c>
-      <c r="M15" s="3">
-        <v>1.29395492257354E-4</v>
-      </c>
-      <c r="N15" s="3">
-        <v>1.2912919417246599E-4</v>
-      </c>
-      <c r="O15" s="3">
-        <v>1.29149652459675E-4</v>
-      </c>
-      <c r="P15" s="3">
-        <v>1.6985912726237101E-4</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>1.2940122871540999E-4</v>
-      </c>
-      <c r="R15" s="3">
-        <v>1.28288053350757E-4</v>
-      </c>
-      <c r="S15" s="3">
-        <v>1.28876243626055E-4</v>
-      </c>
-      <c r="T15" s="3">
-        <v>1.28239416372725E-4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="B16" s="3">
-        <v>-1.52704841429614E-2</v>
-      </c>
-      <c r="C16" s="3">
-        <v>5.7103493780468003E-5</v>
-      </c>
-      <c r="D16" s="3">
-        <v>1.42405086502582E-5</v>
-      </c>
-      <c r="E16" s="3">
-        <v>7.8520358290831098E-8</v>
-      </c>
-      <c r="F16" s="3">
-        <v>-1.13525292221057E-4</v>
-      </c>
-      <c r="G16" s="3">
-        <v>-4.5318350624731501E-8</v>
-      </c>
-      <c r="H16" s="3">
-        <v>-1.50424457315999E-7</v>
-      </c>
-      <c r="I16" s="3">
-        <v>1.6718531950615899E-5</v>
-      </c>
-      <c r="J16" s="3">
-        <v>1.2871086317220299E-4</v>
-      </c>
-      <c r="K16" s="3">
-        <v>1.2823793376952401E-4</v>
-      </c>
-      <c r="L16" s="3">
-        <v>1.2881053694984901E-4</v>
-      </c>
-      <c r="M16" s="3">
-        <v>1.2910775674281099E-4</v>
-      </c>
-      <c r="N16" s="3">
-        <v>1.2898803287014299E-4</v>
-      </c>
-      <c r="O16" s="3">
-        <v>1.2825370519533501E-4</v>
-      </c>
-      <c r="P16" s="3">
-        <v>1.2940122871540999E-4</v>
-      </c>
-      <c r="Q16" s="3">
-        <v>1.9031549287813301E-4</v>
-      </c>
-      <c r="R16" s="3">
-        <v>1.2815557511586801E-4</v>
-      </c>
-      <c r="S16" s="3">
-        <v>1.28557353679376E-4</v>
-      </c>
-      <c r="T16" s="3">
-        <v>1.2823405924706699E-4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B17" s="3">
-        <v>6.8823809369989702E-3</v>
-      </c>
-      <c r="C17" s="3">
-        <v>2.9753483553440498E-6</v>
-      </c>
-      <c r="D17" s="3">
-        <v>-6.9696922151638896E-6</v>
-      </c>
-      <c r="E17" s="3">
-        <v>7.8818250748758297E-8</v>
-      </c>
-      <c r="F17" s="3">
-        <v>-1.28598471605231E-4</v>
-      </c>
-      <c r="G17" s="3">
-        <v>-6.6291409138536298E-10</v>
-      </c>
-      <c r="H17" s="3">
-        <v>3.1528826670931298E-8</v>
-      </c>
-      <c r="I17" s="3">
-        <v>-2.0035426825111801E-5</v>
-      </c>
-      <c r="J17" s="3">
-        <v>1.28157377023514E-4</v>
-      </c>
-      <c r="K17" s="3">
-        <v>1.2800878876395E-4</v>
-      </c>
-      <c r="L17" s="3">
-        <v>1.2813856128638499E-4</v>
-      </c>
-      <c r="M17" s="3">
-        <v>1.2822982475839699E-4</v>
-      </c>
-      <c r="N17" s="3">
-        <v>1.28185529936824E-4</v>
-      </c>
-      <c r="O17" s="3">
-        <v>1.28387798462399E-4</v>
-      </c>
-      <c r="P17" s="3">
-        <v>1.28288053350757E-4</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>1.2815557511586801E-4</v>
-      </c>
-      <c r="R17" s="3">
-        <v>2.32080654378979E-4</v>
-      </c>
-      <c r="S17" s="3">
-        <v>1.2807525024838501E-4</v>
-      </c>
-      <c r="T17" s="3">
-        <v>1.27809838639794E-4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="B18" s="3">
-        <v>-1.56186443086244E-2</v>
-      </c>
-      <c r="C18" s="3">
-        <v>-4.3012352796894299E-5</v>
-      </c>
-      <c r="D18" s="3">
-        <v>1.3029580279298299E-5</v>
-      </c>
-      <c r="E18" s="3">
-        <v>1.5682050871755901E-8</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-1.15812272087677E-4</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-2.649256276039E-8</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-5.4401984672664301E-8</v>
-      </c>
-      <c r="I18" s="3">
-        <v>4.9436262853670103E-5</v>
-      </c>
-      <c r="J18" s="3">
-        <v>1.2850517839577201E-4</v>
-      </c>
-      <c r="K18" s="3">
-        <v>1.2806925814576499E-4</v>
-      </c>
-      <c r="L18" s="3">
-        <v>1.2847479183651601E-4</v>
-      </c>
-      <c r="M18" s="3">
-        <v>1.2871723215705601E-4</v>
-      </c>
-      <c r="N18" s="3">
-        <v>1.2851062493150799E-4</v>
-      </c>
-      <c r="O18" s="3">
-        <v>1.29171340856517E-4</v>
-      </c>
-      <c r="P18" s="3">
-        <v>1.28876243626055E-4</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>1.28557353679376E-4</v>
-      </c>
-      <c r="R18" s="3">
-        <v>1.2807525024838501E-4</v>
-      </c>
-      <c r="S18" s="3">
-        <v>1.9081121324572101E-4</v>
-      </c>
-      <c r="T18" s="3">
-        <v>1.2781627363187101E-4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B19" s="3">
-        <v>-1.07160697847995E-2</v>
-      </c>
-      <c r="C19" s="3">
-        <v>3.7008445852146098E-5</v>
-      </c>
-      <c r="D19" s="3">
-        <v>1.42629557258721E-5</v>
-      </c>
-      <c r="E19" s="3">
-        <v>-2.5143497513425999E-8</v>
-      </c>
-      <c r="F19" s="3">
-        <v>-1.3430966264520999E-4</v>
-      </c>
-      <c r="G19" s="3">
-        <v>2.5363953227354399E-8</v>
-      </c>
-      <c r="H19" s="3">
-        <v>-1.12458184845013E-7</v>
-      </c>
-      <c r="I19" s="3">
-        <v>-8.6720788823514795E-6</v>
-      </c>
-      <c r="J19" s="3">
-        <v>1.2823071191081999E-4</v>
-      </c>
-      <c r="K19" s="3">
-        <v>1.2837966944789301E-4</v>
-      </c>
-      <c r="L19" s="3">
-        <v>1.2804314241824901E-4</v>
-      </c>
-      <c r="M19" s="3">
-        <v>1.2797977117152899E-4</v>
-      </c>
-      <c r="N19" s="3">
-        <v>1.2806928906562701E-4</v>
-      </c>
-      <c r="O19" s="3">
-        <v>1.2725999699466701E-4</v>
-      </c>
-      <c r="P19" s="3">
-        <v>1.28239416372725E-4</v>
-      </c>
-      <c r="Q19" s="3">
-        <v>1.2823405924706699E-4</v>
-      </c>
-      <c r="R19" s="3">
-        <v>1.27809838639794E-4</v>
-      </c>
-      <c r="S19" s="3">
-        <v>1.2781627363187101E-4</v>
-      </c>
-      <c r="T19" s="3">
-        <v>2.34453101567099E-4</v>
+      <c r="B30" s="3">
+        <v>-0.145958808742086</v>
+      </c>
+      <c r="C30" s="3">
+        <v>-2.2330706184271899E-3</v>
+      </c>
+      <c r="D30" s="3">
+        <v>4.3812634503501296E-6</v>
+      </c>
+      <c r="E30" s="3">
+        <v>1.55477749858987E-10</v>
+      </c>
+      <c r="F30" s="3">
+        <v>8.1497248508666505E-6</v>
+      </c>
+      <c r="G30" s="3">
+        <v>-4.2281946664544297E-9</v>
+      </c>
+      <c r="H30" s="3">
+        <v>-3.4521369531308798E-8</v>
+      </c>
+      <c r="I30" s="3">
+        <v>3.96136649828362E-5</v>
+      </c>
+      <c r="J30" s="3">
+        <v>-2.49820286317083E-7</v>
+      </c>
+      <c r="K30" s="3">
+        <v>3.2304296443269002E-5</v>
+      </c>
+      <c r="L30" s="3">
+        <v>1.0551011155236501E-8</v>
+      </c>
+      <c r="M30" s="3">
+        <v>-1.5113910206191199E-8</v>
+      </c>
+      <c r="N30" s="3">
+        <v>-1.7818291051150901E-5</v>
+      </c>
+      <c r="O30" s="3">
+        <v>3.3219196627751998E-5</v>
+      </c>
+      <c r="P30" s="3">
+        <v>7.2427379996700101E-7</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>4.2266834945770703E-5</v>
+      </c>
+      <c r="R30" s="3">
+        <v>1.8904408457533699E-6</v>
+      </c>
+      <c r="S30" s="3">
+        <v>2.3811754538130601E-5</v>
+      </c>
+      <c r="T30" s="3">
+        <v>2.47460032621245E-6</v>
+      </c>
+      <c r="U30" s="3">
+        <v>2.3294289001235301E-5</v>
+      </c>
+      <c r="V30" s="3">
+        <v>3.1230377465330602E-6</v>
+      </c>
+      <c r="W30" s="3">
+        <v>9.9045831466263909E-4</v>
+      </c>
+      <c r="X30" s="3">
+        <v>1.94750503173308E-6</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>5.9539551208076402E-5</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>6.0782956779033998E-6</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>1.9575599343321999E-3</v>
+      </c>
+      <c r="AB30" s="3">
+        <v>8.5759200785433493E-6</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>2.2818452156688901E-3</v>
+      </c>
+      <c r="AD30" s="3">
+        <v>1.1074340482789701E-5</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>3.91235661825894E-2</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_labourSupplyUtility.xlsx
+++ b/input/reg_labourSupplyUtility.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\andy_local\SimPaths project files\SimPaths\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D899717B-DFCA-4FB0-91B0-5DDF60A2240C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E711D168-67C9-46C7-A4B9-2ABA38379D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B28C262A-F414-4C9F-9F20-D497875F2897}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="7" xr2:uid="{B28C262A-F414-4C9F-9F20-D497875F2897}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="8" r:id="rId1"/>
-    <sheet name="UK_Single_Females" sheetId="23" r:id="rId2"/>
-    <sheet name="UK_Single_Males" sheetId="24" r:id="rId3"/>
-    <sheet name="UK_Couples" sheetId="25" r:id="rId4"/>
-    <sheet name="UK_Females_With_Dep" sheetId="26" r:id="rId5"/>
-    <sheet name="UK_Males_With_Dep" sheetId="27" r:id="rId6"/>
-    <sheet name="UK_SingleAC_Females" sheetId="28" r:id="rId7"/>
-    <sheet name="UK_SingleAC_Males" sheetId="29" r:id="rId8"/>
+    <sheet name="UK_Single_Females" sheetId="16" r:id="rId2"/>
+    <sheet name="UK_Single_Males" sheetId="17" r:id="rId3"/>
+    <sheet name="UK_Couples" sheetId="18" r:id="rId4"/>
+    <sheet name="UK_Females_With_Dep" sheetId="19" r:id="rId5"/>
+    <sheet name="UK_Males_With_Dep" sheetId="20" r:id="rId6"/>
+    <sheet name="UK_SingleAC_Females" sheetId="21" r:id="rId7"/>
+    <sheet name="UK_SingleAC_Males" sheetId="22" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="233">
   <si>
     <t>REGRESSOR</t>
   </si>
@@ -247,6 +247,9 @@
   </si>
   <si>
     <t>UKH_20</t>
+  </si>
+  <si>
+    <t>UKI_2-0</t>
   </si>
   <si>
     <t>UKJ_20</t>
@@ -675,70 +678,70 @@
     <t>Liwwh_Female_440</t>
   </si>
   <si>
-    <t>FemaleIncomeDiv100</t>
+    <t>FemaleLeisure_UKN</t>
   </si>
   <si>
-    <t>FemaleIncomeSqDiv10000</t>
+    <t>FemaleLeisure_UKM</t>
   </si>
   <si>
-    <t>MaleIncomeDiv100</t>
+    <t>FemaleLeisure_UKL</t>
   </si>
   <si>
-    <t>MaleIncomeSqDiv10000</t>
+    <t>FemaleLeisure_UKK</t>
   </si>
   <si>
-    <t>FixedCost_Female</t>
+    <t>FemaleLeisure_UKJ</t>
   </si>
   <si>
-    <t>Liwwh_1</t>
+    <t>FemaleLeisure_UKI</t>
   </si>
   <si>
-    <t>Liwwh_10</t>
+    <t>FemaleLeisure_UKH</t>
   </si>
   <si>
-    <t>Liwwh_11</t>
+    <t>FemaleLeisure_UKG</t>
   </si>
   <si>
-    <t>Liwwh_20</t>
+    <t>FemaleLeisure_UKF</t>
   </si>
   <si>
-    <t>Liwwh_21</t>
+    <t>FemaleLeisure_UKE</t>
   </si>
   <si>
-    <t>Liwwh_30</t>
+    <t>FemaleLeisure_UKD</t>
   </si>
   <si>
-    <t>Liwwh_31</t>
+    <t>MaleLeisure_UKN</t>
   </si>
   <si>
-    <t>Liwwh_40</t>
+    <t>MaleLeisure_UKM</t>
   </si>
   <si>
-    <t>Liwwh_41</t>
+    <t>MaleLeisure_UKL</t>
   </si>
   <si>
-    <t>Liwwh_100</t>
+    <t>MaleLeisure_UKK</t>
   </si>
   <si>
-    <t>Liwwh_101</t>
+    <t>MaleLeisure_UKJ</t>
   </si>
   <si>
-    <t>Liwwh_200</t>
+    <t>MaleLeisure_UKI</t>
   </si>
   <si>
-    <t>Liwwh_201</t>
+    <t>MaleLeisure_UKH</t>
   </si>
   <si>
-    <t>Liwwh_300</t>
+    <t>MaleLeisure_UKG</t>
   </si>
   <si>
-    <t>Liwwh_301</t>
+    <t>MaleLeisure_UKF</t>
   </si>
   <si>
-    <t>Liwwh_400</t>
+    <t>MaleLeisure_UKE</t>
   </si>
   <si>
-    <t>Liwwh_401</t>
+    <t>MaleLeisure_UKD</t>
   </si>
 </sst>
 </file>
@@ -1233,11 +1236,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{144D37F1-E874-493E-874F-A5B6CB3C3127}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2497E15-6FF7-4BEA-8049-BA4982ADFA83}">
   <dimension ref="A1:DD107"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="11.42578125" style="3"/>
+    <col min="1" max="1" width="28.28515625" style="3" customWidth="1"/>
+    <col min="2" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:108" x14ac:dyDescent="0.25">
@@ -1383,187 +1387,187 @@
         <v>67</v>
       </c>
       <c r="AV1" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AW1" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="AX1" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AY1" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="AZ1" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="BA1" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="BB1" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC1" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD1" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="BE1" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="BF1" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="BG1" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="BH1" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="BI1" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="BJ1" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="BK1" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="BL1" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="BM1" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="BN1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="BO1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="BP1" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="BQ1" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="BR1" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="BS1" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="BT1" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="BU1" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="BV1" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="BW1" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="BX1" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="BY1" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="BZ1" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="CA1" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="CB1" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="CC1" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="CD1" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="CE1" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="CF1" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="CG1" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="CH1" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="CI1" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="CJ1" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="CK1" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="CL1" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="CM1" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="CN1" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="CO1" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="CP1" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="CQ1" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="CR1" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="CS1" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="CT1" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="CU1" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="CV1" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CW1" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="CX1" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="CY1" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="CZ1" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DA1" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="DB1" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="DC1" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="DD1" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="AW1" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="AX1" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="AY1" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="AZ1" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="BA1" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="BB1" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="BC1" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="BD1" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE1" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="BF1" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="BG1" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="BH1" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="BI1" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="BJ1" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="BK1" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="BL1" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="BM1" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="BN1" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="BO1" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="BP1" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="BQ1" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="BR1" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="BS1" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="BT1" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="BU1" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="BV1" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="BW1" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="BX1" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="BY1" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="BZ1" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="CA1" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="CB1" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="CC1" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="CD1" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="CE1" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="CF1" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="CG1" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="CH1" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="CI1" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="CJ1" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="CK1" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="CL1" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="CM1" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="CN1" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="CO1" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="CP1" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="CQ1" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="CR1" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="CS1" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="CT1" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="CU1" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="CV1" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="CW1" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="CX1" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="CY1" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="CZ1" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="DA1" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="DB1" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="DC1" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="DD1" s="3" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:108" x14ac:dyDescent="0.25">
@@ -16238,7 +16242,7 @@
     </row>
     <row r="47" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B47" s="3">
         <v>0.32911331288270901</v>
@@ -16564,7 +16568,7 @@
     </row>
     <row r="48" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B48" s="3">
         <v>0.45997248895694198</v>
@@ -16890,7 +16894,7 @@
     </row>
     <row r="49" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B49" s="3">
         <v>0.614402059337812</v>
@@ -17216,7 +17220,7 @@
     </row>
     <row r="50" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B50" s="3">
         <v>0.40166801846043998</v>
@@ -17542,7 +17546,7 @@
     </row>
     <row r="51" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B51" s="3">
         <v>0.74839241815767299</v>
@@ -17868,7 +17872,7 @@
     </row>
     <row r="52" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B52" s="3">
         <v>0.15716690481010401</v>
@@ -18194,7 +18198,7 @@
     </row>
     <row r="53" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B53" s="3">
         <v>3.0431555359667799</v>
@@ -18520,7 +18524,7 @@
     </row>
     <row r="54" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B54" s="3">
         <v>2.1883363678169001</v>
@@ -18846,7 +18850,7 @@
     </row>
     <row r="55" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B55" s="3">
         <v>0.96359623739205003</v>
@@ -19172,7 +19176,7 @@
     </row>
     <row r="56" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B56" s="3">
         <v>1.66965909179537</v>
@@ -19498,7 +19502,7 @@
     </row>
     <row r="57" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B57" s="3">
         <v>-15.7318676354512</v>
@@ -19824,7 +19828,7 @@
     </row>
     <row r="58" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B58" s="3">
         <v>0.24070453007246401</v>
@@ -20150,7 +20154,7 @@
     </row>
     <row r="59" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B59" s="3">
         <v>1.9554590678089501</v>
@@ -20476,7 +20480,7 @@
     </row>
     <row r="60" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B60" s="3">
         <v>1.6577650756654301</v>
@@ -20802,7 +20806,7 @@
     </row>
     <row r="61" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B61" s="3">
         <v>1.12894494926212</v>
@@ -21128,7 +21132,7 @@
     </row>
     <row r="62" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B62" s="3">
         <v>1.99296722813993</v>
@@ -21454,7 +21458,7 @@
     </row>
     <row r="63" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B63" s="3">
         <v>-0.23446454411062401</v>
@@ -21780,7 +21784,7 @@
     </row>
     <row r="64" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B64" s="3">
         <v>1.2087767744831099</v>
@@ -22106,7 +22110,7 @@
     </row>
     <row r="65" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B65" s="3">
         <v>0.81982745729659701</v>
@@ -22432,7 +22436,7 @@
     </row>
     <row r="66" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B66" s="3">
         <v>0.85579426617710297</v>
@@ -22758,7 +22762,7 @@
     </row>
     <row r="67" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B67" s="3">
         <v>0.85055520989919497</v>
@@ -23084,7 +23088,7 @@
     </row>
     <row r="68" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B68" s="3">
         <v>1.08489702603608</v>
@@ -23410,7 +23414,7 @@
     </row>
     <row r="69" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B69" s="3">
         <v>0.52963387601230505</v>
@@ -23736,7 +23740,7 @@
     </row>
     <row r="70" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B70" s="3">
         <v>0.60433852964892198</v>
@@ -24062,7 +24066,7 @@
     </row>
     <row r="71" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B71" s="3">
         <v>0.67531150898639403</v>
@@ -24388,7 +24392,7 @@
     </row>
     <row r="72" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B72" s="3">
         <v>0.761953243874393</v>
@@ -24714,7 +24718,7 @@
     </row>
     <row r="73" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B73" s="3">
         <v>0.84761871661198696</v>
@@ -25040,7 +25044,7 @@
     </row>
     <row r="74" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B74" s="3">
         <v>3.2313787165111199E-2</v>
@@ -25366,7 +25370,7 @@
     </row>
     <row r="75" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B75" s="3">
         <v>1.3743912216502701</v>
@@ -25692,7 +25696,7 @@
     </row>
     <row r="76" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B76" s="3">
         <v>1.1413033658515599</v>
@@ -26018,7 +26022,7 @@
     </row>
     <row r="77" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B77" s="3">
         <v>-15.573977076464001</v>
@@ -26344,7 +26348,7 @@
     </row>
     <row r="78" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B78" s="3">
         <v>0.98908927873806296</v>
@@ -26670,7 +26674,7 @@
     </row>
     <row r="79" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B79" s="3">
         <v>-15.4540437289527</v>
@@ -26996,7 +27000,7 @@
     </row>
     <row r="80" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B80" s="3">
         <v>2.0279809393841801</v>
@@ -27322,7 +27326,7 @@
     </row>
     <row r="81" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B81" s="3">
         <v>-15.3887942610164</v>
@@ -27648,7 +27652,7 @@
     </row>
     <row r="82" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B82" s="3">
         <v>-15.423251370342999</v>
@@ -27974,7 +27978,7 @@
     </row>
     <row r="83" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B83" s="3">
         <v>2.34711565303735</v>
@@ -28300,7 +28304,7 @@
     </row>
     <row r="84" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B84" s="3">
         <v>1.21360351738299</v>
@@ -28626,7 +28630,7 @@
     </row>
     <row r="85" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B85" s="3">
         <v>-15.973537729956901</v>
@@ -28952,7 +28956,7 @@
     </row>
     <row r="86" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B86" s="3">
         <v>1.30007945773239</v>
@@ -29278,7 +29282,7 @@
     </row>
     <row r="87" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B87" s="3">
         <v>0.73840566099272398</v>
@@ -29604,7 +29608,7 @@
     </row>
     <row r="88" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B88" s="3">
         <v>0.21778564323168101</v>
@@ -29930,7 +29934,7 @@
     </row>
     <row r="89" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B89" s="3">
         <v>0.80106059086288695</v>
@@ -30256,7 +30260,7 @@
     </row>
     <row r="90" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B90" s="3">
         <v>0.935798561797897</v>
@@ -30582,7 +30586,7 @@
     </row>
     <row r="91" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B91" s="3">
         <v>0.71958372166728302</v>
@@ -30908,7 +30912,7 @@
     </row>
     <row r="92" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B92" s="3">
         <v>0.83314270312517502</v>
@@ -31234,7 +31238,7 @@
     </row>
     <row r="93" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B93" s="3">
         <v>0.59198516916880295</v>
@@ -31560,7 +31564,7 @@
     </row>
     <row r="94" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B94" s="3">
         <v>1.3087267214679701</v>
@@ -31886,7 +31890,7 @@
     </row>
     <row r="95" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B95" s="3">
         <v>1.2306438372528901</v>
@@ -32212,7 +32216,7 @@
     </row>
     <row r="96" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B96" s="3">
         <v>-0.37863775445417303</v>
@@ -32538,7 +32542,7 @@
     </row>
     <row r="97" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B97" s="3">
         <v>1.0771617064993999</v>
@@ -32864,7 +32868,7 @@
     </row>
     <row r="98" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B98" s="3">
         <v>0.83808859567167704</v>
@@ -33190,7 +33194,7 @@
     </row>
     <row r="99" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B99" s="3">
         <v>0.289305021165008</v>
@@ -33516,7 +33520,7 @@
     </row>
     <row r="100" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B100" s="3">
         <v>0.72322716375276397</v>
@@ -33842,7 +33846,7 @@
     </row>
     <row r="101" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B101" s="3">
         <v>0.53196355282499797</v>
@@ -34168,7 +34172,7 @@
     </row>
     <row r="102" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B102" s="3">
         <v>0.62844340538296295</v>
@@ -34494,7 +34498,7 @@
     </row>
     <row r="103" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B103" s="3">
         <v>-15.6126122275612</v>
@@ -34820,7 +34824,7 @@
     </row>
     <row r="104" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B104" s="3">
         <v>-15.643508532469101</v>
@@ -35146,7 +35150,7 @@
     </row>
     <row r="105" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B105" s="3">
         <v>-15.412131421771701</v>
@@ -35472,7 +35476,7 @@
     </row>
     <row r="106" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B106" s="3">
         <v>-15.4735629004484</v>
@@ -35798,7 +35802,7 @@
     </row>
     <row r="107" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B107" s="3">
         <v>-16.204091179354201</v>
@@ -36129,11 +36133,12 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{055024F4-33A1-4F47-A2A4-B66D5D612658}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DB56E65-A028-41C8-8E37-C957AEE6B4E5}">
   <dimension ref="A1:I8"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="11.42578125" style="3"/>
+    <col min="1" max="1" width="39.7109375" style="3" customWidth="1"/>
+    <col min="2" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -36162,7 +36167,7 @@
         <v>9</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -36341,7 +36346,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B8" s="3">
         <v>0.54258700000000004</v>
@@ -36375,11 +36380,12 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{380EAEAD-4CDB-4A7C-AFE3-0A8A39C9D904}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{713A1631-5A78-441A-A83A-D84683700833}">
   <dimension ref="A1:CP93"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="11.42578125" style="3"/>
+    <col min="1" max="1" width="33" style="3" customWidth="1"/>
+    <col min="2" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:94" x14ac:dyDescent="0.25">
@@ -36420,250 +36426,250 @@
         <v>6</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>29</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AD1" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AE1" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AF1" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG1" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AI1" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AJ1" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AK1" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AL1" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AM1" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AN1" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AQ1" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AR1" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AS1" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AT1" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AU1" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AV1" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AW1" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AX1" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AY1" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AZ1" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="BA1" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="BB1" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="BC1" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="BD1" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="BE1" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="BF1" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="BG1" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="BH1" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="BI1" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="BJ1" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="BK1" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="BL1" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="BM1" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="BN1" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="BO1" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="BP1" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="BQ1" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="BR1" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="BS1" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="BT1" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="BU1" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="BV1" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="BW1" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="BX1" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="BY1" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BZ1" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="CA1" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="CB1" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="CC1" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="CD1" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="CE1" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="CF1" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="CG1" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="CH1" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="CI1" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="CJ1" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="CK1" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="CL1" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="CM1" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="CN1" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="CO1" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="CP1" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:94" x14ac:dyDescent="0.25">
@@ -39508,7 +39514,7 @@
     </row>
     <row r="12" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B12" s="3">
         <v>3.56416819514497</v>
@@ -40076,7 +40082,7 @@
     </row>
     <row r="14" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B14" s="3">
         <v>-0.24851257653206699</v>
@@ -40360,7 +40366,7 @@
     </row>
     <row r="15" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B15" s="3">
         <v>-0.15501650152683599</v>
@@ -40644,7 +40650,7 @@
     </row>
     <row r="16" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B16" s="3">
         <v>-3.3557569295545202E-2</v>
@@ -40928,7 +40934,7 @@
     </row>
     <row r="17" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B17" s="3">
         <v>3.1086688130075299E-2</v>
@@ -41212,7 +41218,7 @@
     </row>
     <row r="18" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B18" s="3">
         <v>-3.54804655910477E-2</v>
@@ -41496,7 +41502,7 @@
     </row>
     <row r="19" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B19" s="3">
         <v>0.104490784522007</v>
@@ -41780,7 +41786,7 @@
     </row>
     <row r="20" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B20" s="3">
         <v>-1.6740910505204602E-2</v>
@@ -42064,7 +42070,7 @@
     </row>
     <row r="21" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B21" s="3">
         <v>2.68411381805354E-2</v>
@@ -42348,7 +42354,7 @@
     </row>
     <row r="22" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B22" s="3">
         <v>3.9140421628870901E-2</v>
@@ -42632,7 +42638,7 @@
     </row>
     <row r="23" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B23" s="3">
         <v>3.6009585048853501E-2</v>
@@ -42916,7 +42922,7 @@
     </row>
     <row r="24" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B24" s="3">
         <v>-4.1153464270304002E-2</v>
@@ -43200,7 +43206,7 @@
     </row>
     <row r="25" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B25" s="3">
         <v>5.2805973843852799E-2</v>
@@ -43484,7 +43490,7 @@
     </row>
     <row r="26" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B26" s="3">
         <v>-0.24664046507380399</v>
@@ -43768,7 +43774,7 @@
     </row>
     <row r="27" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B27" s="3">
         <v>-8.16818341777997E-2</v>
@@ -44052,7 +44058,7 @@
     </row>
     <row r="28" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B28" s="3">
         <v>-2.7376636525575999E-2</v>
@@ -44336,7 +44342,7 @@
     </row>
     <row r="29" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B29" s="3">
         <v>3.6859599206483303E-2</v>
@@ -44620,7 +44626,7 @@
     </row>
     <row r="30" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B30" s="3">
         <v>-0.266921014426866</v>
@@ -44904,7 +44910,7 @@
     </row>
     <row r="31" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B31" s="3">
         <v>-9.4004542275197001E-2</v>
@@ -45188,7 +45194,7 @@
     </row>
     <row r="32" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B32" s="3">
         <v>-1.28983256881103E-2</v>
@@ -45472,7 +45478,7 @@
     </row>
     <row r="33" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B33" s="3">
         <v>1.39806666058512E-2</v>
@@ -45756,7 +45762,7 @@
     </row>
     <row r="34" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B34" s="3">
         <v>-0.241530621994761</v>
@@ -46040,7 +46046,7 @@
     </row>
     <row r="35" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B35" s="3">
         <v>-0.147615297043832</v>
@@ -46324,7 +46330,7 @@
     </row>
     <row r="36" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B36" s="3">
         <v>-3.0341143642342298E-2</v>
@@ -46608,7 +46614,7 @@
     </row>
     <row r="37" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B37" s="3">
         <v>3.07085183522318E-2</v>
@@ -46892,7 +46898,7 @@
     </row>
     <row r="38" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B38" s="3">
         <v>-0.235620706291398</v>
@@ -47176,7 +47182,7 @@
     </row>
     <row r="39" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B39" s="3">
         <v>-0.14108344291893599</v>
@@ -47460,7 +47466,7 @@
     </row>
     <row r="40" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B40" s="3">
         <v>-3.1069493186529198E-2</v>
@@ -47744,7 +47750,7 @@
     </row>
     <row r="41" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B41" s="3">
         <v>4.4659950017029999E-2</v>
@@ -48028,7 +48034,7 @@
     </row>
     <row r="42" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B42" s="3">
         <v>-0.25460426377618001</v>
@@ -48312,7 +48318,7 @@
     </row>
     <row r="43" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B43" s="3">
         <v>-8.3970811896098896E-2</v>
@@ -48596,7 +48602,7 @@
     </row>
     <row r="44" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B44" s="3">
         <v>-2.3993425911259199E-2</v>
@@ -48880,7 +48886,7 @@
     </row>
     <row r="45" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B45" s="3">
         <v>4.06632647854046E-2</v>
@@ -49164,7 +49170,7 @@
     </row>
     <row r="46" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B46" s="3">
         <v>-0.245869225848625</v>
@@ -49448,7 +49454,7 @@
     </row>
     <row r="47" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B47" s="3">
         <v>-8.1010365828426203E-2</v>
@@ -49732,7 +49738,7 @@
     </row>
     <row r="48" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B48" s="3">
         <v>-2.7620053894158701E-2</v>
@@ -50016,7 +50022,7 @@
     </row>
     <row r="49" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B49" s="3">
         <v>3.3648476392357199E-2</v>
@@ -50300,7 +50306,7 @@
     </row>
     <row r="50" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B50" s="3">
         <v>-0.27974082537358902</v>
@@ -50584,7 +50590,7 @@
     </row>
     <row r="51" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B51" s="3">
         <v>-7.9125985712695704E-2</v>
@@ -50868,7 +50874,7 @@
     </row>
     <row r="52" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B52" s="3">
         <v>1.16923849670512E-2</v>
@@ -51152,7 +51158,7 @@
     </row>
     <row r="53" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B53" s="3">
         <v>-2.37213448911E-3</v>
@@ -51436,7 +51442,7 @@
     </row>
     <row r="54" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B54" s="3">
         <v>-0.23817014524878</v>
@@ -51720,7 +51726,7 @@
     </row>
     <row r="55" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B55" s="3">
         <v>-0.143863760962225</v>
@@ -52004,7 +52010,7 @@
     </row>
     <row r="56" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B56" s="3">
         <v>-1.9193132946093001E-2</v>
@@ -52288,7 +52294,7 @@
     </row>
     <row r="57" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B57" s="3">
         <v>2.9104616195848799E-2</v>
@@ -52572,7 +52578,7 @@
     </row>
     <row r="58" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B58" s="3">
         <v>-0.26222573600960403</v>
@@ -52856,7 +52862,7 @@
     </row>
     <row r="59" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B59" s="3">
         <v>-8.7324478884078599E-2</v>
@@ -53140,7 +53146,7 @@
     </row>
     <row r="60" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B60" s="3">
         <v>-8.0538958530602008E-3</v>
@@ -53424,7 +53430,7 @@
     </row>
     <row r="61" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B61" s="3">
         <v>3.4468551042118899E-2</v>
@@ -53708,7 +53714,7 @@
     </row>
     <row r="62" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B62" s="3">
         <v>-5.8149600710401704E-3</v>
@@ -53992,7 +53998,7 @@
     </row>
     <row r="63" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B63" s="3">
         <v>3.2403465051017197E-2</v>
@@ -54276,7 +54282,7 @@
     </row>
     <row r="64" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B64" s="3">
         <v>-1.95968544991071E-2</v>
@@ -54560,7 +54566,7 @@
     </row>
     <row r="65" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B65" s="3">
         <v>4.3088570435007703E-2</v>
@@ -54844,7 +54850,7 @@
     </row>
     <row r="66" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B66" s="3">
         <v>1.3782593123408699E-2</v>
@@ -55128,7 +55134,7 @@
     </row>
     <row r="67" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B67" s="3">
         <v>4.2217819515446E-3</v>
@@ -55412,7 +55418,7 @@
     </row>
     <row r="68" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B68" s="3">
         <v>-0.24101550673286201</v>
@@ -55696,7 +55702,7 @@
     </row>
     <row r="69" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B69" s="3">
         <v>-0.14407589532802201</v>
@@ -55980,7 +55986,7 @@
     </row>
     <row r="70" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B70" s="3">
         <v>-1.37294896327869E-2</v>
@@ -56264,7 +56270,7 @@
     </row>
     <row r="71" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B71" s="3">
         <v>3.73680753415431E-2</v>
@@ -56548,7 +56554,7 @@
     </row>
     <row r="72" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B72" s="3">
         <v>-0.26682852387940398</v>
@@ -56832,7 +56838,7 @@
     </row>
     <row r="73" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B73" s="3">
         <v>-8.8436226125812104E-2</v>
@@ -57116,7 +57122,7 @@
     </row>
     <row r="74" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B74" s="3">
         <v>6.8005805226868698E-4</v>
@@ -57400,7 +57406,7 @@
     </row>
     <row r="75" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B75" s="3">
         <v>3.3848348666552203E-2</v>
@@ -57684,7 +57690,7 @@
     </row>
     <row r="76" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B76" s="3">
         <v>-8.8371173287494901E-4</v>
@@ -57968,7 +57974,7 @@
     </row>
     <row r="77" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B77" s="3">
         <v>4.04919256273501E-2</v>
@@ -58252,7 +58258,7 @@
     </row>
     <row r="78" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B78" s="3">
         <v>-1.24503691831E-2</v>
@@ -58536,7 +58542,7 @@
     </row>
     <row r="79" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B79" s="3">
         <v>4.4795385372791097E-2</v>
@@ -58820,7 +58826,7 @@
     </row>
     <row r="80" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B80" s="3">
         <v>2.0286667152899299E-3</v>
@@ -59104,7 +59110,7 @@
     </row>
     <row r="81" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B81" s="3">
         <v>3.6560329427985602E-3</v>
@@ -59388,7 +59394,7 @@
     </row>
     <row r="82" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B82" s="3">
         <v>7.0307314940585106E-2</v>
@@ -59672,7 +59678,7 @@
     </row>
     <row r="83" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B83" s="3">
         <v>-1.33212316156076</v>
@@ -59956,7 +59962,7 @@
     </row>
     <row r="84" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B84" s="3">
         <v>-8.9552728282690404E-3</v>
@@ -60240,7 +60246,7 @@
     </row>
     <row r="85" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B85" s="3">
         <v>1.9935071355956201E-2</v>
@@ -60524,7 +60530,7 @@
     </row>
     <row r="86" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B86" s="3">
         <v>-0.28281924164622801</v>
@@ -60808,7 +60814,7 @@
     </row>
     <row r="87" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B87" s="3">
         <v>-9.6856980827706898E-2</v>
@@ -61092,7 +61098,7 @@
     </row>
     <row r="88" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B88" s="3">
         <v>-1.0029218489704599E-2</v>
@@ -61376,7 +61382,7 @@
     </row>
     <row r="89" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B89" s="3">
         <v>3.4912659661339801E-2</v>
@@ -61660,7 +61666,7 @@
     </row>
     <row r="90" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B90" s="3">
         <v>-6.8797262004654299E-3</v>
@@ -61944,7 +61950,7 @@
     </row>
     <row r="91" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B91" s="3">
         <v>3.8238204748118503E-2</v>
@@ -62228,7 +62234,7 @@
     </row>
     <row r="92" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B92" s="3">
         <v>-1.19181161641839E-2</v>
@@ -62512,7 +62518,7 @@
     </row>
     <row r="93" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B93" s="3">
         <v>3.7717663714500901E-2</v>
@@ -62801,11 +62807,12 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DD78F2F-CA77-4446-BA41-A05647792E31}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A52A53A-8337-4C79-8847-E5AFC5268D50}">
   <dimension ref="A1:I8"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="11.42578125" style="3"/>
+    <col min="1" max="1" width="33.42578125" style="3" customWidth="1"/>
+    <col min="2" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -63047,11 +63054,12 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D14D180-CF6C-4231-A992-F9B2E75CDC6D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9164393-5E7D-4422-9A61-B7FFE1623344}">
   <dimension ref="A1:I8"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="11.42578125" style="3"/>
+    <col min="1" max="1" width="30" style="3" customWidth="1"/>
+    <col min="2" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -63080,7 +63088,7 @@
         <v>9</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -63259,7 +63267,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B8" s="3">
         <v>0.99929437674511601</v>
@@ -63293,14 +63301,15 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4EAA4B1-7298-4DD6-AF4D-494334F187ED}">
-  <dimension ref="A1:AE30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46DFF46C-488E-4562-9683-A336EF32C45A}">
+  <dimension ref="A1:T19"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="11.42578125" style="3"/>
+    <col min="1" max="1" width="46.140625" style="3" customWidth="1"/>
+    <col min="2" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -63311,10 +63320,10 @@
         <v>28</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>210</v>
+        <v>2</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>211</v>
+        <v>3</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>4</v>
@@ -63326,2828 +63335,1156 @@
         <v>6</v>
       </c>
       <c r="I1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="S1" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>219</v>
-      </c>
       <c r="T1" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="Y1" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="Z1" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="AA1" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="AB1" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="AC1" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="AD1" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="AE1" s="3" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B2" s="3">
-        <v>-1.0073555552515301</v>
+        <v>-4.0410153827671103</v>
       </c>
       <c r="C2" s="3">
-        <v>2.9856881717883501E-2</v>
+        <v>0.21581828600289299</v>
       </c>
       <c r="D2" s="3">
-        <v>-5.8994148035503802E-5</v>
+        <v>-3.6000664365707898E-3</v>
       </c>
       <c r="E2" s="3">
-        <v>5.7386565427299501E-8</v>
+        <v>1.7992908634939001E-5</v>
       </c>
       <c r="F2" s="3">
-        <v>-2.0510879438839099E-4</v>
+        <v>-9.4737634710239304E-4</v>
       </c>
       <c r="G2" s="3">
-        <v>2.32207103902407E-7</v>
+        <v>4.6046051895759601E-7</v>
       </c>
       <c r="H2" s="3">
-        <v>4.2627333639507602E-7</v>
+        <v>1.03941423048226E-5</v>
       </c>
       <c r="I2" s="3">
-        <v>-1.9450413424968002E-5</v>
+        <v>-6.9841930969792099E-4</v>
       </c>
       <c r="J2" s="3">
-        <v>-5.7012562247928403E-9</v>
+        <v>-1.9951459761529201E-5</v>
       </c>
       <c r="K2" s="3">
-        <v>5.4792089090609801E-5</v>
+        <v>-1.56280416303169E-5</v>
       </c>
       <c r="L2" s="3">
-        <v>-2.2681141620312401E-7</v>
+        <v>-1.6085496742759701E-5</v>
       </c>
       <c r="M2" s="3">
-        <v>1.3345356051517001E-7</v>
+        <v>-1.6810972813864102E-5</v>
       </c>
       <c r="N2" s="3">
-        <v>-1.45976076676486E-3</v>
+        <v>2.8045648463842E-5</v>
       </c>
       <c r="O2" s="3">
-        <v>-4.4239560392802401E-4</v>
+        <v>-1.69121915246763E-4</v>
       </c>
       <c r="P2" s="3">
-        <v>-1.38273208057125E-5</v>
+        <v>-3.7489818026374599E-6</v>
       </c>
       <c r="Q2" s="3">
-        <v>-5.7002713262109203E-4</v>
+        <v>5.7103493780468003E-5</v>
       </c>
       <c r="R2" s="3">
-        <v>-3.2806140748527603E-5</v>
+        <v>2.9753483553440498E-6</v>
       </c>
       <c r="S2" s="3">
-        <v>-3.2657794885813701E-4</v>
+        <v>-4.3012352796894299E-5</v>
       </c>
       <c r="T2" s="3">
-        <v>-4.4083097124947101E-5</v>
-      </c>
-      <c r="U2" s="3">
-        <v>-3.2367230722205498E-4</v>
-      </c>
-      <c r="V2" s="3">
-        <v>-4.3004050441810102E-5</v>
-      </c>
-      <c r="W2" s="3">
-        <v>-1.3131505351304499E-2</v>
-      </c>
-      <c r="X2" s="3">
-        <v>-4.98718667466059E-6</v>
-      </c>
-      <c r="Y2" s="3">
-        <v>-7.4770951320942802E-4</v>
-      </c>
-      <c r="Z2" s="3">
-        <v>-3.37532068332918E-5</v>
-      </c>
-      <c r="AA2" s="3">
-        <v>-2.6582967533709399E-2</v>
-      </c>
-      <c r="AB2" s="3">
-        <v>-4.7165081493678701E-5</v>
-      </c>
-      <c r="AC2" s="3">
-        <v>-2.7998752126199601E-2</v>
-      </c>
-      <c r="AD2" s="3">
-        <v>-4.5599648325824797E-5</v>
-      </c>
-      <c r="AE2" s="3">
-        <v>-2.2330706184271899E-3</v>
+        <v>3.7008445852146098E-5</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>210</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>1.23361213363856E-2</v>
+        <v>-0.14537907813996001</v>
       </c>
       <c r="C3" s="3">
-        <v>-5.8994148035503802E-5</v>
+        <v>-3.6000664365707898E-3</v>
       </c>
       <c r="D3" s="3">
-        <v>2.0618273889906101E-3</v>
+        <v>4.37059910039388E-3</v>
       </c>
       <c r="E3" s="3">
-        <v>-5.6033360392489203E-6</v>
+        <v>-1.96417855377994E-5</v>
       </c>
       <c r="F3" s="3">
-        <v>1.6703013930095499E-3</v>
+        <v>1.44751455474659E-3</v>
       </c>
       <c r="G3" s="3">
-        <v>-5.0389905385463597E-6</v>
+        <v>-3.0367310729731402E-6</v>
       </c>
       <c r="H3" s="3">
-        <v>-1.2730687267039199E-5</v>
+        <v>-2.20678822207496E-5</v>
       </c>
       <c r="I3" s="3">
-        <v>-2.06160105552984E-3</v>
+        <v>-2.12410488986844E-4</v>
       </c>
       <c r="J3" s="3">
-        <v>5.6033032571383701E-6</v>
+        <v>6.1214312387262998E-6</v>
       </c>
       <c r="K3" s="3">
-        <v>-1.66963385651895E-3</v>
+        <v>8.6132197989848994E-6</v>
       </c>
       <c r="L3" s="3">
-        <v>5.0383735027121401E-6</v>
+        <v>2.2536356875863299E-5</v>
       </c>
       <c r="M3" s="3">
-        <v>1.2728986499007001E-5</v>
+        <v>1.81868866518548E-5</v>
       </c>
       <c r="N3" s="3">
-        <v>7.7905118409062795E-6</v>
+        <v>-9.3509941745020897E-7</v>
       </c>
       <c r="O3" s="3">
-        <v>-1.3099796384693701E-8</v>
+        <v>4.96156039309976E-6</v>
       </c>
       <c r="P3" s="3">
-        <v>8.8767747496532897E-8</v>
+        <v>3.0444920369570299E-5</v>
       </c>
       <c r="Q3" s="3">
-        <v>-5.5865571930154203E-6</v>
+        <v>1.42405086502582E-5</v>
       </c>
       <c r="R3" s="3">
-        <v>1.2827442790502899E-7</v>
+        <v>-6.9696922151638896E-6</v>
       </c>
       <c r="S3" s="3">
-        <v>-5.7799354375200503E-6</v>
+        <v>1.3029580279298299E-5</v>
       </c>
       <c r="T3" s="3">
-        <v>-1.1773492092786599E-6</v>
-      </c>
-      <c r="U3" s="3">
-        <v>-3.9686892538799602E-6</v>
-      </c>
-      <c r="V3" s="3">
-        <v>-3.37284148752009E-6</v>
-      </c>
-      <c r="W3" s="3">
-        <v>2.2205913617525199E-4</v>
-      </c>
-      <c r="X3" s="3">
-        <v>-3.7473548779964399E-8</v>
-      </c>
-      <c r="Y3" s="3">
-        <v>1.41243484717148E-6</v>
-      </c>
-      <c r="Z3" s="3">
-        <v>4.6697030234485799E-8</v>
-      </c>
-      <c r="AA3" s="3">
-        <v>5.4139270552216797E-5</v>
-      </c>
-      <c r="AB3" s="3">
-        <v>8.9180820089915702E-8</v>
-      </c>
-      <c r="AC3" s="3">
-        <v>5.8856609363805299E-5</v>
-      </c>
-      <c r="AD3" s="3">
-        <v>6.0364329442624597E-8</v>
-      </c>
-      <c r="AE3" s="3">
-        <v>4.3812634503501296E-6</v>
+        <v>1.42629557258721E-5</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>211</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>-9.85002475685855E-5</v>
+        <v>4.2860594032363897E-4</v>
       </c>
       <c r="C4" s="3">
-        <v>5.7386565427299501E-8</v>
+        <v>1.7992908634939001E-5</v>
       </c>
       <c r="D4" s="3">
-        <v>-5.6033360392489203E-6</v>
+        <v>-1.96417855377994E-5</v>
       </c>
       <c r="E4" s="3">
-        <v>2.4048571711024799E-8</v>
+        <v>1.0460874449851E-7</v>
       </c>
       <c r="F4" s="3">
-        <v>-3.93022265644805E-6</v>
+        <v>-6.2739541160480204E-6</v>
       </c>
       <c r="G4" s="3">
-        <v>1.0919523456037499E-8</v>
+        <v>1.26134153255488E-8</v>
       </c>
       <c r="H4" s="3">
-        <v>2.89037012688621E-8</v>
+        <v>9.3244115645968599E-8</v>
       </c>
       <c r="I4" s="3">
-        <v>5.6158890554165002E-6</v>
+        <v>-1.67647453075414E-6</v>
       </c>
       <c r="J4" s="3">
-        <v>-2.4037970488982201E-8</v>
+        <v>8.4998118401502599E-8</v>
       </c>
       <c r="K4" s="3">
-        <v>3.8888376684996798E-6</v>
+        <v>3.23626215977667E-8</v>
       </c>
       <c r="L4" s="3">
-        <v>-1.08547654697684E-8</v>
+        <v>3.4279766294984102E-9</v>
       </c>
       <c r="M4" s="3">
-        <v>-2.9015396737953202E-8</v>
+        <v>5.00464040914354E-8</v>
       </c>
       <c r="N4" s="3">
-        <v>-8.42224261010507E-7</v>
+        <v>1.26981749798527E-7</v>
       </c>
       <c r="O4" s="3">
-        <v>-1.5768931082986501E-9</v>
+        <v>6.7466998015694194E-8</v>
       </c>
       <c r="P4" s="3">
-        <v>1.2794883453042E-8</v>
+        <v>2.9257034913650999E-8</v>
       </c>
       <c r="Q4" s="3">
-        <v>1.7855419920635701E-8</v>
+        <v>7.8520358290831098E-8</v>
       </c>
       <c r="R4" s="3">
-        <v>1.99766442914547E-8</v>
+        <v>7.8818250748758297E-8</v>
       </c>
       <c r="S4" s="3">
-        <v>2.32256623767341E-8</v>
+        <v>1.5682050871755901E-8</v>
       </c>
       <c r="T4" s="3">
-        <v>1.47597078118045E-8</v>
-      </c>
-      <c r="U4" s="3">
-        <v>1.07615780554663E-8</v>
-      </c>
-      <c r="V4" s="3">
-        <v>6.8335268027798396E-9</v>
-      </c>
-      <c r="W4" s="3">
-        <v>-1.4392591456924201E-6</v>
-      </c>
-      <c r="X4" s="3">
-        <v>-2.3475894752501299E-9</v>
-      </c>
-      <c r="Y4" s="3">
-        <v>-4.6272621780540504E-9</v>
-      </c>
-      <c r="Z4" s="3">
-        <v>-4.0507049891447397E-9</v>
-      </c>
-      <c r="AA4" s="3">
-        <v>-3.2418727783093902E-7</v>
-      </c>
-      <c r="AB4" s="3">
-        <v>-5.7142343693600102E-9</v>
-      </c>
-      <c r="AC4" s="3">
-        <v>-5.5960630678884497E-7</v>
-      </c>
-      <c r="AD4" s="3">
-        <v>-8.0603069833631301E-10</v>
-      </c>
-      <c r="AE4" s="3">
-        <v>1.55477749858987E-10</v>
+        <v>-2.5143497513425999E-8</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>8.5664508032301606E-2</v>
+        <v>-4.04007740193267E-2</v>
       </c>
       <c r="C5" s="3">
-        <v>-2.0510879438839099E-4</v>
+        <v>-9.4737634710239304E-4</v>
       </c>
       <c r="D5" s="3">
-        <v>1.6703013930095499E-3</v>
+        <v>1.44751455474659E-3</v>
       </c>
       <c r="E5" s="3">
-        <v>-3.93022265644805E-6</v>
+        <v>-6.2739541160480204E-6</v>
       </c>
       <c r="F5" s="3">
-        <v>2.1916298571871E-3</v>
+        <v>1.1618200264724499E-3</v>
       </c>
       <c r="G5" s="3">
-        <v>-6.85746585669935E-6</v>
+        <v>-2.8739050191418401E-6</v>
       </c>
       <c r="H5" s="3">
-        <v>-1.07550805011178E-5</v>
+        <v>-7.5835894890573899E-6</v>
       </c>
       <c r="I5" s="3">
-        <v>-1.6899105423629601E-3</v>
+        <v>1.08148072343284E-3</v>
       </c>
       <c r="J5" s="3">
-        <v>3.9132371300900496E-6</v>
+        <v>-1.31449874069332E-4</v>
       </c>
       <c r="K5" s="3">
-        <v>-2.1239481131728301E-3</v>
+        <v>-1.4110878557804701E-4</v>
       </c>
       <c r="L5" s="3">
-        <v>6.7523665847881301E-6</v>
+        <v>-1.16254410988808E-4</v>
       </c>
       <c r="M5" s="3">
-        <v>1.0930183137874E-5</v>
+        <v>-1.1205120093657801E-4</v>
       </c>
       <c r="N5" s="3">
-        <v>1.3648730633539401E-3</v>
+        <v>-1.2246688883600201E-4</v>
       </c>
       <c r="O5" s="3">
-        <v>2.0305308604558202E-6</v>
+        <v>-1.16349003759329E-4</v>
       </c>
       <c r="P5" s="3">
-        <v>-2.3901403872406398E-6</v>
+        <v>-1.12737357219583E-4</v>
       </c>
       <c r="Q5" s="3">
-        <v>-7.7677387885546099E-6</v>
+        <v>-1.13525292221057E-4</v>
       </c>
       <c r="R5" s="3">
-        <v>1.51652690158799E-6</v>
+        <v>-1.28598471605231E-4</v>
       </c>
       <c r="S5" s="3">
-        <v>-2.7993631971185E-6</v>
+        <v>-1.15812272087677E-4</v>
       </c>
       <c r="T5" s="3">
-        <v>5.7273347152628699E-6</v>
-      </c>
-      <c r="U5" s="3">
-        <v>4.33079258177218E-6</v>
-      </c>
-      <c r="V5" s="3">
-        <v>1.2500867592743E-6</v>
-      </c>
-      <c r="W5" s="3">
-        <v>2.0962679688493001E-4</v>
-      </c>
-      <c r="X5" s="3">
-        <v>3.65862187673918E-6</v>
-      </c>
-      <c r="Y5" s="3">
-        <v>1.0080933112939599E-5</v>
-      </c>
-      <c r="Z5" s="3">
-        <v>6.5591850107535598E-6</v>
-      </c>
-      <c r="AA5" s="3">
-        <v>6.2344193356711302E-4</v>
-      </c>
-      <c r="AB5" s="3">
-        <v>9.3103839991541404E-6</v>
-      </c>
-      <c r="AC5" s="3">
-        <v>1.0101186114218801E-3</v>
-      </c>
-      <c r="AD5" s="3">
-        <v>1.38971764114735E-6</v>
-      </c>
-      <c r="AE5" s="3">
-        <v>8.1497248508666505E-6</v>
+        <v>-1.3430966264520999E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>-7.7383786237344803E-5</v>
+        <v>1.4390902176363699E-4</v>
       </c>
       <c r="C6" s="3">
-        <v>2.32207103902407E-7</v>
+        <v>4.6046051895759601E-7</v>
       </c>
       <c r="D6" s="3">
-        <v>-5.0389905385463597E-6</v>
+        <v>-3.0367310729731402E-6</v>
       </c>
       <c r="E6" s="3">
-        <v>1.0919523456037499E-8</v>
+        <v>1.26134153255488E-8</v>
       </c>
       <c r="F6" s="3">
-        <v>-6.85746585669935E-6</v>
+        <v>-2.8739050191418401E-6</v>
       </c>
       <c r="G6" s="3">
-        <v>2.1950280876478901E-8</v>
+        <v>8.6486014744328504E-9</v>
       </c>
       <c r="H6" s="3">
-        <v>3.35153263200716E-8</v>
+        <v>1.7276047392776699E-8</v>
       </c>
       <c r="I6" s="3">
-        <v>5.0754976343013002E-6</v>
+        <v>-2.3635878554329899E-6</v>
       </c>
       <c r="J6" s="3">
-        <v>-1.08884644638723E-8</v>
+        <v>1.8569949547692401E-8</v>
       </c>
       <c r="K6" s="3">
-        <v>6.73467369315291E-6</v>
+        <v>4.9362830960052602E-8</v>
       </c>
       <c r="L6" s="3">
-        <v>-2.1758561176163999E-8</v>
+        <v>-2.97719140735268E-8</v>
       </c>
       <c r="M6" s="3">
-        <v>-3.3840560782707297E-8</v>
+        <v>-4.4378821342023198E-8</v>
       </c>
       <c r="N6" s="3">
-        <v>-2.4887305256268201E-6</v>
+        <v>-1.84627955760693E-8</v>
       </c>
       <c r="O6" s="3">
-        <v>-3.2854750580198301E-9</v>
+        <v>-1.95762401573888E-8</v>
       </c>
       <c r="P6" s="3">
-        <v>1.6150131807205499E-8</v>
+        <v>-3.6634297609672803E-8</v>
       </c>
       <c r="Q6" s="3">
-        <v>3.7241227150176697E-8</v>
+        <v>-4.5318350624731501E-8</v>
       </c>
       <c r="R6" s="3">
-        <v>1.02422739239568E-8</v>
+        <v>-6.6291409138536298E-10</v>
       </c>
       <c r="S6" s="3">
-        <v>2.7873815411059302E-8</v>
+        <v>-2.649256276039E-8</v>
       </c>
       <c r="T6" s="3">
-        <v>2.7910252330068198E-9</v>
-      </c>
-      <c r="U6" s="3">
-        <v>1.37649092255024E-8</v>
-      </c>
-      <c r="V6" s="3">
-        <v>8.9633571572751406E-9</v>
-      </c>
-      <c r="W6" s="3">
-        <v>6.2164446363434603E-8</v>
-      </c>
-      <c r="X6" s="3">
-        <v>-6.7816117227708904E-9</v>
-      </c>
-      <c r="Y6" s="3">
-        <v>-1.5014541176193999E-8</v>
-      </c>
-      <c r="Z6" s="3">
-        <v>-1.19142248251213E-8</v>
-      </c>
-      <c r="AA6" s="3">
-        <v>-1.01277183497874E-6</v>
-      </c>
-      <c r="AB6" s="3">
-        <v>-1.6868568583899298E-8</v>
-      </c>
-      <c r="AC6" s="3">
-        <v>-1.7119884677995299E-6</v>
-      </c>
-      <c r="AD6" s="3">
-        <v>-2.38728256149929E-9</v>
-      </c>
-      <c r="AE6" s="3">
-        <v>-4.2281946664544297E-9</v>
+        <v>2.5363953227354399E-8</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>5.5861475364458103E-5</v>
+        <v>1.24602766933448E-3</v>
       </c>
       <c r="C7" s="3">
-        <v>4.2627333639507602E-7</v>
+        <v>1.03941423048226E-5</v>
       </c>
       <c r="D7" s="3">
-        <v>-1.2730687267039199E-5</v>
+        <v>-2.20678822207496E-5</v>
       </c>
       <c r="E7" s="3">
-        <v>2.89037012688621E-8</v>
+        <v>9.3244115645968599E-8</v>
       </c>
       <c r="F7" s="3">
-        <v>-1.07550805011178E-5</v>
+        <v>-7.5835894890573899E-6</v>
       </c>
       <c r="G7" s="3">
-        <v>3.35153263200716E-8</v>
+        <v>1.7276047392776699E-8</v>
       </c>
       <c r="H7" s="3">
-        <v>8.4342195222668002E-8</v>
+        <v>1.2018761467241101E-7</v>
       </c>
       <c r="I7" s="3">
-        <v>1.2720708958473899E-5</v>
+        <v>2.4896603746977202E-6</v>
       </c>
       <c r="J7" s="3">
-        <v>-2.8910371809689999E-8</v>
+        <v>-4.6649077666843097E-8</v>
       </c>
       <c r="K7" s="3">
-        <v>1.0776633131646701E-5</v>
+        <v>-5.4253202543022897E-8</v>
       </c>
       <c r="L7" s="3">
-        <v>-3.3552400714094101E-8</v>
+        <v>-1.40962918782938E-7</v>
       </c>
       <c r="M7" s="3">
-        <v>-8.4255885474116597E-8</v>
+        <v>-1.25313845761621E-7</v>
       </c>
       <c r="N7" s="3">
-        <v>4.85171799704477E-7</v>
+        <v>-3.87969118862372E-8</v>
       </c>
       <c r="O7" s="3">
-        <v>1.4718208970971601E-9</v>
+        <v>7.1569427468724803E-8</v>
       </c>
       <c r="P7" s="3">
-        <v>-1.08912156633368E-8</v>
+        <v>-1.98445037526611E-7</v>
       </c>
       <c r="Q7" s="3">
-        <v>2.11765600072742E-8</v>
+        <v>-1.50424457315999E-7</v>
       </c>
       <c r="R7" s="3">
-        <v>-2.1509396451579401E-8</v>
+        <v>3.1528826670931298E-8</v>
       </c>
       <c r="S7" s="3">
-        <v>1.7858979455248701E-8</v>
+        <v>-5.4401984672664301E-8</v>
       </c>
       <c r="T7" s="3">
-        <v>-1.07598233820826E-8</v>
-      </c>
-      <c r="U7" s="3">
-        <v>1.5763048125408299E-8</v>
-      </c>
-      <c r="V7" s="3">
-        <v>1.0591673151090299E-8</v>
-      </c>
-      <c r="W7" s="3">
-        <v>-2.7545664026340501E-8</v>
-      </c>
-      <c r="X7" s="3">
-        <v>1.8410488850628699E-9</v>
-      </c>
-      <c r="Y7" s="3">
-        <v>-8.0628341323405592E-9</v>
-      </c>
-      <c r="Z7" s="3">
-        <v>2.2777434251636898E-9</v>
-      </c>
-      <c r="AA7" s="3">
-        <v>-2.1505393777460999E-7</v>
-      </c>
-      <c r="AB7" s="3">
-        <v>3.0206602250118798E-9</v>
-      </c>
-      <c r="AC7" s="3">
-        <v>-9.9609670178794306E-8</v>
-      </c>
-      <c r="AD7" s="3">
-        <v>6.1800208495018004E-11</v>
-      </c>
-      <c r="AE7" s="3">
-        <v>-3.4521369531308798E-8</v>
+        <v>-1.12458184845013E-7</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0.99572501928013102</v>
+      </c>
+      <c r="C8" s="3">
+        <v>-6.9841930969792099E-4</v>
+      </c>
+      <c r="D8" s="3">
+        <v>-2.12410488986844E-4</v>
+      </c>
+      <c r="E8" s="3">
+        <v>-1.67647453075414E-6</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1.08148072343284E-3</v>
+      </c>
+      <c r="G8" s="3">
+        <v>-2.3635878554329899E-6</v>
+      </c>
+      <c r="H8" s="3">
+        <v>2.4896603746977202E-6</v>
+      </c>
+      <c r="I8" s="3">
+        <v>1.60895116724665E-2</v>
+      </c>
+      <c r="J8" s="3">
+        <v>-4.6727534814555196E-6</v>
+      </c>
+      <c r="K8" s="3">
+        <v>-3.7158793142576402E-5</v>
+      </c>
+      <c r="L8" s="3">
+        <v>-1.3780982442612601E-5</v>
+      </c>
+      <c r="M8" s="3">
+        <v>5.1049345243527497E-6</v>
+      </c>
+      <c r="N8" s="3">
+        <v>6.2379790741545796E-6</v>
+      </c>
+      <c r="O8" s="3">
+        <v>1.7583205855964999E-5</v>
+      </c>
+      <c r="P8" s="3">
+        <v>-2.1144908080539602E-6</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>1.6718531950615899E-5</v>
+      </c>
+      <c r="R8" s="3">
+        <v>-2.0035426825111801E-5</v>
+      </c>
+      <c r="S8" s="3">
+        <v>4.9436262853670103E-5</v>
+      </c>
+      <c r="T8" s="3">
+        <v>-8.6720788823514795E-6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B9" s="3">
+        <v>-8.1972965338796E-3</v>
+      </c>
+      <c r="C9" s="3">
+        <v>-1.9951459761529201E-5</v>
+      </c>
+      <c r="D9" s="3">
+        <v>6.1214312387262998E-6</v>
+      </c>
+      <c r="E9" s="3">
+        <v>8.4998118401502599E-8</v>
+      </c>
+      <c r="F9" s="3">
+        <v>-1.31449874069332E-4</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1.8569949547692401E-8</v>
+      </c>
+      <c r="H9" s="3">
+        <v>-4.6649077666843097E-8</v>
+      </c>
+      <c r="I9" s="3">
+        <v>-4.6727534814555196E-6</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1.8271885283959599E-4</v>
+      </c>
+      <c r="K9" s="3">
+        <v>1.2861587344386601E-4</v>
+      </c>
+      <c r="L9" s="3">
+        <v>1.28589387989384E-4</v>
+      </c>
+      <c r="M9" s="3">
+        <v>1.2874140956800799E-4</v>
+      </c>
+      <c r="N9" s="3">
+        <v>1.2867264665216999E-4</v>
+      </c>
+      <c r="O9" s="3">
+        <v>1.28798172267812E-4</v>
+      </c>
+      <c r="P9" s="3">
+        <v>1.2908218446648799E-4</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>1.2871086317220299E-4</v>
+      </c>
+      <c r="R9" s="3">
+        <v>1.28157377023514E-4</v>
+      </c>
+      <c r="S9" s="3">
+        <v>1.2850517839577201E-4</v>
+      </c>
+      <c r="T9" s="3">
+        <v>1.2823071191081999E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B10" s="3">
+        <v>-6.8212570985156198E-4</v>
+      </c>
+      <c r="C10" s="3">
+        <v>-1.56280416303169E-5</v>
+      </c>
+      <c r="D10" s="3">
+        <v>8.6132197989848994E-6</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3.23626215977667E-8</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-1.4110878557804701E-4</v>
+      </c>
+      <c r="G10" s="3">
+        <v>4.9362830960052602E-8</v>
+      </c>
+      <c r="H10" s="3">
+        <v>-5.4253202543022897E-8</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-3.7158793142576402E-5</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1.2861587344386601E-4</v>
+      </c>
+      <c r="K10" s="3">
+        <v>1.9429699234282E-4</v>
+      </c>
+      <c r="L10" s="3">
+        <v>1.28268875179628E-4</v>
+      </c>
+      <c r="M10" s="3">
+        <v>1.2823086318456201E-4</v>
+      </c>
+      <c r="N10" s="3">
+        <v>1.28263976140674E-4</v>
+      </c>
+      <c r="O10" s="3">
+        <v>1.2815158340243201E-4</v>
+      </c>
+      <c r="P10" s="3">
+        <v>1.2857424237435299E-4</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>1.2823793376952401E-4</v>
+      </c>
+      <c r="R10" s="3">
+        <v>1.2800878876395E-4</v>
+      </c>
+      <c r="S10" s="3">
+        <v>1.2806925814576499E-4</v>
+      </c>
+      <c r="T10" s="3">
+        <v>1.2837966944789301E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B11" s="3">
+        <v>-4.4596424160110298E-4</v>
+      </c>
+      <c r="C11" s="3">
+        <v>-1.6085496742759701E-5</v>
+      </c>
+      <c r="D11" s="3">
+        <v>2.2536356875863299E-5</v>
+      </c>
+      <c r="E11" s="3">
+        <v>3.4279766294984102E-9</v>
+      </c>
+      <c r="F11" s="3">
+        <v>-1.16254410988808E-4</v>
+      </c>
+      <c r="G11" s="3">
+        <v>-2.97719140735268E-8</v>
+      </c>
+      <c r="H11" s="3">
+        <v>-1.40962918782938E-7</v>
+      </c>
+      <c r="I11" s="3">
+        <v>-1.3780982442612601E-5</v>
+      </c>
+      <c r="J11" s="3">
+        <v>1.28589387989384E-4</v>
+      </c>
+      <c r="K11" s="3">
+        <v>1.28268875179628E-4</v>
+      </c>
+      <c r="L11" s="3">
+        <v>2.19627493319524E-4</v>
+      </c>
+      <c r="M11" s="3">
+        <v>1.2884193331577599E-4</v>
+      </c>
+      <c r="N11" s="3">
+        <v>1.2863839335840199E-4</v>
+      </c>
+      <c r="O11" s="3">
+        <v>1.28716701703317E-4</v>
+      </c>
+      <c r="P11" s="3">
+        <v>1.2909668980630199E-4</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>1.2881053694984901E-4</v>
+      </c>
+      <c r="R11" s="3">
+        <v>1.2813856128638499E-4</v>
+      </c>
+      <c r="S11" s="3">
+        <v>1.2847479183651601E-4</v>
+      </c>
+      <c r="T11" s="3">
+        <v>1.2804314241824901E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B12" s="3">
+        <v>-5.4173523046E-3</v>
+      </c>
+      <c r="C12" s="3">
+        <v>-1.6810972813864102E-5</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1.81868866518548E-5</v>
+      </c>
+      <c r="E12" s="3">
+        <v>5.00464040914354E-8</v>
+      </c>
+      <c r="F12" s="3">
+        <v>-1.1205120093657801E-4</v>
+      </c>
+      <c r="G12" s="3">
+        <v>-4.4378821342023198E-8</v>
+      </c>
+      <c r="H12" s="3">
+        <v>-1.25313845761621E-7</v>
+      </c>
+      <c r="I12" s="3">
+        <v>5.1049345243527497E-6</v>
+      </c>
+      <c r="J12" s="3">
+        <v>1.2874140956800799E-4</v>
+      </c>
+      <c r="K12" s="3">
+        <v>1.2823086318456201E-4</v>
+      </c>
+      <c r="L12" s="3">
+        <v>1.2884193331577599E-4</v>
+      </c>
+      <c r="M12" s="3">
+        <v>2.0167687277329699E-4</v>
+      </c>
+      <c r="N12" s="3">
+        <v>1.2889660150704901E-4</v>
+      </c>
+      <c r="O12" s="3">
+        <v>1.29047466392553E-4</v>
+      </c>
+      <c r="P12" s="3">
+        <v>1.29395492257354E-4</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>1.2910775674281099E-4</v>
+      </c>
+      <c r="R12" s="3">
+        <v>1.2822982475839699E-4</v>
+      </c>
+      <c r="S12" s="3">
+        <v>1.2871723215705601E-4</v>
+      </c>
+      <c r="T12" s="3">
+        <v>1.2797977117152899E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B13" s="3">
+        <v>-8.3842014307038606E-3</v>
+      </c>
+      <c r="C13" s="3">
+        <v>2.8045648463842E-5</v>
+      </c>
+      <c r="D13" s="3">
+        <v>-9.3509941745020897E-7</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1.26981749798527E-7</v>
+      </c>
+      <c r="F13" s="3">
+        <v>-1.2246688883600201E-4</v>
+      </c>
+      <c r="G13" s="3">
+        <v>-1.84627955760693E-8</v>
+      </c>
+      <c r="H13" s="3">
+        <v>-3.87969118862372E-8</v>
+      </c>
+      <c r="I13" s="3">
+        <v>6.2379790741545796E-6</v>
+      </c>
+      <c r="J13" s="3">
+        <v>1.2867264665216999E-4</v>
+      </c>
+      <c r="K13" s="3">
+        <v>1.28263976140674E-4</v>
+      </c>
+      <c r="L13" s="3">
+        <v>1.2863839335840199E-4</v>
+      </c>
+      <c r="M13" s="3">
+        <v>1.2889660150704901E-4</v>
+      </c>
+      <c r="N13" s="3">
+        <v>1.8497035979113499E-4</v>
+      </c>
+      <c r="O13" s="3">
+        <v>1.2861294772255899E-4</v>
+      </c>
+      <c r="P13" s="3">
+        <v>1.2912919417246599E-4</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>1.2898803287014299E-4</v>
+      </c>
+      <c r="R13" s="3">
+        <v>1.28185529936824E-4</v>
+      </c>
+      <c r="S13" s="3">
+        <v>1.2851062493150799E-4</v>
+      </c>
+      <c r="T13" s="3">
+        <v>1.2806928906562701E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B14" s="3">
+        <v>7.0813954923913802E-3</v>
+      </c>
+      <c r="C14" s="3">
+        <v>-1.69121915246763E-4</v>
+      </c>
+      <c r="D14" s="3">
+        <v>4.96156039309976E-6</v>
+      </c>
+      <c r="E14" s="3">
+        <v>6.7466998015694194E-8</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-1.16349003759329E-4</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-1.95762401573888E-8</v>
+      </c>
+      <c r="H14" s="3">
+        <v>7.1569427468724803E-8</v>
+      </c>
+      <c r="I14" s="3">
+        <v>1.7583205855964999E-5</v>
+      </c>
+      <c r="J14" s="3">
+        <v>1.28798172267812E-4</v>
+      </c>
+      <c r="K14" s="3">
+        <v>1.2815158340243201E-4</v>
+      </c>
+      <c r="L14" s="3">
+        <v>1.28716701703317E-4</v>
+      </c>
+      <c r="M14" s="3">
+        <v>1.29047466392553E-4</v>
+      </c>
+      <c r="N14" s="3">
+        <v>1.2861294772255899E-4</v>
+      </c>
+      <c r="O14" s="3">
+        <v>2.0162779045955801E-4</v>
+      </c>
+      <c r="P14" s="3">
+        <v>1.29149652459675E-4</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>1.2825370519533501E-4</v>
+      </c>
+      <c r="R14" s="3">
+        <v>1.28387798462399E-4</v>
+      </c>
+      <c r="S14" s="3">
+        <v>1.29171340856517E-4</v>
+      </c>
+      <c r="T14" s="3">
+        <v>1.2725999699466701E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B15" s="3">
+        <v>-8.6466993167642007E-3</v>
+      </c>
+      <c r="C15" s="3">
+        <v>-3.7489818026374599E-6</v>
+      </c>
+      <c r="D15" s="3">
+        <v>3.0444920369570299E-5</v>
+      </c>
+      <c r="E15" s="3">
+        <v>2.9257034913650999E-8</v>
+      </c>
+      <c r="F15" s="3">
+        <v>-1.12737357219583E-4</v>
+      </c>
+      <c r="G15" s="3">
+        <v>-3.6634297609672803E-8</v>
+      </c>
+      <c r="H15" s="3">
+        <v>-1.98445037526611E-7</v>
+      </c>
+      <c r="I15" s="3">
+        <v>-2.1144908080539602E-6</v>
+      </c>
+      <c r="J15" s="3">
+        <v>1.2908218446648799E-4</v>
+      </c>
+      <c r="K15" s="3">
+        <v>1.2857424237435299E-4</v>
+      </c>
+      <c r="L15" s="3">
+        <v>1.2909668980630199E-4</v>
+      </c>
+      <c r="M15" s="3">
+        <v>1.29395492257354E-4</v>
+      </c>
+      <c r="N15" s="3">
+        <v>1.2912919417246599E-4</v>
+      </c>
+      <c r="O15" s="3">
+        <v>1.29149652459675E-4</v>
+      </c>
+      <c r="P15" s="3">
+        <v>1.6985912726237101E-4</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>1.2940122871540999E-4</v>
+      </c>
+      <c r="R15" s="3">
+        <v>1.28288053350757E-4</v>
+      </c>
+      <c r="S15" s="3">
+        <v>1.28876243626055E-4</v>
+      </c>
+      <c r="T15" s="3">
+        <v>1.28239416372725E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B16" s="3">
+        <v>-1.52704841429614E-2</v>
+      </c>
+      <c r="C16" s="3">
+        <v>5.7103493780468003E-5</v>
+      </c>
+      <c r="D16" s="3">
+        <v>1.42405086502582E-5</v>
+      </c>
+      <c r="E16" s="3">
+        <v>7.8520358290831098E-8</v>
+      </c>
+      <c r="F16" s="3">
+        <v>-1.13525292221057E-4</v>
+      </c>
+      <c r="G16" s="3">
+        <v>-4.5318350624731501E-8</v>
+      </c>
+      <c r="H16" s="3">
+        <v>-1.50424457315999E-7</v>
+      </c>
+      <c r="I16" s="3">
+        <v>1.6718531950615899E-5</v>
+      </c>
+      <c r="J16" s="3">
+        <v>1.2871086317220299E-4</v>
+      </c>
+      <c r="K16" s="3">
+        <v>1.2823793376952401E-4</v>
+      </c>
+      <c r="L16" s="3">
+        <v>1.2881053694984901E-4</v>
+      </c>
+      <c r="M16" s="3">
+        <v>1.2910775674281099E-4</v>
+      </c>
+      <c r="N16" s="3">
+        <v>1.2898803287014299E-4</v>
+      </c>
+      <c r="O16" s="3">
+        <v>1.2825370519533501E-4</v>
+      </c>
+      <c r="P16" s="3">
+        <v>1.2940122871540999E-4</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>1.9031549287813301E-4</v>
+      </c>
+      <c r="R16" s="3">
+        <v>1.2815557511586801E-4</v>
+      </c>
+      <c r="S16" s="3">
+        <v>1.28557353679376E-4</v>
+      </c>
+      <c r="T16" s="3">
+        <v>1.2823405924706699E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B17" s="3">
+        <v>6.8823809369989702E-3</v>
+      </c>
+      <c r="C17" s="3">
+        <v>2.9753483553440498E-6</v>
+      </c>
+      <c r="D17" s="3">
+        <v>-6.9696922151638896E-6</v>
+      </c>
+      <c r="E17" s="3">
+        <v>7.8818250748758297E-8</v>
+      </c>
+      <c r="F17" s="3">
+        <v>-1.28598471605231E-4</v>
+      </c>
+      <c r="G17" s="3">
+        <v>-6.6291409138536298E-10</v>
+      </c>
+      <c r="H17" s="3">
+        <v>3.1528826670931298E-8</v>
+      </c>
+      <c r="I17" s="3">
+        <v>-2.0035426825111801E-5</v>
+      </c>
+      <c r="J17" s="3">
+        <v>1.28157377023514E-4</v>
+      </c>
+      <c r="K17" s="3">
+        <v>1.2800878876395E-4</v>
+      </c>
+      <c r="L17" s="3">
+        <v>1.2813856128638499E-4</v>
+      </c>
+      <c r="M17" s="3">
+        <v>1.2822982475839699E-4</v>
+      </c>
+      <c r="N17" s="3">
+        <v>1.28185529936824E-4</v>
+      </c>
+      <c r="O17" s="3">
+        <v>1.28387798462399E-4</v>
+      </c>
+      <c r="P17" s="3">
+        <v>1.28288053350757E-4</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>1.2815557511586801E-4</v>
+      </c>
+      <c r="R17" s="3">
+        <v>2.32080654378979E-4</v>
+      </c>
+      <c r="S17" s="3">
+        <v>1.2807525024838501E-4</v>
+      </c>
+      <c r="T17" s="3">
+        <v>1.27809838639794E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B8" s="3">
-        <v>1.5674779902935899E-2</v>
-      </c>
-      <c r="C8" s="3">
-        <v>-1.9450413424968002E-5</v>
-      </c>
-      <c r="D8" s="3">
-        <v>-2.06160105552984E-3</v>
-      </c>
-      <c r="E8" s="3">
-        <v>5.6158890554165002E-6</v>
-      </c>
-      <c r="F8" s="3">
-        <v>-1.6899105423629601E-3</v>
-      </c>
-      <c r="G8" s="3">
-        <v>5.0754976343013002E-6</v>
-      </c>
-      <c r="H8" s="3">
-        <v>1.2720708958473899E-5</v>
-      </c>
-      <c r="I8" s="3">
-        <v>4.0682581136420601E-3</v>
-      </c>
-      <c r="J8" s="3">
-        <v>-9.2610457276485895E-6</v>
-      </c>
-      <c r="K8" s="3">
-        <v>3.3314503288669802E-3</v>
-      </c>
-      <c r="L8" s="3">
-        <v>-1.0102331975707099E-5</v>
-      </c>
-      <c r="M8" s="3">
-        <v>-2.5822408089234501E-5</v>
-      </c>
-      <c r="N8" s="3">
-        <v>-3.60314256785438E-4</v>
-      </c>
-      <c r="O8" s="3">
-        <v>-1.0918987652906199E-7</v>
-      </c>
-      <c r="P8" s="3">
-        <v>-1.0221124129057E-6</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>5.9238585619971002E-6</v>
-      </c>
-      <c r="R8" s="3">
-        <v>-1.70294284882643E-6</v>
-      </c>
-      <c r="S8" s="3">
-        <v>4.8283917176307801E-6</v>
-      </c>
-      <c r="T8" s="3">
-        <v>-1.0869179829134801E-6</v>
-      </c>
-      <c r="U8" s="3">
-        <v>2.1773710138984202E-6</v>
-      </c>
-      <c r="V8" s="3">
-        <v>3.1564170494286799E-6</v>
-      </c>
-      <c r="W8" s="3">
-        <v>-1.6330136371509201E-4</v>
-      </c>
-      <c r="X8" s="3">
-        <v>4.8464491858741802E-6</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>-7.8366137303311205E-6</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>5.3127332084190401E-6</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>-4.5652088834934702E-4</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>3.0300240647553599E-7</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>-4.1624261082025998E-4</v>
-      </c>
-      <c r="AD8" s="3">
-        <v>-6.1937828808712196E-6</v>
-      </c>
-      <c r="AE8" s="3">
-        <v>3.96136649828362E-5</v>
+      <c r="B18" s="3">
+        <v>-1.56186443086244E-2</v>
+      </c>
+      <c r="C18" s="3">
+        <v>-4.3012352796894299E-5</v>
+      </c>
+      <c r="D18" s="3">
+        <v>1.3029580279298299E-5</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1.5682050871755901E-8</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-1.15812272087677E-4</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-2.649256276039E-8</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-5.4401984672664301E-8</v>
+      </c>
+      <c r="I18" s="3">
+        <v>4.9436262853670103E-5</v>
+      </c>
+      <c r="J18" s="3">
+        <v>1.2850517839577201E-4</v>
+      </c>
+      <c r="K18" s="3">
+        <v>1.2806925814576499E-4</v>
+      </c>
+      <c r="L18" s="3">
+        <v>1.2847479183651601E-4</v>
+      </c>
+      <c r="M18" s="3">
+        <v>1.2871723215705601E-4</v>
+      </c>
+      <c r="N18" s="3">
+        <v>1.2851062493150799E-4</v>
+      </c>
+      <c r="O18" s="3">
+        <v>1.29171340856517E-4</v>
+      </c>
+      <c r="P18" s="3">
+        <v>1.28876243626055E-4</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>1.28557353679376E-4</v>
+      </c>
+      <c r="R18" s="3">
+        <v>1.2807525024838501E-4</v>
+      </c>
+      <c r="S18" s="3">
+        <v>1.9081121324572101E-4</v>
+      </c>
+      <c r="T18" s="3">
+        <v>1.2781627363187101E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="B9" s="3">
-        <v>1.9799246364819599E-6</v>
-      </c>
-      <c r="C9" s="3">
-        <v>-5.7012562247928403E-9</v>
-      </c>
-      <c r="D9" s="3">
-        <v>5.6033032571383701E-6</v>
-      </c>
-      <c r="E9" s="3">
-        <v>-2.4037970488982201E-8</v>
-      </c>
-      <c r="F9" s="3">
-        <v>3.9132371300900496E-6</v>
-      </c>
-      <c r="G9" s="3">
-        <v>-1.08884644638723E-8</v>
-      </c>
-      <c r="H9" s="3">
-        <v>-2.8910371809689999E-8</v>
-      </c>
-      <c r="I9" s="3">
-        <v>-9.2610457276485895E-6</v>
-      </c>
-      <c r="J9" s="3">
-        <v>3.7039295322054999E-8</v>
-      </c>
-      <c r="K9" s="3">
-        <v>-6.3868700491256098E-6</v>
-      </c>
-      <c r="L9" s="3">
-        <v>1.7578178552832399E-8</v>
-      </c>
-      <c r="M9" s="3">
-        <v>4.78439499748889E-8</v>
-      </c>
-      <c r="N9" s="3">
-        <v>5.4551901115884604E-7</v>
-      </c>
-      <c r="O9" s="3">
-        <v>-3.5846327869169501E-10</v>
-      </c>
-      <c r="P9" s="3">
-        <v>-1.36258977667542E-8</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>-1.9808713530690699E-8</v>
-      </c>
-      <c r="R9" s="3">
-        <v>-2.1409803017793801E-8</v>
-      </c>
-      <c r="S9" s="3">
-        <v>-2.5290579834443499E-8</v>
-      </c>
-      <c r="T9" s="3">
-        <v>-1.680557053617E-8</v>
-      </c>
-      <c r="U9" s="3">
-        <v>-1.3507741620132001E-8</v>
-      </c>
-      <c r="V9" s="3">
-        <v>-7.1843560648331799E-9</v>
-      </c>
-      <c r="W9" s="3">
-        <v>1.4366113284974601E-6</v>
-      </c>
-      <c r="X9" s="3">
-        <v>8.8624719149530201E-9</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>2.39359101820782E-8</v>
-      </c>
-      <c r="Z9" s="3">
-        <v>1.6284997251971601E-8</v>
-      </c>
-      <c r="AA9" s="3">
-        <v>8.4304809464155598E-7</v>
-      </c>
-      <c r="AB9" s="3">
-        <v>1.6328844638368399E-8</v>
-      </c>
-      <c r="AC9" s="3">
-        <v>-2.38213687960778E-7</v>
-      </c>
-      <c r="AD9" s="3">
-        <v>8.9490495832072994E-9</v>
-      </c>
-      <c r="AE9" s="3">
-        <v>-2.49820286317083E-7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="3">
-        <v>2.6758213703980401E-2</v>
-      </c>
-      <c r="C10" s="3">
-        <v>5.4792089090609801E-5</v>
-      </c>
-      <c r="D10" s="3">
-        <v>-1.66963385651895E-3</v>
-      </c>
-      <c r="E10" s="3">
-        <v>3.8888376684996798E-6</v>
-      </c>
-      <c r="F10" s="3">
-        <v>-2.1239481131728301E-3</v>
-      </c>
-      <c r="G10" s="3">
-        <v>6.73467369315291E-6</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1.0776633131646701E-5</v>
-      </c>
-      <c r="I10" s="3">
-        <v>3.3314503288669802E-3</v>
-      </c>
-      <c r="J10" s="3">
-        <v>-6.3868700491256098E-6</v>
-      </c>
-      <c r="K10" s="3">
-        <v>4.6108070650138101E-3</v>
-      </c>
-      <c r="L10" s="3">
-        <v>-1.47718493978646E-5</v>
-      </c>
-      <c r="M10" s="3">
-        <v>-2.20546317335719E-5</v>
-      </c>
-      <c r="N10" s="3">
-        <v>-1.80713894866647E-4</v>
-      </c>
-      <c r="O10" s="3">
-        <v>-1.88335156310336E-6</v>
-      </c>
-      <c r="P10" s="3">
-        <v>5.2792204415593798E-6</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>1.3969282250554E-5</v>
-      </c>
-      <c r="R10" s="3">
-        <v>3.8255747140326004E-6</v>
-      </c>
-      <c r="S10" s="3">
-        <v>1.00859771508938E-5</v>
-      </c>
-      <c r="T10" s="3">
-        <v>2.0783965526135399E-6</v>
-      </c>
-      <c r="U10" s="3">
-        <v>5.7277235040851903E-6</v>
-      </c>
-      <c r="V10" s="3">
-        <v>-2.0387022210041599E-7</v>
-      </c>
-      <c r="W10" s="3">
-        <v>-2.20139485419299E-4</v>
-      </c>
-      <c r="X10" s="3">
-        <v>-8.4216674854528906E-6</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>-2.9167573376397699E-5</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>-5.6181224798459203E-6</v>
-      </c>
-      <c r="AA10" s="3">
-        <v>-1.4426314321205301E-3</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>-4.8313977370567103E-6</v>
-      </c>
-      <c r="AC10" s="3">
-        <v>-1.13668757442359E-3</v>
-      </c>
-      <c r="AD10" s="3">
-        <v>-2.7588637946059201E-6</v>
-      </c>
-      <c r="AE10" s="3">
-        <v>3.2304296443269002E-5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="3">
-        <v>-1.2273139232720301E-4</v>
-      </c>
-      <c r="C11" s="3">
-        <v>-2.2681141620312401E-7</v>
-      </c>
-      <c r="D11" s="3">
-        <v>5.0383735027121401E-6</v>
-      </c>
-      <c r="E11" s="3">
-        <v>-1.08547654697684E-8</v>
-      </c>
-      <c r="F11" s="3">
-        <v>6.7523665847881301E-6</v>
-      </c>
-      <c r="G11" s="3">
-        <v>-2.1758561176163999E-8</v>
-      </c>
-      <c r="H11" s="3">
-        <v>-3.3552400714094101E-8</v>
-      </c>
-      <c r="I11" s="3">
-        <v>-1.0102331975707099E-5</v>
-      </c>
-      <c r="J11" s="3">
-        <v>1.7578178552832399E-8</v>
-      </c>
-      <c r="K11" s="3">
-        <v>-1.47718493978646E-5</v>
-      </c>
-      <c r="L11" s="3">
-        <v>4.8079992001042799E-8</v>
-      </c>
-      <c r="M11" s="3">
-        <v>6.9020313175408906E-8</v>
-      </c>
-      <c r="N11" s="3">
-        <v>6.3347858642379704E-7</v>
-      </c>
-      <c r="O11" s="3">
-        <v>6.7171700757923099E-9</v>
-      </c>
-      <c r="P11" s="3">
-        <v>-2.0582819260719701E-8</v>
-      </c>
-      <c r="Q11" s="3">
-        <v>-4.2577530733342301E-8</v>
-      </c>
-      <c r="R11" s="3">
-        <v>-1.8397198617289299E-8</v>
-      </c>
-      <c r="S11" s="3">
-        <v>-3.6814641556084201E-8</v>
-      </c>
-      <c r="T11" s="3">
-        <v>-1.47430468131336E-8</v>
-      </c>
-      <c r="U11" s="3">
-        <v>-2.7098997092493899E-8</v>
-      </c>
-      <c r="V11" s="3">
-        <v>-1.02694825328009E-8</v>
-      </c>
-      <c r="W11" s="3">
-        <v>5.6115990202953503E-8</v>
-      </c>
-      <c r="X11" s="3">
-        <v>2.9392240946629E-8</v>
-      </c>
-      <c r="Y11" s="3">
-        <v>8.9129318340567906E-8</v>
-      </c>
-      <c r="Z11" s="3">
-        <v>2.5466241507931901E-8</v>
-      </c>
-      <c r="AA11" s="3">
-        <v>4.9028998842065999E-6</v>
-      </c>
-      <c r="AB11" s="3">
-        <v>2.5602908621452001E-8</v>
-      </c>
-      <c r="AC11" s="3">
-        <v>4.5476868020242098E-6</v>
-      </c>
-      <c r="AD11" s="3">
-        <v>2.08158788748257E-8</v>
-      </c>
-      <c r="AE11" s="3">
-        <v>1.0551011155236501E-8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="3">
-        <v>-1.3829572049644501E-4</v>
-      </c>
-      <c r="C12" s="3">
-        <v>1.3345356051517001E-7</v>
-      </c>
-      <c r="D12" s="3">
-        <v>1.2728986499007001E-5</v>
-      </c>
-      <c r="E12" s="3">
-        <v>-2.9015396737953202E-8</v>
-      </c>
-      <c r="F12" s="3">
-        <v>1.0930183137874E-5</v>
-      </c>
-      <c r="G12" s="3">
-        <v>-3.3840560782707297E-8</v>
-      </c>
-      <c r="H12" s="3">
-        <v>-8.4255885474116597E-8</v>
-      </c>
-      <c r="I12" s="3">
-        <v>-2.5822408089234501E-5</v>
-      </c>
-      <c r="J12" s="3">
-        <v>4.78439499748889E-8</v>
-      </c>
-      <c r="K12" s="3">
-        <v>-2.20546317335719E-5</v>
-      </c>
-      <c r="L12" s="3">
-        <v>6.9020313175408906E-8</v>
-      </c>
-      <c r="M12" s="3">
-        <v>1.75215649450174E-7</v>
-      </c>
-      <c r="N12" s="3">
-        <v>2.65238874080156E-6</v>
-      </c>
-      <c r="O12" s="3">
-        <v>1.23953466027715E-9</v>
-      </c>
-      <c r="P12" s="3">
-        <v>1.9219483819745199E-8</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>-2.1589330938787101E-8</v>
-      </c>
-      <c r="R12" s="3">
-        <v>3.5625296281652297E-8</v>
-      </c>
-      <c r="S12" s="3">
-        <v>-7.9312539776170302E-9</v>
-      </c>
-      <c r="T12" s="3">
-        <v>3.1054006457303099E-8</v>
-      </c>
-      <c r="U12" s="3">
-        <v>1.61208966174969E-9</v>
-      </c>
-      <c r="V12" s="3">
-        <v>-8.4887729327274501E-9</v>
-      </c>
-      <c r="W12" s="3">
-        <v>-4.33838734377108E-7</v>
-      </c>
-      <c r="X12" s="3">
-        <v>-4.7401609513606601E-8</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>2.7956348290028201E-8</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>-6.15497249934948E-8</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>3.0354419539865501E-6</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>-2.3891852682965301E-8</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>4.2850359803336201E-6</v>
-      </c>
-      <c r="AD12" s="3">
-        <v>3.1453763039611501E-8</v>
-      </c>
-      <c r="AE12" s="3">
-        <v>-1.5113910206191199E-8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="3">
-        <v>2.2705466677337101</v>
-      </c>
-      <c r="C13" s="3">
-        <v>-1.45976076676486E-3</v>
-      </c>
-      <c r="D13" s="3">
-        <v>7.7905118409062795E-6</v>
-      </c>
-      <c r="E13" s="3">
-        <v>-8.42224261010507E-7</v>
-      </c>
-      <c r="F13" s="3">
-        <v>1.3648730633539401E-3</v>
-      </c>
-      <c r="G13" s="3">
-        <v>-2.4887305256268201E-6</v>
-      </c>
-      <c r="H13" s="3">
-        <v>4.85171799704477E-7</v>
-      </c>
-      <c r="I13" s="3">
-        <v>-3.60314256785438E-4</v>
-      </c>
-      <c r="J13" s="3">
-        <v>5.4551901115884604E-7</v>
-      </c>
-      <c r="K13" s="3">
-        <v>-1.80713894866647E-4</v>
-      </c>
-      <c r="L13" s="3">
-        <v>6.3347858642379704E-7</v>
-      </c>
-      <c r="M13" s="3">
-        <v>2.65238874080156E-6</v>
-      </c>
-      <c r="N13" s="3">
-        <v>2.4002318081982301E-2</v>
-      </c>
-      <c r="O13" s="3">
-        <v>6.7497504647905401E-6</v>
-      </c>
-      <c r="P13" s="3">
-        <v>5.9670896535975101E-5</v>
-      </c>
-      <c r="Q13" s="3">
-        <v>9.7790571324122096E-5</v>
-      </c>
-      <c r="R13" s="3">
-        <v>1.08213961413623E-4</v>
-      </c>
-      <c r="S13" s="3">
-        <v>1.3215419949606899E-4</v>
-      </c>
-      <c r="T13" s="3">
-        <v>1.5757211478519399E-4</v>
-      </c>
-      <c r="U13" s="3">
-        <v>1.88510316173865E-4</v>
-      </c>
-      <c r="V13" s="3">
-        <v>2.0094480297840898E-5</v>
-      </c>
-      <c r="W13" s="3">
-        <v>-9.31251023493098E-4</v>
-      </c>
-      <c r="X13" s="3">
-        <v>6.4462625566343999E-5</v>
-      </c>
-      <c r="Y13" s="3">
-        <v>1.2416583230065201E-4</v>
-      </c>
-      <c r="Z13" s="3">
-        <v>1.13553584448123E-4</v>
-      </c>
-      <c r="AA13" s="3">
-        <v>9.0860139493382005E-3</v>
-      </c>
-      <c r="AB13" s="3">
-        <v>1.61155868338051E-4</v>
-      </c>
-      <c r="AC13" s="3">
-        <v>1.5811559315374198E-2</v>
-      </c>
-      <c r="AD13" s="3">
-        <v>2.1354969270057898E-5</v>
-      </c>
-      <c r="AE13" s="3">
-        <v>-1.7818291051150901E-5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B14" s="3">
-        <v>-1.35734328536476E-2</v>
-      </c>
-      <c r="C14" s="3">
-        <v>-4.4239560392802401E-4</v>
-      </c>
-      <c r="D14" s="3">
-        <v>-1.3099796384693701E-8</v>
-      </c>
-      <c r="E14" s="3">
-        <v>-1.5768931082986501E-9</v>
-      </c>
-      <c r="F14" s="3">
-        <v>2.0305308604558202E-6</v>
-      </c>
-      <c r="G14" s="3">
-        <v>-3.2854750580198301E-9</v>
-      </c>
-      <c r="H14" s="3">
-        <v>1.4718208970971601E-9</v>
-      </c>
-      <c r="I14" s="3">
-        <v>-1.0918987652906199E-7</v>
-      </c>
-      <c r="J14" s="3">
-        <v>-3.5846327869169501E-10</v>
-      </c>
-      <c r="K14" s="3">
-        <v>-1.88335156310336E-6</v>
-      </c>
-      <c r="L14" s="3">
-        <v>6.7171700757923099E-9</v>
-      </c>
-      <c r="M14" s="3">
-        <v>1.23953466027715E-9</v>
-      </c>
-      <c r="N14" s="3">
-        <v>6.7497504647905401E-6</v>
-      </c>
-      <c r="O14" s="3">
-        <v>1.5787346552941502E-5</v>
-      </c>
-      <c r="P14" s="3">
-        <v>7.2649059269395601E-7</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>9.1323982152296103E-6</v>
-      </c>
-      <c r="R14" s="3">
-        <v>8.6875804931833099E-7</v>
-      </c>
-      <c r="S14" s="3">
-        <v>5.2530493865776296E-6</v>
-      </c>
-      <c r="T14" s="3">
-        <v>9.5920177027588999E-7</v>
-      </c>
-      <c r="U14" s="3">
-        <v>5.1186424449172196E-6</v>
-      </c>
-      <c r="V14" s="3">
-        <v>1.0025458430046899E-6</v>
-      </c>
-      <c r="W14" s="3">
-        <v>1.90475354578235E-4</v>
-      </c>
-      <c r="X14" s="3">
-        <v>6.6498492243387699E-7</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>1.18894871016752E-5</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>8.7843892578780003E-7</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>3.8885890278582701E-4</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>9.816471018495259E-7</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>3.9990612529965E-4</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>1.0148492182875601E-6</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>3.3219196627751998E-5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="B15" s="3">
-        <v>-2.0050798941757802E-3</v>
-      </c>
-      <c r="C15" s="3">
-        <v>-1.38273208057125E-5</v>
-      </c>
-      <c r="D15" s="3">
-        <v>8.8767747496532897E-8</v>
-      </c>
-      <c r="E15" s="3">
-        <v>1.2794883453042E-8</v>
-      </c>
-      <c r="F15" s="3">
-        <v>-2.3901403872406398E-6</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1.6150131807205499E-8</v>
-      </c>
-      <c r="H15" s="3">
-        <v>-1.08912156633368E-8</v>
-      </c>
-      <c r="I15" s="3">
-        <v>-1.0221124129057E-6</v>
-      </c>
-      <c r="J15" s="3">
-        <v>-1.36258977667542E-8</v>
-      </c>
-      <c r="K15" s="3">
-        <v>5.2792204415593798E-6</v>
-      </c>
-      <c r="L15" s="3">
-        <v>-2.0582819260719701E-8</v>
-      </c>
-      <c r="M15" s="3">
-        <v>1.9219483819745199E-8</v>
-      </c>
-      <c r="N15" s="3">
-        <v>5.9670896535975101E-5</v>
-      </c>
-      <c r="O15" s="3">
-        <v>7.2649059269395601E-7</v>
-      </c>
-      <c r="P15" s="3">
-        <v>3.9905239920756798E-6</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>1.74371422187407E-6</v>
-      </c>
-      <c r="R15" s="3">
-        <v>1.8611587352190899E-6</v>
-      </c>
-      <c r="S15" s="3">
-        <v>1.9963008630753399E-6</v>
-      </c>
-      <c r="T15" s="3">
-        <v>2.0477484583210298E-6</v>
-      </c>
-      <c r="U15" s="3">
-        <v>2.20403362953372E-6</v>
-      </c>
-      <c r="V15" s="3">
-        <v>1.70850762373849E-6</v>
-      </c>
-      <c r="W15" s="3">
-        <v>1.3914505646704801E-5</v>
-      </c>
-      <c r="X15" s="3">
-        <v>1.9881954989842001E-7</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>6.1461366950348299E-7</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>3.1860895281410102E-7</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>3.1494834524757201E-5</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>4.3653847812177798E-7</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>4.8209162137823403E-5</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>8.9518303641746302E-8</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>7.2427379996700101E-7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B16" s="3">
-        <v>-2.2808771051673199E-2</v>
-      </c>
-      <c r="C16" s="3">
-        <v>-5.7002713262109203E-4</v>
-      </c>
-      <c r="D16" s="3">
-        <v>-5.5865571930154203E-6</v>
-      </c>
-      <c r="E16" s="3">
-        <v>1.7855419920635701E-8</v>
-      </c>
-      <c r="F16" s="3">
-        <v>-7.7677387885546099E-6</v>
-      </c>
-      <c r="G16" s="3">
-        <v>3.7241227150176697E-8</v>
-      </c>
-      <c r="H16" s="3">
-        <v>2.11765600072742E-8</v>
-      </c>
-      <c r="I16" s="3">
-        <v>5.9238585619971002E-6</v>
-      </c>
-      <c r="J16" s="3">
-        <v>-1.9808713530690699E-8</v>
-      </c>
-      <c r="K16" s="3">
-        <v>1.3969282250554E-5</v>
-      </c>
-      <c r="L16" s="3">
-        <v>-4.2577530733342301E-8</v>
-      </c>
-      <c r="M16" s="3">
-        <v>-2.1589330938787101E-8</v>
-      </c>
-      <c r="N16" s="3">
-        <v>9.7790571324122096E-5</v>
-      </c>
-      <c r="O16" s="3">
-        <v>9.1323982152296103E-6</v>
-      </c>
-      <c r="P16" s="3">
-        <v>1.74371422187407E-6</v>
-      </c>
-      <c r="Q16" s="3">
-        <v>1.00898477309969E-4</v>
-      </c>
-      <c r="R16" s="3">
-        <v>2.2187747043785398E-6</v>
-      </c>
-      <c r="S16" s="3">
-        <v>8.0524148358984206E-6</v>
-      </c>
-      <c r="T16" s="3">
-        <v>2.5553660184364099E-6</v>
-      </c>
-      <c r="U16" s="3">
-        <v>8.0723356333049807E-6</v>
-      </c>
-      <c r="V16" s="3">
-        <v>2.0687690594699399E-6</v>
-      </c>
-      <c r="W16" s="3">
-        <v>2.4645639759330402E-4</v>
-      </c>
-      <c r="X16" s="3">
-        <v>3.3277008861697502E-7</v>
-      </c>
-      <c r="Y16" s="3">
-        <v>1.4599664530026599E-5</v>
-      </c>
-      <c r="Z16" s="3">
-        <v>1.0068060718133701E-6</v>
-      </c>
-      <c r="AA16" s="3">
-        <v>5.3025685080780203E-4</v>
-      </c>
-      <c r="AB16" s="3">
-        <v>1.3947852225007701E-6</v>
-      </c>
-      <c r="AC16" s="3">
-        <v>5.7627705007456704E-4</v>
-      </c>
-      <c r="AD16" s="3">
-        <v>9.54243449060503E-7</v>
-      </c>
-      <c r="AE16" s="3">
-        <v>4.2266834945770703E-5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B17" s="3">
-        <v>1.5803642417603601E-2</v>
-      </c>
-      <c r="C17" s="3">
-        <v>-3.2806140748527603E-5</v>
-      </c>
-      <c r="D17" s="3">
-        <v>1.2827442790502899E-7</v>
-      </c>
-      <c r="E17" s="3">
-        <v>1.99766442914547E-8</v>
-      </c>
-      <c r="F17" s="3">
-        <v>1.51652690158799E-6</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1.02422739239568E-8</v>
-      </c>
-      <c r="H17" s="3">
-        <v>-2.1509396451579401E-8</v>
-      </c>
-      <c r="I17" s="3">
-        <v>-1.70294284882643E-6</v>
-      </c>
-      <c r="J17" s="3">
-        <v>-2.1409803017793801E-8</v>
-      </c>
-      <c r="K17" s="3">
-        <v>3.8255747140326004E-6</v>
-      </c>
-      <c r="L17" s="3">
-        <v>-1.8397198617289299E-8</v>
-      </c>
-      <c r="M17" s="3">
-        <v>3.5625296281652297E-8</v>
-      </c>
-      <c r="N17" s="3">
-        <v>1.08213961413623E-4</v>
-      </c>
-      <c r="O17" s="3">
-        <v>8.6875804931833099E-7</v>
-      </c>
-      <c r="P17" s="3">
-        <v>1.8611587352190899E-6</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>2.2187747043785398E-6</v>
-      </c>
-      <c r="R17" s="3">
-        <v>3.0165964169052899E-6</v>
-      </c>
-      <c r="S17" s="3">
-        <v>2.83261234577191E-6</v>
-      </c>
-      <c r="T17" s="3">
-        <v>2.9383419141466999E-6</v>
-      </c>
-      <c r="U17" s="3">
-        <v>3.27033734169333E-6</v>
-      </c>
-      <c r="V17" s="3">
-        <v>2.4122779296801099E-6</v>
-      </c>
-      <c r="W17" s="3">
-        <v>3.1872630737884599E-5</v>
-      </c>
-      <c r="X17" s="3">
-        <v>3.22284399571829E-7</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>1.2539624543418201E-6</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>5.5740761552043E-7</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>6.3887113516178601E-5</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>7.78057907697776E-7</v>
-      </c>
-      <c r="AC17" s="3">
-        <v>9.4814081961460301E-5</v>
-      </c>
-      <c r="AD17" s="3">
-        <v>1.52395911667508E-7</v>
-      </c>
-      <c r="AE17" s="3">
-        <v>1.8904408457533699E-6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B18" s="3">
-        <v>9.9177244178018896E-3</v>
-      </c>
-      <c r="C18" s="3">
-        <v>-3.2657794885813701E-4</v>
-      </c>
-      <c r="D18" s="3">
-        <v>-5.7799354375200503E-6</v>
-      </c>
-      <c r="E18" s="3">
-        <v>2.32256623767341E-8</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-2.7993631971185E-6</v>
-      </c>
-      <c r="G18" s="3">
-        <v>2.7873815411059302E-8</v>
-      </c>
-      <c r="H18" s="3">
-        <v>1.7858979455248701E-8</v>
-      </c>
-      <c r="I18" s="3">
-        <v>4.8283917176307801E-6</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-2.5290579834443499E-8</v>
-      </c>
-      <c r="K18" s="3">
-        <v>1.00859771508938E-5</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-3.6814641556084201E-8</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-7.9312539776170302E-9</v>
-      </c>
-      <c r="N18" s="3">
-        <v>1.3215419949606899E-4</v>
-      </c>
-      <c r="O18" s="3">
-        <v>5.2530493865776296E-6</v>
-      </c>
-      <c r="P18" s="3">
-        <v>1.9963008630753399E-6</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>8.0524148358984206E-6</v>
-      </c>
-      <c r="R18" s="3">
-        <v>2.83261234577191E-6</v>
-      </c>
-      <c r="S18" s="3">
-        <v>2.5105415915978999E-5</v>
-      </c>
-      <c r="T18" s="3">
-        <v>3.3850573630791099E-6</v>
-      </c>
-      <c r="U18" s="3">
-        <v>6.9411978985472099E-6</v>
-      </c>
-      <c r="V18" s="3">
-        <v>2.82136290694417E-6</v>
-      </c>
-      <c r="W18" s="3">
-        <v>1.58726801581819E-4</v>
-      </c>
-      <c r="X18" s="3">
-        <v>3.9961202020835003E-7</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>8.6494912281384898E-6</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>9.3611507080432402E-7</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>3.2856112513123599E-4</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>1.30724854001861E-6</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>3.7605886421803603E-4</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>6.1014253744220205E-7</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>2.3811754538130601E-5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="B19" s="3">
-        <v>2.2488293912465498E-2</v>
+        <v>-1.07160697847995E-2</v>
       </c>
       <c r="C19" s="3">
-        <v>-4.4083097124947101E-5</v>
+        <v>3.7008445852146098E-5</v>
       </c>
       <c r="D19" s="3">
-        <v>-1.1773492092786599E-6</v>
+        <v>1.42629557258721E-5</v>
       </c>
       <c r="E19" s="3">
-        <v>1.47597078118045E-8</v>
+        <v>-2.5143497513425999E-8</v>
       </c>
       <c r="F19" s="3">
-        <v>5.7273347152628699E-6</v>
+        <v>-1.3430966264520999E-4</v>
       </c>
       <c r="G19" s="3">
-        <v>2.7910252330068198E-9</v>
+        <v>2.5363953227354399E-8</v>
       </c>
       <c r="H19" s="3">
-        <v>-1.07598233820826E-8</v>
+        <v>-1.12458184845013E-7</v>
       </c>
       <c r="I19" s="3">
-        <v>-1.0869179829134801E-6</v>
+        <v>-8.6720788823514795E-6</v>
       </c>
       <c r="J19" s="3">
-        <v>-1.680557053617E-8</v>
+        <v>1.2823071191081999E-4</v>
       </c>
       <c r="K19" s="3">
-        <v>2.0783965526135399E-6</v>
+        <v>1.2837966944789301E-4</v>
       </c>
       <c r="L19" s="3">
-        <v>-1.47430468131336E-8</v>
+        <v>1.2804314241824901E-4</v>
       </c>
       <c r="M19" s="3">
-        <v>3.1054006457303099E-8</v>
+        <v>1.2797977117152899E-4</v>
       </c>
       <c r="N19" s="3">
-        <v>1.5757211478519399E-4</v>
+        <v>1.2806928906562701E-4</v>
       </c>
       <c r="O19" s="3">
-        <v>9.5920177027588999E-7</v>
+        <v>1.2725999699466701E-4</v>
       </c>
       <c r="P19" s="3">
-        <v>2.0477484583210298E-6</v>
+        <v>1.28239416372725E-4</v>
       </c>
       <c r="Q19" s="3">
-        <v>2.5553660184364099E-6</v>
+        <v>1.2823405924706699E-4</v>
       </c>
       <c r="R19" s="3">
-        <v>2.9383419141466999E-6</v>
+        <v>1.27809838639794E-4</v>
       </c>
       <c r="S19" s="3">
-        <v>3.3850573630791099E-6</v>
+        <v>1.2781627363187101E-4</v>
       </c>
       <c r="T19" s="3">
-        <v>3.9077793697805003E-6</v>
-      </c>
-      <c r="U19" s="3">
-        <v>4.0249455424304601E-6</v>
-      </c>
-      <c r="V19" s="3">
-        <v>2.8510125047791102E-6</v>
-      </c>
-      <c r="W19" s="3">
-        <v>4.3420305045676701E-5</v>
-      </c>
-      <c r="X19" s="3">
-        <v>4.5197342012618002E-7</v>
-      </c>
-      <c r="Y19" s="3">
-        <v>1.7107070791313099E-6</v>
-      </c>
-      <c r="Z19" s="3">
-        <v>7.9613280323215095E-7</v>
-      </c>
-      <c r="AA19" s="3">
-        <v>8.9808522990028405E-5</v>
-      </c>
-      <c r="AB19" s="3">
-        <v>1.1179285224098299E-6</v>
-      </c>
-      <c r="AC19" s="3">
-        <v>1.34874783864406E-4</v>
-      </c>
-      <c r="AD19" s="3">
-        <v>2.06862585445913E-7</v>
-      </c>
-      <c r="AE19" s="3">
-        <v>2.47460032621245E-6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B20" s="3">
-        <v>1.28100266221424E-2</v>
-      </c>
-      <c r="C20" s="3">
-        <v>-3.2367230722205498E-4</v>
-      </c>
-      <c r="D20" s="3">
-        <v>-3.9686892538799602E-6</v>
-      </c>
-      <c r="E20" s="3">
-        <v>1.07615780554663E-8</v>
-      </c>
-      <c r="F20" s="3">
-        <v>4.33079258177218E-6</v>
-      </c>
-      <c r="G20" s="3">
-        <v>1.37649092255024E-8</v>
-      </c>
-      <c r="H20" s="3">
-        <v>1.5763048125408299E-8</v>
-      </c>
-      <c r="I20" s="3">
-        <v>2.1773710138984202E-6</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-1.3507741620132001E-8</v>
-      </c>
-      <c r="K20" s="3">
-        <v>5.7277235040851903E-6</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-2.7098997092493899E-8</v>
-      </c>
-      <c r="M20" s="3">
-        <v>1.61208966174969E-9</v>
-      </c>
-      <c r="N20" s="3">
-        <v>1.88510316173865E-4</v>
-      </c>
-      <c r="O20" s="3">
-        <v>5.1186424449172196E-6</v>
-      </c>
-      <c r="P20" s="3">
-        <v>2.20403362953372E-6</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>8.0723356333049807E-6</v>
-      </c>
-      <c r="R20" s="3">
-        <v>3.27033734169333E-6</v>
-      </c>
-      <c r="S20" s="3">
-        <v>6.9411978985472099E-6</v>
-      </c>
-      <c r="T20" s="3">
-        <v>4.0249455424304601E-6</v>
-      </c>
-      <c r="U20" s="3">
-        <v>5.7135421380955798E-5</v>
-      </c>
-      <c r="V20" s="3">
-        <v>3.2426650992799402E-6</v>
-      </c>
-      <c r="W20" s="3">
-        <v>1.68120147784875E-4</v>
-      </c>
-      <c r="X20" s="3">
-        <v>5.4689304561624302E-7</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>8.7782861841766895E-6</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>1.1942906010439699E-6</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>3.4435782274324598E-4</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>1.67535851537749E-6</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>4.0746789479650198E-4</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>6.4871772972224199E-7</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>2.3294289001235301E-5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B21" s="3">
-        <v>1.7396586469329098E-2</v>
-      </c>
-      <c r="C21" s="3">
-        <v>-4.3004050441810102E-5</v>
-      </c>
-      <c r="D21" s="3">
-        <v>-3.37284148752009E-6</v>
-      </c>
-      <c r="E21" s="3">
-        <v>6.8335268027798396E-9</v>
-      </c>
-      <c r="F21" s="3">
-        <v>1.2500867592743E-6</v>
-      </c>
-      <c r="G21" s="3">
-        <v>8.9633571572751406E-9</v>
-      </c>
-      <c r="H21" s="3">
-        <v>1.0591673151090299E-8</v>
-      </c>
-      <c r="I21" s="3">
-        <v>3.1564170494286799E-6</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-7.1843560648331799E-9</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-2.0387022210041599E-7</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-1.02694825328009E-8</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-8.4887729327274501E-9</v>
-      </c>
-      <c r="N21" s="3">
-        <v>2.0094480297840898E-5</v>
-      </c>
-      <c r="O21" s="3">
-        <v>1.0025458430046899E-6</v>
-      </c>
-      <c r="P21" s="3">
-        <v>1.70850762373849E-6</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>2.0687690594699399E-6</v>
-      </c>
-      <c r="R21" s="3">
-        <v>2.4122779296801099E-6</v>
-      </c>
-      <c r="S21" s="3">
-        <v>2.82136290694417E-6</v>
-      </c>
-      <c r="T21" s="3">
-        <v>2.8510125047791102E-6</v>
-      </c>
-      <c r="U21" s="3">
-        <v>3.2426650992799402E-6</v>
-      </c>
-      <c r="V21" s="3">
-        <v>3.2318151967271399E-6</v>
-      </c>
-      <c r="W21" s="3">
-        <v>6.3758249088219094E-5</v>
-      </c>
-      <c r="X21" s="3">
-        <v>8.1226195860351397E-8</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>1.1781359996067501E-6</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>1.5103326048991601E-7</v>
-      </c>
-      <c r="AA21" s="3">
-        <v>4.4134912942978601E-5</v>
-      </c>
-      <c r="AB21" s="3">
-        <v>2.0293873847977999E-7</v>
-      </c>
-      <c r="AC21" s="3">
-        <v>5.0942068467121303E-5</v>
-      </c>
-      <c r="AD21" s="3">
-        <v>9.4391075617084197E-8</v>
-      </c>
-      <c r="AE21" s="3">
-        <v>3.1230377465330602E-6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="B22" s="3">
-        <v>-5.54366381774049</v>
-      </c>
-      <c r="C22" s="3">
-        <v>-1.3131505351304499E-2</v>
-      </c>
-      <c r="D22" s="3">
-        <v>2.2205913617525199E-4</v>
-      </c>
-      <c r="E22" s="3">
-        <v>-1.4392591456924201E-6</v>
-      </c>
-      <c r="F22" s="3">
-        <v>2.0962679688493001E-4</v>
-      </c>
-      <c r="G22" s="3">
-        <v>6.2164446363434603E-8</v>
-      </c>
-      <c r="H22" s="3">
-        <v>-2.7545664026340501E-8</v>
-      </c>
-      <c r="I22" s="3">
-        <v>-1.6330136371509201E-4</v>
-      </c>
-      <c r="J22" s="3">
-        <v>1.4366113284974601E-6</v>
-      </c>
-      <c r="K22" s="3">
-        <v>-2.20139485419299E-4</v>
-      </c>
-      <c r="L22" s="3">
-        <v>5.6115990202953503E-8</v>
-      </c>
-      <c r="M22" s="3">
-        <v>-4.33838734377108E-7</v>
-      </c>
-      <c r="N22" s="3">
-        <v>-9.31251023493098E-4</v>
-      </c>
-      <c r="O22" s="3">
-        <v>1.90475354578235E-4</v>
-      </c>
-      <c r="P22" s="3">
-        <v>1.3914505646704801E-5</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>2.4645639759330402E-4</v>
-      </c>
-      <c r="R22" s="3">
-        <v>3.1872630737884599E-5</v>
-      </c>
-      <c r="S22" s="3">
-        <v>1.58726801581819E-4</v>
-      </c>
-      <c r="T22" s="3">
-        <v>4.3420305045676701E-5</v>
-      </c>
-      <c r="U22" s="3">
-        <v>1.68120147784875E-4</v>
-      </c>
-      <c r="V22" s="3">
-        <v>6.3758249088219094E-5</v>
-      </c>
-      <c r="W22" s="3">
-        <v>180965.413391195</v>
-      </c>
-      <c r="X22" s="3">
-        <v>-2.3756800638668999E-6</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>3.2261829690493E-4</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>7.24192615771289E-6</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>1.11797997728235E-2</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>1.0090793471891E-5</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>1.13680680694851E-2</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>1.8604867054813401E-5</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>9.9045831466263909E-4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B23" s="3">
-        <v>-1.53561020646784E-2</v>
-      </c>
-      <c r="C23" s="3">
-        <v>-4.98718667466059E-6</v>
-      </c>
-      <c r="D23" s="3">
-        <v>-3.7473548779964399E-8</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-2.3475894752501299E-9</v>
-      </c>
-      <c r="F23" s="3">
-        <v>3.65862187673918E-6</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-6.7816117227708904E-9</v>
-      </c>
-      <c r="H23" s="3">
-        <v>1.8410488850628699E-9</v>
-      </c>
-      <c r="I23" s="3">
-        <v>4.8464491858741802E-6</v>
-      </c>
-      <c r="J23" s="3">
-        <v>8.8624719149530201E-9</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-8.4216674854528906E-6</v>
-      </c>
-      <c r="L23" s="3">
-        <v>2.9392240946629E-8</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-4.7401609513606601E-8</v>
-      </c>
-      <c r="N23" s="3">
-        <v>6.4462625566343999E-5</v>
-      </c>
-      <c r="O23" s="3">
-        <v>6.6498492243387699E-7</v>
-      </c>
-      <c r="P23" s="3">
-        <v>1.9881954989842001E-7</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>3.3277008861697502E-7</v>
-      </c>
-      <c r="R23" s="3">
-        <v>3.22284399571829E-7</v>
-      </c>
-      <c r="S23" s="3">
-        <v>3.9961202020835003E-7</v>
-      </c>
-      <c r="T23" s="3">
-        <v>4.5197342012618002E-7</v>
-      </c>
-      <c r="U23" s="3">
-        <v>5.4689304561624302E-7</v>
-      </c>
-      <c r="V23" s="3">
-        <v>8.1226195860351397E-8</v>
-      </c>
-      <c r="W23" s="3">
-        <v>-2.3756800638668999E-6</v>
-      </c>
-      <c r="X23" s="3">
-        <v>1.11277617700828E-5</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>2.1923723492404899E-6</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>1.9927526473481899E-6</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>4.1546726855648198E-5</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>2.0383028853820201E-6</v>
-      </c>
-      <c r="AC23" s="3">
-        <v>5.6576407337050302E-5</v>
-      </c>
-      <c r="AD23" s="3">
-        <v>1.4846901326516201E-6</v>
-      </c>
-      <c r="AE23" s="3">
-        <v>1.94750503173308E-6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="B24" s="3">
-        <v>-3.7360726666322598E-2</v>
-      </c>
-      <c r="C24" s="3">
-        <v>-7.4770951320942802E-4</v>
-      </c>
-      <c r="D24" s="3">
-        <v>1.41243484717148E-6</v>
-      </c>
-      <c r="E24" s="3">
-        <v>-4.6272621780540504E-9</v>
-      </c>
-      <c r="F24" s="3">
-        <v>1.0080933112939599E-5</v>
-      </c>
-      <c r="G24" s="3">
-        <v>-1.5014541176193999E-8</v>
-      </c>
-      <c r="H24" s="3">
-        <v>-8.0628341323405592E-9</v>
-      </c>
-      <c r="I24" s="3">
-        <v>-7.8366137303311205E-6</v>
-      </c>
-      <c r="J24" s="3">
-        <v>2.39359101820782E-8</v>
-      </c>
-      <c r="K24" s="3">
-        <v>-2.9167573376397699E-5</v>
-      </c>
-      <c r="L24" s="3">
-        <v>8.9129318340567906E-8</v>
-      </c>
-      <c r="M24" s="3">
-        <v>2.7956348290028201E-8</v>
-      </c>
-      <c r="N24" s="3">
-        <v>1.2416583230065201E-4</v>
-      </c>
-      <c r="O24" s="3">
-        <v>1.18894871016752E-5</v>
-      </c>
-      <c r="P24" s="3">
-        <v>6.1461366950348299E-7</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>1.4599664530026599E-5</v>
-      </c>
-      <c r="R24" s="3">
-        <v>1.2539624543418201E-6</v>
-      </c>
-      <c r="S24" s="3">
-        <v>8.6494912281384898E-6</v>
-      </c>
-      <c r="T24" s="3">
-        <v>1.7107070791313099E-6</v>
-      </c>
-      <c r="U24" s="3">
-        <v>8.7782861841766895E-6</v>
-      </c>
-      <c r="V24" s="3">
-        <v>1.1781359996067501E-6</v>
-      </c>
-      <c r="W24" s="3">
-        <v>3.2261829690493E-4</v>
-      </c>
-      <c r="X24" s="3">
-        <v>2.1923723492404899E-6</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>2.71122548519406E-4</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>2.5860546501435299E-6</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>7.2915130476653204E-4</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>2.8355353644538502E-6</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>7.624437791238E-4</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>1.9956415163245901E-6</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>5.9539551208076402E-5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="B25" s="3">
-        <v>3.57891790059023E-3</v>
-      </c>
-      <c r="C25" s="3">
-        <v>-3.37532068332918E-5</v>
-      </c>
-      <c r="D25" s="3">
-        <v>4.6697030234485799E-8</v>
-      </c>
-      <c r="E25" s="3">
-        <v>-4.0507049891447397E-9</v>
-      </c>
-      <c r="F25" s="3">
-        <v>6.5591850107535598E-6</v>
-      </c>
-      <c r="G25" s="3">
-        <v>-1.19142248251213E-8</v>
-      </c>
-      <c r="H25" s="3">
-        <v>2.2777434251636898E-9</v>
-      </c>
-      <c r="I25" s="3">
-        <v>5.3127332084190401E-6</v>
-      </c>
-      <c r="J25" s="3">
-        <v>1.6284997251971601E-8</v>
-      </c>
-      <c r="K25" s="3">
-        <v>-5.6181224798459203E-6</v>
-      </c>
-      <c r="L25" s="3">
-        <v>2.5466241507931901E-8</v>
-      </c>
-      <c r="M25" s="3">
-        <v>-6.15497249934948E-8</v>
-      </c>
-      <c r="N25" s="3">
-        <v>1.13553584448123E-4</v>
-      </c>
-      <c r="O25" s="3">
-        <v>8.7843892578780003E-7</v>
-      </c>
-      <c r="P25" s="3">
-        <v>3.1860895281410102E-7</v>
-      </c>
-      <c r="Q25" s="3">
-        <v>1.0068060718133701E-6</v>
-      </c>
-      <c r="R25" s="3">
-        <v>5.5740761552043E-7</v>
-      </c>
-      <c r="S25" s="3">
-        <v>9.3611507080432402E-7</v>
-      </c>
-      <c r="T25" s="3">
-        <v>7.9613280323215095E-7</v>
-      </c>
-      <c r="U25" s="3">
-        <v>1.1942906010439699E-6</v>
-      </c>
-      <c r="V25" s="3">
-        <v>1.5103326048991601E-7</v>
-      </c>
-      <c r="W25" s="3">
-        <v>7.24192615771289E-6</v>
-      </c>
-      <c r="X25" s="3">
-        <v>1.9927526473481899E-6</v>
-      </c>
-      <c r="Y25" s="3">
-        <v>2.5860546501435299E-6</v>
-      </c>
-      <c r="Z25" s="3">
-        <v>4.82446404640032E-6</v>
-      </c>
-      <c r="AA25" s="3">
-        <v>8.4675770933115806E-5</v>
-      </c>
-      <c r="AB25" s="3">
-        <v>3.2483271297367001E-6</v>
-      </c>
-      <c r="AC25" s="3">
-        <v>1.3265384960738799E-4</v>
-      </c>
-      <c r="AD25" s="3">
-        <v>2.5695133733992802E-6</v>
-      </c>
-      <c r="AE25" s="3">
-        <v>6.0782956779033998E-6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="B26" s="3">
-        <v>-10.3024581492006</v>
-      </c>
-      <c r="C26" s="3">
-        <v>-2.6582967533709399E-2</v>
-      </c>
-      <c r="D26" s="3">
-        <v>5.4139270552216797E-5</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-3.2418727783093902E-7</v>
-      </c>
-      <c r="F26" s="3">
-        <v>6.2344193356711302E-4</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-1.01277183497874E-6</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-2.1505393777460999E-7</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-4.5652088834934702E-4</v>
-      </c>
-      <c r="J26" s="3">
-        <v>8.4304809464155598E-7</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-1.4426314321205301E-3</v>
-      </c>
-      <c r="L26" s="3">
-        <v>4.9028998842065999E-6</v>
-      </c>
-      <c r="M26" s="3">
-        <v>3.0354419539865501E-6</v>
-      </c>
-      <c r="N26" s="3">
-        <v>9.0860139493382005E-3</v>
-      </c>
-      <c r="O26" s="3">
-        <v>3.8885890278582701E-4</v>
-      </c>
-      <c r="P26" s="3">
-        <v>3.1494834524757201E-5</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>5.3025685080780203E-4</v>
-      </c>
-      <c r="R26" s="3">
-        <v>6.3887113516178601E-5</v>
-      </c>
-      <c r="S26" s="3">
-        <v>3.2856112513123599E-4</v>
-      </c>
-      <c r="T26" s="3">
-        <v>8.9808522990028405E-5</v>
-      </c>
-      <c r="U26" s="3">
-        <v>3.4435782274324598E-4</v>
-      </c>
-      <c r="V26" s="3">
-        <v>4.4134912942978601E-5</v>
-      </c>
-      <c r="W26" s="3">
-        <v>1.11797997728235E-2</v>
-      </c>
-      <c r="X26" s="3">
-        <v>4.1546726855648198E-5</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>7.2915130476653204E-4</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>8.4675770933115806E-5</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>856957.56080078403</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>1.09604996617301E-4</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>1.0304112192745301</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>5.6523492884616402E-5</v>
-      </c>
-      <c r="AE26" s="3">
-        <v>1.9575599343321999E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="B27" s="3">
-        <v>1.3622042802456401E-2</v>
-      </c>
-      <c r="C27" s="3">
-        <v>-4.7165081493678701E-5</v>
-      </c>
-      <c r="D27" s="3">
-        <v>8.9180820089915702E-8</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-5.7142343693600102E-9</v>
-      </c>
-      <c r="F27" s="3">
-        <v>9.3103839991541404E-6</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-1.6868568583899298E-8</v>
-      </c>
-      <c r="H27" s="3">
-        <v>3.0206602250118798E-9</v>
-      </c>
-      <c r="I27" s="3">
-        <v>3.0300240647553599E-7</v>
-      </c>
-      <c r="J27" s="3">
-        <v>1.6328844638368399E-8</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-4.8313977370567103E-6</v>
-      </c>
-      <c r="L27" s="3">
-        <v>2.5602908621452001E-8</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-2.3891852682965301E-8</v>
-      </c>
-      <c r="N27" s="3">
-        <v>1.61155868338051E-4</v>
-      </c>
-      <c r="O27" s="3">
-        <v>9.816471018495259E-7</v>
-      </c>
-      <c r="P27" s="3">
-        <v>4.3653847812177798E-7</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>1.3947852225007701E-6</v>
-      </c>
-      <c r="R27" s="3">
-        <v>7.78057907697776E-7</v>
-      </c>
-      <c r="S27" s="3">
-        <v>1.30724854001861E-6</v>
-      </c>
-      <c r="T27" s="3">
-        <v>1.1179285224098299E-6</v>
-      </c>
-      <c r="U27" s="3">
-        <v>1.67535851537749E-6</v>
-      </c>
-      <c r="V27" s="3">
-        <v>2.0293873847977999E-7</v>
-      </c>
-      <c r="W27" s="3">
-        <v>1.0090793471891E-5</v>
-      </c>
-      <c r="X27" s="3">
-        <v>2.0383028853820201E-6</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>2.8355353644538502E-6</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>3.2483271297367001E-6</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>1.09604996617301E-4</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>4.8167789408419004E-6</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>1.83336115491247E-4</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>3.1387210313176601E-6</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>8.5759200785433493E-6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="B28" s="3">
-        <v>-10.6084327042271</v>
-      </c>
-      <c r="C28" s="3">
-        <v>-2.7998752126199601E-2</v>
-      </c>
-      <c r="D28" s="3">
-        <v>5.8856609363805299E-5</v>
-      </c>
-      <c r="E28" s="3">
-        <v>-5.5960630678884497E-7</v>
-      </c>
-      <c r="F28" s="3">
-        <v>1.0101186114218801E-3</v>
-      </c>
-      <c r="G28" s="3">
-        <v>-1.7119884677995299E-6</v>
-      </c>
-      <c r="H28" s="3">
-        <v>-9.9609670178794306E-8</v>
-      </c>
-      <c r="I28" s="3">
-        <v>-4.1624261082025998E-4</v>
-      </c>
-      <c r="J28" s="3">
-        <v>-2.38213687960778E-7</v>
-      </c>
-      <c r="K28" s="3">
-        <v>-1.13668757442359E-3</v>
-      </c>
-      <c r="L28" s="3">
-        <v>4.5476868020242098E-6</v>
-      </c>
-      <c r="M28" s="3">
-        <v>4.2850359803336201E-6</v>
-      </c>
-      <c r="N28" s="3">
-        <v>1.5811559315374198E-2</v>
-      </c>
-      <c r="O28" s="3">
-        <v>3.9990612529965E-4</v>
-      </c>
-      <c r="P28" s="3">
-        <v>4.8209162137823403E-5</v>
-      </c>
-      <c r="Q28" s="3">
-        <v>5.7627705007456704E-4</v>
-      </c>
-      <c r="R28" s="3">
-        <v>9.4814081961460301E-5</v>
-      </c>
-      <c r="S28" s="3">
-        <v>3.7605886421803603E-4</v>
-      </c>
-      <c r="T28" s="3">
-        <v>1.34874783864406E-4</v>
-      </c>
-      <c r="U28" s="3">
-        <v>4.0746789479650198E-4</v>
-      </c>
-      <c r="V28" s="3">
-        <v>5.0942068467121303E-5</v>
-      </c>
-      <c r="W28" s="3">
-        <v>1.13680680694851E-2</v>
-      </c>
-      <c r="X28" s="3">
-        <v>5.6576407337050302E-5</v>
-      </c>
-      <c r="Y28" s="3">
-        <v>7.624437791238E-4</v>
-      </c>
-      <c r="Z28" s="3">
-        <v>1.3265384960738799E-4</v>
-      </c>
-      <c r="AA28" s="3">
-        <v>1.0304112192745301</v>
-      </c>
-      <c r="AB28" s="3">
-        <v>1.83336115491247E-4</v>
-      </c>
-      <c r="AC28" s="3">
-        <v>1916068.6111050099</v>
-      </c>
-      <c r="AD28" s="3">
-        <v>1.04417393733796E-4</v>
-      </c>
-      <c r="AE28" s="3">
-        <v>2.2818452156688901E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="B29" s="3">
-        <v>1.7355003996953899E-2</v>
-      </c>
-      <c r="C29" s="3">
-        <v>-4.5599648325824797E-5</v>
-      </c>
-      <c r="D29" s="3">
-        <v>6.0364329442624597E-8</v>
-      </c>
-      <c r="E29" s="3">
-        <v>-8.0603069833631301E-10</v>
-      </c>
-      <c r="F29" s="3">
-        <v>1.38971764114735E-6</v>
-      </c>
-      <c r="G29" s="3">
-        <v>-2.38728256149929E-9</v>
-      </c>
-      <c r="H29" s="3">
-        <v>6.1800208495018004E-11</v>
-      </c>
-      <c r="I29" s="3">
-        <v>-6.1937828808712196E-6</v>
-      </c>
-      <c r="J29" s="3">
-        <v>8.9490495832072994E-9</v>
-      </c>
-      <c r="K29" s="3">
-        <v>-2.7588637946059201E-6</v>
-      </c>
-      <c r="L29" s="3">
-        <v>2.08158788748257E-8</v>
-      </c>
-      <c r="M29" s="3">
-        <v>3.1453763039611501E-8</v>
-      </c>
-      <c r="N29" s="3">
-        <v>2.1354969270057898E-5</v>
-      </c>
-      <c r="O29" s="3">
-        <v>1.0148492182875601E-6</v>
-      </c>
-      <c r="P29" s="3">
-        <v>8.9518303641746302E-8</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>9.54243449060503E-7</v>
-      </c>
-      <c r="R29" s="3">
-        <v>1.52395911667508E-7</v>
-      </c>
-      <c r="S29" s="3">
-        <v>6.1014253744220205E-7</v>
-      </c>
-      <c r="T29" s="3">
-        <v>2.06862585445913E-7</v>
-      </c>
-      <c r="U29" s="3">
-        <v>6.4871772972224199E-7</v>
-      </c>
-      <c r="V29" s="3">
-        <v>9.4391075617084197E-8</v>
-      </c>
-      <c r="W29" s="3">
-        <v>1.8604867054813401E-5</v>
-      </c>
-      <c r="X29" s="3">
-        <v>1.4846901326516201E-6</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>1.9956415163245901E-6</v>
-      </c>
-      <c r="Z29" s="3">
-        <v>2.5695133733992802E-6</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>5.6523492884616402E-5</v>
-      </c>
-      <c r="AB29" s="3">
-        <v>3.1387210313176601E-6</v>
-      </c>
-      <c r="AC29" s="3">
-        <v>1.04417393733796E-4</v>
-      </c>
-      <c r="AD29" s="3">
-        <v>3.52589795475612E-6</v>
-      </c>
-      <c r="AE29" s="3">
-        <v>1.1074340482789701E-5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B30" s="3">
-        <v>-0.145958808742086</v>
-      </c>
-      <c r="C30" s="3">
-        <v>-2.2330706184271899E-3</v>
-      </c>
-      <c r="D30" s="3">
-        <v>4.3812634503501296E-6</v>
-      </c>
-      <c r="E30" s="3">
-        <v>1.55477749858987E-10</v>
-      </c>
-      <c r="F30" s="3">
-        <v>8.1497248508666505E-6</v>
-      </c>
-      <c r="G30" s="3">
-        <v>-4.2281946664544297E-9</v>
-      </c>
-      <c r="H30" s="3">
-        <v>-3.4521369531308798E-8</v>
-      </c>
-      <c r="I30" s="3">
-        <v>3.96136649828362E-5</v>
-      </c>
-      <c r="J30" s="3">
-        <v>-2.49820286317083E-7</v>
-      </c>
-      <c r="K30" s="3">
-        <v>3.2304296443269002E-5</v>
-      </c>
-      <c r="L30" s="3">
-        <v>1.0551011155236501E-8</v>
-      </c>
-      <c r="M30" s="3">
-        <v>-1.5113910206191199E-8</v>
-      </c>
-      <c r="N30" s="3">
-        <v>-1.7818291051150901E-5</v>
-      </c>
-      <c r="O30" s="3">
-        <v>3.3219196627751998E-5</v>
-      </c>
-      <c r="P30" s="3">
-        <v>7.2427379996700101E-7</v>
-      </c>
-      <c r="Q30" s="3">
-        <v>4.2266834945770703E-5</v>
-      </c>
-      <c r="R30" s="3">
-        <v>1.8904408457533699E-6</v>
-      </c>
-      <c r="S30" s="3">
-        <v>2.3811754538130601E-5</v>
-      </c>
-      <c r="T30" s="3">
-        <v>2.47460032621245E-6</v>
-      </c>
-      <c r="U30" s="3">
-        <v>2.3294289001235301E-5</v>
-      </c>
-      <c r="V30" s="3">
-        <v>3.1230377465330602E-6</v>
-      </c>
-      <c r="W30" s="3">
-        <v>9.9045831466263909E-4</v>
-      </c>
-      <c r="X30" s="3">
-        <v>1.94750503173308E-6</v>
-      </c>
-      <c r="Y30" s="3">
-        <v>5.9539551208076402E-5</v>
-      </c>
-      <c r="Z30" s="3">
-        <v>6.0782956779033998E-6</v>
-      </c>
-      <c r="AA30" s="3">
-        <v>1.9575599343321999E-3</v>
-      </c>
-      <c r="AB30" s="3">
-        <v>8.5759200785433493E-6</v>
-      </c>
-      <c r="AC30" s="3">
-        <v>2.2818452156688901E-3</v>
-      </c>
-      <c r="AD30" s="3">
-        <v>1.1074340482789701E-5</v>
-      </c>
-      <c r="AE30" s="3">
-        <v>3.91235661825894E-2</v>
+        <v>2.34453101567099E-4</v>
       </c>
     </row>
   </sheetData>
@@ -66157,14 +64494,15 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC885E71-EA21-464C-BF5E-AB7813186B3F}">
-  <dimension ref="A1:AE30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DFE8567-67A3-41A3-9804-ADC448CEC0EA}">
+  <dimension ref="A1:T19"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="11.42578125" style="3"/>
+    <col min="1" max="1" width="32.140625" style="3" customWidth="1"/>
+    <col min="2" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -66175,2843 +64513,1171 @@
         <v>28</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>210</v>
+        <v>2</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>211</v>
+        <v>3</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>212</v>
+        <v>130</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>7</v>
+        <v>231</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>8</v>
+        <v>230</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>9</v>
+        <v>229</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="V1" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="W1" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="Y1" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="Z1" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="AA1" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="AB1" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="AC1" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="AD1" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="AE1" s="3" t="s">
-        <v>231</v>
-      </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B2" s="3">
-        <v>-1.0073555552515301</v>
+        <v>-4.0410153827671103</v>
       </c>
       <c r="C2" s="3">
-        <v>2.9856881717883501E-2</v>
+        <v>0.21581828600289299</v>
       </c>
       <c r="D2" s="3">
-        <v>-5.8994148035503802E-5</v>
+        <v>-3.6000664365707898E-3</v>
       </c>
       <c r="E2" s="3">
-        <v>5.7386565427299501E-8</v>
+        <v>1.7992908634939001E-5</v>
       </c>
       <c r="F2" s="3">
-        <v>-2.0510879438839099E-4</v>
+        <v>-9.4737634710239304E-4</v>
       </c>
       <c r="G2" s="3">
-        <v>2.32207103902407E-7</v>
+        <v>4.6046051895759601E-7</v>
       </c>
       <c r="H2" s="3">
-        <v>4.2627333639507602E-7</v>
+        <v>1.03941423048226E-5</v>
       </c>
       <c r="I2" s="3">
-        <v>-1.9450413424968002E-5</v>
+        <v>-6.9841930969792099E-4</v>
       </c>
       <c r="J2" s="3">
-        <v>-5.7012562247928403E-9</v>
+        <v>-1.9951459761529201E-5</v>
       </c>
       <c r="K2" s="3">
-        <v>5.4792089090609801E-5</v>
+        <v>-1.56280416303169E-5</v>
       </c>
       <c r="L2" s="3">
-        <v>-2.2681141620312401E-7</v>
+        <v>-1.6085496742759701E-5</v>
       </c>
       <c r="M2" s="3">
-        <v>1.3345356051517001E-7</v>
+        <v>-1.6810972813864102E-5</v>
       </c>
       <c r="N2" s="3">
-        <v>-1.45976076676486E-3</v>
+        <v>2.8045648463842E-5</v>
       </c>
       <c r="O2" s="3">
-        <v>-4.4239560392802401E-4</v>
+        <v>-1.69121915246763E-4</v>
       </c>
       <c r="P2" s="3">
-        <v>-1.38273208057125E-5</v>
+        <v>-3.7489818026374599E-6</v>
       </c>
       <c r="Q2" s="3">
-        <v>-5.7002713262109203E-4</v>
+        <v>5.7103493780468003E-5</v>
       </c>
       <c r="R2" s="3">
-        <v>-3.2806140748527603E-5</v>
+        <v>2.9753483553440498E-6</v>
       </c>
       <c r="S2" s="3">
-        <v>-3.2657794885813701E-4</v>
+        <v>-4.3012352796894299E-5</v>
       </c>
       <c r="T2" s="3">
-        <v>-4.4083097124947101E-5</v>
-      </c>
-      <c r="U2" s="3">
-        <v>-3.2367230722205498E-4</v>
-      </c>
-      <c r="V2" s="3">
-        <v>-4.3004050441810102E-5</v>
-      </c>
-      <c r="W2" s="3">
-        <v>-1.3131505351304499E-2</v>
-      </c>
-      <c r="X2" s="3">
-        <v>-4.98718667466059E-6</v>
-      </c>
-      <c r="Y2" s="3">
-        <v>-7.4770951320942802E-4</v>
-      </c>
-      <c r="Z2" s="3">
-        <v>-3.37532068332918E-5</v>
-      </c>
-      <c r="AA2" s="3">
-        <v>-2.6582967533709399E-2</v>
-      </c>
-      <c r="AB2" s="3">
-        <v>-4.7165081493678701E-5</v>
-      </c>
-      <c r="AC2" s="3">
-        <v>-2.7998752126199601E-2</v>
-      </c>
-      <c r="AD2" s="3">
-        <v>-4.5599648325824797E-5</v>
-      </c>
-      <c r="AE2" s="3">
-        <v>-2.2330706184271899E-3</v>
+        <v>3.7008445852146098E-5</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>210</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>1.23361213363856E-2</v>
+        <v>-0.14537907813996001</v>
       </c>
       <c r="C3" s="3">
-        <v>-5.8994148035503802E-5</v>
+        <v>-3.6000664365707898E-3</v>
       </c>
       <c r="D3" s="3">
-        <v>2.0618273889906101E-3</v>
+        <v>4.37059910039388E-3</v>
       </c>
       <c r="E3" s="3">
-        <v>-5.6033360392489203E-6</v>
+        <v>-1.96417855377994E-5</v>
       </c>
       <c r="F3" s="3">
-        <v>1.6703013930095499E-3</v>
+        <v>1.44751455474659E-3</v>
       </c>
       <c r="G3" s="3">
-        <v>-5.0389905385463597E-6</v>
+        <v>-3.0367310729731402E-6</v>
       </c>
       <c r="H3" s="3">
-        <v>-1.2730687267039199E-5</v>
+        <v>-2.20678822207496E-5</v>
       </c>
       <c r="I3" s="3">
-        <v>-2.06160105552984E-3</v>
+        <v>-2.12410488986844E-4</v>
       </c>
       <c r="J3" s="3">
-        <v>5.6033032571383701E-6</v>
+        <v>6.1214312387262998E-6</v>
       </c>
       <c r="K3" s="3">
-        <v>-1.66963385651895E-3</v>
+        <v>8.6132197989848994E-6</v>
       </c>
       <c r="L3" s="3">
-        <v>5.0383735027121401E-6</v>
+        <v>2.2536356875863299E-5</v>
       </c>
       <c r="M3" s="3">
-        <v>1.2728986499007001E-5</v>
+        <v>1.81868866518548E-5</v>
       </c>
       <c r="N3" s="3">
-        <v>7.7905118409062795E-6</v>
+        <v>-9.3509941745020897E-7</v>
       </c>
       <c r="O3" s="3">
-        <v>-1.3099796384693701E-8</v>
+        <v>4.96156039309976E-6</v>
       </c>
       <c r="P3" s="3">
-        <v>8.8767747496532897E-8</v>
+        <v>3.0444920369570299E-5</v>
       </c>
       <c r="Q3" s="3">
-        <v>-5.5865571930154203E-6</v>
+        <v>1.42405086502582E-5</v>
       </c>
       <c r="R3" s="3">
-        <v>1.2827442790502899E-7</v>
+        <v>-6.9696922151638896E-6</v>
       </c>
       <c r="S3" s="3">
-        <v>-5.7799354375200503E-6</v>
+        <v>1.3029580279298299E-5</v>
       </c>
       <c r="T3" s="3">
-        <v>-1.1773492092786599E-6</v>
-      </c>
-      <c r="U3" s="3">
-        <v>-3.9686892538799602E-6</v>
-      </c>
-      <c r="V3" s="3">
-        <v>-3.37284148752009E-6</v>
-      </c>
-      <c r="W3" s="3">
-        <v>2.2205913617525199E-4</v>
-      </c>
-      <c r="X3" s="3">
-        <v>-3.7473548779964399E-8</v>
-      </c>
-      <c r="Y3" s="3">
-        <v>1.41243484717148E-6</v>
-      </c>
-      <c r="Z3" s="3">
-        <v>4.6697030234485799E-8</v>
-      </c>
-      <c r="AA3" s="3">
-        <v>5.4139270552216797E-5</v>
-      </c>
-      <c r="AB3" s="3">
-        <v>8.9180820089915702E-8</v>
-      </c>
-      <c r="AC3" s="3">
-        <v>5.8856609363805299E-5</v>
-      </c>
-      <c r="AD3" s="3">
-        <v>6.0364329442624597E-8</v>
-      </c>
-      <c r="AE3" s="3">
-        <v>4.3812634503501296E-6</v>
+        <v>1.42629557258721E-5</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>211</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>-9.85002475685855E-5</v>
+        <v>4.2860594032363897E-4</v>
       </c>
       <c r="C4" s="3">
-        <v>5.7386565427299501E-8</v>
+        <v>1.7992908634939001E-5</v>
       </c>
       <c r="D4" s="3">
-        <v>-5.6033360392489203E-6</v>
+        <v>-1.96417855377994E-5</v>
       </c>
       <c r="E4" s="3">
-        <v>2.4048571711024799E-8</v>
+        <v>1.0460874449851E-7</v>
       </c>
       <c r="F4" s="3">
-        <v>-3.93022265644805E-6</v>
+        <v>-6.2739541160480204E-6</v>
       </c>
       <c r="G4" s="3">
-        <v>1.0919523456037499E-8</v>
+        <v>1.26134153255488E-8</v>
       </c>
       <c r="H4" s="3">
-        <v>2.89037012688621E-8</v>
+        <v>9.3244115645968599E-8</v>
       </c>
       <c r="I4" s="3">
-        <v>5.6158890554165002E-6</v>
+        <v>-1.67647453075414E-6</v>
       </c>
       <c r="J4" s="3">
-        <v>-2.4037970488982201E-8</v>
+        <v>8.4998118401502599E-8</v>
       </c>
       <c r="K4" s="3">
-        <v>3.8888376684996798E-6</v>
+        <v>3.23626215977667E-8</v>
       </c>
       <c r="L4" s="3">
-        <v>-1.08547654697684E-8</v>
+        <v>3.4279766294984102E-9</v>
       </c>
       <c r="M4" s="3">
-        <v>-2.9015396737953202E-8</v>
+        <v>5.00464040914354E-8</v>
       </c>
       <c r="N4" s="3">
-        <v>-8.42224261010507E-7</v>
+        <v>1.26981749798527E-7</v>
       </c>
       <c r="O4" s="3">
-        <v>-1.5768931082986501E-9</v>
+        <v>6.7466998015694194E-8</v>
       </c>
       <c r="P4" s="3">
-        <v>1.2794883453042E-8</v>
+        <v>2.9257034913650999E-8</v>
       </c>
       <c r="Q4" s="3">
-        <v>1.7855419920635701E-8</v>
+        <v>7.8520358290831098E-8</v>
       </c>
       <c r="R4" s="3">
-        <v>1.99766442914547E-8</v>
+        <v>7.8818250748758297E-8</v>
       </c>
       <c r="S4" s="3">
-        <v>2.32256623767341E-8</v>
+        <v>1.5682050871755901E-8</v>
       </c>
       <c r="T4" s="3">
-        <v>1.47597078118045E-8</v>
-      </c>
-      <c r="U4" s="3">
-        <v>1.07615780554663E-8</v>
-      </c>
-      <c r="V4" s="3">
-        <v>6.8335268027798396E-9</v>
-      </c>
-      <c r="W4" s="3">
-        <v>-1.4392591456924201E-6</v>
-      </c>
-      <c r="X4" s="3">
-        <v>-2.3475894752501299E-9</v>
-      </c>
-      <c r="Y4" s="3">
-        <v>-4.6272621780540504E-9</v>
-      </c>
-      <c r="Z4" s="3">
-        <v>-4.0507049891447397E-9</v>
-      </c>
-      <c r="AA4" s="3">
-        <v>-3.2418727783093902E-7</v>
-      </c>
-      <c r="AB4" s="3">
-        <v>-5.7142343693600102E-9</v>
-      </c>
-      <c r="AC4" s="3">
-        <v>-5.5960630678884497E-7</v>
-      </c>
-      <c r="AD4" s="3">
-        <v>-8.0603069833631301E-10</v>
-      </c>
-      <c r="AE4" s="3">
-        <v>1.55477749858987E-10</v>
+        <v>-2.5143497513425999E-8</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B5" s="3">
-        <v>8.5664508032301606E-2</v>
+        <v>-4.04007740193267E-2</v>
       </c>
       <c r="C5" s="3">
-        <v>-2.0510879438839099E-4</v>
+        <v>-9.4737634710239304E-4</v>
       </c>
       <c r="D5" s="3">
-        <v>1.6703013930095499E-3</v>
+        <v>1.44751455474659E-3</v>
       </c>
       <c r="E5" s="3">
-        <v>-3.93022265644805E-6</v>
+        <v>-6.2739541160480204E-6</v>
       </c>
       <c r="F5" s="3">
-        <v>2.1916298571871E-3</v>
+        <v>1.1618200264724499E-3</v>
       </c>
       <c r="G5" s="3">
-        <v>-6.85746585669935E-6</v>
+        <v>-2.8739050191418401E-6</v>
       </c>
       <c r="H5" s="3">
-        <v>-1.07550805011178E-5</v>
+        <v>-7.5835894890573899E-6</v>
       </c>
       <c r="I5" s="3">
-        <v>-1.6899105423629601E-3</v>
+        <v>1.08148072343284E-3</v>
       </c>
       <c r="J5" s="3">
-        <v>3.9132371300900496E-6</v>
+        <v>-1.31449874069332E-4</v>
       </c>
       <c r="K5" s="3">
-        <v>-2.1239481131728301E-3</v>
+        <v>-1.4110878557804701E-4</v>
       </c>
       <c r="L5" s="3">
-        <v>6.7523665847881301E-6</v>
+        <v>-1.16254410988808E-4</v>
       </c>
       <c r="M5" s="3">
-        <v>1.0930183137874E-5</v>
+        <v>-1.1205120093657801E-4</v>
       </c>
       <c r="N5" s="3">
-        <v>1.3648730633539401E-3</v>
+        <v>-1.2246688883600201E-4</v>
       </c>
       <c r="O5" s="3">
-        <v>2.0305308604558202E-6</v>
+        <v>-1.16349003759329E-4</v>
       </c>
       <c r="P5" s="3">
-        <v>-2.3901403872406398E-6</v>
+        <v>-1.12737357219583E-4</v>
       </c>
       <c r="Q5" s="3">
-        <v>-7.7677387885546099E-6</v>
+        <v>-1.13525292221057E-4</v>
       </c>
       <c r="R5" s="3">
-        <v>1.51652690158799E-6</v>
+        <v>-1.28598471605231E-4</v>
       </c>
       <c r="S5" s="3">
-        <v>-2.7993631971185E-6</v>
+        <v>-1.15812272087677E-4</v>
       </c>
       <c r="T5" s="3">
-        <v>5.7273347152628699E-6</v>
-      </c>
-      <c r="U5" s="3">
-        <v>4.33079258177218E-6</v>
-      </c>
-      <c r="V5" s="3">
-        <v>1.2500867592743E-6</v>
-      </c>
-      <c r="W5" s="3">
-        <v>2.0962679688493001E-4</v>
-      </c>
-      <c r="X5" s="3">
-        <v>3.65862187673918E-6</v>
-      </c>
-      <c r="Y5" s="3">
-        <v>1.0080933112939599E-5</v>
-      </c>
-      <c r="Z5" s="3">
-        <v>6.5591850107535598E-6</v>
-      </c>
-      <c r="AA5" s="3">
-        <v>6.2344193356711302E-4</v>
-      </c>
-      <c r="AB5" s="3">
-        <v>9.3103839991541404E-6</v>
-      </c>
-      <c r="AC5" s="3">
-        <v>1.0101186114218801E-3</v>
-      </c>
-      <c r="AD5" s="3">
-        <v>1.38971764114735E-6</v>
-      </c>
-      <c r="AE5" s="3">
-        <v>8.1497248508666505E-6</v>
+        <v>-1.3430966264520999E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" s="3">
-        <v>-7.7383786237344803E-5</v>
+        <v>1.4390902176363699E-4</v>
       </c>
       <c r="C6" s="3">
-        <v>2.32207103902407E-7</v>
+        <v>4.6046051895759601E-7</v>
       </c>
       <c r="D6" s="3">
-        <v>-5.0389905385463597E-6</v>
+        <v>-3.0367310729731402E-6</v>
       </c>
       <c r="E6" s="3">
-        <v>1.0919523456037499E-8</v>
+        <v>1.26134153255488E-8</v>
       </c>
       <c r="F6" s="3">
-        <v>-6.85746585669935E-6</v>
+        <v>-2.8739050191418401E-6</v>
       </c>
       <c r="G6" s="3">
-        <v>2.1950280876478901E-8</v>
+        <v>8.6486014744328504E-9</v>
       </c>
       <c r="H6" s="3">
-        <v>3.35153263200716E-8</v>
+        <v>1.7276047392776699E-8</v>
       </c>
       <c r="I6" s="3">
-        <v>5.0754976343013002E-6</v>
+        <v>-2.3635878554329899E-6</v>
       </c>
       <c r="J6" s="3">
-        <v>-1.08884644638723E-8</v>
+        <v>1.8569949547692401E-8</v>
       </c>
       <c r="K6" s="3">
-        <v>6.73467369315291E-6</v>
+        <v>4.9362830960052602E-8</v>
       </c>
       <c r="L6" s="3">
-        <v>-2.1758561176163999E-8</v>
+        <v>-2.97719140735268E-8</v>
       </c>
       <c r="M6" s="3">
-        <v>-3.3840560782707297E-8</v>
+        <v>-4.4378821342023198E-8</v>
       </c>
       <c r="N6" s="3">
-        <v>-2.4887305256268201E-6</v>
+        <v>-1.84627955760693E-8</v>
       </c>
       <c r="O6" s="3">
-        <v>-3.2854750580198301E-9</v>
+        <v>-1.95762401573888E-8</v>
       </c>
       <c r="P6" s="3">
-        <v>1.6150131807205499E-8</v>
+        <v>-3.6634297609672803E-8</v>
       </c>
       <c r="Q6" s="3">
-        <v>3.7241227150176697E-8</v>
+        <v>-4.5318350624731501E-8</v>
       </c>
       <c r="R6" s="3">
-        <v>1.02422739239568E-8</v>
+        <v>-6.6291409138536298E-10</v>
       </c>
       <c r="S6" s="3">
-        <v>2.7873815411059302E-8</v>
+        <v>-2.649256276039E-8</v>
       </c>
       <c r="T6" s="3">
-        <v>2.7910252330068198E-9</v>
-      </c>
-      <c r="U6" s="3">
-        <v>1.37649092255024E-8</v>
-      </c>
-      <c r="V6" s="3">
-        <v>8.9633571572751406E-9</v>
-      </c>
-      <c r="W6" s="3">
-        <v>6.2164446363434603E-8</v>
-      </c>
-      <c r="X6" s="3">
-        <v>-6.7816117227708904E-9</v>
-      </c>
-      <c r="Y6" s="3">
-        <v>-1.5014541176193999E-8</v>
-      </c>
-      <c r="Z6" s="3">
-        <v>-1.19142248251213E-8</v>
-      </c>
-      <c r="AA6" s="3">
-        <v>-1.01277183497874E-6</v>
-      </c>
-      <c r="AB6" s="3">
-        <v>-1.6868568583899298E-8</v>
-      </c>
-      <c r="AC6" s="3">
-        <v>-1.7119884677995299E-6</v>
-      </c>
-      <c r="AD6" s="3">
-        <v>-2.38728256149929E-9</v>
-      </c>
-      <c r="AE6" s="3">
-        <v>-4.2281946664544297E-9</v>
+        <v>2.5363953227354399E-8</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" s="3">
-        <v>5.5861475364458103E-5</v>
+        <v>1.24602766933448E-3</v>
       </c>
       <c r="C7" s="3">
-        <v>4.2627333639507602E-7</v>
+        <v>1.03941423048226E-5</v>
       </c>
       <c r="D7" s="3">
-        <v>-1.2730687267039199E-5</v>
+        <v>-2.20678822207496E-5</v>
       </c>
       <c r="E7" s="3">
-        <v>2.89037012688621E-8</v>
+        <v>9.3244115645968599E-8</v>
       </c>
       <c r="F7" s="3">
-        <v>-1.07550805011178E-5</v>
+        <v>-7.5835894890573899E-6</v>
       </c>
       <c r="G7" s="3">
-        <v>3.35153263200716E-8</v>
+        <v>1.7276047392776699E-8</v>
       </c>
       <c r="H7" s="3">
-        <v>8.4342195222668002E-8</v>
+        <v>1.2018761467241101E-7</v>
       </c>
       <c r="I7" s="3">
-        <v>1.2720708958473899E-5</v>
+        <v>2.4896603746977202E-6</v>
       </c>
       <c r="J7" s="3">
-        <v>-2.8910371809689999E-8</v>
+        <v>-4.6649077666843097E-8</v>
       </c>
       <c r="K7" s="3">
-        <v>1.0776633131646701E-5</v>
+        <v>-5.4253202543022897E-8</v>
       </c>
       <c r="L7" s="3">
-        <v>-3.3552400714094101E-8</v>
+        <v>-1.40962918782938E-7</v>
       </c>
       <c r="M7" s="3">
-        <v>-8.4255885474116597E-8</v>
+        <v>-1.25313845761621E-7</v>
       </c>
       <c r="N7" s="3">
-        <v>4.85171799704477E-7</v>
+        <v>-3.87969118862372E-8</v>
       </c>
       <c r="O7" s="3">
-        <v>1.4718208970971601E-9</v>
+        <v>7.1569427468724803E-8</v>
       </c>
       <c r="P7" s="3">
-        <v>-1.08912156633368E-8</v>
+        <v>-1.98445037526611E-7</v>
       </c>
       <c r="Q7" s="3">
-        <v>2.11765600072742E-8</v>
+        <v>-1.50424457315999E-7</v>
       </c>
       <c r="R7" s="3">
-        <v>-2.1509396451579401E-8</v>
+        <v>3.1528826670931298E-8</v>
       </c>
       <c r="S7" s="3">
-        <v>1.7858979455248701E-8</v>
+        <v>-5.4401984672664301E-8</v>
       </c>
       <c r="T7" s="3">
-        <v>-1.07598233820826E-8</v>
-      </c>
-      <c r="U7" s="3">
-        <v>1.5763048125408299E-8</v>
-      </c>
-      <c r="V7" s="3">
-        <v>1.0591673151090299E-8</v>
-      </c>
-      <c r="W7" s="3">
-        <v>-2.7545664026340501E-8</v>
-      </c>
-      <c r="X7" s="3">
-        <v>1.8410488850628699E-9</v>
-      </c>
-      <c r="Y7" s="3">
-        <v>-8.0628341323405592E-9</v>
-      </c>
-      <c r="Z7" s="3">
-        <v>2.2777434251636898E-9</v>
-      </c>
-      <c r="AA7" s="3">
-        <v>-2.1505393777460999E-7</v>
-      </c>
-      <c r="AB7" s="3">
-        <v>3.0206602250118798E-9</v>
-      </c>
-      <c r="AC7" s="3">
-        <v>-9.9609670178794306E-8</v>
-      </c>
-      <c r="AD7" s="3">
-        <v>6.1800208495018004E-11</v>
-      </c>
-      <c r="AE7" s="3">
-        <v>-3.4521369531308798E-8</v>
+        <v>-1.12458184845013E-7</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>212</v>
+        <v>130</v>
       </c>
       <c r="B8" s="3">
-        <v>1.5674779902935899E-2</v>
+        <v>0.99572501928013102</v>
       </c>
       <c r="C8" s="3">
-        <v>-1.9450413424968002E-5</v>
+        <v>-6.9841930969792099E-4</v>
       </c>
       <c r="D8" s="3">
-        <v>-2.06160105552984E-3</v>
+        <v>-2.12410488986844E-4</v>
       </c>
       <c r="E8" s="3">
-        <v>5.6158890554165002E-6</v>
+        <v>-1.67647453075414E-6</v>
       </c>
       <c r="F8" s="3">
-        <v>-1.6899105423629601E-3</v>
+        <v>1.08148072343284E-3</v>
       </c>
       <c r="G8" s="3">
-        <v>5.0754976343013002E-6</v>
+        <v>-2.3635878554329899E-6</v>
       </c>
       <c r="H8" s="3">
-        <v>1.2720708958473899E-5</v>
+        <v>2.4896603746977202E-6</v>
       </c>
       <c r="I8" s="3">
-        <v>4.0682581136420601E-3</v>
+        <v>1.60895116724665E-2</v>
       </c>
       <c r="J8" s="3">
-        <v>-9.2610457276485895E-6</v>
+        <v>-4.6727534814555196E-6</v>
       </c>
       <c r="K8" s="3">
-        <v>3.3314503288669802E-3</v>
+        <v>-3.7158793142576402E-5</v>
       </c>
       <c r="L8" s="3">
-        <v>-1.0102331975707099E-5</v>
+        <v>-1.3780982442612601E-5</v>
       </c>
       <c r="M8" s="3">
-        <v>-2.5822408089234501E-5</v>
+        <v>5.1049345243527497E-6</v>
       </c>
       <c r="N8" s="3">
-        <v>-3.60314256785438E-4</v>
+        <v>6.2379790741545796E-6</v>
       </c>
       <c r="O8" s="3">
-        <v>-1.0918987652906199E-7</v>
+        <v>1.7583205855964999E-5</v>
       </c>
       <c r="P8" s="3">
-        <v>-1.0221124129057E-6</v>
+        <v>-2.1144908080539602E-6</v>
       </c>
       <c r="Q8" s="3">
-        <v>5.9238585619971002E-6</v>
+        <v>1.6718531950615899E-5</v>
       </c>
       <c r="R8" s="3">
-        <v>-1.70294284882643E-6</v>
+        <v>-2.0035426825111801E-5</v>
       </c>
       <c r="S8" s="3">
-        <v>4.8283917176307801E-6</v>
+        <v>4.9436262853670103E-5</v>
       </c>
       <c r="T8" s="3">
-        <v>-1.0869179829134801E-6</v>
-      </c>
-      <c r="U8" s="3">
-        <v>2.1773710138984202E-6</v>
-      </c>
-      <c r="V8" s="3">
-        <v>3.1564170494286799E-6</v>
-      </c>
-      <c r="W8" s="3">
-        <v>-1.6330136371509201E-4</v>
-      </c>
-      <c r="X8" s="3">
-        <v>4.8464491858741802E-6</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>-7.8366137303311205E-6</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>5.3127332084190401E-6</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>-4.5652088834934702E-4</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>3.0300240647553599E-7</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>-4.1624261082025998E-4</v>
-      </c>
-      <c r="AD8" s="3">
-        <v>-6.1937828808712196E-6</v>
-      </c>
-      <c r="AE8" s="3">
-        <v>3.96136649828362E-5</v>
+        <v>-8.6720788823514795E-6</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="B9" s="3">
-        <v>1.9799246364819599E-6</v>
+        <v>-8.1972965338796E-3</v>
       </c>
       <c r="C9" s="3">
-        <v>-5.7012562247928403E-9</v>
+        <v>-1.9951459761529201E-5</v>
       </c>
       <c r="D9" s="3">
-        <v>5.6033032571383701E-6</v>
+        <v>6.1214312387262998E-6</v>
       </c>
       <c r="E9" s="3">
-        <v>-2.4037970488982201E-8</v>
+        <v>8.4998118401502599E-8</v>
       </c>
       <c r="F9" s="3">
-        <v>3.9132371300900496E-6</v>
+        <v>-1.31449874069332E-4</v>
       </c>
       <c r="G9" s="3">
-        <v>-1.08884644638723E-8</v>
+        <v>1.8569949547692401E-8</v>
       </c>
       <c r="H9" s="3">
-        <v>-2.8910371809689999E-8</v>
+        <v>-4.6649077666843097E-8</v>
       </c>
       <c r="I9" s="3">
-        <v>-9.2610457276485895E-6</v>
+        <v>-4.6727534814555196E-6</v>
       </c>
       <c r="J9" s="3">
-        <v>3.7039295322054999E-8</v>
+        <v>1.8271885283959599E-4</v>
       </c>
       <c r="K9" s="3">
-        <v>-6.3868700491256098E-6</v>
+        <v>1.2861587344386601E-4</v>
       </c>
       <c r="L9" s="3">
-        <v>1.7578178552832399E-8</v>
+        <v>1.28589387989384E-4</v>
       </c>
       <c r="M9" s="3">
-        <v>4.78439499748889E-8</v>
+        <v>1.2874140956800799E-4</v>
       </c>
       <c r="N9" s="3">
-        <v>5.4551901115884604E-7</v>
+        <v>1.2867264665216999E-4</v>
       </c>
       <c r="O9" s="3">
-        <v>-3.5846327869169501E-10</v>
+        <v>1.28798172267812E-4</v>
       </c>
       <c r="P9" s="3">
-        <v>-1.36258977667542E-8</v>
+        <v>1.2908218446648799E-4</v>
       </c>
       <c r="Q9" s="3">
-        <v>-1.9808713530690699E-8</v>
+        <v>1.2871086317220299E-4</v>
       </c>
       <c r="R9" s="3">
-        <v>-2.1409803017793801E-8</v>
+        <v>1.28157377023514E-4</v>
       </c>
       <c r="S9" s="3">
-        <v>-2.5290579834443499E-8</v>
+        <v>1.2850517839577201E-4</v>
       </c>
       <c r="T9" s="3">
-        <v>-1.680557053617E-8</v>
-      </c>
-      <c r="U9" s="3">
-        <v>-1.3507741620132001E-8</v>
-      </c>
-      <c r="V9" s="3">
-        <v>-7.1843560648331799E-9</v>
-      </c>
-      <c r="W9" s="3">
-        <v>1.4366113284974601E-6</v>
-      </c>
-      <c r="X9" s="3">
-        <v>8.8624719149530201E-9</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>2.39359101820782E-8</v>
-      </c>
-      <c r="Z9" s="3">
-        <v>1.6284997251971601E-8</v>
-      </c>
-      <c r="AA9" s="3">
-        <v>8.4304809464155598E-7</v>
-      </c>
-      <c r="AB9" s="3">
-        <v>1.6328844638368399E-8</v>
-      </c>
-      <c r="AC9" s="3">
-        <v>-2.38213687960778E-7</v>
-      </c>
-      <c r="AD9" s="3">
-        <v>8.9490495832072994E-9</v>
-      </c>
-      <c r="AE9" s="3">
-        <v>-2.49820286317083E-7</v>
+        <v>1.2823071191081999E-4</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>7</v>
+        <v>231</v>
       </c>
       <c r="B10" s="3">
-        <v>2.6758213703980401E-2</v>
+        <v>-6.8212570985156198E-4</v>
       </c>
       <c r="C10" s="3">
-        <v>5.4792089090609801E-5</v>
+        <v>-1.56280416303169E-5</v>
       </c>
       <c r="D10" s="3">
-        <v>-1.66963385651895E-3</v>
+        <v>8.6132197989848994E-6</v>
       </c>
       <c r="E10" s="3">
-        <v>3.8888376684996798E-6</v>
+        <v>3.23626215977667E-8</v>
       </c>
       <c r="F10" s="3">
-        <v>-2.1239481131728301E-3</v>
+        <v>-1.4110878557804701E-4</v>
       </c>
       <c r="G10" s="3">
-        <v>6.73467369315291E-6</v>
+        <v>4.9362830960052602E-8</v>
       </c>
       <c r="H10" s="3">
-        <v>1.0776633131646701E-5</v>
+        <v>-5.4253202543022897E-8</v>
       </c>
       <c r="I10" s="3">
-        <v>3.3314503288669802E-3</v>
+        <v>-3.7158793142576402E-5</v>
       </c>
       <c r="J10" s="3">
-        <v>-6.3868700491256098E-6</v>
+        <v>1.2861587344386601E-4</v>
       </c>
       <c r="K10" s="3">
-        <v>4.6108070650138101E-3</v>
+        <v>1.9429699234282E-4</v>
       </c>
       <c r="L10" s="3">
-        <v>-1.47718493978646E-5</v>
+        <v>1.28268875179628E-4</v>
       </c>
       <c r="M10" s="3">
-        <v>-2.20546317335719E-5</v>
+        <v>1.2823086318456201E-4</v>
       </c>
       <c r="N10" s="3">
-        <v>-1.80713894866647E-4</v>
+        <v>1.28263976140674E-4</v>
       </c>
       <c r="O10" s="3">
-        <v>-1.88335156310336E-6</v>
+        <v>1.2815158340243201E-4</v>
       </c>
       <c r="P10" s="3">
-        <v>5.2792204415593798E-6</v>
+        <v>1.2857424237435299E-4</v>
       </c>
       <c r="Q10" s="3">
-        <v>1.3969282250554E-5</v>
+        <v>1.2823793376952401E-4</v>
       </c>
       <c r="R10" s="3">
-        <v>3.8255747140326004E-6</v>
+        <v>1.2800878876395E-4</v>
       </c>
       <c r="S10" s="3">
-        <v>1.00859771508938E-5</v>
+        <v>1.2806925814576499E-4</v>
       </c>
       <c r="T10" s="3">
-        <v>2.0783965526135399E-6</v>
-      </c>
-      <c r="U10" s="3">
-        <v>5.7277235040851903E-6</v>
-      </c>
-      <c r="V10" s="3">
-        <v>-2.0387022210041599E-7</v>
-      </c>
-      <c r="W10" s="3">
-        <v>-2.20139485419299E-4</v>
-      </c>
-      <c r="X10" s="3">
-        <v>-8.4216674854528906E-6</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>-2.9167573376397699E-5</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>-5.6181224798459203E-6</v>
-      </c>
-      <c r="AA10" s="3">
-        <v>-1.4426314321205301E-3</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>-4.8313977370567103E-6</v>
-      </c>
-      <c r="AC10" s="3">
-        <v>-1.13668757442359E-3</v>
-      </c>
-      <c r="AD10" s="3">
-        <v>-2.7588637946059201E-6</v>
-      </c>
-      <c r="AE10" s="3">
-        <v>3.2304296443269002E-5</v>
+        <v>1.2837966944789301E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>8</v>
+        <v>230</v>
       </c>
       <c r="B11" s="3">
-        <v>-1.2273139232720301E-4</v>
+        <v>-4.4596424160110298E-4</v>
       </c>
       <c r="C11" s="3">
-        <v>-2.2681141620312401E-7</v>
+        <v>-1.6085496742759701E-5</v>
       </c>
       <c r="D11" s="3">
-        <v>5.0383735027121401E-6</v>
+        <v>2.2536356875863299E-5</v>
       </c>
       <c r="E11" s="3">
-        <v>-1.08547654697684E-8</v>
+        <v>3.4279766294984102E-9</v>
       </c>
       <c r="F11" s="3">
-        <v>6.7523665847881301E-6</v>
+        <v>-1.16254410988808E-4</v>
       </c>
       <c r="G11" s="3">
-        <v>-2.1758561176163999E-8</v>
+        <v>-2.97719140735268E-8</v>
       </c>
       <c r="H11" s="3">
-        <v>-3.3552400714094101E-8</v>
+        <v>-1.40962918782938E-7</v>
       </c>
       <c r="I11" s="3">
-        <v>-1.0102331975707099E-5</v>
+        <v>-1.3780982442612601E-5</v>
       </c>
       <c r="J11" s="3">
-        <v>1.7578178552832399E-8</v>
+        <v>1.28589387989384E-4</v>
       </c>
       <c r="K11" s="3">
-        <v>-1.47718493978646E-5</v>
+        <v>1.28268875179628E-4</v>
       </c>
       <c r="L11" s="3">
-        <v>4.8079992001042799E-8</v>
+        <v>2.19627493319524E-4</v>
       </c>
       <c r="M11" s="3">
-        <v>6.9020313175408906E-8</v>
+        <v>1.2884193331577599E-4</v>
       </c>
       <c r="N11" s="3">
-        <v>6.3347858642379704E-7</v>
+        <v>1.2863839335840199E-4</v>
       </c>
       <c r="O11" s="3">
-        <v>6.7171700757923099E-9</v>
+        <v>1.28716701703317E-4</v>
       </c>
       <c r="P11" s="3">
-        <v>-2.0582819260719701E-8</v>
+        <v>1.2909668980630199E-4</v>
       </c>
       <c r="Q11" s="3">
-        <v>-4.2577530733342301E-8</v>
+        <v>1.2881053694984901E-4</v>
       </c>
       <c r="R11" s="3">
-        <v>-1.8397198617289299E-8</v>
+        <v>1.2813856128638499E-4</v>
       </c>
       <c r="S11" s="3">
-        <v>-3.6814641556084201E-8</v>
+        <v>1.2847479183651601E-4</v>
       </c>
       <c r="T11" s="3">
-        <v>-1.47430468131336E-8</v>
-      </c>
-      <c r="U11" s="3">
-        <v>-2.7098997092493899E-8</v>
-      </c>
-      <c r="V11" s="3">
-        <v>-1.02694825328009E-8</v>
-      </c>
-      <c r="W11" s="3">
-        <v>5.6115990202953503E-8</v>
-      </c>
-      <c r="X11" s="3">
-        <v>2.9392240946629E-8</v>
-      </c>
-      <c r="Y11" s="3">
-        <v>8.9129318340567906E-8</v>
-      </c>
-      <c r="Z11" s="3">
-        <v>2.5466241507931901E-8</v>
-      </c>
-      <c r="AA11" s="3">
-        <v>4.9028998842065999E-6</v>
-      </c>
-      <c r="AB11" s="3">
-        <v>2.5602908621452001E-8</v>
-      </c>
-      <c r="AC11" s="3">
-        <v>4.5476868020242098E-6</v>
-      </c>
-      <c r="AD11" s="3">
-        <v>2.08158788748257E-8</v>
-      </c>
-      <c r="AE11" s="3">
-        <v>1.0551011155236501E-8</v>
+        <v>1.2804314241824901E-4</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>9</v>
+        <v>229</v>
       </c>
       <c r="B12" s="3">
-        <v>-1.3829572049644501E-4</v>
+        <v>-5.4173523046E-3</v>
       </c>
       <c r="C12" s="3">
-        <v>1.3345356051517001E-7</v>
+        <v>-1.6810972813864102E-5</v>
       </c>
       <c r="D12" s="3">
-        <v>1.2728986499007001E-5</v>
+        <v>1.81868866518548E-5</v>
       </c>
       <c r="E12" s="3">
-        <v>-2.9015396737953202E-8</v>
+        <v>5.00464040914354E-8</v>
       </c>
       <c r="F12" s="3">
-        <v>1.0930183137874E-5</v>
+        <v>-1.1205120093657801E-4</v>
       </c>
       <c r="G12" s="3">
-        <v>-3.3840560782707297E-8</v>
+        <v>-4.4378821342023198E-8</v>
       </c>
       <c r="H12" s="3">
-        <v>-8.4255885474116597E-8</v>
+        <v>-1.25313845761621E-7</v>
       </c>
       <c r="I12" s="3">
-        <v>-2.5822408089234501E-5</v>
+        <v>5.1049345243527497E-6</v>
       </c>
       <c r="J12" s="3">
-        <v>4.78439499748889E-8</v>
+        <v>1.2874140956800799E-4</v>
       </c>
       <c r="K12" s="3">
-        <v>-2.20546317335719E-5</v>
+        <v>1.2823086318456201E-4</v>
       </c>
       <c r="L12" s="3">
-        <v>6.9020313175408906E-8</v>
+        <v>1.2884193331577599E-4</v>
       </c>
       <c r="M12" s="3">
-        <v>1.75215649450174E-7</v>
+        <v>2.0167687277329699E-4</v>
       </c>
       <c r="N12" s="3">
-        <v>2.65238874080156E-6</v>
+        <v>1.2889660150704901E-4</v>
       </c>
       <c r="O12" s="3">
-        <v>1.23953466027715E-9</v>
+        <v>1.29047466392553E-4</v>
       </c>
       <c r="P12" s="3">
-        <v>1.9219483819745199E-8</v>
+        <v>1.29395492257354E-4</v>
       </c>
       <c r="Q12" s="3">
-        <v>-2.1589330938787101E-8</v>
+        <v>1.2910775674281099E-4</v>
       </c>
       <c r="R12" s="3">
-        <v>3.5625296281652297E-8</v>
+        <v>1.2822982475839699E-4</v>
       </c>
       <c r="S12" s="3">
-        <v>-7.9312539776170302E-9</v>
+        <v>1.2871723215705601E-4</v>
       </c>
       <c r="T12" s="3">
-        <v>3.1054006457303099E-8</v>
-      </c>
-      <c r="U12" s="3">
-        <v>1.61208966174969E-9</v>
-      </c>
-      <c r="V12" s="3">
-        <v>-8.4887729327274501E-9</v>
-      </c>
-      <c r="W12" s="3">
-        <v>-4.33838734377108E-7</v>
-      </c>
-      <c r="X12" s="3">
-        <v>-4.7401609513606601E-8</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>2.7956348290028201E-8</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>-6.15497249934948E-8</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>3.0354419539865501E-6</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>-2.3891852682965301E-8</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>4.2850359803336201E-6</v>
-      </c>
-      <c r="AD12" s="3">
-        <v>3.1453763039611501E-8</v>
-      </c>
-      <c r="AE12" s="3">
-        <v>-1.5113910206191199E-8</v>
+        <v>1.2797977117152899E-4</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>129</v>
+        <v>228</v>
       </c>
       <c r="B13" s="3">
-        <v>2.2705466677337101</v>
+        <v>-8.3842014307038606E-3</v>
       </c>
       <c r="C13" s="3">
-        <v>-1.45976076676486E-3</v>
+        <v>2.8045648463842E-5</v>
       </c>
       <c r="D13" s="3">
-        <v>7.7905118409062795E-6</v>
+        <v>-9.3509941745020897E-7</v>
       </c>
       <c r="E13" s="3">
-        <v>-8.42224261010507E-7</v>
+        <v>1.26981749798527E-7</v>
       </c>
       <c r="F13" s="3">
-        <v>1.3648730633539401E-3</v>
+        <v>-1.2246688883600201E-4</v>
       </c>
       <c r="G13" s="3">
-        <v>-2.4887305256268201E-6</v>
+        <v>-1.84627955760693E-8</v>
       </c>
       <c r="H13" s="3">
-        <v>4.85171799704477E-7</v>
+        <v>-3.87969118862372E-8</v>
       </c>
       <c r="I13" s="3">
-        <v>-3.60314256785438E-4</v>
+        <v>6.2379790741545796E-6</v>
       </c>
       <c r="J13" s="3">
-        <v>5.4551901115884604E-7</v>
+        <v>1.2867264665216999E-4</v>
       </c>
       <c r="K13" s="3">
-        <v>-1.80713894866647E-4</v>
+        <v>1.28263976140674E-4</v>
       </c>
       <c r="L13" s="3">
-        <v>6.3347858642379704E-7</v>
+        <v>1.2863839335840199E-4</v>
       </c>
       <c r="M13" s="3">
-        <v>2.65238874080156E-6</v>
+        <v>1.2889660150704901E-4</v>
       </c>
       <c r="N13" s="3">
-        <v>2.4002318081982301E-2</v>
+        <v>1.8497035979113499E-4</v>
       </c>
       <c r="O13" s="3">
-        <v>6.7497504647905401E-6</v>
+        <v>1.2861294772255899E-4</v>
       </c>
       <c r="P13" s="3">
-        <v>5.9670896535975101E-5</v>
+        <v>1.2912919417246599E-4</v>
       </c>
       <c r="Q13" s="3">
-        <v>9.7790571324122096E-5</v>
+        <v>1.2898803287014299E-4</v>
       </c>
       <c r="R13" s="3">
-        <v>1.08213961413623E-4</v>
+        <v>1.28185529936824E-4</v>
       </c>
       <c r="S13" s="3">
-        <v>1.3215419949606899E-4</v>
+        <v>1.2851062493150799E-4</v>
       </c>
       <c r="T13" s="3">
-        <v>1.5757211478519399E-4</v>
-      </c>
-      <c r="U13" s="3">
-        <v>1.88510316173865E-4</v>
-      </c>
-      <c r="V13" s="3">
-        <v>2.0094480297840898E-5</v>
-      </c>
-      <c r="W13" s="3">
-        <v>-9.31251023493098E-4</v>
-      </c>
-      <c r="X13" s="3">
-        <v>6.4462625566343999E-5</v>
-      </c>
-      <c r="Y13" s="3">
-        <v>1.2416583230065201E-4</v>
-      </c>
-      <c r="Z13" s="3">
-        <v>1.13553584448123E-4</v>
-      </c>
-      <c r="AA13" s="3">
-        <v>9.0860139493382005E-3</v>
-      </c>
-      <c r="AB13" s="3">
-        <v>1.61155868338051E-4</v>
-      </c>
-      <c r="AC13" s="3">
-        <v>1.5811559315374198E-2</v>
-      </c>
-      <c r="AD13" s="3">
-        <v>2.1354969270057898E-5</v>
-      </c>
-      <c r="AE13" s="3">
-        <v>-1.7818291051150901E-5</v>
+        <v>1.2806928906562701E-4</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="B14" s="3">
-        <v>-1.35734328536476E-2</v>
+        <v>7.0813954923913802E-3</v>
       </c>
       <c r="C14" s="3">
-        <v>-4.4239560392802401E-4</v>
+        <v>-1.69121915246763E-4</v>
       </c>
       <c r="D14" s="3">
-        <v>-1.3099796384693701E-8</v>
+        <v>4.96156039309976E-6</v>
       </c>
       <c r="E14" s="3">
-        <v>-1.5768931082986501E-9</v>
+        <v>6.7466998015694194E-8</v>
       </c>
       <c r="F14" s="3">
-        <v>2.0305308604558202E-6</v>
+        <v>-1.16349003759329E-4</v>
       </c>
       <c r="G14" s="3">
-        <v>-3.2854750580198301E-9</v>
+        <v>-1.95762401573888E-8</v>
       </c>
       <c r="H14" s="3">
-        <v>1.4718208970971601E-9</v>
+        <v>7.1569427468724803E-8</v>
       </c>
       <c r="I14" s="3">
-        <v>-1.0918987652906199E-7</v>
+        <v>1.7583205855964999E-5</v>
       </c>
       <c r="J14" s="3">
-        <v>-3.5846327869169501E-10</v>
+        <v>1.28798172267812E-4</v>
       </c>
       <c r="K14" s="3">
-        <v>-1.88335156310336E-6</v>
+        <v>1.2815158340243201E-4</v>
       </c>
       <c r="L14" s="3">
-        <v>6.7171700757923099E-9</v>
+        <v>1.28716701703317E-4</v>
       </c>
       <c r="M14" s="3">
-        <v>1.23953466027715E-9</v>
+        <v>1.29047466392553E-4</v>
       </c>
       <c r="N14" s="3">
-        <v>6.7497504647905401E-6</v>
+        <v>1.2861294772255899E-4</v>
       </c>
       <c r="O14" s="3">
-        <v>1.5787346552941502E-5</v>
+        <v>2.0162779045955801E-4</v>
       </c>
       <c r="P14" s="3">
-        <v>7.2649059269395601E-7</v>
+        <v>1.29149652459675E-4</v>
       </c>
       <c r="Q14" s="3">
-        <v>9.1323982152296103E-6</v>
+        <v>1.2825370519533501E-4</v>
       </c>
       <c r="R14" s="3">
-        <v>8.6875804931833099E-7</v>
+        <v>1.28387798462399E-4</v>
       </c>
       <c r="S14" s="3">
-        <v>5.2530493865776296E-6</v>
+        <v>1.29171340856517E-4</v>
       </c>
       <c r="T14" s="3">
-        <v>9.5920177027588999E-7</v>
-      </c>
-      <c r="U14" s="3">
-        <v>5.1186424449172196E-6</v>
-      </c>
-      <c r="V14" s="3">
-        <v>1.0025458430046899E-6</v>
-      </c>
-      <c r="W14" s="3">
-        <v>1.90475354578235E-4</v>
-      </c>
-      <c r="X14" s="3">
-        <v>6.6498492243387699E-7</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>1.18894871016752E-5</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>8.7843892578780003E-7</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>3.8885890278582701E-4</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>9.816471018495259E-7</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>3.9990612529965E-4</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>1.0148492182875601E-6</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>3.3219196627751998E-5</v>
+        <v>1.2725999699466701E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="B15" s="3">
-        <v>-2.0050798941757802E-3</v>
+        <v>-8.6466993167642007E-3</v>
       </c>
       <c r="C15" s="3">
-        <v>-1.38273208057125E-5</v>
+        <v>-3.7489818026374599E-6</v>
       </c>
       <c r="D15" s="3">
-        <v>8.8767747496532897E-8</v>
+        <v>3.0444920369570299E-5</v>
       </c>
       <c r="E15" s="3">
-        <v>1.2794883453042E-8</v>
+        <v>2.9257034913650999E-8</v>
       </c>
       <c r="F15" s="3">
-        <v>-2.3901403872406398E-6</v>
+        <v>-1.12737357219583E-4</v>
       </c>
       <c r="G15" s="3">
-        <v>1.6150131807205499E-8</v>
+        <v>-3.6634297609672803E-8</v>
       </c>
       <c r="H15" s="3">
-        <v>-1.08912156633368E-8</v>
+        <v>-1.98445037526611E-7</v>
       </c>
       <c r="I15" s="3">
-        <v>-1.0221124129057E-6</v>
+        <v>-2.1144908080539602E-6</v>
       </c>
       <c r="J15" s="3">
-        <v>-1.36258977667542E-8</v>
+        <v>1.2908218446648799E-4</v>
       </c>
       <c r="K15" s="3">
-        <v>5.2792204415593798E-6</v>
+        <v>1.2857424237435299E-4</v>
       </c>
       <c r="L15" s="3">
-        <v>-2.0582819260719701E-8</v>
+        <v>1.2909668980630199E-4</v>
       </c>
       <c r="M15" s="3">
-        <v>1.9219483819745199E-8</v>
+        <v>1.29395492257354E-4</v>
       </c>
       <c r="N15" s="3">
-        <v>5.9670896535975101E-5</v>
+        <v>1.2912919417246599E-4</v>
       </c>
       <c r="O15" s="3">
-        <v>7.2649059269395601E-7</v>
+        <v>1.29149652459675E-4</v>
       </c>
       <c r="P15" s="3">
-        <v>3.9905239920756798E-6</v>
+        <v>1.6985912726237101E-4</v>
       </c>
       <c r="Q15" s="3">
-        <v>1.74371422187407E-6</v>
+        <v>1.2940122871540999E-4</v>
       </c>
       <c r="R15" s="3">
-        <v>1.8611587352190899E-6</v>
+        <v>1.28288053350757E-4</v>
       </c>
       <c r="S15" s="3">
-        <v>1.9963008630753399E-6</v>
+        <v>1.28876243626055E-4</v>
       </c>
       <c r="T15" s="3">
-        <v>2.0477484583210298E-6</v>
-      </c>
-      <c r="U15" s="3">
-        <v>2.20403362953372E-6</v>
-      </c>
-      <c r="V15" s="3">
-        <v>1.70850762373849E-6</v>
-      </c>
-      <c r="W15" s="3">
-        <v>1.3914505646704801E-5</v>
-      </c>
-      <c r="X15" s="3">
-        <v>1.9881954989842001E-7</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>6.1461366950348299E-7</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>3.1860895281410102E-7</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>3.1494834524757201E-5</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>4.3653847812177798E-7</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>4.8209162137823403E-5</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>8.9518303641746302E-8</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>7.2427379996700101E-7</v>
+        <v>1.28239416372725E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B16" s="3">
-        <v>-2.2808771051673199E-2</v>
+        <v>-1.52704841429614E-2</v>
       </c>
       <c r="C16" s="3">
-        <v>-5.7002713262109203E-4</v>
+        <v>5.7103493780468003E-5</v>
       </c>
       <c r="D16" s="3">
-        <v>-5.5865571930154203E-6</v>
+        <v>1.42405086502582E-5</v>
       </c>
       <c r="E16" s="3">
-        <v>1.7855419920635701E-8</v>
+        <v>7.8520358290831098E-8</v>
       </c>
       <c r="F16" s="3">
-        <v>-7.7677387885546099E-6</v>
+        <v>-1.13525292221057E-4</v>
       </c>
       <c r="G16" s="3">
-        <v>3.7241227150176697E-8</v>
+        <v>-4.5318350624731501E-8</v>
       </c>
       <c r="H16" s="3">
-        <v>2.11765600072742E-8</v>
+        <v>-1.50424457315999E-7</v>
       </c>
       <c r="I16" s="3">
-        <v>5.9238585619971002E-6</v>
+        <v>1.6718531950615899E-5</v>
       </c>
       <c r="J16" s="3">
-        <v>-1.9808713530690699E-8</v>
+        <v>1.2871086317220299E-4</v>
       </c>
       <c r="K16" s="3">
-        <v>1.3969282250554E-5</v>
+        <v>1.2823793376952401E-4</v>
       </c>
       <c r="L16" s="3">
-        <v>-4.2577530733342301E-8</v>
+        <v>1.2881053694984901E-4</v>
       </c>
       <c r="M16" s="3">
-        <v>-2.1589330938787101E-8</v>
+        <v>1.2910775674281099E-4</v>
       </c>
       <c r="N16" s="3">
-        <v>9.7790571324122096E-5</v>
+        <v>1.2898803287014299E-4</v>
       </c>
       <c r="O16" s="3">
-        <v>9.1323982152296103E-6</v>
+        <v>1.2825370519533501E-4</v>
       </c>
       <c r="P16" s="3">
-        <v>1.74371422187407E-6</v>
+        <v>1.2940122871540999E-4</v>
       </c>
       <c r="Q16" s="3">
-        <v>1.00898477309969E-4</v>
+        <v>1.9031549287813301E-4</v>
       </c>
       <c r="R16" s="3">
-        <v>2.2187747043785398E-6</v>
+        <v>1.2815557511586801E-4</v>
       </c>
       <c r="S16" s="3">
-        <v>8.0524148358984206E-6</v>
+        <v>1.28557353679376E-4</v>
       </c>
       <c r="T16" s="3">
-        <v>2.5553660184364099E-6</v>
-      </c>
-      <c r="U16" s="3">
-        <v>8.0723356333049807E-6</v>
-      </c>
-      <c r="V16" s="3">
-        <v>2.0687690594699399E-6</v>
-      </c>
-      <c r="W16" s="3">
-        <v>2.4645639759330402E-4</v>
-      </c>
-      <c r="X16" s="3">
-        <v>3.3277008861697502E-7</v>
-      </c>
-      <c r="Y16" s="3">
-        <v>1.4599664530026599E-5</v>
-      </c>
-      <c r="Z16" s="3">
-        <v>1.0068060718133701E-6</v>
-      </c>
-      <c r="AA16" s="3">
-        <v>5.3025685080780203E-4</v>
-      </c>
-      <c r="AB16" s="3">
-        <v>1.3947852225007701E-6</v>
-      </c>
-      <c r="AC16" s="3">
-        <v>5.7627705007456704E-4</v>
-      </c>
-      <c r="AD16" s="3">
-        <v>9.54243449060503E-7</v>
-      </c>
-      <c r="AE16" s="3">
-        <v>4.2266834945770703E-5</v>
+        <v>1.2823405924706699E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B17" s="3">
-        <v>1.5803642417603601E-2</v>
+        <v>6.8823809369989702E-3</v>
       </c>
       <c r="C17" s="3">
-        <v>-3.2806140748527603E-5</v>
+        <v>2.9753483553440498E-6</v>
       </c>
       <c r="D17" s="3">
-        <v>1.2827442790502899E-7</v>
+        <v>-6.9696922151638896E-6</v>
       </c>
       <c r="E17" s="3">
-        <v>1.99766442914547E-8</v>
+        <v>7.8818250748758297E-8</v>
       </c>
       <c r="F17" s="3">
-        <v>1.51652690158799E-6</v>
+        <v>-1.28598471605231E-4</v>
       </c>
       <c r="G17" s="3">
-        <v>1.02422739239568E-8</v>
+        <v>-6.6291409138536298E-10</v>
       </c>
       <c r="H17" s="3">
-        <v>-2.1509396451579401E-8</v>
+        <v>3.1528826670931298E-8</v>
       </c>
       <c r="I17" s="3">
-        <v>-1.70294284882643E-6</v>
+        <v>-2.0035426825111801E-5</v>
       </c>
       <c r="J17" s="3">
-        <v>-2.1409803017793801E-8</v>
+        <v>1.28157377023514E-4</v>
       </c>
       <c r="K17" s="3">
-        <v>3.8255747140326004E-6</v>
+        <v>1.2800878876395E-4</v>
       </c>
       <c r="L17" s="3">
-        <v>-1.8397198617289299E-8</v>
+        <v>1.2813856128638499E-4</v>
       </c>
       <c r="M17" s="3">
-        <v>3.5625296281652297E-8</v>
+        <v>1.2822982475839699E-4</v>
       </c>
       <c r="N17" s="3">
-        <v>1.08213961413623E-4</v>
+        <v>1.28185529936824E-4</v>
       </c>
       <c r="O17" s="3">
-        <v>8.6875804931833099E-7</v>
+        <v>1.28387798462399E-4</v>
       </c>
       <c r="P17" s="3">
-        <v>1.8611587352190899E-6</v>
+        <v>1.28288053350757E-4</v>
       </c>
       <c r="Q17" s="3">
-        <v>2.2187747043785398E-6</v>
+        <v>1.2815557511586801E-4</v>
       </c>
       <c r="R17" s="3">
-        <v>3.0165964169052899E-6</v>
+        <v>2.32080654378979E-4</v>
       </c>
       <c r="S17" s="3">
-        <v>2.83261234577191E-6</v>
+        <v>1.2807525024838501E-4</v>
       </c>
       <c r="T17" s="3">
-        <v>2.9383419141466999E-6</v>
-      </c>
-      <c r="U17" s="3">
-        <v>3.27033734169333E-6</v>
-      </c>
-      <c r="V17" s="3">
-        <v>2.4122779296801099E-6</v>
-      </c>
-      <c r="W17" s="3">
-        <v>3.1872630737884599E-5</v>
-      </c>
-      <c r="X17" s="3">
-        <v>3.22284399571829E-7</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>1.2539624543418201E-6</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>5.5740761552043E-7</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>6.3887113516178601E-5</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>7.78057907697776E-7</v>
-      </c>
-      <c r="AC17" s="3">
-        <v>9.4814081961460301E-5</v>
-      </c>
-      <c r="AD17" s="3">
-        <v>1.52395911667508E-7</v>
-      </c>
-      <c r="AE17" s="3">
-        <v>1.8904408457533699E-6</v>
+        <v>1.27809838639794E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B18" s="3">
-        <v>9.9177244178018896E-3</v>
+        <v>-1.56186443086244E-2</v>
       </c>
       <c r="C18" s="3">
-        <v>-3.2657794885813701E-4</v>
+        <v>-4.3012352796894299E-5</v>
       </c>
       <c r="D18" s="3">
-        <v>-5.7799354375200503E-6</v>
+        <v>1.3029580279298299E-5</v>
       </c>
       <c r="E18" s="3">
-        <v>2.32256623767341E-8</v>
+        <v>1.5682050871755901E-8</v>
       </c>
       <c r="F18" s="3">
-        <v>-2.7993631971185E-6</v>
+        <v>-1.15812272087677E-4</v>
       </c>
       <c r="G18" s="3">
-        <v>2.7873815411059302E-8</v>
+        <v>-2.649256276039E-8</v>
       </c>
       <c r="H18" s="3">
-        <v>1.7858979455248701E-8</v>
+        <v>-5.4401984672664301E-8</v>
       </c>
       <c r="I18" s="3">
-        <v>4.8283917176307801E-6</v>
+        <v>4.9436262853670103E-5</v>
       </c>
       <c r="J18" s="3">
-        <v>-2.5290579834443499E-8</v>
+        <v>1.2850517839577201E-4</v>
       </c>
       <c r="K18" s="3">
-        <v>1.00859771508938E-5</v>
+        <v>1.2806925814576499E-4</v>
       </c>
       <c r="L18" s="3">
-        <v>-3.6814641556084201E-8</v>
+        <v>1.2847479183651601E-4</v>
       </c>
       <c r="M18" s="3">
-        <v>-7.9312539776170302E-9</v>
+        <v>1.2871723215705601E-4</v>
       </c>
       <c r="N18" s="3">
-        <v>1.3215419949606899E-4</v>
+        <v>1.2851062493150799E-4</v>
       </c>
       <c r="O18" s="3">
-        <v>5.2530493865776296E-6</v>
+        <v>1.29171340856517E-4</v>
       </c>
       <c r="P18" s="3">
-        <v>1.9963008630753399E-6</v>
+        <v>1.28876243626055E-4</v>
       </c>
       <c r="Q18" s="3">
-        <v>8.0524148358984206E-6</v>
+        <v>1.28557353679376E-4</v>
       </c>
       <c r="R18" s="3">
-        <v>2.83261234577191E-6</v>
+        <v>1.2807525024838501E-4</v>
       </c>
       <c r="S18" s="3">
-        <v>2.5105415915978999E-5</v>
+        <v>1.9081121324572101E-4</v>
       </c>
       <c r="T18" s="3">
-        <v>3.3850573630791099E-6</v>
-      </c>
-      <c r="U18" s="3">
-        <v>6.9411978985472099E-6</v>
-      </c>
-      <c r="V18" s="3">
-        <v>2.82136290694417E-6</v>
-      </c>
-      <c r="W18" s="3">
-        <v>1.58726801581819E-4</v>
-      </c>
-      <c r="X18" s="3">
-        <v>3.9961202020835003E-7</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>8.6494912281384898E-6</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>9.3611507080432402E-7</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>3.2856112513123599E-4</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>1.30724854001861E-6</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>3.7605886421803603E-4</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>6.1014253744220205E-7</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>2.3811754538130601E-5</v>
+        <v>1.2781627363187101E-4</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B19" s="3">
-        <v>2.2488293912465498E-2</v>
+        <v>-1.07160697847995E-2</v>
       </c>
       <c r="C19" s="3">
-        <v>-4.4083097124947101E-5</v>
+        <v>3.7008445852146098E-5</v>
       </c>
       <c r="D19" s="3">
-        <v>-1.1773492092786599E-6</v>
+        <v>1.42629557258721E-5</v>
       </c>
       <c r="E19" s="3">
-        <v>1.47597078118045E-8</v>
+        <v>-2.5143497513425999E-8</v>
       </c>
       <c r="F19" s="3">
-        <v>5.7273347152628699E-6</v>
+        <v>-1.3430966264520999E-4</v>
       </c>
       <c r="G19" s="3">
-        <v>2.7910252330068198E-9</v>
+        <v>2.5363953227354399E-8</v>
       </c>
       <c r="H19" s="3">
-        <v>-1.07598233820826E-8</v>
+        <v>-1.12458184845013E-7</v>
       </c>
       <c r="I19" s="3">
-        <v>-1.0869179829134801E-6</v>
+        <v>-8.6720788823514795E-6</v>
       </c>
       <c r="J19" s="3">
-        <v>-1.680557053617E-8</v>
+        <v>1.2823071191081999E-4</v>
       </c>
       <c r="K19" s="3">
-        <v>2.0783965526135399E-6</v>
+        <v>1.2837966944789301E-4</v>
       </c>
       <c r="L19" s="3">
-        <v>-1.47430468131336E-8</v>
+        <v>1.2804314241824901E-4</v>
       </c>
       <c r="M19" s="3">
-        <v>3.1054006457303099E-8</v>
+        <v>1.2797977117152899E-4</v>
       </c>
       <c r="N19" s="3">
-        <v>1.5757211478519399E-4</v>
+        <v>1.2806928906562701E-4</v>
       </c>
       <c r="O19" s="3">
-        <v>9.5920177027588999E-7</v>
+        <v>1.2725999699466701E-4</v>
       </c>
       <c r="P19" s="3">
-        <v>2.0477484583210298E-6</v>
+        <v>1.28239416372725E-4</v>
       </c>
       <c r="Q19" s="3">
-        <v>2.5553660184364099E-6</v>
+        <v>1.2823405924706699E-4</v>
       </c>
       <c r="R19" s="3">
-        <v>2.9383419141466999E-6</v>
+        <v>1.27809838639794E-4</v>
       </c>
       <c r="S19" s="3">
-        <v>3.3850573630791099E-6</v>
+        <v>1.2781627363187101E-4</v>
       </c>
       <c r="T19" s="3">
-        <v>3.9077793697805003E-6</v>
-      </c>
-      <c r="U19" s="3">
-        <v>4.0249455424304601E-6</v>
-      </c>
-      <c r="V19" s="3">
-        <v>2.8510125047791102E-6</v>
-      </c>
-      <c r="W19" s="3">
-        <v>4.3420305045676701E-5</v>
-      </c>
-      <c r="X19" s="3">
-        <v>4.5197342012618002E-7</v>
-      </c>
-      <c r="Y19" s="3">
-        <v>1.7107070791313099E-6</v>
-      </c>
-      <c r="Z19" s="3">
-        <v>7.9613280323215095E-7</v>
-      </c>
-      <c r="AA19" s="3">
-        <v>8.9808522990028405E-5</v>
-      </c>
-      <c r="AB19" s="3">
-        <v>1.1179285224098299E-6</v>
-      </c>
-      <c r="AC19" s="3">
-        <v>1.34874783864406E-4</v>
-      </c>
-      <c r="AD19" s="3">
-        <v>2.06862585445913E-7</v>
-      </c>
-      <c r="AE19" s="3">
-        <v>2.47460032621245E-6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B20" s="3">
-        <v>1.28100266221424E-2</v>
-      </c>
-      <c r="C20" s="3">
-        <v>-3.2367230722205498E-4</v>
-      </c>
-      <c r="D20" s="3">
-        <v>-3.9686892538799602E-6</v>
-      </c>
-      <c r="E20" s="3">
-        <v>1.07615780554663E-8</v>
-      </c>
-      <c r="F20" s="3">
-        <v>4.33079258177218E-6</v>
-      </c>
-      <c r="G20" s="3">
-        <v>1.37649092255024E-8</v>
-      </c>
-      <c r="H20" s="3">
-        <v>1.5763048125408299E-8</v>
-      </c>
-      <c r="I20" s="3">
-        <v>2.1773710138984202E-6</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-1.3507741620132001E-8</v>
-      </c>
-      <c r="K20" s="3">
-        <v>5.7277235040851903E-6</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-2.7098997092493899E-8</v>
-      </c>
-      <c r="M20" s="3">
-        <v>1.61208966174969E-9</v>
-      </c>
-      <c r="N20" s="3">
-        <v>1.88510316173865E-4</v>
-      </c>
-      <c r="O20" s="3">
-        <v>5.1186424449172196E-6</v>
-      </c>
-      <c r="P20" s="3">
-        <v>2.20403362953372E-6</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>8.0723356333049807E-6</v>
-      </c>
-      <c r="R20" s="3">
-        <v>3.27033734169333E-6</v>
-      </c>
-      <c r="S20" s="3">
-        <v>6.9411978985472099E-6</v>
-      </c>
-      <c r="T20" s="3">
-        <v>4.0249455424304601E-6</v>
-      </c>
-      <c r="U20" s="3">
-        <v>5.7135421380955798E-5</v>
-      </c>
-      <c r="V20" s="3">
-        <v>3.2426650992799402E-6</v>
-      </c>
-      <c r="W20" s="3">
-        <v>1.68120147784875E-4</v>
-      </c>
-      <c r="X20" s="3">
-        <v>5.4689304561624302E-7</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>8.7782861841766895E-6</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>1.1942906010439699E-6</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>3.4435782274324598E-4</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>1.67535851537749E-6</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>4.0746789479650198E-4</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>6.4871772972224199E-7</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>2.3294289001235301E-5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B21" s="3">
-        <v>1.7396586469329098E-2</v>
-      </c>
-      <c r="C21" s="3">
-        <v>-4.3004050441810102E-5</v>
-      </c>
-      <c r="D21" s="3">
-        <v>-3.37284148752009E-6</v>
-      </c>
-      <c r="E21" s="3">
-        <v>6.8335268027798396E-9</v>
-      </c>
-      <c r="F21" s="3">
-        <v>1.2500867592743E-6</v>
-      </c>
-      <c r="G21" s="3">
-        <v>8.9633571572751406E-9</v>
-      </c>
-      <c r="H21" s="3">
-        <v>1.0591673151090299E-8</v>
-      </c>
-      <c r="I21" s="3">
-        <v>3.1564170494286799E-6</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-7.1843560648331799E-9</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-2.0387022210041599E-7</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-1.02694825328009E-8</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-8.4887729327274501E-9</v>
-      </c>
-      <c r="N21" s="3">
-        <v>2.0094480297840898E-5</v>
-      </c>
-      <c r="O21" s="3">
-        <v>1.0025458430046899E-6</v>
-      </c>
-      <c r="P21" s="3">
-        <v>1.70850762373849E-6</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>2.0687690594699399E-6</v>
-      </c>
-      <c r="R21" s="3">
-        <v>2.4122779296801099E-6</v>
-      </c>
-      <c r="S21" s="3">
-        <v>2.82136290694417E-6</v>
-      </c>
-      <c r="T21" s="3">
-        <v>2.8510125047791102E-6</v>
-      </c>
-      <c r="U21" s="3">
-        <v>3.2426650992799402E-6</v>
-      </c>
-      <c r="V21" s="3">
-        <v>3.2318151967271399E-6</v>
-      </c>
-      <c r="W21" s="3">
-        <v>6.3758249088219094E-5</v>
-      </c>
-      <c r="X21" s="3">
-        <v>8.1226195860351397E-8</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>1.1781359996067501E-6</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>1.5103326048991601E-7</v>
-      </c>
-      <c r="AA21" s="3">
-        <v>4.4134912942978601E-5</v>
-      </c>
-      <c r="AB21" s="3">
-        <v>2.0293873847977999E-7</v>
-      </c>
-      <c r="AC21" s="3">
-        <v>5.0942068467121303E-5</v>
-      </c>
-      <c r="AD21" s="3">
-        <v>9.4391075617084197E-8</v>
-      </c>
-      <c r="AE21" s="3">
-        <v>3.1230377465330602E-6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="B22" s="3">
-        <v>-5.54366381774049</v>
-      </c>
-      <c r="C22" s="3">
-        <v>-1.3131505351304499E-2</v>
-      </c>
-      <c r="D22" s="3">
-        <v>2.2205913617525199E-4</v>
-      </c>
-      <c r="E22" s="3">
-        <v>-1.4392591456924201E-6</v>
-      </c>
-      <c r="F22" s="3">
-        <v>2.0962679688493001E-4</v>
-      </c>
-      <c r="G22" s="3">
-        <v>6.2164446363434603E-8</v>
-      </c>
-      <c r="H22" s="3">
-        <v>-2.7545664026340501E-8</v>
-      </c>
-      <c r="I22" s="3">
-        <v>-1.6330136371509201E-4</v>
-      </c>
-      <c r="J22" s="3">
-        <v>1.4366113284974601E-6</v>
-      </c>
-      <c r="K22" s="3">
-        <v>-2.20139485419299E-4</v>
-      </c>
-      <c r="L22" s="3">
-        <v>5.6115990202953503E-8</v>
-      </c>
-      <c r="M22" s="3">
-        <v>-4.33838734377108E-7</v>
-      </c>
-      <c r="N22" s="3">
-        <v>-9.31251023493098E-4</v>
-      </c>
-      <c r="O22" s="3">
-        <v>1.90475354578235E-4</v>
-      </c>
-      <c r="P22" s="3">
-        <v>1.3914505646704801E-5</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>2.4645639759330402E-4</v>
-      </c>
-      <c r="R22" s="3">
-        <v>3.1872630737884599E-5</v>
-      </c>
-      <c r="S22" s="3">
-        <v>1.58726801581819E-4</v>
-      </c>
-      <c r="T22" s="3">
-        <v>4.3420305045676701E-5</v>
-      </c>
-      <c r="U22" s="3">
-        <v>1.68120147784875E-4</v>
-      </c>
-      <c r="V22" s="3">
-        <v>6.3758249088219094E-5</v>
-      </c>
-      <c r="W22" s="3">
-        <v>180965.413391195</v>
-      </c>
-      <c r="X22" s="3">
-        <v>-2.3756800638668999E-6</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>3.2261829690493E-4</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>7.24192615771289E-6</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>1.11797997728235E-2</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>1.0090793471891E-5</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>1.13680680694851E-2</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>1.8604867054813401E-5</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>9.9045831466263909E-4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B23" s="3">
-        <v>-1.53561020646784E-2</v>
-      </c>
-      <c r="C23" s="3">
-        <v>-4.98718667466059E-6</v>
-      </c>
-      <c r="D23" s="3">
-        <v>-3.7473548779964399E-8</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-2.3475894752501299E-9</v>
-      </c>
-      <c r="F23" s="3">
-        <v>3.65862187673918E-6</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-6.7816117227708904E-9</v>
-      </c>
-      <c r="H23" s="3">
-        <v>1.8410488850628699E-9</v>
-      </c>
-      <c r="I23" s="3">
-        <v>4.8464491858741802E-6</v>
-      </c>
-      <c r="J23" s="3">
-        <v>8.8624719149530201E-9</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-8.4216674854528906E-6</v>
-      </c>
-      <c r="L23" s="3">
-        <v>2.9392240946629E-8</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-4.7401609513606601E-8</v>
-      </c>
-      <c r="N23" s="3">
-        <v>6.4462625566343999E-5</v>
-      </c>
-      <c r="O23" s="3">
-        <v>6.6498492243387699E-7</v>
-      </c>
-      <c r="P23" s="3">
-        <v>1.9881954989842001E-7</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>3.3277008861697502E-7</v>
-      </c>
-      <c r="R23" s="3">
-        <v>3.22284399571829E-7</v>
-      </c>
-      <c r="S23" s="3">
-        <v>3.9961202020835003E-7</v>
-      </c>
-      <c r="T23" s="3">
-        <v>4.5197342012618002E-7</v>
-      </c>
-      <c r="U23" s="3">
-        <v>5.4689304561624302E-7</v>
-      </c>
-      <c r="V23" s="3">
-        <v>8.1226195860351397E-8</v>
-      </c>
-      <c r="W23" s="3">
-        <v>-2.3756800638668999E-6</v>
-      </c>
-      <c r="X23" s="3">
-        <v>1.11277617700828E-5</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>2.1923723492404899E-6</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>1.9927526473481899E-6</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>4.1546726855648198E-5</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>2.0383028853820201E-6</v>
-      </c>
-      <c r="AC23" s="3">
-        <v>5.6576407337050302E-5</v>
-      </c>
-      <c r="AD23" s="3">
-        <v>1.4846901326516201E-6</v>
-      </c>
-      <c r="AE23" s="3">
-        <v>1.94750503173308E-6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="B24" s="3">
-        <v>-3.7360726666322598E-2</v>
-      </c>
-      <c r="C24" s="3">
-        <v>-7.4770951320942802E-4</v>
-      </c>
-      <c r="D24" s="3">
-        <v>1.41243484717148E-6</v>
-      </c>
-      <c r="E24" s="3">
-        <v>-4.6272621780540504E-9</v>
-      </c>
-      <c r="F24" s="3">
-        <v>1.0080933112939599E-5</v>
-      </c>
-      <c r="G24" s="3">
-        <v>-1.5014541176193999E-8</v>
-      </c>
-      <c r="H24" s="3">
-        <v>-8.0628341323405592E-9</v>
-      </c>
-      <c r="I24" s="3">
-        <v>-7.8366137303311205E-6</v>
-      </c>
-      <c r="J24" s="3">
-        <v>2.39359101820782E-8</v>
-      </c>
-      <c r="K24" s="3">
-        <v>-2.9167573376397699E-5</v>
-      </c>
-      <c r="L24" s="3">
-        <v>8.9129318340567906E-8</v>
-      </c>
-      <c r="M24" s="3">
-        <v>2.7956348290028201E-8</v>
-      </c>
-      <c r="N24" s="3">
-        <v>1.2416583230065201E-4</v>
-      </c>
-      <c r="O24" s="3">
-        <v>1.18894871016752E-5</v>
-      </c>
-      <c r="P24" s="3">
-        <v>6.1461366950348299E-7</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>1.4599664530026599E-5</v>
-      </c>
-      <c r="R24" s="3">
-        <v>1.2539624543418201E-6</v>
-      </c>
-      <c r="S24" s="3">
-        <v>8.6494912281384898E-6</v>
-      </c>
-      <c r="T24" s="3">
-        <v>1.7107070791313099E-6</v>
-      </c>
-      <c r="U24" s="3">
-        <v>8.7782861841766895E-6</v>
-      </c>
-      <c r="V24" s="3">
-        <v>1.1781359996067501E-6</v>
-      </c>
-      <c r="W24" s="3">
-        <v>3.2261829690493E-4</v>
-      </c>
-      <c r="X24" s="3">
-        <v>2.1923723492404899E-6</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>2.71122548519406E-4</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>2.5860546501435299E-6</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>7.2915130476653204E-4</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>2.8355353644538502E-6</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>7.624437791238E-4</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>1.9956415163245901E-6</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>5.9539551208076402E-5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="B25" s="3">
-        <v>3.57891790059023E-3</v>
-      </c>
-      <c r="C25" s="3">
-        <v>-3.37532068332918E-5</v>
-      </c>
-      <c r="D25" s="3">
-        <v>4.6697030234485799E-8</v>
-      </c>
-      <c r="E25" s="3">
-        <v>-4.0507049891447397E-9</v>
-      </c>
-      <c r="F25" s="3">
-        <v>6.5591850107535598E-6</v>
-      </c>
-      <c r="G25" s="3">
-        <v>-1.19142248251213E-8</v>
-      </c>
-      <c r="H25" s="3">
-        <v>2.2777434251636898E-9</v>
-      </c>
-      <c r="I25" s="3">
-        <v>5.3127332084190401E-6</v>
-      </c>
-      <c r="J25" s="3">
-        <v>1.6284997251971601E-8</v>
-      </c>
-      <c r="K25" s="3">
-        <v>-5.6181224798459203E-6</v>
-      </c>
-      <c r="L25" s="3">
-        <v>2.5466241507931901E-8</v>
-      </c>
-      <c r="M25" s="3">
-        <v>-6.15497249934948E-8</v>
-      </c>
-      <c r="N25" s="3">
-        <v>1.13553584448123E-4</v>
-      </c>
-      <c r="O25" s="3">
-        <v>8.7843892578780003E-7</v>
-      </c>
-      <c r="P25" s="3">
-        <v>3.1860895281410102E-7</v>
-      </c>
-      <c r="Q25" s="3">
-        <v>1.0068060718133701E-6</v>
-      </c>
-      <c r="R25" s="3">
-        <v>5.5740761552043E-7</v>
-      </c>
-      <c r="S25" s="3">
-        <v>9.3611507080432402E-7</v>
-      </c>
-      <c r="T25" s="3">
-        <v>7.9613280323215095E-7</v>
-      </c>
-      <c r="U25" s="3">
-        <v>1.1942906010439699E-6</v>
-      </c>
-      <c r="V25" s="3">
-        <v>1.5103326048991601E-7</v>
-      </c>
-      <c r="W25" s="3">
-        <v>7.24192615771289E-6</v>
-      </c>
-      <c r="X25" s="3">
-        <v>1.9927526473481899E-6</v>
-      </c>
-      <c r="Y25" s="3">
-        <v>2.5860546501435299E-6</v>
-      </c>
-      <c r="Z25" s="3">
-        <v>4.82446404640032E-6</v>
-      </c>
-      <c r="AA25" s="3">
-        <v>8.4675770933115806E-5</v>
-      </c>
-      <c r="AB25" s="3">
-        <v>3.2483271297367001E-6</v>
-      </c>
-      <c r="AC25" s="3">
-        <v>1.3265384960738799E-4</v>
-      </c>
-      <c r="AD25" s="3">
-        <v>2.5695133733992802E-6</v>
-      </c>
-      <c r="AE25" s="3">
-        <v>6.0782956779033998E-6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="B26" s="3">
-        <v>-10.3024581492006</v>
-      </c>
-      <c r="C26" s="3">
-        <v>-2.6582967533709399E-2</v>
-      </c>
-      <c r="D26" s="3">
-        <v>5.4139270552216797E-5</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-3.2418727783093902E-7</v>
-      </c>
-      <c r="F26" s="3">
-        <v>6.2344193356711302E-4</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-1.01277183497874E-6</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-2.1505393777460999E-7</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-4.5652088834934702E-4</v>
-      </c>
-      <c r="J26" s="3">
-        <v>8.4304809464155598E-7</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-1.4426314321205301E-3</v>
-      </c>
-      <c r="L26" s="3">
-        <v>4.9028998842065999E-6</v>
-      </c>
-      <c r="M26" s="3">
-        <v>3.0354419539865501E-6</v>
-      </c>
-      <c r="N26" s="3">
-        <v>9.0860139493382005E-3</v>
-      </c>
-      <c r="O26" s="3">
-        <v>3.8885890278582701E-4</v>
-      </c>
-      <c r="P26" s="3">
-        <v>3.1494834524757201E-5</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>5.3025685080780203E-4</v>
-      </c>
-      <c r="R26" s="3">
-        <v>6.3887113516178601E-5</v>
-      </c>
-      <c r="S26" s="3">
-        <v>3.2856112513123599E-4</v>
-      </c>
-      <c r="T26" s="3">
-        <v>8.9808522990028405E-5</v>
-      </c>
-      <c r="U26" s="3">
-        <v>3.4435782274324598E-4</v>
-      </c>
-      <c r="V26" s="3">
-        <v>4.4134912942978601E-5</v>
-      </c>
-      <c r="W26" s="3">
-        <v>1.11797997728235E-2</v>
-      </c>
-      <c r="X26" s="3">
-        <v>4.1546726855648198E-5</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>7.2915130476653204E-4</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>8.4675770933115806E-5</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>856957.56080078403</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>1.09604996617301E-4</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>1.0304112192745301</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>5.6523492884616402E-5</v>
-      </c>
-      <c r="AE26" s="3">
-        <v>1.9575599343321999E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="B27" s="3">
-        <v>1.3622042802456401E-2</v>
-      </c>
-      <c r="C27" s="3">
-        <v>-4.7165081493678701E-5</v>
-      </c>
-      <c r="D27" s="3">
-        <v>8.9180820089915702E-8</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-5.7142343693600102E-9</v>
-      </c>
-      <c r="F27" s="3">
-        <v>9.3103839991541404E-6</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-1.6868568583899298E-8</v>
-      </c>
-      <c r="H27" s="3">
-        <v>3.0206602250118798E-9</v>
-      </c>
-      <c r="I27" s="3">
-        <v>3.0300240647553599E-7</v>
-      </c>
-      <c r="J27" s="3">
-        <v>1.6328844638368399E-8</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-4.8313977370567103E-6</v>
-      </c>
-      <c r="L27" s="3">
-        <v>2.5602908621452001E-8</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-2.3891852682965301E-8</v>
-      </c>
-      <c r="N27" s="3">
-        <v>1.61155868338051E-4</v>
-      </c>
-      <c r="O27" s="3">
-        <v>9.816471018495259E-7</v>
-      </c>
-      <c r="P27" s="3">
-        <v>4.3653847812177798E-7</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>1.3947852225007701E-6</v>
-      </c>
-      <c r="R27" s="3">
-        <v>7.78057907697776E-7</v>
-      </c>
-      <c r="S27" s="3">
-        <v>1.30724854001861E-6</v>
-      </c>
-      <c r="T27" s="3">
-        <v>1.1179285224098299E-6</v>
-      </c>
-      <c r="U27" s="3">
-        <v>1.67535851537749E-6</v>
-      </c>
-      <c r="V27" s="3">
-        <v>2.0293873847977999E-7</v>
-      </c>
-      <c r="W27" s="3">
-        <v>1.0090793471891E-5</v>
-      </c>
-      <c r="X27" s="3">
-        <v>2.0383028853820201E-6</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>2.8355353644538502E-6</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>3.2483271297367001E-6</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>1.09604996617301E-4</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>4.8167789408419004E-6</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>1.83336115491247E-4</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>3.1387210313176601E-6</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>8.5759200785433493E-6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="B28" s="3">
-        <v>-10.6084327042271</v>
-      </c>
-      <c r="C28" s="3">
-        <v>-2.7998752126199601E-2</v>
-      </c>
-      <c r="D28" s="3">
-        <v>5.8856609363805299E-5</v>
-      </c>
-      <c r="E28" s="3">
-        <v>-5.5960630678884497E-7</v>
-      </c>
-      <c r="F28" s="3">
-        <v>1.0101186114218801E-3</v>
-      </c>
-      <c r="G28" s="3">
-        <v>-1.7119884677995299E-6</v>
-      </c>
-      <c r="H28" s="3">
-        <v>-9.9609670178794306E-8</v>
-      </c>
-      <c r="I28" s="3">
-        <v>-4.1624261082025998E-4</v>
-      </c>
-      <c r="J28" s="3">
-        <v>-2.38213687960778E-7</v>
-      </c>
-      <c r="K28" s="3">
-        <v>-1.13668757442359E-3</v>
-      </c>
-      <c r="L28" s="3">
-        <v>4.5476868020242098E-6</v>
-      </c>
-      <c r="M28" s="3">
-        <v>4.2850359803336201E-6</v>
-      </c>
-      <c r="N28" s="3">
-        <v>1.5811559315374198E-2</v>
-      </c>
-      <c r="O28" s="3">
-        <v>3.9990612529965E-4</v>
-      </c>
-      <c r="P28" s="3">
-        <v>4.8209162137823403E-5</v>
-      </c>
-      <c r="Q28" s="3">
-        <v>5.7627705007456704E-4</v>
-      </c>
-      <c r="R28" s="3">
-        <v>9.4814081961460301E-5</v>
-      </c>
-      <c r="S28" s="3">
-        <v>3.7605886421803603E-4</v>
-      </c>
-      <c r="T28" s="3">
-        <v>1.34874783864406E-4</v>
-      </c>
-      <c r="U28" s="3">
-        <v>4.0746789479650198E-4</v>
-      </c>
-      <c r="V28" s="3">
-        <v>5.0942068467121303E-5</v>
-      </c>
-      <c r="W28" s="3">
-        <v>1.13680680694851E-2</v>
-      </c>
-      <c r="X28" s="3">
-        <v>5.6576407337050302E-5</v>
-      </c>
-      <c r="Y28" s="3">
-        <v>7.624437791238E-4</v>
-      </c>
-      <c r="Z28" s="3">
-        <v>1.3265384960738799E-4</v>
-      </c>
-      <c r="AA28" s="3">
-        <v>1.0304112192745301</v>
-      </c>
-      <c r="AB28" s="3">
-        <v>1.83336115491247E-4</v>
-      </c>
-      <c r="AC28" s="3">
-        <v>1916068.6111050099</v>
-      </c>
-      <c r="AD28" s="3">
-        <v>1.04417393733796E-4</v>
-      </c>
-      <c r="AE28" s="3">
-        <v>2.2818452156688901E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="B29" s="3">
-        <v>1.7355003996953899E-2</v>
-      </c>
-      <c r="C29" s="3">
-        <v>-4.5599648325824797E-5</v>
-      </c>
-      <c r="D29" s="3">
-        <v>6.0364329442624597E-8</v>
-      </c>
-      <c r="E29" s="3">
-        <v>-8.0603069833631301E-10</v>
-      </c>
-      <c r="F29" s="3">
-        <v>1.38971764114735E-6</v>
-      </c>
-      <c r="G29" s="3">
-        <v>-2.38728256149929E-9</v>
-      </c>
-      <c r="H29" s="3">
-        <v>6.1800208495018004E-11</v>
-      </c>
-      <c r="I29" s="3">
-        <v>-6.1937828808712196E-6</v>
-      </c>
-      <c r="J29" s="3">
-        <v>8.9490495832072994E-9</v>
-      </c>
-      <c r="K29" s="3">
-        <v>-2.7588637946059201E-6</v>
-      </c>
-      <c r="L29" s="3">
-        <v>2.08158788748257E-8</v>
-      </c>
-      <c r="M29" s="3">
-        <v>3.1453763039611501E-8</v>
-      </c>
-      <c r="N29" s="3">
-        <v>2.1354969270057898E-5</v>
-      </c>
-      <c r="O29" s="3">
-        <v>1.0148492182875601E-6</v>
-      </c>
-      <c r="P29" s="3">
-        <v>8.9518303641746302E-8</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>9.54243449060503E-7</v>
-      </c>
-      <c r="R29" s="3">
-        <v>1.52395911667508E-7</v>
-      </c>
-      <c r="S29" s="3">
-        <v>6.1014253744220205E-7</v>
-      </c>
-      <c r="T29" s="3">
-        <v>2.06862585445913E-7</v>
-      </c>
-      <c r="U29" s="3">
-        <v>6.4871772972224199E-7</v>
-      </c>
-      <c r="V29" s="3">
-        <v>9.4391075617084197E-8</v>
-      </c>
-      <c r="W29" s="3">
-        <v>1.8604867054813401E-5</v>
-      </c>
-      <c r="X29" s="3">
-        <v>1.4846901326516201E-6</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>1.9956415163245901E-6</v>
-      </c>
-      <c r="Z29" s="3">
-        <v>2.5695133733992802E-6</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>5.6523492884616402E-5</v>
-      </c>
-      <c r="AB29" s="3">
-        <v>3.1387210313176601E-6</v>
-      </c>
-      <c r="AC29" s="3">
-        <v>1.04417393733796E-4</v>
-      </c>
-      <c r="AD29" s="3">
-        <v>3.52589795475612E-6</v>
-      </c>
-      <c r="AE29" s="3">
-        <v>1.1074340482789701E-5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B30" s="3">
-        <v>-0.145958808742086</v>
-      </c>
-      <c r="C30" s="3">
-        <v>-2.2330706184271899E-3</v>
-      </c>
-      <c r="D30" s="3">
-        <v>4.3812634503501296E-6</v>
-      </c>
-      <c r="E30" s="3">
-        <v>1.55477749858987E-10</v>
-      </c>
-      <c r="F30" s="3">
-        <v>8.1497248508666505E-6</v>
-      </c>
-      <c r="G30" s="3">
-        <v>-4.2281946664544297E-9</v>
-      </c>
-      <c r="H30" s="3">
-        <v>-3.4521369531308798E-8</v>
-      </c>
-      <c r="I30" s="3">
-        <v>3.96136649828362E-5</v>
-      </c>
-      <c r="J30" s="3">
-        <v>-2.49820286317083E-7</v>
-      </c>
-      <c r="K30" s="3">
-        <v>3.2304296443269002E-5</v>
-      </c>
-      <c r="L30" s="3">
-        <v>1.0551011155236501E-8</v>
-      </c>
-      <c r="M30" s="3">
-        <v>-1.5113910206191199E-8</v>
-      </c>
-      <c r="N30" s="3">
-        <v>-1.7818291051150901E-5</v>
-      </c>
-      <c r="O30" s="3">
-        <v>3.3219196627751998E-5</v>
-      </c>
-      <c r="P30" s="3">
-        <v>7.2427379996700101E-7</v>
-      </c>
-      <c r="Q30" s="3">
-        <v>4.2266834945770703E-5</v>
-      </c>
-      <c r="R30" s="3">
-        <v>1.8904408457533699E-6</v>
-      </c>
-      <c r="S30" s="3">
-        <v>2.3811754538130601E-5</v>
-      </c>
-      <c r="T30" s="3">
-        <v>2.47460032621245E-6</v>
-      </c>
-      <c r="U30" s="3">
-        <v>2.3294289001235301E-5</v>
-      </c>
-      <c r="V30" s="3">
-        <v>3.1230377465330602E-6</v>
-      </c>
-      <c r="W30" s="3">
-        <v>9.9045831466263909E-4</v>
-      </c>
-      <c r="X30" s="3">
-        <v>1.94750503173308E-6</v>
-      </c>
-      <c r="Y30" s="3">
-        <v>5.9539551208076402E-5</v>
-      </c>
-      <c r="Z30" s="3">
-        <v>6.0782956779033998E-6</v>
-      </c>
-      <c r="AA30" s="3">
-        <v>1.9575599343321999E-3</v>
-      </c>
-      <c r="AB30" s="3">
-        <v>8.5759200785433493E-6</v>
-      </c>
-      <c r="AC30" s="3">
-        <v>2.2818452156688901E-3</v>
-      </c>
-      <c r="AD30" s="3">
-        <v>1.1074340482789701E-5</v>
-      </c>
-      <c r="AE30" s="3">
-        <v>3.91235661825894E-2</v>
+        <v>2.34453101567099E-4</v>
       </c>
     </row>
   </sheetData>
